--- a/saida_skus/SKU_UTD-145-ESCORREDOR-DUPLO-COM-BICA-ARTHI.xlsx
+++ b/saida_skus/SKU_UTD-145-ESCORREDOR-DUPLO-COM-BICA-ARTHI.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Analise" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$77</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$83</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O77"/>
+  <dimension ref="A1:O83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -559,12 +559,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -592,17 +592,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H2" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J2" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
@@ -632,12 +632,12 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -673,9 +673,9 @@
       <c r="I3" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J3" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
@@ -705,12 +705,12 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>R$ 110,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -743,47 +743,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I4" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J4" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="n">
-        <v>1</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -811,17 +815,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I5" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -851,12 +855,12 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -890,11 +894,11 @@
         </is>
       </c>
       <c r="I6" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -924,12 +928,12 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -954,7 +958,7 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 110,00</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -963,24 +967,24 @@
         </is>
       </c>
       <c r="I7" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>50,0%</t>
         </is>
       </c>
       <c r="L7" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -997,12 +1001,12 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -1030,17 +1034,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H8" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I8" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1070,12 +1074,12 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -1109,11 +1113,11 @@
         </is>
       </c>
       <c r="I9" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J9" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -1143,12 +1147,12 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -1173,7 +1177,7 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 110,00</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -1182,24 +1186,24 @@
         </is>
       </c>
       <c r="I10" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>1</v>
+      </c>
+      <c r="J10" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="L10" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1216,12 +1220,12 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -1255,11 +1259,11 @@
         </is>
       </c>
       <c r="I11" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1289,12 +1293,12 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -1328,11 +1332,11 @@
         </is>
       </c>
       <c r="I12" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J12" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1362,12 +1366,12 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -1401,11 +1405,11 @@
         </is>
       </c>
       <c r="I13" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J13" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -1435,12 +1439,12 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -1478,7 +1482,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1508,12 +1512,12 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1547,11 +1551,11 @@
         </is>
       </c>
       <c r="I15" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J15" s="3" t="inlineStr">
-        <is>
-          <t>▼ 66,7%</t>
+        <v>2</v>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -1581,12 +1585,12 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1620,7 +1624,7 @@
         </is>
       </c>
       <c r="I16" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
@@ -1654,12 +1658,12 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1693,11 +1697,11 @@
         </is>
       </c>
       <c r="I17" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -1727,12 +1731,12 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1800,12 +1804,12 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -1839,7 +1843,7 @@
         </is>
       </c>
       <c r="I19" s="2" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
@@ -1873,12 +1877,12 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -1912,7 +1916,7 @@
         </is>
       </c>
       <c r="I20" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
@@ -1939,19 +1943,19 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -1985,11 +1989,11 @@
         </is>
       </c>
       <c r="I21" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>1</v>
+      </c>
+      <c r="J21" s="3" t="inlineStr">
+        <is>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
@@ -2012,19 +2016,19 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -2058,11 +2062,11 @@
         </is>
       </c>
       <c r="I22" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J22" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
@@ -2085,19 +2089,19 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -2131,11 +2135,11 @@
         </is>
       </c>
       <c r="I23" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
-          <t>▼ 100,0%</t>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -2158,19 +2162,19 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -2204,11 +2208,11 @@
         </is>
       </c>
       <c r="I24" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J24" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
@@ -2231,19 +2235,19 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -2277,11 +2281,11 @@
         </is>
       </c>
       <c r="I25" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J25" s="3" t="inlineStr">
-        <is>
-          <t>▼ 66,7%</t>
+        <v>6</v>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
@@ -2304,19 +2308,19 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -2350,7 +2354,7 @@
         </is>
       </c>
       <c r="I26" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
@@ -2384,12 +2388,12 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -2423,11 +2427,11 @@
         </is>
       </c>
       <c r="I27" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J27" s="4" t="inlineStr">
-        <is>
-          <t>▲ 200,0%</t>
+        <v>6</v>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
@@ -2457,12 +2461,12 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -2496,11 +2500,11 @@
         </is>
       </c>
       <c r="I28" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J28" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J28" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
@@ -2530,12 +2534,12 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -2569,11 +2573,11 @@
         </is>
       </c>
       <c r="I29" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J29" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -2603,12 +2607,12 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -2642,11 +2646,11 @@
         </is>
       </c>
       <c r="I30" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J30" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
@@ -2676,12 +2680,12 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -2706,7 +2710,7 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
@@ -2714,51 +2718,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I31" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J31" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I31" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J31" s="3" t="inlineStr">
+        <is>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L31" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L31" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -2794,9 +2794,9 @@
       <c r="I32" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="J32" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -2856,7 +2856,7 @@
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
@@ -2864,51 +2864,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I33" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J33" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I33" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="J33" s="4" t="inlineStr">
+        <is>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L33" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L33" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -2942,11 +2938,11 @@
         </is>
       </c>
       <c r="I34" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J34" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J34" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
@@ -2976,12 +2972,12 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -3015,7 +3011,7 @@
         </is>
       </c>
       <c r="I35" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
@@ -3049,12 +3045,12 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -3088,11 +3084,11 @@
         </is>
       </c>
       <c r="I36" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J36" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>1</v>
+      </c>
+      <c r="J36" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
@@ -3110,7 +3106,7 @@
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
@@ -3122,12 +3118,12 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -3152,7 +3148,7 @@
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
@@ -3160,47 +3156,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I37" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J37" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L37" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L37" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -3234,11 +3234,11 @@
         </is>
       </c>
       <c r="I38" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J38" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>2</v>
+      </c>
+      <c r="J38" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
@@ -3268,12 +3268,12 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -3298,7 +3298,7 @@
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
@@ -3306,47 +3306,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I39" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J39" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L39" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L39" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -3380,11 +3384,11 @@
         </is>
       </c>
       <c r="I40" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J40" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>1</v>
+      </c>
+      <c r="J40" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
@@ -3414,12 +3418,12 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -3453,7 +3457,7 @@
         </is>
       </c>
       <c r="I41" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J41" s="2" t="inlineStr">
         <is>
@@ -3487,12 +3491,12 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -3526,7 +3530,7 @@
         </is>
       </c>
       <c r="I42" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
@@ -3548,7 +3552,7 @@
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr">
@@ -3560,12 +3564,12 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -3601,9 +3605,9 @@
       <c r="I43" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J43" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="J43" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr">
@@ -3633,12 +3637,12 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -3674,9 +3678,9 @@
       <c r="I44" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J44" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J44" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
@@ -3706,12 +3710,12 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -3745,11 +3749,11 @@
         </is>
       </c>
       <c r="I45" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J45" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>4</v>
+      </c>
+      <c r="J45" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr">
@@ -3779,12 +3783,12 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -3818,7 +3822,7 @@
         </is>
       </c>
       <c r="I46" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
@@ -3852,12 +3856,12 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -3891,11 +3895,11 @@
         </is>
       </c>
       <c r="I47" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J47" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K47" s="2" t="inlineStr">
@@ -3925,12 +3929,12 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -3966,9 +3970,9 @@
       <c r="I48" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J48" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J48" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr">
@@ -3998,12 +4002,12 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -4037,11 +4041,11 @@
         </is>
       </c>
       <c r="I49" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J49" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K49" s="2" t="inlineStr">
@@ -4071,12 +4075,12 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -4110,11 +4114,11 @@
         </is>
       </c>
       <c r="I50" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J50" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J50" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K50" s="2" t="inlineStr">
@@ -4144,12 +4148,12 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -4183,11 +4187,11 @@
         </is>
       </c>
       <c r="I51" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J51" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J51" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K51" s="2" t="inlineStr">
@@ -4217,12 +4221,12 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -4260,7 +4264,7 @@
       </c>
       <c r="J52" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K52" s="2" t="inlineStr">
@@ -4290,12 +4294,12 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -4363,12 +4367,12 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -4402,11 +4406,11 @@
         </is>
       </c>
       <c r="I54" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J54" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J54" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr">
@@ -4436,12 +4440,12 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -4479,7 +4483,7 @@
       </c>
       <c r="J55" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K55" s="2" t="inlineStr">
@@ -4509,12 +4513,12 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -4548,11 +4552,11 @@
         </is>
       </c>
       <c r="I56" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J56" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J56" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr">
@@ -4582,12 +4586,12 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -4621,11 +4625,11 @@
         </is>
       </c>
       <c r="I57" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J57" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J57" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K57" s="2" t="inlineStr">
@@ -4655,12 +4659,12 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -4728,12 +4732,12 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -4767,11 +4771,11 @@
         </is>
       </c>
       <c r="I59" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J59" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K59" s="2" t="inlineStr">
@@ -4801,12 +4805,12 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -4874,12 +4878,12 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -4913,7 +4917,7 @@
         </is>
       </c>
       <c r="I61" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J61" s="2" t="inlineStr">
         <is>
@@ -4947,12 +4951,12 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -4980,17 +4984,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H62" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I62" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J62" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+      <c r="J62" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K62" s="2" t="inlineStr">
@@ -5020,12 +5024,12 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -5093,12 +5097,12 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -5123,38 +5127,38 @@
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>R$ 110,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I64" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J64" s="2" t="inlineStr">
+        <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="I64" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J64" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
-        </is>
-      </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L64" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O64" s="2" t="inlineStr">
@@ -5166,12 +5170,12 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -5205,7 +5209,7 @@
         </is>
       </c>
       <c r="I65" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J65" s="2" t="inlineStr">
         <is>
@@ -5239,12 +5243,12 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -5269,7 +5273,7 @@
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>R$ 110,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
@@ -5287,15 +5291,15 @@
       </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L66" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N66" s="2" t="inlineStr">
@@ -5312,12 +5316,12 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -5385,12 +5389,12 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -5418,9 +5422,9 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H68" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H68" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I68" s="2" t="n">
@@ -5428,7 +5432,7 @@
       </c>
       <c r="J68" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K68" s="2" t="inlineStr">
@@ -5458,12 +5462,12 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -5531,12 +5535,12 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
@@ -5561,38 +5565,38 @@
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 110,00</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I70" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J70" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>1</v>
+      </c>
+      <c r="J70" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="L70" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="N70" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O70" s="2" t="inlineStr">
@@ -5604,12 +5608,12 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -5643,7 +5647,7 @@
         </is>
       </c>
       <c r="I71" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J71" s="2" t="inlineStr">
         <is>
@@ -5677,12 +5681,12 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
@@ -5707,7 +5711,7 @@
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 110,00</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
@@ -5716,24 +5720,24 @@
         </is>
       </c>
       <c r="I72" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J72" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J72" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>50,0%</t>
         </is>
       </c>
       <c r="L72" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="N72" s="2" t="inlineStr">
@@ -5750,12 +5754,12 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -5791,9 +5795,9 @@
       <c r="I73" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J73" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J73" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K73" s="2" t="inlineStr">
@@ -5823,12 +5827,12 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -5864,9 +5868,9 @@
       <c r="I74" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J74" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+      <c r="J74" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr">
@@ -5896,12 +5900,12 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -5935,11 +5939,11 @@
         </is>
       </c>
       <c r="I75" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J75" s="3" t="inlineStr">
         <is>
-          <t>▼ 66,7%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K75" s="2" t="inlineStr">
@@ -5969,12 +5973,12 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>31/03/2026</t>
+          <t>03/04/2026</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -6008,7 +6012,7 @@
         </is>
       </c>
       <c r="I76" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J76" s="2" t="inlineStr">
         <is>
@@ -6042,78 +6046,516 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>UTD-145</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor duplo com bica arthi</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>4498058823</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>R$ 157,65</t>
+        </is>
+      </c>
+      <c r="G77" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H77" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I77" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J77" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K77" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L77" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M77" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N77" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O77" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>UTD-145</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor duplo com bica arthi</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>4645710434</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>R$ 157,65</t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H78" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I78" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J78" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="K78" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L78" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M78" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N78" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O78" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>UTD-145</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor duplo com bica arthi</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>4498058823</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>R$ 157,65</t>
+        </is>
+      </c>
+      <c r="G79" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H79" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I79" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J79" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="K79" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L79" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M79" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N79" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O79" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B77" s="2" t="inlineStr">
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>UTD-145</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor duplo com bica arthi</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>4645710434</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>R$ 157,65</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H80" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I80" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J80" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
+        </is>
+      </c>
+      <c r="K80" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L80" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M80" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N80" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O80" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>UTD-145</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor duplo com bica arthi</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>4498058823</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>R$ 157,65</t>
+        </is>
+      </c>
+      <c r="G81" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H81" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I81" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J81" s="3" t="inlineStr">
+        <is>
+          <t>▼ 66,7%</t>
+        </is>
+      </c>
+      <c r="K81" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L81" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M81" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N81" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O81" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
         <is>
           <t>31/03/2026</t>
         </is>
       </c>
-      <c r="C77" s="2" t="inlineStr">
-        <is>
-          <t>UTD-145</t>
-        </is>
-      </c>
-      <c r="D77" s="2" t="inlineStr">
-        <is>
-          <t>Escorredor duplo com bica arthi</t>
-        </is>
-      </c>
-      <c r="E77" s="2" t="inlineStr">
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>UTD-145</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor duplo com bica arthi</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>4645710434</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>R$ 157,65</t>
+        </is>
+      </c>
+      <c r="G82" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H82" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I82" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J82" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K82" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L82" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M82" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N82" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O82" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>UTD-145</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor duplo com bica arthi</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
         <is>
           <t>4498058823</t>
         </is>
       </c>
-      <c r="F77" s="2" t="inlineStr">
-        <is>
-          <t>R$ 157,65</t>
-        </is>
-      </c>
-      <c r="G77" s="2" t="inlineStr">
-        <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H77" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I77" s="2" t="n">
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>R$ 157,65</t>
+        </is>
+      </c>
+      <c r="G83" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H83" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I83" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="J77" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K77" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L77" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M77" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="N77" s="2" t="inlineStr">
+      <c r="J83" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K83" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L83" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M83" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N83" s="2" t="inlineStr">
         <is>
           <t>Sem calcular</t>
         </is>
       </c>
-      <c r="O77" s="2" t="inlineStr">
+      <c r="O83" s="2" t="inlineStr">
         <is>
           <t>Média</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O77"/>
+  <autoFilter ref="A1:O83"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/saida_skus/SKU_UTD-145-ESCORREDOR-DUPLO-COM-BICA-ARTHI.xlsx
+++ b/saida_skus/SKU_UTD-145-ESCORREDOR-DUPLO-COM-BICA-ARTHI.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Analise" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$83</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$85</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O83"/>
+  <dimension ref="A1:O85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -559,14 +559,14 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
+          <t>12/05/2026</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
           <t>11/05/2026</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>10/05/2026</t>
-        </is>
-      </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -598,11 +598,11 @@
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J2" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
@@ -632,14 +632,14 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
+          <t>12/05/2026</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
           <t>11/05/2026</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>10/05/2026</t>
-        </is>
-      </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -662,7 +662,7 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
@@ -670,8 +670,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I3" s="2" t="n">
-        <v>0</v>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
@@ -680,39 +682,41 @@
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L3" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
+          <t>11/05/2026</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
           <t>10/05/2026</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>09/05/2026</t>
-        </is>
-      </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -735,7 +739,7 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -743,10 +747,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I4" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
@@ -755,41 +757,39 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
+          <t>11/05/2026</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
           <t>10/05/2026</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>09/05/2026</t>
-        </is>
-      </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -815,17 +815,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H5" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I5" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J5" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -855,14 +855,14 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
+          <t>10/05/2026</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
           <t>09/05/2026</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>08/05/2026</t>
-        </is>
-      </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -885,7 +885,7 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -893,8 +893,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I6" s="2" t="n">
-        <v>0</v>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
@@ -903,39 +905,41 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
+          <t>10/05/2026</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
           <t>09/05/2026</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>08/05/2026</t>
-        </is>
-      </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -958,33 +962,33 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>R$ 110,00</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H7" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I7" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J7" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L7" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1001,14 +1005,14 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
           <t>08/05/2026</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
-        </is>
-      </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -1034,17 +1038,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H8" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I8" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J8" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1074,14 +1078,14 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
           <t>08/05/2026</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
-        </is>
-      </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -1104,7 +1108,7 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 110,00</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -1113,24 +1117,24 @@
         </is>
       </c>
       <c r="I9" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>50,0%</t>
         </is>
       </c>
       <c r="L9" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1147,14 +1151,14 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
+          <t>08/05/2026</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
           <t>07/05/2026</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>06/05/2026</t>
-        </is>
-      </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -1177,33 +1181,33 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>R$ 110,00</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I10" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L10" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1220,14 +1224,14 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
+          <t>08/05/2026</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
           <t>07/05/2026</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>06/05/2026</t>
-        </is>
-      </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -1259,11 +1263,11 @@
         </is>
       </c>
       <c r="I11" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J11" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1293,14 +1297,14 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
           <t>06/05/2026</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>05/05/2026</t>
-        </is>
-      </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -1323,7 +1327,7 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 110,00</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -1332,24 +1336,24 @@
         </is>
       </c>
       <c r="I12" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>1</v>
+      </c>
+      <c r="J12" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="L12" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1366,14 +1370,14 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
           <t>06/05/2026</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>05/05/2026</t>
-        </is>
-      </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -1405,11 +1409,11 @@
         </is>
       </c>
       <c r="I13" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J13" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -1439,12 +1443,12 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
+          <t>06/05/2026</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
           <t>05/05/2026</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -1482,7 +1486,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1512,14 +1516,14 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
+          <t>06/05/2026</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
           <t>05/05/2026</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>04/05/2026</t>
-        </is>
-      </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -1551,11 +1555,11 @@
         </is>
       </c>
       <c r="I15" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J15" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -1585,14 +1589,14 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
+          <t>05/05/2026</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
           <t>04/05/2026</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>03/05/2026</t>
-        </is>
-      </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -1624,7 +1628,7 @@
         </is>
       </c>
       <c r="I16" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
@@ -1658,14 +1662,14 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
+          <t>05/05/2026</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
           <t>04/05/2026</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>03/05/2026</t>
-        </is>
-      </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -1697,11 +1701,11 @@
         </is>
       </c>
       <c r="I17" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J17" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -1731,14 +1735,14 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
           <t>03/05/2026</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>02/05/2026</t>
-        </is>
-      </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -1772,9 +1776,9 @@
       <c r="I18" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J18" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1804,14 +1808,14 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
           <t>03/05/2026</t>
         </is>
       </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>02/05/2026</t>
-        </is>
-      </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -1843,11 +1847,11 @@
         </is>
       </c>
       <c r="I19" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J19" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -1877,14 +1881,14 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
+          <t>03/05/2026</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
           <t>02/05/2026</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>01/05/2026</t>
-        </is>
-      </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -1916,11 +1920,11 @@
         </is>
       </c>
       <c r="I20" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J20" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1950,12 +1954,12 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
+          <t>03/05/2026</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
           <t>02/05/2026</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -1991,9 +1995,9 @@
       <c r="I21" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J21" s="3" t="inlineStr">
-        <is>
-          <t>▼ 66,7%</t>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
@@ -2023,12 +2027,12 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
+          <t>02/05/2026</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
           <t>01/05/2026</t>
-        </is>
-      </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -2066,7 +2070,7 @@
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
@@ -2096,14 +2100,14 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
+          <t>02/05/2026</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
           <t>01/05/2026</t>
         </is>
       </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>30/04/2026</t>
-        </is>
-      </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -2135,11 +2139,11 @@
         </is>
       </c>
       <c r="I23" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -2169,14 +2173,14 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
+          <t>01/05/2026</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
           <t>30/04/2026</t>
         </is>
       </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>29/04/2026</t>
-        </is>
-      </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -2208,11 +2212,11 @@
         </is>
       </c>
       <c r="I24" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J24" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
@@ -2242,14 +2246,14 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
+          <t>01/05/2026</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
           <t>30/04/2026</t>
         </is>
       </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>29/04/2026</t>
-        </is>
-      </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -2281,11 +2285,11 @@
         </is>
       </c>
       <c r="I25" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>3</v>
+      </c>
+      <c r="J25" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
@@ -2315,14 +2319,14 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
           <t>29/04/2026</t>
         </is>
       </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>28/04/2026</t>
-        </is>
-      </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -2354,11 +2358,11 @@
         </is>
       </c>
       <c r="I26" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J26" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -2381,19 +2385,19 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
           <t>29/04/2026</t>
-        </is>
-      </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -2431,7 +2435,7 @@
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
@@ -2454,19 +2458,19 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
+          <t>29/04/2026</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
           <t>28/04/2026</t>
-        </is>
-      </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -2502,9 +2506,9 @@
       <c r="I28" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J28" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
@@ -2534,14 +2538,14 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
+          <t>29/04/2026</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
           <t>28/04/2026</t>
         </is>
       </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
-        </is>
-      </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -2573,11 +2577,11 @@
         </is>
       </c>
       <c r="I29" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J29" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>6</v>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -2607,14 +2611,14 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
+          <t>28/04/2026</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
           <t>27/04/2026</t>
         </is>
       </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>26/04/2026</t>
-        </is>
-      </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -2646,11 +2650,11 @@
         </is>
       </c>
       <c r="I30" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>1</v>
+      </c>
+      <c r="J30" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
@@ -2680,14 +2684,14 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
+          <t>28/04/2026</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
           <t>27/04/2026</t>
         </is>
       </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>26/04/2026</t>
-        </is>
-      </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -2719,11 +2723,11 @@
         </is>
       </c>
       <c r="I31" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
-          <t>▼ 66,7%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
@@ -2753,12 +2757,12 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
           <t>26/04/2026</t>
-        </is>
-      </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -2826,14 +2830,14 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
           <t>26/04/2026</t>
         </is>
       </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>25/04/2026</t>
-        </is>
-      </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -2865,11 +2869,11 @@
         </is>
       </c>
       <c r="I33" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J33" s="4" t="inlineStr">
-        <is>
-          <t>▲ 200,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J33" s="3" t="inlineStr">
+        <is>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
@@ -2899,12 +2903,12 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
+          <t>26/04/2026</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
           <t>25/04/2026</t>
-        </is>
-      </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -2940,9 +2944,9 @@
       <c r="I34" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="J34" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
@@ -2972,14 +2976,14 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
+          <t>26/04/2026</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
           <t>25/04/2026</t>
         </is>
       </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>24/04/2026</t>
-        </is>
-      </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -3011,11 +3015,11 @@
         </is>
       </c>
       <c r="I35" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J35" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>3</v>
+      </c>
+      <c r="J35" s="4" t="inlineStr">
+        <is>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
@@ -3045,14 +3049,14 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
+          <t>25/04/2026</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
           <t>24/04/2026</t>
         </is>
       </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>23/04/2026</t>
-        </is>
-      </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -3084,11 +3088,11 @@
         </is>
       </c>
       <c r="I36" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J36" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J36" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
@@ -3118,14 +3122,14 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
+          <t>25/04/2026</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
           <t>24/04/2026</t>
         </is>
       </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>23/04/2026</t>
-        </is>
-      </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -3148,7 +3152,7 @@
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
@@ -3156,10 +3160,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I37" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I37" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
@@ -3168,41 +3170,39 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L37" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L37" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
+          <t>24/04/2026</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
           <t>23/04/2026</t>
         </is>
       </c>
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>22/04/2026</t>
-        </is>
-      </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -3234,11 +3234,11 @@
         </is>
       </c>
       <c r="I38" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J38" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J38" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
@@ -3268,12 +3268,12 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
+          <t>24/04/2026</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
           <t>23/04/2026</t>
-        </is>
-      </c>
-      <c r="B39" s="2" t="inlineStr">
-        <is>
-          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -3345,14 +3345,14 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
+          <t>23/04/2026</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
           <t>22/04/2026</t>
         </is>
       </c>
-      <c r="B40" s="2" t="inlineStr">
-        <is>
-          <t>21/04/2026</t>
-        </is>
-      </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -3384,11 +3384,11 @@
         </is>
       </c>
       <c r="I40" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J40" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J40" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
@@ -3418,14 +3418,14 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
+          <t>23/04/2026</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
           <t>22/04/2026</t>
         </is>
       </c>
-      <c r="B41" s="2" t="inlineStr">
-        <is>
-          <t>21/04/2026</t>
-        </is>
-      </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -3448,7 +3448,7 @@
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
@@ -3456,8 +3456,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I41" s="2" t="n">
-        <v>0</v>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
         <is>
@@ -3466,39 +3468,41 @@
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L41" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L41" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
+          <t>22/04/2026</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
           <t>21/04/2026</t>
         </is>
       </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
-        </is>
-      </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -3530,11 +3534,11 @@
         </is>
       </c>
       <c r="I42" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J42" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>1</v>
+      </c>
+      <c r="J42" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
@@ -3552,7 +3556,7 @@
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr">
@@ -3564,14 +3568,14 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
+          <t>22/04/2026</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
           <t>21/04/2026</t>
         </is>
       </c>
-      <c r="B43" s="2" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
-        </is>
-      </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -3605,9 +3609,9 @@
       <c r="I43" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J43" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J43" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr">
@@ -3637,14 +3641,14 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
           <t>20/04/2026</t>
         </is>
       </c>
-      <c r="B44" s="2" t="inlineStr">
-        <is>
-          <t>19/04/2026</t>
-        </is>
-      </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -3676,7 +3680,7 @@
         </is>
       </c>
       <c r="I44" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J44" s="2" t="inlineStr">
         <is>
@@ -3698,7 +3702,7 @@
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O44" s="2" t="inlineStr">
@@ -3710,14 +3714,14 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
           <t>20/04/2026</t>
         </is>
       </c>
-      <c r="B45" s="2" t="inlineStr">
-        <is>
-          <t>19/04/2026</t>
-        </is>
-      </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -3749,11 +3753,11 @@
         </is>
       </c>
       <c r="I45" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J45" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J45" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr">
@@ -3783,12 +3787,12 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
           <t>19/04/2026</t>
-        </is>
-      </c>
-      <c r="B46" s="2" t="inlineStr">
-        <is>
-          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -3856,14 +3860,14 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
           <t>19/04/2026</t>
         </is>
       </c>
-      <c r="B47" s="2" t="inlineStr">
-        <is>
-          <t>18/04/2026</t>
-        </is>
-      </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -3895,11 +3899,11 @@
         </is>
       </c>
       <c r="I47" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J47" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>4</v>
+      </c>
+      <c r="J47" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K47" s="2" t="inlineStr">
@@ -3929,12 +3933,12 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
           <t>18/04/2026</t>
-        </is>
-      </c>
-      <c r="B48" s="2" t="inlineStr">
-        <is>
-          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -4002,14 +4006,14 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
           <t>18/04/2026</t>
         </is>
       </c>
-      <c r="B49" s="2" t="inlineStr">
-        <is>
-          <t>17/04/2026</t>
-        </is>
-      </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -4041,7 +4045,7 @@
         </is>
       </c>
       <c r="I49" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J49" s="2" t="inlineStr">
         <is>
@@ -4075,14 +4079,14 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
           <t>17/04/2026</t>
         </is>
       </c>
-      <c r="B50" s="2" t="inlineStr">
-        <is>
-          <t>16/04/2026</t>
-        </is>
-      </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -4116,9 +4120,9 @@
       <c r="I50" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J50" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J50" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K50" s="2" t="inlineStr">
@@ -4148,14 +4152,14 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
           <t>17/04/2026</t>
         </is>
       </c>
-      <c r="B51" s="2" t="inlineStr">
-        <is>
-          <t>16/04/2026</t>
-        </is>
-      </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -4189,9 +4193,9 @@
       <c r="I51" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J51" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J51" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K51" s="2" t="inlineStr">
@@ -4221,14 +4225,14 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
           <t>16/04/2026</t>
         </is>
       </c>
-      <c r="B52" s="2" t="inlineStr">
-        <is>
-          <t>15/04/2026</t>
-        </is>
-      </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -4260,11 +4264,11 @@
         </is>
       </c>
       <c r="I52" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J52" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J52" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K52" s="2" t="inlineStr">
@@ -4294,14 +4298,14 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
           <t>16/04/2026</t>
         </is>
       </c>
-      <c r="B53" s="2" t="inlineStr">
-        <is>
-          <t>15/04/2026</t>
-        </is>
-      </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -4333,11 +4337,11 @@
         </is>
       </c>
       <c r="I53" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J53" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J53" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K53" s="2" t="inlineStr">
@@ -4367,14 +4371,14 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
           <t>15/04/2026</t>
         </is>
       </c>
-      <c r="B54" s="2" t="inlineStr">
-        <is>
-          <t>14/04/2026</t>
-        </is>
-      </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -4406,11 +4410,11 @@
         </is>
       </c>
       <c r="I54" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J54" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J54" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr">
@@ -4440,12 +4444,12 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
           <t>15/04/2026</t>
-        </is>
-      </c>
-      <c r="B55" s="2" t="inlineStr">
-        <is>
-          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -4513,14 +4517,14 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
           <t>14/04/2026</t>
         </is>
       </c>
-      <c r="B56" s="2" t="inlineStr">
-        <is>
-          <t>13/04/2026</t>
-        </is>
-      </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -4552,11 +4556,11 @@
         </is>
       </c>
       <c r="I56" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J56" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J56" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr">
@@ -4586,12 +4590,12 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
           <t>14/04/2026</t>
-        </is>
-      </c>
-      <c r="B57" s="2" t="inlineStr">
-        <is>
-          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -4659,12 +4663,12 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
           <t>13/04/2026</t>
-        </is>
-      </c>
-      <c r="B58" s="2" t="inlineStr">
-        <is>
-          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -4732,12 +4736,12 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
           <t>13/04/2026</t>
-        </is>
-      </c>
-      <c r="B59" s="2" t="inlineStr">
-        <is>
-          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -4805,12 +4809,12 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
           <t>12/04/2026</t>
-        </is>
-      </c>
-      <c r="B60" s="2" t="inlineStr">
-        <is>
-          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -4846,9 +4850,9 @@
       <c r="I60" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="J60" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+      <c r="J60" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K60" s="2" t="inlineStr">
@@ -4878,12 +4882,12 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
           <t>12/04/2026</t>
-        </is>
-      </c>
-      <c r="B61" s="2" t="inlineStr">
-        <is>
-          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -4921,7 +4925,7 @@
       </c>
       <c r="J61" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K61" s="2" t="inlineStr">
@@ -4951,14 +4955,14 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
           <t>11/04/2026</t>
         </is>
       </c>
-      <c r="B62" s="2" t="inlineStr">
-        <is>
-          <t>10/04/2026</t>
-        </is>
-      </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -4990,11 +4994,11 @@
         </is>
       </c>
       <c r="I62" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J62" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J62" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K62" s="2" t="inlineStr">
@@ -5024,14 +5028,14 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
           <t>11/04/2026</t>
         </is>
       </c>
-      <c r="B63" s="2" t="inlineStr">
-        <is>
-          <t>10/04/2026</t>
-        </is>
-      </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -5063,11 +5067,11 @@
         </is>
       </c>
       <c r="I63" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J63" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J63" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K63" s="2" t="inlineStr">
@@ -5097,14 +5101,14 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
           <t>10/04/2026</t>
         </is>
       </c>
-      <c r="B64" s="2" t="inlineStr">
-        <is>
-          <t>09/04/2026</t>
-        </is>
-      </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -5136,11 +5140,11 @@
         </is>
       </c>
       <c r="I64" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J64" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>1</v>
+      </c>
+      <c r="J64" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K64" s="2" t="inlineStr">
@@ -5170,14 +5174,14 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
           <t>10/04/2026</t>
         </is>
       </c>
-      <c r="B65" s="2" t="inlineStr">
-        <is>
-          <t>09/04/2026</t>
-        </is>
-      </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -5209,11 +5213,11 @@
         </is>
       </c>
       <c r="I65" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J65" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J65" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K65" s="2" t="inlineStr">
@@ -5243,12 +5247,12 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
           <t>09/04/2026</t>
-        </is>
-      </c>
-      <c r="B66" s="2" t="inlineStr">
-        <is>
-          <t>08/04/2026</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -5284,9 +5288,9 @@
       <c r="I66" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="J66" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+      <c r="J66" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K66" s="2" t="inlineStr">
@@ -5316,14 +5320,14 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
           <t>09/04/2026</t>
         </is>
       </c>
-      <c r="B67" s="2" t="inlineStr">
-        <is>
-          <t>08/04/2026</t>
-        </is>
-      </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -5355,7 +5359,7 @@
         </is>
       </c>
       <c r="I67" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J67" s="2" t="inlineStr">
         <is>
@@ -5389,14 +5393,14 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
           <t>08/04/2026</t>
         </is>
       </c>
-      <c r="B68" s="2" t="inlineStr">
-        <is>
-          <t>07/04/2026</t>
-        </is>
-      </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -5422,17 +5426,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H68" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H68" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I68" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J68" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>2</v>
+      </c>
+      <c r="J68" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K68" s="2" t="inlineStr">
@@ -5462,14 +5466,14 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
           <t>08/04/2026</t>
         </is>
       </c>
-      <c r="B69" s="2" t="inlineStr">
-        <is>
-          <t>07/04/2026</t>
-        </is>
-      </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -5503,9 +5507,9 @@
       <c r="I69" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J69" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J69" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K69" s="2" t="inlineStr">
@@ -5535,14 +5539,14 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
           <t>07/04/2026</t>
         </is>
       </c>
-      <c r="B70" s="2" t="inlineStr">
-        <is>
-          <t>06/04/2026</t>
-        </is>
-      </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -5565,38 +5569,38 @@
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>R$ 110,00</t>
-        </is>
-      </c>
-      <c r="H70" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H70" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I70" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J70" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+      <c r="J70" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L70" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N70" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O70" s="2" t="inlineStr">
@@ -5608,14 +5612,14 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
           <t>07/04/2026</t>
         </is>
       </c>
-      <c r="B71" s="2" t="inlineStr">
-        <is>
-          <t>06/04/2026</t>
-        </is>
-      </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -5647,11 +5651,11 @@
         </is>
       </c>
       <c r="I71" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J71" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J71" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K71" s="2" t="inlineStr">
@@ -5681,14 +5685,14 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
           <t>06/04/2026</t>
         </is>
       </c>
-      <c r="B72" s="2" t="inlineStr">
-        <is>
-          <t>05/04/2026</t>
-        </is>
-      </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -5716,20 +5720,20 @@
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I72" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J72" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J72" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="L72" s="2" t="n">
@@ -5737,12 +5741,12 @@
       </c>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="N72" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O72" s="2" t="inlineStr">
@@ -5754,14 +5758,14 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
           <t>06/04/2026</t>
         </is>
       </c>
-      <c r="B73" s="2" t="inlineStr">
-        <is>
-          <t>05/04/2026</t>
-        </is>
-      </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -5793,7 +5797,7 @@
         </is>
       </c>
       <c r="I73" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J73" s="2" t="inlineStr">
         <is>
@@ -5827,14 +5831,14 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
           <t>05/04/2026</t>
         </is>
       </c>
-      <c r="B74" s="2" t="inlineStr">
-        <is>
-          <t>04/04/2026</t>
-        </is>
-      </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -5857,7 +5861,7 @@
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 110,00</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
@@ -5866,24 +5870,24 @@
         </is>
       </c>
       <c r="I74" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J74" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
+        </is>
+      </c>
+      <c r="K74" s="2" t="inlineStr">
+        <is>
+          <t>50,0%</t>
+        </is>
+      </c>
+      <c r="L74" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J74" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K74" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L74" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="N74" s="2" t="inlineStr">
@@ -5900,14 +5904,14 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
           <t>05/04/2026</t>
         </is>
       </c>
-      <c r="B75" s="2" t="inlineStr">
-        <is>
-          <t>04/04/2026</t>
-        </is>
-      </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -5941,9 +5945,9 @@
       <c r="I75" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J75" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J75" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K75" s="2" t="inlineStr">
@@ -5973,14 +5977,14 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
           <t>04/04/2026</t>
         </is>
       </c>
-      <c r="B76" s="2" t="inlineStr">
-        <is>
-          <t>03/04/2026</t>
-        </is>
-      </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -6012,7 +6016,7 @@
         </is>
       </c>
       <c r="I76" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J76" s="2" t="inlineStr">
         <is>
@@ -6046,14 +6050,14 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
           <t>04/04/2026</t>
         </is>
       </c>
-      <c r="B77" s="2" t="inlineStr">
-        <is>
-          <t>03/04/2026</t>
-        </is>
-      </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -6085,11 +6089,11 @@
         </is>
       </c>
       <c r="I77" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J77" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J77" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K77" s="2" t="inlineStr">
@@ -6119,14 +6123,14 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
           <t>03/04/2026</t>
         </is>
       </c>
-      <c r="B78" s="2" t="inlineStr">
-        <is>
-          <t>02/04/2026</t>
-        </is>
-      </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -6160,9 +6164,9 @@
       <c r="I78" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J78" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J78" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K78" s="2" t="inlineStr">
@@ -6192,14 +6196,14 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
           <t>03/04/2026</t>
         </is>
       </c>
-      <c r="B79" s="2" t="inlineStr">
-        <is>
-          <t>02/04/2026</t>
-        </is>
-      </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -6231,11 +6235,11 @@
         </is>
       </c>
       <c r="I79" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J79" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J79" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K79" s="2" t="inlineStr">
@@ -6265,14 +6269,14 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
           <t>02/04/2026</t>
         </is>
       </c>
-      <c r="B80" s="2" t="inlineStr">
-        <is>
-          <t>01/04/2026</t>
-        </is>
-      </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -6304,11 +6308,11 @@
         </is>
       </c>
       <c r="I80" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J80" s="3" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K80" s="2" t="inlineStr">
@@ -6338,14 +6342,14 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
           <t>02/04/2026</t>
         </is>
       </c>
-      <c r="B81" s="2" t="inlineStr">
-        <is>
-          <t>01/04/2026</t>
-        </is>
-      </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -6377,11 +6381,11 @@
         </is>
       </c>
       <c r="I81" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J81" s="3" t="inlineStr">
         <is>
-          <t>▼ 66,7%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K81" s="2" t="inlineStr">
@@ -6411,14 +6415,14 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B82" s="2" t="inlineStr">
-        <is>
-          <t>31/03/2026</t>
-        </is>
-      </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -6450,11 +6454,11 @@
         </is>
       </c>
       <c r="I82" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J82" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>1</v>
+      </c>
+      <c r="J82" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K82" s="2" t="inlineStr">
@@ -6484,78 +6488,224 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B83" s="2" t="inlineStr">
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>UTD-145</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor duplo com bica arthi</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>4498058823</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>R$ 157,65</t>
+        </is>
+      </c>
+      <c r="G83" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H83" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I83" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J83" s="3" t="inlineStr">
+        <is>
+          <t>▼ 66,7%</t>
+        </is>
+      </c>
+      <c r="K83" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L83" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M83" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N83" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O83" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
         <is>
           <t>31/03/2026</t>
         </is>
       </c>
-      <c r="C83" s="2" t="inlineStr">
-        <is>
-          <t>UTD-145</t>
-        </is>
-      </c>
-      <c r="D83" s="2" t="inlineStr">
-        <is>
-          <t>Escorredor duplo com bica arthi</t>
-        </is>
-      </c>
-      <c r="E83" s="2" t="inlineStr">
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>UTD-145</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor duplo com bica arthi</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>4645710434</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>R$ 157,65</t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H84" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I84" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J84" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K84" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L84" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M84" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N84" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O84" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>UTD-145</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor duplo com bica arthi</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
         <is>
           <t>4498058823</t>
         </is>
       </c>
-      <c r="F83" s="2" t="inlineStr">
-        <is>
-          <t>R$ 157,65</t>
-        </is>
-      </c>
-      <c r="G83" s="2" t="inlineStr">
-        <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H83" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I83" s="2" t="n">
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>R$ 157,65</t>
+        </is>
+      </c>
+      <c r="G85" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H85" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I85" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="J83" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K83" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L83" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M83" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="N83" s="2" t="inlineStr">
+      <c r="J85" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K85" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L85" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M85" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N85" s="2" t="inlineStr">
         <is>
           <t>Sem calcular</t>
         </is>
       </c>
-      <c r="O83" s="2" t="inlineStr">
+      <c r="O85" s="2" t="inlineStr">
         <is>
           <t>Média</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O83"/>
+  <autoFilter ref="A1:O85"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/saida_skus/SKU_UTD-145-ESCORREDOR-DUPLO-COM-BICA-ARTHI.xlsx
+++ b/saida_skus/SKU_UTD-145-ESCORREDOR-DUPLO-COM-BICA-ARTHI.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Analise" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$85</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$91</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O85"/>
+  <dimension ref="A1:O91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -559,12 +559,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -598,11 +598,11 @@
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J2" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
@@ -632,12 +632,12 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -662,7 +662,7 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
@@ -670,51 +670,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I3" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J3" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L3" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L3" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -748,11 +744,11 @@
         </is>
       </c>
       <c r="I4" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -782,12 +778,12 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -821,7 +817,7 @@
         </is>
       </c>
       <c r="I5" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
@@ -855,12 +851,12 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -885,7 +881,7 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -893,10 +889,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I6" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
@@ -905,39 +899,37 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -962,55 +954,59 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H7" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -1046,9 +1042,9 @@
       <c r="I8" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1078,12 +1074,12 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -1108,7 +1104,7 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>R$ 110,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -1116,8 +1112,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I9" s="2" t="n">
-        <v>2</v>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
@@ -1126,37 +1124,39 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="n">
-        <v>1</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -1184,17 +1184,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H10" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I10" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -1265,9 +1265,9 @@
       <c r="I11" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J11" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1297,12 +1297,12 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -1327,7 +1327,7 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>R$ 110,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -1335,47 +1335,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I12" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J12" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="n">
-        <v>1</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -1403,17 +1407,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H13" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I13" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J13" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -1443,12 +1447,12 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -1482,11 +1486,11 @@
         </is>
       </c>
       <c r="I14" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1516,12 +1520,12 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1546,7 +1550,7 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 110,00</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1555,24 +1559,24 @@
         </is>
       </c>
       <c r="I15" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J15" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>50,0%</t>
         </is>
       </c>
       <c r="L15" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -1589,12 +1593,12 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1622,17 +1626,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H16" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I16" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J16" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1662,12 +1666,12 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1701,11 +1705,11 @@
         </is>
       </c>
       <c r="I17" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J17" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -1735,12 +1739,12 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1765,7 +1769,7 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 110,00</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
@@ -1774,24 +1778,24 @@
         </is>
       </c>
       <c r="I18" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>1</v>
+      </c>
+      <c r="J18" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="L18" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -1808,12 +1812,12 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -1847,11 +1851,11 @@
         </is>
       </c>
       <c r="I19" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J19" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -1881,12 +1885,12 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -1920,11 +1924,11 @@
         </is>
       </c>
       <c r="I20" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J20" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1954,12 +1958,12 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -1993,11 +1997,11 @@
         </is>
       </c>
       <c r="I21" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J21" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
@@ -2027,12 +2031,12 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -2070,7 +2074,7 @@
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
@@ -2100,12 +2104,12 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -2139,11 +2143,11 @@
         </is>
       </c>
       <c r="I23" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J23" s="3" t="inlineStr">
-        <is>
-          <t>▼ 66,7%</t>
+        <v>2</v>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -2173,12 +2177,12 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -2212,7 +2216,7 @@
         </is>
       </c>
       <c r="I24" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
@@ -2246,12 +2250,12 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -2285,11 +2289,11 @@
         </is>
       </c>
       <c r="I25" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
@@ -2319,12 +2323,12 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -2392,12 +2396,12 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -2431,7 +2435,7 @@
         </is>
       </c>
       <c r="I27" s="2" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
@@ -2465,12 +2469,12 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -2504,7 +2508,7 @@
         </is>
       </c>
       <c r="I28" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
@@ -2531,19 +2535,19 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -2577,11 +2581,11 @@
         </is>
       </c>
       <c r="I29" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>1</v>
+      </c>
+      <c r="J29" s="3" t="inlineStr">
+        <is>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -2604,19 +2608,19 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -2650,11 +2654,11 @@
         </is>
       </c>
       <c r="I30" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J30" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
@@ -2677,19 +2681,19 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -2723,11 +2727,11 @@
         </is>
       </c>
       <c r="I31" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
-          <t>▼ 100,0%</t>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
@@ -2750,19 +2754,19 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -2796,11 +2800,11 @@
         </is>
       </c>
       <c r="I32" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J32" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J32" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
@@ -2823,19 +2827,19 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -2869,11 +2873,11 @@
         </is>
       </c>
       <c r="I33" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J33" s="3" t="inlineStr">
-        <is>
-          <t>▼ 66,7%</t>
+        <v>6</v>
+      </c>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
@@ -2896,19 +2900,19 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -2942,7 +2946,7 @@
         </is>
       </c>
       <c r="I34" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
@@ -2976,12 +2980,12 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -3015,11 +3019,11 @@
         </is>
       </c>
       <c r="I35" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J35" s="4" t="inlineStr">
-        <is>
-          <t>▲ 200,0%</t>
+        <v>6</v>
+      </c>
+      <c r="J35" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
@@ -3049,12 +3053,12 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -3088,11 +3092,11 @@
         </is>
       </c>
       <c r="I36" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J36" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J36" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
@@ -3122,12 +3126,12 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -3161,11 +3165,11 @@
         </is>
       </c>
       <c r="I37" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J37" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J37" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
@@ -3195,12 +3199,12 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -3234,11 +3238,11 @@
         </is>
       </c>
       <c r="I38" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J38" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J38" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
@@ -3268,12 +3272,12 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -3298,7 +3302,7 @@
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
@@ -3306,51 +3310,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I39" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J39" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I39" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J39" s="3" t="inlineStr">
+        <is>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L39" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L39" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -3386,9 +3386,9 @@
       <c r="I40" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="J40" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
@@ -3418,12 +3418,12 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -3448,7 +3448,7 @@
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
@@ -3456,51 +3456,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I41" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J41" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I41" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="J41" s="4" t="inlineStr">
+        <is>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L41" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L41" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -3534,11 +3530,11 @@
         </is>
       </c>
       <c r="I42" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J42" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J42" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
@@ -3568,12 +3564,12 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -3607,7 +3603,7 @@
         </is>
       </c>
       <c r="I43" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J43" s="2" t="inlineStr">
         <is>
@@ -3641,12 +3637,12 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -3680,11 +3676,11 @@
         </is>
       </c>
       <c r="I44" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J44" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>1</v>
+      </c>
+      <c r="J44" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
@@ -3702,7 +3698,7 @@
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O44" s="2" t="inlineStr">
@@ -3714,12 +3710,12 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -3744,7 +3740,7 @@
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
@@ -3752,47 +3748,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I45" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J45" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L45" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L45" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -3826,11 +3826,11 @@
         </is>
       </c>
       <c r="I46" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J46" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>2</v>
+      </c>
+      <c r="J46" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
@@ -3860,12 +3860,12 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -3890,7 +3890,7 @@
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
@@ -3898,47 +3898,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I47" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J47" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L47" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L47" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -3972,11 +3976,11 @@
         </is>
       </c>
       <c r="I48" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J48" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>1</v>
+      </c>
+      <c r="J48" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr">
@@ -4006,12 +4010,12 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -4045,7 +4049,7 @@
         </is>
       </c>
       <c r="I49" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J49" s="2" t="inlineStr">
         <is>
@@ -4079,12 +4083,12 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -4118,7 +4122,7 @@
         </is>
       </c>
       <c r="I50" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J50" s="2" t="inlineStr">
         <is>
@@ -4140,7 +4144,7 @@
       </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O50" s="2" t="inlineStr">
@@ -4152,12 +4156,12 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -4193,9 +4197,9 @@
       <c r="I51" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J51" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="J51" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K51" s="2" t="inlineStr">
@@ -4225,12 +4229,12 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -4266,9 +4270,9 @@
       <c r="I52" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J52" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J52" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K52" s="2" t="inlineStr">
@@ -4298,12 +4302,12 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -4337,11 +4341,11 @@
         </is>
       </c>
       <c r="I53" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J53" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>4</v>
+      </c>
+      <c r="J53" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K53" s="2" t="inlineStr">
@@ -4371,12 +4375,12 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -4410,7 +4414,7 @@
         </is>
       </c>
       <c r="I54" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J54" s="2" t="inlineStr">
         <is>
@@ -4444,12 +4448,12 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -4483,11 +4487,11 @@
         </is>
       </c>
       <c r="I55" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J55" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K55" s="2" t="inlineStr">
@@ -4517,12 +4521,12 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -4558,9 +4562,9 @@
       <c r="I56" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J56" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J56" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr">
@@ -4590,12 +4594,12 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -4629,11 +4633,11 @@
         </is>
       </c>
       <c r="I57" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J57" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K57" s="2" t="inlineStr">
@@ -4663,12 +4667,12 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -4702,11 +4706,11 @@
         </is>
       </c>
       <c r="I58" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J58" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J58" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr">
@@ -4736,12 +4740,12 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -4775,11 +4779,11 @@
         </is>
       </c>
       <c r="I59" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J59" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J59" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K59" s="2" t="inlineStr">
@@ -4809,12 +4813,12 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -4852,7 +4856,7 @@
       </c>
       <c r="J60" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K60" s="2" t="inlineStr">
@@ -4882,12 +4886,12 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -4955,12 +4959,12 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -4994,11 +4998,11 @@
         </is>
       </c>
       <c r="I62" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J62" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J62" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K62" s="2" t="inlineStr">
@@ -5028,12 +5032,12 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -5071,7 +5075,7 @@
       </c>
       <c r="J63" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K63" s="2" t="inlineStr">
@@ -5101,12 +5105,12 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -5140,11 +5144,11 @@
         </is>
       </c>
       <c r="I64" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J64" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J64" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K64" s="2" t="inlineStr">
@@ -5174,12 +5178,12 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -5213,11 +5217,11 @@
         </is>
       </c>
       <c r="I65" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J65" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J65" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K65" s="2" t="inlineStr">
@@ -5247,12 +5251,12 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -5320,12 +5324,12 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -5359,11 +5363,11 @@
         </is>
       </c>
       <c r="I67" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J67" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K67" s="2" t="inlineStr">
@@ -5393,12 +5397,12 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -5466,12 +5470,12 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -5505,7 +5509,7 @@
         </is>
       </c>
       <c r="I69" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J69" s="2" t="inlineStr">
         <is>
@@ -5539,12 +5543,12 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
@@ -5572,17 +5576,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H70" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I70" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J70" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+      <c r="J70" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr">
@@ -5612,12 +5616,12 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -5685,12 +5689,12 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
@@ -5715,38 +5719,38 @@
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>R$ 110,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I72" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J72" s="2" t="inlineStr">
+        <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="I72" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J72" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
-        </is>
-      </c>
       <c r="K72" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L72" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N72" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O72" s="2" t="inlineStr">
@@ -5758,12 +5762,12 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -5797,7 +5801,7 @@
         </is>
       </c>
       <c r="I73" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J73" s="2" t="inlineStr">
         <is>
@@ -5831,12 +5835,12 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -5861,7 +5865,7 @@
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>R$ 110,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
@@ -5879,15 +5883,15 @@
       </c>
       <c r="K74" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L74" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N74" s="2" t="inlineStr">
@@ -5904,12 +5908,12 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -5977,12 +5981,12 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -6010,9 +6014,9 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H76" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H76" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I76" s="2" t="n">
@@ -6020,7 +6024,7 @@
       </c>
       <c r="J76" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K76" s="2" t="inlineStr">
@@ -6050,12 +6054,12 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
@@ -6123,12 +6127,12 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
@@ -6153,38 +6157,38 @@
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 110,00</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I78" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J78" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>1</v>
+      </c>
+      <c r="J78" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K78" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="L78" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M78" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="N78" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O78" s="2" t="inlineStr">
@@ -6196,12 +6200,12 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
@@ -6235,7 +6239,7 @@
         </is>
       </c>
       <c r="I79" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J79" s="2" t="inlineStr">
         <is>
@@ -6269,12 +6273,12 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
@@ -6299,7 +6303,7 @@
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 110,00</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
@@ -6308,24 +6312,24 @@
         </is>
       </c>
       <c r="I80" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J80" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J80" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K80" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>50,0%</t>
         </is>
       </c>
       <c r="L80" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M80" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="N80" s="2" t="inlineStr">
@@ -6342,12 +6346,12 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
@@ -6383,9 +6387,9 @@
       <c r="I81" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J81" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J81" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K81" s="2" t="inlineStr">
@@ -6415,12 +6419,12 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
@@ -6456,9 +6460,9 @@
       <c r="I82" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J82" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+      <c r="J82" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K82" s="2" t="inlineStr">
@@ -6488,12 +6492,12 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
@@ -6527,11 +6531,11 @@
         </is>
       </c>
       <c r="I83" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J83" s="3" t="inlineStr">
         <is>
-          <t>▼ 66,7%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K83" s="2" t="inlineStr">
@@ -6561,12 +6565,12 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>31/03/2026</t>
+          <t>03/04/2026</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
@@ -6600,7 +6604,7 @@
         </is>
       </c>
       <c r="I84" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J84" s="2" t="inlineStr">
         <is>
@@ -6634,78 +6638,516 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>UTD-145</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor duplo com bica arthi</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>4498058823</t>
+        </is>
+      </c>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>R$ 157,65</t>
+        </is>
+      </c>
+      <c r="G85" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H85" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I85" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J85" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K85" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L85" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M85" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N85" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O85" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>UTD-145</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor duplo com bica arthi</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>4645710434</t>
+        </is>
+      </c>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>R$ 157,65</t>
+        </is>
+      </c>
+      <c r="G86" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H86" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I86" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J86" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="K86" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L86" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M86" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N86" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O86" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>UTD-145</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor duplo com bica arthi</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t>4498058823</t>
+        </is>
+      </c>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
+          <t>R$ 157,65</t>
+        </is>
+      </c>
+      <c r="G87" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H87" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I87" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J87" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="K87" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L87" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M87" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N87" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O87" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B85" s="2" t="inlineStr">
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>UTD-145</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor duplo com bica arthi</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>4645710434</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>R$ 157,65</t>
+        </is>
+      </c>
+      <c r="G88" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H88" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I88" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J88" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
+        </is>
+      </c>
+      <c r="K88" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L88" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M88" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N88" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O88" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>UTD-145</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor duplo com bica arthi</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
+          <t>4498058823</t>
+        </is>
+      </c>
+      <c r="F89" s="2" t="inlineStr">
+        <is>
+          <t>R$ 157,65</t>
+        </is>
+      </c>
+      <c r="G89" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H89" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I89" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J89" s="3" t="inlineStr">
+        <is>
+          <t>▼ 66,7%</t>
+        </is>
+      </c>
+      <c r="K89" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L89" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M89" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N89" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O89" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
         <is>
           <t>31/03/2026</t>
         </is>
       </c>
-      <c r="C85" s="2" t="inlineStr">
-        <is>
-          <t>UTD-145</t>
-        </is>
-      </c>
-      <c r="D85" s="2" t="inlineStr">
-        <is>
-          <t>Escorredor duplo com bica arthi</t>
-        </is>
-      </c>
-      <c r="E85" s="2" t="inlineStr">
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>UTD-145</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor duplo com bica arthi</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t>4645710434</t>
+        </is>
+      </c>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
+          <t>R$ 157,65</t>
+        </is>
+      </c>
+      <c r="G90" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H90" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I90" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J90" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K90" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L90" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M90" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N90" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O90" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>UTD-145</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor duplo com bica arthi</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
         <is>
           <t>4498058823</t>
         </is>
       </c>
-      <c r="F85" s="2" t="inlineStr">
-        <is>
-          <t>R$ 157,65</t>
-        </is>
-      </c>
-      <c r="G85" s="2" t="inlineStr">
-        <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H85" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I85" s="2" t="n">
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t>R$ 157,65</t>
+        </is>
+      </c>
+      <c r="G91" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H91" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I91" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="J85" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K85" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L85" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M85" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="N85" s="2" t="inlineStr">
+      <c r="J91" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K91" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L91" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M91" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N91" s="2" t="inlineStr">
         <is>
           <t>Sem calcular</t>
         </is>
       </c>
-      <c r="O85" s="2" t="inlineStr">
+      <c r="O91" s="2" t="inlineStr">
         <is>
           <t>Média</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O85"/>
+  <autoFilter ref="A1:O91"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/saida_skus/SKU_UTD-145-ESCORREDOR-DUPLO-COM-BICA-ARTHI.xlsx
+++ b/saida_skus/SKU_UTD-145-ESCORREDOR-DUPLO-COM-BICA-ARTHI.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Analise" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$91</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$97</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O91"/>
+  <dimension ref="A1:O97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -559,12 +559,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -598,11 +598,11 @@
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J2" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
@@ -632,12 +632,12 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -673,9 +673,9 @@
       <c r="I3" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J3" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
@@ -705,12 +705,12 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -744,11 +744,11 @@
         </is>
       </c>
       <c r="I4" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -778,12 +778,12 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -808,7 +808,7 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -816,8 +816,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I5" s="2" t="n">
-        <v>1</v>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
@@ -826,37 +828,39 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -890,11 +894,11 @@
         </is>
       </c>
       <c r="I6" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J6" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -924,12 +928,12 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -954,7 +958,7 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -962,10 +966,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I7" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
@@ -974,39 +976,37 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -1040,11 +1040,11 @@
         </is>
       </c>
       <c r="I8" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1074,12 +1074,12 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -1112,51 +1112,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I9" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -1190,11 +1186,11 @@
         </is>
       </c>
       <c r="I10" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J10" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1224,12 +1220,12 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -1263,7 +1259,7 @@
         </is>
       </c>
       <c r="I11" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
@@ -1297,12 +1293,12 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -1327,7 +1323,7 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -1335,10 +1331,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I12" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
@@ -1347,39 +1341,37 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -1404,55 +1396,59 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H13" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J13" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -1488,9 +1484,9 @@
       <c r="I14" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="J14" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1520,12 +1516,12 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1550,7 +1546,7 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>R$ 110,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1558,8 +1554,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I15" s="2" t="n">
-        <v>2</v>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
@@ -1568,37 +1566,39 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="n">
-        <v>1</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1626,17 +1626,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H16" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I16" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J16" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1666,12 +1666,12 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1707,9 +1707,9 @@
       <c r="I17" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J17" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -1739,12 +1739,12 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1769,7 +1769,7 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>R$ 110,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
@@ -1777,47 +1777,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I18" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J18" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="n">
-        <v>1</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -1845,17 +1849,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H19" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I19" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J19" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -1885,12 +1889,12 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -1924,11 +1928,11 @@
         </is>
       </c>
       <c r="I20" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1958,12 +1962,12 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -1988,7 +1992,7 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 110,00</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -1997,24 +2001,24 @@
         </is>
       </c>
       <c r="I21" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J21" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>50,0%</t>
         </is>
       </c>
       <c r="L21" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2031,12 +2035,12 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -2064,17 +2068,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H22" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I22" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J22" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
@@ -2104,12 +2108,12 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -2143,11 +2147,11 @@
         </is>
       </c>
       <c r="I23" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J23" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -2177,12 +2181,12 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -2207,7 +2211,7 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 110,00</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
@@ -2216,24 +2220,24 @@
         </is>
       </c>
       <c r="I24" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>1</v>
+      </c>
+      <c r="J24" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="L24" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -2250,12 +2254,12 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -2289,11 +2293,11 @@
         </is>
       </c>
       <c r="I25" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J25" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
@@ -2323,12 +2327,12 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -2362,11 +2366,11 @@
         </is>
       </c>
       <c r="I26" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J26" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -2396,12 +2400,12 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -2435,11 +2439,11 @@
         </is>
       </c>
       <c r="I27" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J27" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
@@ -2469,12 +2473,12 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -2512,7 +2516,7 @@
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
@@ -2542,12 +2546,12 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -2581,11 +2585,11 @@
         </is>
       </c>
       <c r="I29" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J29" s="3" t="inlineStr">
-        <is>
-          <t>▼ 66,7%</t>
+        <v>2</v>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -2615,12 +2619,12 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -2654,7 +2658,7 @@
         </is>
       </c>
       <c r="I30" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
@@ -2688,12 +2692,12 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -2727,11 +2731,11 @@
         </is>
       </c>
       <c r="I31" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
@@ -2761,12 +2765,12 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -2834,12 +2838,12 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -2873,7 +2877,7 @@
         </is>
       </c>
       <c r="I33" s="2" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
@@ -2907,12 +2911,12 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -2946,7 +2950,7 @@
         </is>
       </c>
       <c r="I34" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
@@ -2973,19 +2977,19 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -3019,11 +3023,11 @@
         </is>
       </c>
       <c r="I35" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J35" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>1</v>
+      </c>
+      <c r="J35" s="3" t="inlineStr">
+        <is>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
@@ -3046,19 +3050,19 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -3092,11 +3096,11 @@
         </is>
       </c>
       <c r="I36" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J36" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
@@ -3119,19 +3123,19 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -3165,11 +3169,11 @@
         </is>
       </c>
       <c r="I37" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
-          <t>▼ 100,0%</t>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
@@ -3192,19 +3196,19 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -3238,11 +3242,11 @@
         </is>
       </c>
       <c r="I38" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J38" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J38" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
@@ -3265,19 +3269,19 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -3311,11 +3315,11 @@
         </is>
       </c>
       <c r="I39" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J39" s="3" t="inlineStr">
-        <is>
-          <t>▼ 66,7%</t>
+        <v>6</v>
+      </c>
+      <c r="J39" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
@@ -3338,19 +3342,19 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -3384,7 +3388,7 @@
         </is>
       </c>
       <c r="I40" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
@@ -3418,12 +3422,12 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -3457,11 +3461,11 @@
         </is>
       </c>
       <c r="I41" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J41" s="4" t="inlineStr">
-        <is>
-          <t>▲ 200,0%</t>
+        <v>6</v>
+      </c>
+      <c r="J41" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
@@ -3491,12 +3495,12 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -3530,11 +3534,11 @@
         </is>
       </c>
       <c r="I42" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J42" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J42" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
@@ -3564,12 +3568,12 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -3603,11 +3607,11 @@
         </is>
       </c>
       <c r="I43" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J43" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J43" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr">
@@ -3637,12 +3641,12 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -3676,11 +3680,11 @@
         </is>
       </c>
       <c r="I44" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J44" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J44" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
@@ -3710,12 +3714,12 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -3740,7 +3744,7 @@
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
@@ -3748,51 +3752,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I45" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J45" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I45" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J45" s="3" t="inlineStr">
+        <is>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L45" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L45" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -3828,9 +3828,9 @@
       <c r="I46" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="J46" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+      <c r="J46" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
@@ -3860,12 +3860,12 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -3890,7 +3890,7 @@
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
@@ -3898,51 +3898,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I47" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J47" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I47" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="J47" s="4" t="inlineStr">
+        <is>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L47" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L47" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -3976,11 +3972,11 @@
         </is>
       </c>
       <c r="I48" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J48" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J48" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr">
@@ -4010,12 +4006,12 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -4049,7 +4045,7 @@
         </is>
       </c>
       <c r="I49" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J49" s="2" t="inlineStr">
         <is>
@@ -4083,12 +4079,12 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -4122,11 +4118,11 @@
         </is>
       </c>
       <c r="I50" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J50" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>1</v>
+      </c>
+      <c r="J50" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K50" s="2" t="inlineStr">
@@ -4144,7 +4140,7 @@
       </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O50" s="2" t="inlineStr">
@@ -4156,12 +4152,12 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -4186,7 +4182,7 @@
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
@@ -4194,47 +4190,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I51" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J51" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J51" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L51" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L51" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -4268,11 +4268,11 @@
         </is>
       </c>
       <c r="I52" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J52" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>2</v>
+      </c>
+      <c r="J52" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K52" s="2" t="inlineStr">
@@ -4302,12 +4302,12 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -4332,7 +4332,7 @@
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
@@ -4340,47 +4340,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I53" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J53" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J53" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K53" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L53" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L53" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -4414,11 +4418,11 @@
         </is>
       </c>
       <c r="I54" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J54" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>1</v>
+      </c>
+      <c r="J54" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr">
@@ -4448,12 +4452,12 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -4487,7 +4491,7 @@
         </is>
       </c>
       <c r="I55" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J55" s="2" t="inlineStr">
         <is>
@@ -4521,12 +4525,12 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -4560,7 +4564,7 @@
         </is>
       </c>
       <c r="I56" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J56" s="2" t="inlineStr">
         <is>
@@ -4582,7 +4586,7 @@
       </c>
       <c r="N56" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O56" s="2" t="inlineStr">
@@ -4594,12 +4598,12 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -4635,9 +4639,9 @@
       <c r="I57" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J57" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="J57" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K57" s="2" t="inlineStr">
@@ -4667,12 +4671,12 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -4708,9 +4712,9 @@
       <c r="I58" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J58" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J58" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr">
@@ -4740,12 +4744,12 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -4779,11 +4783,11 @@
         </is>
       </c>
       <c r="I59" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J59" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>4</v>
+      </c>
+      <c r="J59" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K59" s="2" t="inlineStr">
@@ -4813,12 +4817,12 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -4852,7 +4856,7 @@
         </is>
       </c>
       <c r="I60" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J60" s="2" t="inlineStr">
         <is>
@@ -4886,12 +4890,12 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -4925,11 +4929,11 @@
         </is>
       </c>
       <c r="I61" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J61" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K61" s="2" t="inlineStr">
@@ -4959,12 +4963,12 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -5000,9 +5004,9 @@
       <c r="I62" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J62" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J62" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K62" s="2" t="inlineStr">
@@ -5032,12 +5036,12 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -5071,11 +5075,11 @@
         </is>
       </c>
       <c r="I63" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J63" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K63" s="2" t="inlineStr">
@@ -5105,12 +5109,12 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -5144,11 +5148,11 @@
         </is>
       </c>
       <c r="I64" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J64" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J64" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K64" s="2" t="inlineStr">
@@ -5178,12 +5182,12 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -5217,11 +5221,11 @@
         </is>
       </c>
       <c r="I65" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J65" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J65" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K65" s="2" t="inlineStr">
@@ -5251,12 +5255,12 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -5294,7 +5298,7 @@
       </c>
       <c r="J66" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K66" s="2" t="inlineStr">
@@ -5324,12 +5328,12 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -5397,12 +5401,12 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -5436,11 +5440,11 @@
         </is>
       </c>
       <c r="I68" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J68" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J68" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K68" s="2" t="inlineStr">
@@ -5470,12 +5474,12 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -5513,7 +5517,7 @@
       </c>
       <c r="J69" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K69" s="2" t="inlineStr">
@@ -5543,12 +5547,12 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
@@ -5582,11 +5586,11 @@
         </is>
       </c>
       <c r="I70" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J70" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J70" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr">
@@ -5616,12 +5620,12 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -5655,11 +5659,11 @@
         </is>
       </c>
       <c r="I71" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J71" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J71" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K71" s="2" t="inlineStr">
@@ -5689,12 +5693,12 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
@@ -5762,12 +5766,12 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -5801,11 +5805,11 @@
         </is>
       </c>
       <c r="I73" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J73" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K73" s="2" t="inlineStr">
@@ -5835,12 +5839,12 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -5908,12 +5912,12 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -5947,7 +5951,7 @@
         </is>
       </c>
       <c r="I75" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J75" s="2" t="inlineStr">
         <is>
@@ -5981,12 +5985,12 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -6014,17 +6018,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H76" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H76" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I76" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J76" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+      <c r="J76" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K76" s="2" t="inlineStr">
@@ -6054,12 +6058,12 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
@@ -6127,12 +6131,12 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
@@ -6157,38 +6161,38 @@
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>R$ 110,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I78" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J78" s="2" t="inlineStr">
+        <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="I78" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J78" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
-        </is>
-      </c>
       <c r="K78" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L78" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M78" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N78" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O78" s="2" t="inlineStr">
@@ -6200,12 +6204,12 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
@@ -6239,7 +6243,7 @@
         </is>
       </c>
       <c r="I79" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J79" s="2" t="inlineStr">
         <is>
@@ -6273,12 +6277,12 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
@@ -6303,7 +6307,7 @@
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>R$ 110,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
@@ -6321,15 +6325,15 @@
       </c>
       <c r="K80" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L80" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M80" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N80" s="2" t="inlineStr">
@@ -6346,12 +6350,12 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
@@ -6419,12 +6423,12 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
@@ -6452,9 +6456,9 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H82" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H82" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I82" s="2" t="n">
@@ -6462,7 +6466,7 @@
       </c>
       <c r="J82" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K82" s="2" t="inlineStr">
@@ -6492,12 +6496,12 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
@@ -6565,12 +6569,12 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
@@ -6595,38 +6599,38 @@
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 110,00</t>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I84" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J84" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>1</v>
+      </c>
+      <c r="J84" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K84" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="L84" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M84" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="N84" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O84" s="2" t="inlineStr">
@@ -6638,12 +6642,12 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
@@ -6677,7 +6681,7 @@
         </is>
       </c>
       <c r="I85" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J85" s="2" t="inlineStr">
         <is>
@@ -6711,12 +6715,12 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
@@ -6741,7 +6745,7 @@
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 110,00</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr">
@@ -6750,24 +6754,24 @@
         </is>
       </c>
       <c r="I86" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J86" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J86" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K86" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>50,0%</t>
         </is>
       </c>
       <c r="L86" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M86" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="N86" s="2" t="inlineStr">
@@ -6784,12 +6788,12 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
@@ -6825,9 +6829,9 @@
       <c r="I87" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J87" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J87" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K87" s="2" t="inlineStr">
@@ -6857,12 +6861,12 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
@@ -6898,9 +6902,9 @@
       <c r="I88" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J88" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+      <c r="J88" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K88" s="2" t="inlineStr">
@@ -6930,12 +6934,12 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
@@ -6969,11 +6973,11 @@
         </is>
       </c>
       <c r="I89" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J89" s="3" t="inlineStr">
         <is>
-          <t>▼ 66,7%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K89" s="2" t="inlineStr">
@@ -7003,12 +7007,12 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>31/03/2026</t>
+          <t>03/04/2026</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
@@ -7042,7 +7046,7 @@
         </is>
       </c>
       <c r="I90" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J90" s="2" t="inlineStr">
         <is>
@@ -7076,78 +7080,516 @@
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>UTD-145</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor duplo com bica arthi</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
+          <t>4498058823</t>
+        </is>
+      </c>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t>R$ 157,65</t>
+        </is>
+      </c>
+      <c r="G91" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H91" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I91" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J91" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K91" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L91" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M91" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N91" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O91" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>UTD-145</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor duplo com bica arthi</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
+          <t>4645710434</t>
+        </is>
+      </c>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t>R$ 157,65</t>
+        </is>
+      </c>
+      <c r="G92" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H92" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I92" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J92" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="K92" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L92" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M92" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N92" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O92" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>UTD-145</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor duplo com bica arthi</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="inlineStr">
+        <is>
+          <t>4498058823</t>
+        </is>
+      </c>
+      <c r="F93" s="2" t="inlineStr">
+        <is>
+          <t>R$ 157,65</t>
+        </is>
+      </c>
+      <c r="G93" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H93" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I93" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J93" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="K93" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L93" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M93" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N93" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O93" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B91" s="2" t="inlineStr">
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>UTD-145</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor duplo com bica arthi</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
+          <t>4645710434</t>
+        </is>
+      </c>
+      <c r="F94" s="2" t="inlineStr">
+        <is>
+          <t>R$ 157,65</t>
+        </is>
+      </c>
+      <c r="G94" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H94" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I94" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J94" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
+        </is>
+      </c>
+      <c r="K94" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L94" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M94" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N94" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O94" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>UTD-145</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor duplo com bica arthi</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="inlineStr">
+        <is>
+          <t>4498058823</t>
+        </is>
+      </c>
+      <c r="F95" s="2" t="inlineStr">
+        <is>
+          <t>R$ 157,65</t>
+        </is>
+      </c>
+      <c r="G95" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H95" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I95" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J95" s="3" t="inlineStr">
+        <is>
+          <t>▼ 66,7%</t>
+        </is>
+      </c>
+      <c r="K95" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L95" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M95" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N95" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O95" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
         <is>
           <t>31/03/2026</t>
         </is>
       </c>
-      <c r="C91" s="2" t="inlineStr">
-        <is>
-          <t>UTD-145</t>
-        </is>
-      </c>
-      <c r="D91" s="2" t="inlineStr">
-        <is>
-          <t>Escorredor duplo com bica arthi</t>
-        </is>
-      </c>
-      <c r="E91" s="2" t="inlineStr">
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>UTD-145</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor duplo com bica arthi</t>
+        </is>
+      </c>
+      <c r="E96" s="2" t="inlineStr">
+        <is>
+          <t>4645710434</t>
+        </is>
+      </c>
+      <c r="F96" s="2" t="inlineStr">
+        <is>
+          <t>R$ 157,65</t>
+        </is>
+      </c>
+      <c r="G96" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H96" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I96" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J96" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K96" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L96" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M96" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N96" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O96" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>UTD-145</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor duplo com bica arthi</t>
+        </is>
+      </c>
+      <c r="E97" s="2" t="inlineStr">
         <is>
           <t>4498058823</t>
         </is>
       </c>
-      <c r="F91" s="2" t="inlineStr">
-        <is>
-          <t>R$ 157,65</t>
-        </is>
-      </c>
-      <c r="G91" s="2" t="inlineStr">
-        <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H91" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I91" s="2" t="n">
+      <c r="F97" s="2" t="inlineStr">
+        <is>
+          <t>R$ 157,65</t>
+        </is>
+      </c>
+      <c r="G97" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H97" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I97" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="J91" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K91" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L91" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M91" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="N91" s="2" t="inlineStr">
+      <c r="J97" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K97" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L97" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M97" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N97" s="2" t="inlineStr">
         <is>
           <t>Sem calcular</t>
         </is>
       </c>
-      <c r="O91" s="2" t="inlineStr">
+      <c r="O97" s="2" t="inlineStr">
         <is>
           <t>Média</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O91"/>
+  <autoFilter ref="A1:O97"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/saida_skus/SKU_UTD-145-ESCORREDOR-DUPLO-COM-BICA-ARTHI.xlsx
+++ b/saida_skus/SKU_UTD-145-ESCORREDOR-DUPLO-COM-BICA-ARTHI.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Analise" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$97</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$99</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O97"/>
+  <dimension ref="A1:O99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -559,14 +559,14 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
           <t>18/05/2026</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>17/05/2026</t>
-        </is>
-      </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -600,9 +600,9 @@
       <c r="I2" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J2" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
@@ -632,12 +632,12 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
           <t>18/05/2026</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>17/05/2026</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -705,14 +705,14 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
           <t>17/05/2026</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>16/05/2026</t>
-        </is>
-      </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -744,11 +744,11 @@
         </is>
       </c>
       <c r="I4" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -778,14 +778,14 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
           <t>17/05/2026</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>16/05/2026</t>
-        </is>
-      </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -808,7 +808,7 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -816,10 +816,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I5" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
@@ -828,41 +826,39 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
+          <t>17/05/2026</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
           <t>16/05/2026</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>15/05/2026</t>
-        </is>
-      </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -894,11 +890,11 @@
         </is>
       </c>
       <c r="I6" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -928,14 +924,14 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
+          <t>17/05/2026</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
           <t>16/05/2026</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>15/05/2026</t>
-        </is>
-      </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -958,7 +954,7 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -966,8 +962,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I7" s="2" t="n">
-        <v>0</v>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
@@ -976,39 +974,41 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
+          <t>16/05/2026</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
           <t>15/05/2026</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
-        </is>
-      </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -1040,11 +1040,11 @@
         </is>
       </c>
       <c r="I8" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1074,14 +1074,14 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
+          <t>16/05/2026</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
           <t>15/05/2026</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
-        </is>
-      </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -1115,9 +1115,9 @@
       <c r="I9" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J9" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -1147,14 +1147,14 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
+          <t>15/05/2026</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
           <t>14/05/2026</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>13/05/2026</t>
-        </is>
-      </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -1186,11 +1186,11 @@
         </is>
       </c>
       <c r="I10" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1220,14 +1220,14 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
+          <t>15/05/2026</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
           <t>14/05/2026</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>13/05/2026</t>
-        </is>
-      </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -1259,11 +1259,11 @@
         </is>
       </c>
       <c r="I11" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J11" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1293,14 +1293,14 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
+          <t>14/05/2026</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
           <t>13/05/2026</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>12/05/2026</t>
-        </is>
-      </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -1332,11 +1332,11 @@
         </is>
       </c>
       <c r="I12" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J12" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1366,14 +1366,14 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
+          <t>14/05/2026</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
           <t>13/05/2026</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>12/05/2026</t>
-        </is>
-      </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -1396,7 +1396,7 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1404,10 +1404,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I13" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
@@ -1416,41 +1414,39 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
+          <t>13/05/2026</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
           <t>12/05/2026</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>11/05/2026</t>
-        </is>
-      </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -1482,11 +1478,11 @@
         </is>
       </c>
       <c r="I14" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J14" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1516,12 +1512,12 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
+          <t>13/05/2026</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
           <t>12/05/2026</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1593,14 +1589,14 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
+          <t>12/05/2026</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
           <t>11/05/2026</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>10/05/2026</t>
-        </is>
-      </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -1632,11 +1628,11 @@
         </is>
       </c>
       <c r="I16" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J16" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1666,14 +1662,14 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
+          <t>12/05/2026</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
           <t>11/05/2026</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>10/05/2026</t>
-        </is>
-      </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -1696,7 +1692,7 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -1704,8 +1700,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I17" s="2" t="n">
-        <v>0</v>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
@@ -1714,39 +1712,41 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
+          <t>11/05/2026</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
           <t>10/05/2026</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>09/05/2026</t>
-        </is>
-      </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -1769,7 +1769,7 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
@@ -1777,10 +1777,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I18" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
@@ -1789,41 +1787,39 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
+          <t>11/05/2026</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
           <t>10/05/2026</t>
         </is>
       </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>09/05/2026</t>
-        </is>
-      </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -1849,17 +1845,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H19" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I19" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J19" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -1889,14 +1885,14 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
+          <t>10/05/2026</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
           <t>09/05/2026</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>08/05/2026</t>
-        </is>
-      </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -1919,7 +1915,7 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
@@ -1927,8 +1923,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I20" s="2" t="n">
-        <v>0</v>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
@@ -1937,39 +1935,41 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
+          <t>10/05/2026</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
           <t>09/05/2026</t>
         </is>
       </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>08/05/2026</t>
-        </is>
-      </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -1992,33 +1992,33 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>R$ 110,00</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H21" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I21" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J21" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L21" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2035,14 +2035,14 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
           <t>08/05/2026</t>
         </is>
       </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
-        </is>
-      </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -2068,17 +2068,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H22" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I22" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J22" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
@@ -2108,14 +2108,14 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
           <t>08/05/2026</t>
         </is>
       </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
-        </is>
-      </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -2138,7 +2138,7 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 110,00</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
@@ -2147,24 +2147,24 @@
         </is>
       </c>
       <c r="I23" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J23" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>50,0%</t>
         </is>
       </c>
       <c r="L23" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2181,14 +2181,14 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
+          <t>08/05/2026</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
           <t>07/05/2026</t>
         </is>
       </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>06/05/2026</t>
-        </is>
-      </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -2211,33 +2211,33 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>R$ 110,00</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H24" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I24" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L24" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -2254,14 +2254,14 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
+          <t>08/05/2026</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
           <t>07/05/2026</t>
         </is>
       </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>06/05/2026</t>
-        </is>
-      </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -2293,11 +2293,11 @@
         </is>
       </c>
       <c r="I25" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J25" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
@@ -2327,14 +2327,14 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
           <t>06/05/2026</t>
         </is>
       </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>05/05/2026</t>
-        </is>
-      </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -2357,7 +2357,7 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 110,00</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
@@ -2366,24 +2366,24 @@
         </is>
       </c>
       <c r="I26" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>1</v>
+      </c>
+      <c r="J26" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="L26" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -2400,14 +2400,14 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
           <t>06/05/2026</t>
         </is>
       </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>05/05/2026</t>
-        </is>
-      </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -2439,11 +2439,11 @@
         </is>
       </c>
       <c r="I27" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J27" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
@@ -2473,12 +2473,12 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
+          <t>06/05/2026</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
           <t>05/05/2026</t>
-        </is>
-      </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
@@ -2546,14 +2546,14 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
+          <t>06/05/2026</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
           <t>05/05/2026</t>
         </is>
       </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>04/05/2026</t>
-        </is>
-      </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -2585,11 +2585,11 @@
         </is>
       </c>
       <c r="I29" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J29" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -2619,14 +2619,14 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
+          <t>05/05/2026</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
           <t>04/05/2026</t>
         </is>
       </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>03/05/2026</t>
-        </is>
-      </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -2658,7 +2658,7 @@
         </is>
       </c>
       <c r="I30" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
@@ -2692,14 +2692,14 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
+          <t>05/05/2026</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
           <t>04/05/2026</t>
         </is>
       </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>03/05/2026</t>
-        </is>
-      </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -2731,11 +2731,11 @@
         </is>
       </c>
       <c r="I31" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J31" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
@@ -2765,14 +2765,14 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
           <t>03/05/2026</t>
         </is>
       </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>02/05/2026</t>
-        </is>
-      </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -2806,9 +2806,9 @@
       <c r="I32" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J32" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
@@ -2838,14 +2838,14 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
           <t>03/05/2026</t>
         </is>
       </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>02/05/2026</t>
-        </is>
-      </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -2877,11 +2877,11 @@
         </is>
       </c>
       <c r="I33" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J33" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J33" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
@@ -2911,14 +2911,14 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
+          <t>03/05/2026</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
           <t>02/05/2026</t>
         </is>
       </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>01/05/2026</t>
-        </is>
-      </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -2950,11 +2950,11 @@
         </is>
       </c>
       <c r="I34" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J34" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J34" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
@@ -2984,12 +2984,12 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
+          <t>03/05/2026</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
           <t>02/05/2026</t>
-        </is>
-      </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -3025,9 +3025,9 @@
       <c r="I35" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J35" s="3" t="inlineStr">
-        <is>
-          <t>▼ 66,7%</t>
+      <c r="J35" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
@@ -3057,12 +3057,12 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
+          <t>02/05/2026</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
           <t>01/05/2026</t>
-        </is>
-      </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -3100,7 +3100,7 @@
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
@@ -3130,14 +3130,14 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
+          <t>02/05/2026</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
           <t>01/05/2026</t>
         </is>
       </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>30/04/2026</t>
-        </is>
-      </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -3169,11 +3169,11 @@
         </is>
       </c>
       <c r="I37" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
@@ -3203,14 +3203,14 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
+          <t>01/05/2026</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
           <t>30/04/2026</t>
         </is>
       </c>
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>29/04/2026</t>
-        </is>
-      </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -3242,11 +3242,11 @@
         </is>
       </c>
       <c r="I38" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J38" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J38" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
@@ -3276,14 +3276,14 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
+          <t>01/05/2026</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
           <t>30/04/2026</t>
         </is>
       </c>
-      <c r="B39" s="2" t="inlineStr">
-        <is>
-          <t>29/04/2026</t>
-        </is>
-      </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -3315,11 +3315,11 @@
         </is>
       </c>
       <c r="I39" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J39" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>3</v>
+      </c>
+      <c r="J39" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
@@ -3349,14 +3349,14 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
           <t>29/04/2026</t>
         </is>
       </c>
-      <c r="B40" s="2" t="inlineStr">
-        <is>
-          <t>28/04/2026</t>
-        </is>
-      </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -3388,11 +3388,11 @@
         </is>
       </c>
       <c r="I40" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J40" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J40" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
@@ -3415,19 +3415,19 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
           <t>29/04/2026</t>
-        </is>
-      </c>
-      <c r="B41" s="2" t="inlineStr">
-        <is>
-          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -3465,7 +3465,7 @@
       </c>
       <c r="J41" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
@@ -3488,19 +3488,19 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
+          <t>29/04/2026</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
           <t>28/04/2026</t>
-        </is>
-      </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -3536,9 +3536,9 @@
       <c r="I42" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J42" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+      <c r="J42" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
@@ -3568,14 +3568,14 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
+          <t>29/04/2026</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
           <t>28/04/2026</t>
         </is>
       </c>
-      <c r="B43" s="2" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
-        </is>
-      </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -3607,11 +3607,11 @@
         </is>
       </c>
       <c r="I43" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J43" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>6</v>
+      </c>
+      <c r="J43" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr">
@@ -3641,14 +3641,14 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
+          <t>28/04/2026</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
           <t>27/04/2026</t>
         </is>
       </c>
-      <c r="B44" s="2" t="inlineStr">
-        <is>
-          <t>26/04/2026</t>
-        </is>
-      </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -3680,11 +3680,11 @@
         </is>
       </c>
       <c r="I44" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J44" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>1</v>
+      </c>
+      <c r="J44" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
@@ -3714,14 +3714,14 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
+          <t>28/04/2026</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
           <t>27/04/2026</t>
         </is>
       </c>
-      <c r="B45" s="2" t="inlineStr">
-        <is>
-          <t>26/04/2026</t>
-        </is>
-      </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -3753,11 +3753,11 @@
         </is>
       </c>
       <c r="I45" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
-          <t>▼ 66,7%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr">
@@ -3787,12 +3787,12 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
           <t>26/04/2026</t>
-        </is>
-      </c>
-      <c r="B46" s="2" t="inlineStr">
-        <is>
-          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -3860,14 +3860,14 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
           <t>26/04/2026</t>
         </is>
       </c>
-      <c r="B47" s="2" t="inlineStr">
-        <is>
-          <t>25/04/2026</t>
-        </is>
-      </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -3899,11 +3899,11 @@
         </is>
       </c>
       <c r="I47" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J47" s="4" t="inlineStr">
-        <is>
-          <t>▲ 200,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J47" s="3" t="inlineStr">
+        <is>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K47" s="2" t="inlineStr">
@@ -3933,12 +3933,12 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
+          <t>26/04/2026</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
           <t>25/04/2026</t>
-        </is>
-      </c>
-      <c r="B48" s="2" t="inlineStr">
-        <is>
-          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -3974,9 +3974,9 @@
       <c r="I48" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="J48" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+      <c r="J48" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr">
@@ -4006,14 +4006,14 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
+          <t>26/04/2026</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
           <t>25/04/2026</t>
         </is>
       </c>
-      <c r="B49" s="2" t="inlineStr">
-        <is>
-          <t>24/04/2026</t>
-        </is>
-      </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -4045,11 +4045,11 @@
         </is>
       </c>
       <c r="I49" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J49" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>3</v>
+      </c>
+      <c r="J49" s="4" t="inlineStr">
+        <is>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="K49" s="2" t="inlineStr">
@@ -4079,14 +4079,14 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
+          <t>25/04/2026</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
           <t>24/04/2026</t>
         </is>
       </c>
-      <c r="B50" s="2" t="inlineStr">
-        <is>
-          <t>23/04/2026</t>
-        </is>
-      </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -4118,11 +4118,11 @@
         </is>
       </c>
       <c r="I50" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J50" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J50" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K50" s="2" t="inlineStr">
@@ -4152,14 +4152,14 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
+          <t>25/04/2026</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
           <t>24/04/2026</t>
         </is>
       </c>
-      <c r="B51" s="2" t="inlineStr">
-        <is>
-          <t>23/04/2026</t>
-        </is>
-      </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -4182,7 +4182,7 @@
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
@@ -4190,10 +4190,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I51" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I51" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J51" s="2" t="inlineStr">
         <is>
@@ -4202,41 +4200,39 @@
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L51" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L51" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
+          <t>24/04/2026</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
           <t>23/04/2026</t>
         </is>
       </c>
-      <c r="B52" s="2" t="inlineStr">
-        <is>
-          <t>22/04/2026</t>
-        </is>
-      </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -4268,11 +4264,11 @@
         </is>
       </c>
       <c r="I52" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J52" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J52" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K52" s="2" t="inlineStr">
@@ -4302,12 +4298,12 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
+          <t>24/04/2026</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
           <t>23/04/2026</t>
-        </is>
-      </c>
-      <c r="B53" s="2" t="inlineStr">
-        <is>
-          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -4379,14 +4375,14 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
+          <t>23/04/2026</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
           <t>22/04/2026</t>
         </is>
       </c>
-      <c r="B54" s="2" t="inlineStr">
-        <is>
-          <t>21/04/2026</t>
-        </is>
-      </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -4418,11 +4414,11 @@
         </is>
       </c>
       <c r="I54" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J54" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J54" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr">
@@ -4452,14 +4448,14 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
+          <t>23/04/2026</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
           <t>22/04/2026</t>
         </is>
       </c>
-      <c r="B55" s="2" t="inlineStr">
-        <is>
-          <t>21/04/2026</t>
-        </is>
-      </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -4482,7 +4478,7 @@
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
@@ -4490,8 +4486,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I55" s="2" t="n">
-        <v>0</v>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
         <is>
@@ -4500,39 +4498,41 @@
       </c>
       <c r="K55" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L55" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L55" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
+          <t>22/04/2026</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
           <t>21/04/2026</t>
         </is>
       </c>
-      <c r="B56" s="2" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
-        </is>
-      </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -4564,11 +4564,11 @@
         </is>
       </c>
       <c r="I56" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J56" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>1</v>
+      </c>
+      <c r="J56" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr">
@@ -4586,7 +4586,7 @@
       </c>
       <c r="N56" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O56" s="2" t="inlineStr">
@@ -4598,14 +4598,14 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
+          <t>22/04/2026</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
           <t>21/04/2026</t>
         </is>
       </c>
-      <c r="B57" s="2" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
-        </is>
-      </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -4639,9 +4639,9 @@
       <c r="I57" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J57" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J57" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K57" s="2" t="inlineStr">
@@ -4671,14 +4671,14 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
           <t>20/04/2026</t>
         </is>
       </c>
-      <c r="B58" s="2" t="inlineStr">
-        <is>
-          <t>19/04/2026</t>
-        </is>
-      </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -4710,7 +4710,7 @@
         </is>
       </c>
       <c r="I58" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J58" s="2" t="inlineStr">
         <is>
@@ -4732,7 +4732,7 @@
       </c>
       <c r="N58" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O58" s="2" t="inlineStr">
@@ -4744,14 +4744,14 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
           <t>20/04/2026</t>
         </is>
       </c>
-      <c r="B59" s="2" t="inlineStr">
-        <is>
-          <t>19/04/2026</t>
-        </is>
-      </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -4783,11 +4783,11 @@
         </is>
       </c>
       <c r="I59" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J59" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J59" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K59" s="2" t="inlineStr">
@@ -4817,12 +4817,12 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
           <t>19/04/2026</t>
-        </is>
-      </c>
-      <c r="B60" s="2" t="inlineStr">
-        <is>
-          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -4890,14 +4890,14 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
           <t>19/04/2026</t>
         </is>
       </c>
-      <c r="B61" s="2" t="inlineStr">
-        <is>
-          <t>18/04/2026</t>
-        </is>
-      </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -4929,11 +4929,11 @@
         </is>
       </c>
       <c r="I61" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J61" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>4</v>
+      </c>
+      <c r="J61" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K61" s="2" t="inlineStr">
@@ -4963,12 +4963,12 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
           <t>18/04/2026</t>
-        </is>
-      </c>
-      <c r="B62" s="2" t="inlineStr">
-        <is>
-          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -5036,14 +5036,14 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
           <t>18/04/2026</t>
         </is>
       </c>
-      <c r="B63" s="2" t="inlineStr">
-        <is>
-          <t>17/04/2026</t>
-        </is>
-      </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -5075,7 +5075,7 @@
         </is>
       </c>
       <c r="I63" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J63" s="2" t="inlineStr">
         <is>
@@ -5109,14 +5109,14 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
           <t>17/04/2026</t>
         </is>
       </c>
-      <c r="B64" s="2" t="inlineStr">
-        <is>
-          <t>16/04/2026</t>
-        </is>
-      </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -5150,9 +5150,9 @@
       <c r="I64" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J64" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J64" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K64" s="2" t="inlineStr">
@@ -5182,14 +5182,14 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
           <t>17/04/2026</t>
         </is>
       </c>
-      <c r="B65" s="2" t="inlineStr">
-        <is>
-          <t>16/04/2026</t>
-        </is>
-      </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -5223,9 +5223,9 @@
       <c r="I65" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J65" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J65" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K65" s="2" t="inlineStr">
@@ -5255,14 +5255,14 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
           <t>16/04/2026</t>
         </is>
       </c>
-      <c r="B66" s="2" t="inlineStr">
-        <is>
-          <t>15/04/2026</t>
-        </is>
-      </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -5294,11 +5294,11 @@
         </is>
       </c>
       <c r="I66" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J66" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J66" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K66" s="2" t="inlineStr">
@@ -5328,14 +5328,14 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
           <t>16/04/2026</t>
         </is>
       </c>
-      <c r="B67" s="2" t="inlineStr">
-        <is>
-          <t>15/04/2026</t>
-        </is>
-      </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -5367,11 +5367,11 @@
         </is>
       </c>
       <c r="I67" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J67" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J67" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K67" s="2" t="inlineStr">
@@ -5401,14 +5401,14 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
           <t>15/04/2026</t>
         </is>
       </c>
-      <c r="B68" s="2" t="inlineStr">
-        <is>
-          <t>14/04/2026</t>
-        </is>
-      </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -5440,11 +5440,11 @@
         </is>
       </c>
       <c r="I68" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J68" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J68" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K68" s="2" t="inlineStr">
@@ -5474,12 +5474,12 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
           <t>15/04/2026</t>
-        </is>
-      </c>
-      <c r="B69" s="2" t="inlineStr">
-        <is>
-          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -5547,14 +5547,14 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
           <t>14/04/2026</t>
         </is>
       </c>
-      <c r="B70" s="2" t="inlineStr">
-        <is>
-          <t>13/04/2026</t>
-        </is>
-      </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -5586,11 +5586,11 @@
         </is>
       </c>
       <c r="I70" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J70" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J70" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr">
@@ -5620,12 +5620,12 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
           <t>14/04/2026</t>
-        </is>
-      </c>
-      <c r="B71" s="2" t="inlineStr">
-        <is>
-          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -5693,12 +5693,12 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
           <t>13/04/2026</t>
-        </is>
-      </c>
-      <c r="B72" s="2" t="inlineStr">
-        <is>
-          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
@@ -5766,12 +5766,12 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
           <t>13/04/2026</t>
-        </is>
-      </c>
-      <c r="B73" s="2" t="inlineStr">
-        <is>
-          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
           <t>12/04/2026</t>
-        </is>
-      </c>
-      <c r="B74" s="2" t="inlineStr">
-        <is>
-          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -5880,9 +5880,9 @@
       <c r="I74" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="J74" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+      <c r="J74" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr">
@@ -5912,12 +5912,12 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
           <t>12/04/2026</t>
-        </is>
-      </c>
-      <c r="B75" s="2" t="inlineStr">
-        <is>
-          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -5955,7 +5955,7 @@
       </c>
       <c r="J75" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K75" s="2" t="inlineStr">
@@ -5985,14 +5985,14 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
           <t>11/04/2026</t>
         </is>
       </c>
-      <c r="B76" s="2" t="inlineStr">
-        <is>
-          <t>10/04/2026</t>
-        </is>
-      </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -6024,11 +6024,11 @@
         </is>
       </c>
       <c r="I76" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J76" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J76" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K76" s="2" t="inlineStr">
@@ -6058,14 +6058,14 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
           <t>11/04/2026</t>
         </is>
       </c>
-      <c r="B77" s="2" t="inlineStr">
-        <is>
-          <t>10/04/2026</t>
-        </is>
-      </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -6097,11 +6097,11 @@
         </is>
       </c>
       <c r="I77" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J77" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J77" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K77" s="2" t="inlineStr">
@@ -6131,14 +6131,14 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
           <t>10/04/2026</t>
         </is>
       </c>
-      <c r="B78" s="2" t="inlineStr">
-        <is>
-          <t>09/04/2026</t>
-        </is>
-      </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -6170,11 +6170,11 @@
         </is>
       </c>
       <c r="I78" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J78" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>1</v>
+      </c>
+      <c r="J78" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K78" s="2" t="inlineStr">
@@ -6204,14 +6204,14 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
           <t>10/04/2026</t>
         </is>
       </c>
-      <c r="B79" s="2" t="inlineStr">
-        <is>
-          <t>09/04/2026</t>
-        </is>
-      </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -6243,11 +6243,11 @@
         </is>
       </c>
       <c r="I79" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J79" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J79" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K79" s="2" t="inlineStr">
@@ -6277,12 +6277,12 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
           <t>09/04/2026</t>
-        </is>
-      </c>
-      <c r="B80" s="2" t="inlineStr">
-        <is>
-          <t>08/04/2026</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
@@ -6318,9 +6318,9 @@
       <c r="I80" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="J80" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+      <c r="J80" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K80" s="2" t="inlineStr">
@@ -6350,14 +6350,14 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
           <t>09/04/2026</t>
         </is>
       </c>
-      <c r="B81" s="2" t="inlineStr">
-        <is>
-          <t>08/04/2026</t>
-        </is>
-      </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -6389,7 +6389,7 @@
         </is>
       </c>
       <c r="I81" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J81" s="2" t="inlineStr">
         <is>
@@ -6423,14 +6423,14 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
           <t>08/04/2026</t>
         </is>
       </c>
-      <c r="B82" s="2" t="inlineStr">
-        <is>
-          <t>07/04/2026</t>
-        </is>
-      </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -6456,17 +6456,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H82" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H82" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I82" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J82" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>2</v>
+      </c>
+      <c r="J82" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K82" s="2" t="inlineStr">
@@ -6496,14 +6496,14 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
           <t>08/04/2026</t>
         </is>
       </c>
-      <c r="B83" s="2" t="inlineStr">
-        <is>
-          <t>07/04/2026</t>
-        </is>
-      </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -6537,9 +6537,9 @@
       <c r="I83" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J83" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J83" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K83" s="2" t="inlineStr">
@@ -6569,14 +6569,14 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
           <t>07/04/2026</t>
         </is>
       </c>
-      <c r="B84" s="2" t="inlineStr">
-        <is>
-          <t>06/04/2026</t>
-        </is>
-      </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -6599,38 +6599,38 @@
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>R$ 110,00</t>
-        </is>
-      </c>
-      <c r="H84" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H84" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I84" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J84" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+      <c r="J84" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K84" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L84" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M84" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N84" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O84" s="2" t="inlineStr">
@@ -6642,14 +6642,14 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
           <t>07/04/2026</t>
         </is>
       </c>
-      <c r="B85" s="2" t="inlineStr">
-        <is>
-          <t>06/04/2026</t>
-        </is>
-      </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -6681,11 +6681,11 @@
         </is>
       </c>
       <c r="I85" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J85" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J85" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K85" s="2" t="inlineStr">
@@ -6715,14 +6715,14 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
           <t>06/04/2026</t>
         </is>
       </c>
-      <c r="B86" s="2" t="inlineStr">
-        <is>
-          <t>05/04/2026</t>
-        </is>
-      </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -6750,20 +6750,20 @@
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I86" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J86" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J86" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K86" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="L86" s="2" t="n">
@@ -6771,12 +6771,12 @@
       </c>
       <c r="M86" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="N86" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O86" s="2" t="inlineStr">
@@ -6788,14 +6788,14 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
           <t>06/04/2026</t>
         </is>
       </c>
-      <c r="B87" s="2" t="inlineStr">
-        <is>
-          <t>05/04/2026</t>
-        </is>
-      </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -6827,7 +6827,7 @@
         </is>
       </c>
       <c r="I87" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J87" s="2" t="inlineStr">
         <is>
@@ -6861,14 +6861,14 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
           <t>05/04/2026</t>
         </is>
       </c>
-      <c r="B88" s="2" t="inlineStr">
-        <is>
-          <t>04/04/2026</t>
-        </is>
-      </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -6891,7 +6891,7 @@
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 110,00</t>
         </is>
       </c>
       <c r="H88" s="2" t="inlineStr">
@@ -6900,24 +6900,24 @@
         </is>
       </c>
       <c r="I88" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J88" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
+        </is>
+      </c>
+      <c r="K88" s="2" t="inlineStr">
+        <is>
+          <t>50,0%</t>
+        </is>
+      </c>
+      <c r="L88" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J88" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K88" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L88" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="M88" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="N88" s="2" t="inlineStr">
@@ -6934,14 +6934,14 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
           <t>05/04/2026</t>
         </is>
       </c>
-      <c r="B89" s="2" t="inlineStr">
-        <is>
-          <t>04/04/2026</t>
-        </is>
-      </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -6975,9 +6975,9 @@
       <c r="I89" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J89" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J89" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K89" s="2" t="inlineStr">
@@ -7007,14 +7007,14 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
           <t>04/04/2026</t>
         </is>
       </c>
-      <c r="B90" s="2" t="inlineStr">
-        <is>
-          <t>03/04/2026</t>
-        </is>
-      </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -7046,7 +7046,7 @@
         </is>
       </c>
       <c r="I90" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J90" s="2" t="inlineStr">
         <is>
@@ -7080,14 +7080,14 @@
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
           <t>04/04/2026</t>
         </is>
       </c>
-      <c r="B91" s="2" t="inlineStr">
-        <is>
-          <t>03/04/2026</t>
-        </is>
-      </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -7119,11 +7119,11 @@
         </is>
       </c>
       <c r="I91" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J91" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J91" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K91" s="2" t="inlineStr">
@@ -7153,14 +7153,14 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
           <t>03/04/2026</t>
         </is>
       </c>
-      <c r="B92" s="2" t="inlineStr">
-        <is>
-          <t>02/04/2026</t>
-        </is>
-      </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -7194,9 +7194,9 @@
       <c r="I92" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J92" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J92" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K92" s="2" t="inlineStr">
@@ -7226,14 +7226,14 @@
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
           <t>03/04/2026</t>
         </is>
       </c>
-      <c r="B93" s="2" t="inlineStr">
-        <is>
-          <t>02/04/2026</t>
-        </is>
-      </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -7265,11 +7265,11 @@
         </is>
       </c>
       <c r="I93" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J93" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J93" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K93" s="2" t="inlineStr">
@@ -7299,14 +7299,14 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
           <t>02/04/2026</t>
         </is>
       </c>
-      <c r="B94" s="2" t="inlineStr">
-        <is>
-          <t>01/04/2026</t>
-        </is>
-      </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -7338,11 +7338,11 @@
         </is>
       </c>
       <c r="I94" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J94" s="3" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K94" s="2" t="inlineStr">
@@ -7372,14 +7372,14 @@
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
           <t>02/04/2026</t>
         </is>
       </c>
-      <c r="B95" s="2" t="inlineStr">
-        <is>
-          <t>01/04/2026</t>
-        </is>
-      </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -7411,11 +7411,11 @@
         </is>
       </c>
       <c r="I95" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J95" s="3" t="inlineStr">
         <is>
-          <t>▼ 66,7%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K95" s="2" t="inlineStr">
@@ -7445,14 +7445,14 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B96" s="2" t="inlineStr">
-        <is>
-          <t>31/03/2026</t>
-        </is>
-      </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -7484,11 +7484,11 @@
         </is>
       </c>
       <c r="I96" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J96" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>1</v>
+      </c>
+      <c r="J96" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K96" s="2" t="inlineStr">
@@ -7518,78 +7518,224 @@
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B97" s="2" t="inlineStr">
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>UTD-145</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor duplo com bica arthi</t>
+        </is>
+      </c>
+      <c r="E97" s="2" t="inlineStr">
+        <is>
+          <t>4498058823</t>
+        </is>
+      </c>
+      <c r="F97" s="2" t="inlineStr">
+        <is>
+          <t>R$ 157,65</t>
+        </is>
+      </c>
+      <c r="G97" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H97" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I97" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J97" s="3" t="inlineStr">
+        <is>
+          <t>▼ 66,7%</t>
+        </is>
+      </c>
+      <c r="K97" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L97" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M97" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N97" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O97" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
         <is>
           <t>31/03/2026</t>
         </is>
       </c>
-      <c r="C97" s="2" t="inlineStr">
-        <is>
-          <t>UTD-145</t>
-        </is>
-      </c>
-      <c r="D97" s="2" t="inlineStr">
-        <is>
-          <t>Escorredor duplo com bica arthi</t>
-        </is>
-      </c>
-      <c r="E97" s="2" t="inlineStr">
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>UTD-145</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor duplo com bica arthi</t>
+        </is>
+      </c>
+      <c r="E98" s="2" t="inlineStr">
+        <is>
+          <t>4645710434</t>
+        </is>
+      </c>
+      <c r="F98" s="2" t="inlineStr">
+        <is>
+          <t>R$ 157,65</t>
+        </is>
+      </c>
+      <c r="G98" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H98" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I98" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J98" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K98" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L98" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M98" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N98" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O98" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>UTD-145</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor duplo com bica arthi</t>
+        </is>
+      </c>
+      <c r="E99" s="2" t="inlineStr">
         <is>
           <t>4498058823</t>
         </is>
       </c>
-      <c r="F97" s="2" t="inlineStr">
-        <is>
-          <t>R$ 157,65</t>
-        </is>
-      </c>
-      <c r="G97" s="2" t="inlineStr">
-        <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H97" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I97" s="2" t="n">
+      <c r="F99" s="2" t="inlineStr">
+        <is>
+          <t>R$ 157,65</t>
+        </is>
+      </c>
+      <c r="G99" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H99" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I99" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="J97" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K97" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L97" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M97" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="N97" s="2" t="inlineStr">
+      <c r="J99" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K99" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L99" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M99" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N99" s="2" t="inlineStr">
         <is>
           <t>Sem calcular</t>
         </is>
       </c>
-      <c r="O97" s="2" t="inlineStr">
+      <c r="O99" s="2" t="inlineStr">
         <is>
           <t>Média</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O97"/>
+  <autoFilter ref="A1:O99"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/saida_skus/SKU_UTD-145-ESCORREDOR-DUPLO-COM-BICA-ARTHI.xlsx
+++ b/saida_skus/SKU_UTD-145-ESCORREDOR-DUPLO-COM-BICA-ARTHI.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Analise" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$99</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$103</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O99"/>
+  <dimension ref="A1:O103"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -559,12 +559,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -598,7 +598,7 @@
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
@@ -632,12 +632,12 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -673,9 +673,9 @@
       <c r="I3" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J3" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
@@ -705,12 +705,12 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -746,9 +746,9 @@
       <c r="I4" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J4" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -778,12 +778,12 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -817,7 +817,7 @@
         </is>
       </c>
       <c r="I5" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
@@ -851,12 +851,12 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -890,7 +890,7 @@
         </is>
       </c>
       <c r="I6" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
@@ -924,12 +924,12 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -962,10 +962,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I7" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
@@ -974,39 +972,37 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -1074,12 +1070,12 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -1147,12 +1143,12 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -1220,12 +1216,12 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -1250,7 +1246,7 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1258,47 +1254,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I11" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -1366,12 +1366,12 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -1405,7 +1405,7 @@
         </is>
       </c>
       <c r="I13" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
@@ -1439,12 +1439,12 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -1512,12 +1512,12 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1542,7 +1542,7 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1550,51 +1550,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I15" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1662,12 +1658,12 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1692,7 +1688,7 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -1700,10 +1696,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I17" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
@@ -1712,39 +1706,37 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1812,12 +1804,12 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -1842,7 +1834,7 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -1850,8 +1842,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I19" s="2" t="n">
-        <v>0</v>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
@@ -1860,37 +1854,39 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -1915,7 +1911,7 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
@@ -1923,51 +1919,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I20" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -1992,55 +1984,59 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H21" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J21" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -2074,7 +2070,7 @@
         </is>
       </c>
       <c r="I22" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
@@ -2108,12 +2104,12 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -2138,7 +2134,7 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>R$ 110,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
@@ -2147,7 +2143,7 @@
         </is>
       </c>
       <c r="I23" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
@@ -2156,15 +2152,15 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L23" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2181,12 +2177,12 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -2211,55 +2207,59 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H24" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J24" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -2287,9 +2287,9 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H25" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I25" s="2" t="n">
@@ -2327,12 +2327,12 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -2357,7 +2357,7 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>R$ 110,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
@@ -2366,24 +2366,24 @@
         </is>
       </c>
       <c r="I26" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J26" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L26" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -2400,12 +2400,12 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -2430,7 +2430,7 @@
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 110,00</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
@@ -2439,24 +2439,24 @@
         </is>
       </c>
       <c r="I27" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr">
+        <is>
+          <t>50,0%</t>
+        </is>
+      </c>
+      <c r="L27" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K27" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L27" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -2473,12 +2473,12 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -2506,17 +2506,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H28" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I28" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J28" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
@@ -2546,12 +2546,12 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -2619,12 +2619,12 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -2649,7 +2649,7 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 110,00</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
@@ -2658,24 +2658,24 @@
         </is>
       </c>
       <c r="I30" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>1</v>
+      </c>
+      <c r="J30" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="L30" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -2692,12 +2692,12 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -2731,7 +2731,7 @@
         </is>
       </c>
       <c r="I31" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
@@ -2765,12 +2765,12 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -2804,11 +2804,11 @@
         </is>
       </c>
       <c r="I32" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
@@ -2838,12 +2838,12 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -2911,12 +2911,12 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -2950,11 +2950,11 @@
         </is>
       </c>
       <c r="I34" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J34" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
@@ -2984,12 +2984,12 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -3023,11 +3023,11 @@
         </is>
       </c>
       <c r="I35" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
@@ -3057,12 +3057,12 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -3096,11 +3096,11 @@
         </is>
       </c>
       <c r="I36" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
@@ -3130,12 +3130,12 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -3169,11 +3169,11 @@
         </is>
       </c>
       <c r="I37" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
-          <t>▼ 66,7%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
@@ -3203,12 +3203,12 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -3242,11 +3242,11 @@
         </is>
       </c>
       <c r="I38" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J38" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J38" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
@@ -3276,12 +3276,12 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -3315,11 +3315,11 @@
         </is>
       </c>
       <c r="I39" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J39" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J39" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
@@ -3349,12 +3349,12 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -3388,11 +3388,11 @@
         </is>
       </c>
       <c r="I40" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J40" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
@@ -3422,12 +3422,12 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -3461,11 +3461,11 @@
         </is>
       </c>
       <c r="I41" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J41" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>1</v>
+      </c>
+      <c r="J41" s="3" t="inlineStr">
+        <is>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
@@ -3495,12 +3495,12 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -3534,11 +3534,11 @@
         </is>
       </c>
       <c r="I42" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
@@ -3561,19 +3561,19 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -3607,11 +3607,11 @@
         </is>
       </c>
       <c r="I43" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J43" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>3</v>
+      </c>
+      <c r="J43" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr">
@@ -3634,19 +3634,19 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -3680,11 +3680,11 @@
         </is>
       </c>
       <c r="I44" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J44" s="3" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
@@ -3707,19 +3707,19 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -3753,11 +3753,11 @@
         </is>
       </c>
       <c r="I45" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J45" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>6</v>
+      </c>
+      <c r="J45" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr">
@@ -3780,19 +3780,19 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -3826,7 +3826,7 @@
         </is>
       </c>
       <c r="I46" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
@@ -3860,12 +3860,12 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -3899,11 +3899,11 @@
         </is>
       </c>
       <c r="I47" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J47" s="3" t="inlineStr">
-        <is>
-          <t>▼ 66,7%</t>
+        <v>6</v>
+      </c>
+      <c r="J47" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K47" s="2" t="inlineStr">
@@ -3933,12 +3933,12 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -3972,11 +3972,11 @@
         </is>
       </c>
       <c r="I48" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J48" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>1</v>
+      </c>
+      <c r="J48" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr">
@@ -4006,12 +4006,12 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -4045,11 +4045,11 @@
         </is>
       </c>
       <c r="I49" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J49" s="4" t="inlineStr">
-        <is>
-          <t>▲ 200,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J49" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K49" s="2" t="inlineStr">
@@ -4079,12 +4079,12 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -4120,9 +4120,9 @@
       <c r="I50" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="J50" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+      <c r="J50" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K50" s="2" t="inlineStr">
@@ -4152,12 +4152,12 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -4193,9 +4193,9 @@
       <c r="I51" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J51" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="J51" s="3" t="inlineStr">
+        <is>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K51" s="2" t="inlineStr">
@@ -4225,12 +4225,12 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -4264,11 +4264,11 @@
         </is>
       </c>
       <c r="I52" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J52" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J52" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K52" s="2" t="inlineStr">
@@ -4298,12 +4298,12 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -4328,7 +4328,7 @@
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
@@ -4336,51 +4336,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I53" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J53" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I53" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="J53" s="4" t="inlineStr">
+        <is>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="K53" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L53" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L53" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -4448,12 +4444,12 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -4478,7 +4474,7 @@
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
@@ -4486,10 +4482,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I55" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I55" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J55" s="2" t="inlineStr">
         <is>
@@ -4498,39 +4492,37 @@
       </c>
       <c r="K55" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L55" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L55" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -4598,12 +4590,12 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -4628,7 +4620,7 @@
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
@@ -4636,8 +4628,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I57" s="2" t="n">
-        <v>0</v>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J57" s="2" t="inlineStr">
         <is>
@@ -4646,37 +4640,39 @@
       </c>
       <c r="K57" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L57" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L57" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -4712,9 +4708,9 @@
       <c r="I58" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="J58" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="J58" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr">
@@ -4732,7 +4728,7 @@
       </c>
       <c r="N58" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O58" s="2" t="inlineStr">
@@ -4744,12 +4740,12 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -4774,7 +4770,7 @@
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
@@ -4782,47 +4778,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I59" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J59" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="I59" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J59" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K59" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L59" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L59" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N59" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -4856,11 +4856,11 @@
         </is>
       </c>
       <c r="I60" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J60" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>1</v>
+      </c>
+      <c r="J60" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K60" s="2" t="inlineStr">
@@ -4890,12 +4890,12 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -4929,11 +4929,11 @@
         </is>
       </c>
       <c r="I61" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J61" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J61" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K61" s="2" t="inlineStr">
@@ -4963,12 +4963,12 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -5002,7 +5002,7 @@
         </is>
       </c>
       <c r="I62" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J62" s="2" t="inlineStr">
         <is>
@@ -5024,7 +5024,7 @@
       </c>
       <c r="N62" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O62" s="2" t="inlineStr">
@@ -5036,12 +5036,12 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -5075,11 +5075,11 @@
         </is>
       </c>
       <c r="I63" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J63" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J63" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K63" s="2" t="inlineStr">
@@ -5109,12 +5109,12 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -5182,12 +5182,12 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -5221,11 +5221,11 @@
         </is>
       </c>
       <c r="I65" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J65" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>4</v>
+      </c>
+      <c r="J65" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K65" s="2" t="inlineStr">
@@ -5255,12 +5255,12 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -5296,9 +5296,9 @@
       <c r="I66" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J66" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J66" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K66" s="2" t="inlineStr">
@@ -5328,12 +5328,12 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -5367,11 +5367,11 @@
         </is>
       </c>
       <c r="I67" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J67" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J67" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K67" s="2" t="inlineStr">
@@ -5401,12 +5401,12 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -5440,7 +5440,7 @@
         </is>
       </c>
       <c r="I68" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J68" s="2" t="inlineStr">
         <is>
@@ -5474,12 +5474,12 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -5513,11 +5513,11 @@
         </is>
       </c>
       <c r="I69" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J69" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K69" s="2" t="inlineStr">
@@ -5547,12 +5547,12 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
@@ -5620,12 +5620,12 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -5659,11 +5659,11 @@
         </is>
       </c>
       <c r="I71" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J71" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J71" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K71" s="2" t="inlineStr">
@@ -5693,12 +5693,12 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
@@ -5736,7 +5736,7 @@
       </c>
       <c r="J72" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr">
@@ -5766,12 +5766,12 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -5878,11 +5878,11 @@
         </is>
       </c>
       <c r="I74" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J74" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J74" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr">
@@ -5912,12 +5912,12 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -5985,12 +5985,12 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -6026,9 +6026,9 @@
       <c r="I76" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="J76" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+      <c r="J76" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K76" s="2" t="inlineStr">
@@ -6058,12 +6058,12 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
@@ -6101,7 +6101,7 @@
       </c>
       <c r="J77" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K77" s="2" t="inlineStr">
@@ -6131,12 +6131,12 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
@@ -6170,11 +6170,11 @@
         </is>
       </c>
       <c r="I78" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J78" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J78" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K78" s="2" t="inlineStr">
@@ -6204,12 +6204,12 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
@@ -6243,11 +6243,11 @@
         </is>
       </c>
       <c r="I79" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J79" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J79" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K79" s="2" t="inlineStr">
@@ -6277,12 +6277,12 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
@@ -6318,9 +6318,9 @@
       <c r="I80" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="J80" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+      <c r="J80" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K80" s="2" t="inlineStr">
@@ -6350,12 +6350,12 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
@@ -6389,7 +6389,7 @@
         </is>
       </c>
       <c r="I81" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J81" s="2" t="inlineStr">
         <is>
@@ -6423,12 +6423,12 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
@@ -6462,11 +6462,11 @@
         </is>
       </c>
       <c r="I82" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J82" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J82" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K82" s="2" t="inlineStr">
@@ -6496,12 +6496,12 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
@@ -6537,9 +6537,9 @@
       <c r="I83" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J83" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="J83" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K83" s="2" t="inlineStr">
@@ -6569,12 +6569,12 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
@@ -6602,13 +6602,13 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H84" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H84" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I84" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J84" s="2" t="inlineStr">
         <is>
@@ -6642,12 +6642,12 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
@@ -6681,11 +6681,11 @@
         </is>
       </c>
       <c r="I85" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J85" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J85" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K85" s="2" t="inlineStr">
@@ -6715,12 +6715,12 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
@@ -6745,38 +6745,38 @@
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>R$ 110,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I86" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J86" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J86" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K86" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L86" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M86" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N86" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O86" s="2" t="inlineStr">
@@ -6788,12 +6788,12 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
@@ -6827,7 +6827,7 @@
         </is>
       </c>
       <c r="I87" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J87" s="2" t="inlineStr">
         <is>
@@ -6861,12 +6861,12 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
@@ -6891,33 +6891,33 @@
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>R$ 110,00</t>
-        </is>
-      </c>
-      <c r="H88" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H88" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I88" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J88" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J88" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K88" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L88" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M88" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N88" s="2" t="inlineStr">
@@ -6934,12 +6934,12 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
@@ -6975,9 +6975,9 @@
       <c r="I89" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J89" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="J89" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K89" s="2" t="inlineStr">
@@ -7007,12 +7007,12 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
@@ -7037,38 +7037,38 @@
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 110,00</t>
         </is>
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I90" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J90" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="J90" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K90" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="L90" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M90" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="N90" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O90" s="2" t="inlineStr">
@@ -7080,12 +7080,12 @@
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
@@ -7119,11 +7119,11 @@
         </is>
       </c>
       <c r="I91" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J91" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>3</v>
+      </c>
+      <c r="J91" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K91" s="2" t="inlineStr">
@@ -7153,12 +7153,12 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
@@ -7183,7 +7183,7 @@
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 110,00</t>
         </is>
       </c>
       <c r="H92" s="2" t="inlineStr">
@@ -7192,24 +7192,24 @@
         </is>
       </c>
       <c r="I92" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J92" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>2</v>
+      </c>
+      <c r="J92" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K92" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>50,0%</t>
         </is>
       </c>
       <c r="L92" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M92" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="N92" s="2" t="inlineStr">
@@ -7226,12 +7226,12 @@
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
@@ -7265,7 +7265,7 @@
         </is>
       </c>
       <c r="I93" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J93" s="2" t="inlineStr">
         <is>
@@ -7299,12 +7299,12 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
@@ -7338,11 +7338,11 @@
         </is>
       </c>
       <c r="I94" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J94" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J94" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K94" s="2" t="inlineStr">
@@ -7372,12 +7372,12 @@
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
@@ -7445,12 +7445,12 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>03/04/2026</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
@@ -7484,11 +7484,11 @@
         </is>
       </c>
       <c r="I96" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J96" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J96" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K96" s="2" t="inlineStr">
@@ -7518,12 +7518,12 @@
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>03/04/2026</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
@@ -7559,9 +7559,9 @@
       <c r="I97" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J97" s="3" t="inlineStr">
-        <is>
-          <t>▼ 66,7%</t>
+      <c r="J97" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K97" s="2" t="inlineStr">
@@ -7591,12 +7591,12 @@
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>03/04/2026</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>31/03/2026</t>
+          <t>02/04/2026</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
@@ -7630,11 +7630,11 @@
         </is>
       </c>
       <c r="I98" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J98" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J98" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K98" s="2" t="inlineStr">
@@ -7664,78 +7664,370 @@
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>UTD-145</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor duplo com bica arthi</t>
+        </is>
+      </c>
+      <c r="E99" s="2" t="inlineStr">
+        <is>
+          <t>4498058823</t>
+        </is>
+      </c>
+      <c r="F99" s="2" t="inlineStr">
+        <is>
+          <t>R$ 157,65</t>
+        </is>
+      </c>
+      <c r="G99" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H99" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I99" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J99" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="K99" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L99" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M99" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N99" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O99" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B99" s="2" t="inlineStr">
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>UTD-145</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor duplo com bica arthi</t>
+        </is>
+      </c>
+      <c r="E100" s="2" t="inlineStr">
+        <is>
+          <t>4645710434</t>
+        </is>
+      </c>
+      <c r="F100" s="2" t="inlineStr">
+        <is>
+          <t>R$ 157,65</t>
+        </is>
+      </c>
+      <c r="G100" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H100" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I100" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J100" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
+        </is>
+      </c>
+      <c r="K100" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L100" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M100" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N100" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O100" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>UTD-145</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor duplo com bica arthi</t>
+        </is>
+      </c>
+      <c r="E101" s="2" t="inlineStr">
+        <is>
+          <t>4498058823</t>
+        </is>
+      </c>
+      <c r="F101" s="2" t="inlineStr">
+        <is>
+          <t>R$ 157,65</t>
+        </is>
+      </c>
+      <c r="G101" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H101" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I101" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J101" s="3" t="inlineStr">
+        <is>
+          <t>▼ 66,7%</t>
+        </is>
+      </c>
+      <c r="K101" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L101" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M101" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N101" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O101" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
         <is>
           <t>31/03/2026</t>
         </is>
       </c>
-      <c r="C99" s="2" t="inlineStr">
-        <is>
-          <t>UTD-145</t>
-        </is>
-      </c>
-      <c r="D99" s="2" t="inlineStr">
-        <is>
-          <t>Escorredor duplo com bica arthi</t>
-        </is>
-      </c>
-      <c r="E99" s="2" t="inlineStr">
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>UTD-145</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor duplo com bica arthi</t>
+        </is>
+      </c>
+      <c r="E102" s="2" t="inlineStr">
+        <is>
+          <t>4645710434</t>
+        </is>
+      </c>
+      <c r="F102" s="2" t="inlineStr">
+        <is>
+          <t>R$ 157,65</t>
+        </is>
+      </c>
+      <c r="G102" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H102" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I102" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J102" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K102" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L102" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M102" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N102" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O102" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>UTD-145</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor duplo com bica arthi</t>
+        </is>
+      </c>
+      <c r="E103" s="2" t="inlineStr">
         <is>
           <t>4498058823</t>
         </is>
       </c>
-      <c r="F99" s="2" t="inlineStr">
-        <is>
-          <t>R$ 157,65</t>
-        </is>
-      </c>
-      <c r="G99" s="2" t="inlineStr">
-        <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H99" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I99" s="2" t="n">
+      <c r="F103" s="2" t="inlineStr">
+        <is>
+          <t>R$ 157,65</t>
+        </is>
+      </c>
+      <c r="G103" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H103" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I103" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="J99" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K99" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L99" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M99" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="N99" s="2" t="inlineStr">
+      <c r="J103" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K103" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L103" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M103" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N103" s="2" t="inlineStr">
         <is>
           <t>Sem calcular</t>
         </is>
       </c>
-      <c r="O99" s="2" t="inlineStr">
+      <c r="O103" s="2" t="inlineStr">
         <is>
           <t>Média</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O99"/>
+  <autoFilter ref="A1:O103"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/saida_skus/SKU_UTD-145-ESCORREDOR-DUPLO-COM-BICA-ARTHI.xlsx
+++ b/saida_skus/SKU_UTD-145-ESCORREDOR-DUPLO-COM-BICA-ARTHI.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Analise" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$103</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$127</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O103"/>
+  <dimension ref="A1:O127"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -559,12 +559,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -592,17 +592,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J2" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
@@ -632,12 +632,12 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -671,11 +671,11 @@
         </is>
       </c>
       <c r="I3" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J3" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
@@ -705,12 +705,12 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>31/05/2026</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 126,00</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -744,7 +744,7 @@
         </is>
       </c>
       <c r="I4" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
@@ -753,15 +753,15 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="L4" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -778,12 +778,12 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>31/05/2026</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -821,7 +821,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -851,12 +851,12 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>31/05/2026</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>30/05/2026</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -884,17 +884,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H6" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I6" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="J6" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -924,12 +924,12 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>31/05/2026</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>30/05/2026</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -963,11 +963,11 @@
         </is>
       </c>
       <c r="I7" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>1</v>
+      </c>
+      <c r="J7" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -997,12 +997,12 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>30/05/2026</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 126,00</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -1036,24 +1036,24 @@
         </is>
       </c>
       <c r="I8" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t>▼ 100,0%</t>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="L8" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1070,12 +1070,12 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>30/05/2026</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -1109,7 +1109,7 @@
         </is>
       </c>
       <c r="I9" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
@@ -1143,12 +1143,12 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -1182,11 +1182,11 @@
         </is>
       </c>
       <c r="I10" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>2</v>
+      </c>
+      <c r="J10" s="3" t="inlineStr">
+        <is>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1216,12 +1216,12 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -1246,7 +1246,7 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1254,51 +1254,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I11" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -1332,11 +1328,11 @@
         </is>
       </c>
       <c r="I12" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J12" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>3</v>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1366,12 +1362,12 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -1405,11 +1401,11 @@
         </is>
       </c>
       <c r="I13" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>1</v>
+      </c>
+      <c r="J13" s="3" t="inlineStr">
+        <is>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -1439,12 +1435,12 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -1478,11 +1474,11 @@
         </is>
       </c>
       <c r="I14" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J14" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1512,12 +1508,12 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1551,11 +1547,11 @@
         </is>
       </c>
       <c r="I15" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J15" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>3</v>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -1585,12 +1581,12 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1624,11 +1620,11 @@
         </is>
       </c>
       <c r="I16" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J16" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>3</v>
+      </c>
+      <c r="J16" s="4" t="inlineStr">
+        <is>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1658,12 +1654,12 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1697,11 +1693,11 @@
         </is>
       </c>
       <c r="I17" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J17" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -1731,12 +1727,12 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>24/05/2026</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1770,11 +1766,11 @@
         </is>
       </c>
       <c r="I18" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>2</v>
+      </c>
+      <c r="J18" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1804,12 +1800,12 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>24/05/2026</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -1834,7 +1830,7 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -1842,51 +1838,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I19" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J19" s="3" t="inlineStr">
+        <is>
+          <t>▼ 83,3%</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>24/05/2026</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>23/05/2026</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -1914,17 +1906,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H20" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I20" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t>▼ 100,0%</t>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1954,12 +1946,12 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>24/05/2026</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>23/05/2026</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -1984,7 +1976,7 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -1992,51 +1984,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I21" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="J21" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>23/05/2026</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -2061,7 +2049,7 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 126,00</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
@@ -2070,24 +2058,24 @@
         </is>
       </c>
       <c r="I22" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J22" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>50,0%</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2104,12 +2092,12 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>23/05/2026</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -2143,11 +2131,11 @@
         </is>
       </c>
       <c r="I23" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -2177,12 +2165,12 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -2207,7 +2195,7 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
@@ -2215,51 +2203,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I24" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J24" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -2287,17 +2271,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H25" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I25" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J25" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>3</v>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
@@ -2327,12 +2311,12 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -2366,7 +2350,7 @@
         </is>
       </c>
       <c r="I26" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
@@ -2400,12 +2384,12 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -2430,7 +2414,7 @@
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>R$ 110,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
@@ -2439,24 +2423,24 @@
         </is>
       </c>
       <c r="I27" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J27" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L27" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -2473,12 +2457,12 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -2506,17 +2490,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H28" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I28" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J28" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
@@ -2546,12 +2530,12 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -2585,11 +2569,11 @@
         </is>
       </c>
       <c r="I29" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J29" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -2619,12 +2603,12 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -2649,7 +2633,7 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>R$ 110,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
@@ -2658,24 +2642,24 @@
         </is>
       </c>
       <c r="I30" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J30" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L30" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -2692,12 +2676,12 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -2731,7 +2715,7 @@
         </is>
       </c>
       <c r="I31" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
@@ -2765,12 +2749,12 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -2804,11 +2788,11 @@
         </is>
       </c>
       <c r="I32" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J32" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J32" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
@@ -2838,12 +2822,12 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -2879,9 +2863,9 @@
       <c r="I33" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J33" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
@@ -2911,12 +2895,12 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -2950,7 +2934,7 @@
         </is>
       </c>
       <c r="I34" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
@@ -2984,12 +2968,12 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -3014,7 +2998,7 @@
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
@@ -3022,8 +3006,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I35" s="2" t="n">
-        <v>2</v>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
@@ -3032,37 +3018,39 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L35" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L35" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -3098,9 +3086,9 @@
       <c r="I36" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J36" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="J36" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
@@ -3130,12 +3118,12 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -3171,9 +3159,9 @@
       <c r="I37" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J37" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
@@ -3203,12 +3191,12 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -3242,11 +3230,11 @@
         </is>
       </c>
       <c r="I38" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J38" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J38" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
@@ -3276,12 +3264,12 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -3315,11 +3303,11 @@
         </is>
       </c>
       <c r="I39" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J39" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J39" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
@@ -3349,12 +3337,12 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -3388,11 +3376,11 @@
         </is>
       </c>
       <c r="I40" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J40" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J40" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
@@ -3422,12 +3410,12 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -3463,9 +3451,9 @@
       <c r="I41" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J41" s="3" t="inlineStr">
-        <is>
-          <t>▼ 66,7%</t>
+      <c r="J41" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
@@ -3495,12 +3483,12 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -3534,7 +3522,7 @@
         </is>
       </c>
       <c r="I42" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
@@ -3568,12 +3556,12 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -3598,7 +3586,7 @@
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
@@ -3606,47 +3594,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I43" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J43" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L43" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L43" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -3714,12 +3706,12 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -3744,7 +3736,7 @@
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
@@ -3752,47 +3744,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I45" s="2" t="n">
-        <v>6</v>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L45" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L45" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -3830,7 +3826,7 @@
       </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
@@ -3853,19 +3849,19 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -3899,7 +3895,7 @@
         </is>
       </c>
       <c r="I47" s="2" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="J47" s="2" t="inlineStr">
         <is>
@@ -3926,19 +3922,19 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -3963,7 +3959,7 @@
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
@@ -3971,47 +3967,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I48" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J48" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L48" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L48" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -4039,9 +4039,9 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H49" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H49" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I49" s="2" t="n">
@@ -4072,19 +4072,19 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -4118,11 +4118,11 @@
         </is>
       </c>
       <c r="I50" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J50" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K50" s="2" t="inlineStr">
@@ -4145,19 +4145,19 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -4182,7 +4182,7 @@
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 110,00</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
@@ -4191,24 +4191,24 @@
         </is>
       </c>
       <c r="I51" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J51" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K51" s="2" t="inlineStr">
+        <is>
+          <t>50,0%</t>
+        </is>
+      </c>
+      <c r="L51" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J51" s="3" t="inlineStr">
-        <is>
-          <t>▼ 66,7%</t>
-        </is>
-      </c>
-      <c r="K51" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L51" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
@@ -4218,19 +4218,19 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -4258,17 +4258,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H52" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H52" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I52" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J52" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J52" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K52" s="2" t="inlineStr">
@@ -4291,19 +4291,19 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -4337,11 +4337,11 @@
         </is>
       </c>
       <c r="I53" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J53" s="4" t="inlineStr">
-        <is>
-          <t>▲ 200,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J53" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K53" s="2" t="inlineStr">
@@ -4364,19 +4364,19 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -4401,7 +4401,7 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 110,00</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
@@ -4410,24 +4410,24 @@
         </is>
       </c>
       <c r="I54" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J54" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J54" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="L54" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -4437,19 +4437,19 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -4510,19 +4510,19 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -4556,11 +4556,11 @@
         </is>
       </c>
       <c r="I56" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J56" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J56" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr">
@@ -4583,19 +4583,19 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -4620,7 +4620,7 @@
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
@@ -4628,51 +4628,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I57" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J57" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I57" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J57" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K57" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L57" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L57" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -4708,9 +4704,9 @@
       <c r="I58" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="J58" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+      <c r="J58" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr">
@@ -4733,19 +4729,19 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -4770,7 +4766,7 @@
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
@@ -4778,10 +4774,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I59" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I59" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="J59" s="2" t="inlineStr">
         <is>
@@ -4790,39 +4784,37 @@
       </c>
       <c r="K59" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L59" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L59" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N59" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -4856,11 +4848,11 @@
         </is>
       </c>
       <c r="I60" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J60" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J60" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K60" s="2" t="inlineStr">
@@ -4883,19 +4875,19 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -4931,9 +4923,9 @@
       <c r="I61" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J61" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="J61" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K61" s="2" t="inlineStr">
@@ -4956,19 +4948,19 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -5002,11 +4994,11 @@
         </is>
       </c>
       <c r="I62" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J62" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J62" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K62" s="2" t="inlineStr">
@@ -5024,24 +5016,24 @@
       </c>
       <c r="N62" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -5075,11 +5067,11 @@
         </is>
       </c>
       <c r="I63" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J63" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J63" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K63" s="2" t="inlineStr">
@@ -5102,19 +5094,19 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -5148,11 +5140,11 @@
         </is>
       </c>
       <c r="I64" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J64" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K64" s="2" t="inlineStr">
@@ -5175,19 +5167,19 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -5221,11 +5213,11 @@
         </is>
       </c>
       <c r="I65" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J65" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J65" s="3" t="inlineStr">
+        <is>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K65" s="2" t="inlineStr">
@@ -5248,19 +5240,19 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -5294,7 +5286,7 @@
         </is>
       </c>
       <c r="I66" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J66" s="2" t="inlineStr">
         <is>
@@ -5321,19 +5313,19 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -5367,11 +5359,11 @@
         </is>
       </c>
       <c r="I67" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J67" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>3</v>
+      </c>
+      <c r="J67" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K67" s="2" t="inlineStr">
@@ -5394,19 +5386,19 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -5442,9 +5434,9 @@
       <c r="I68" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J68" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="J68" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K68" s="2" t="inlineStr">
@@ -5467,19 +5459,19 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -5513,11 +5505,11 @@
         </is>
       </c>
       <c r="I69" s="2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J69" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K69" s="2" t="inlineStr">
@@ -5540,19 +5532,19 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
@@ -5586,11 +5578,11 @@
         </is>
       </c>
       <c r="I70" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J70" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J70" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr">
@@ -5620,12 +5612,12 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -5659,11 +5651,11 @@
         </is>
       </c>
       <c r="I71" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J71" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>6</v>
+      </c>
+      <c r="J71" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K71" s="2" t="inlineStr">
@@ -5693,12 +5685,12 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
@@ -5732,11 +5724,11 @@
         </is>
       </c>
       <c r="I72" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J72" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>1</v>
+      </c>
+      <c r="J72" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr">
@@ -5766,12 +5758,12 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -5805,11 +5797,11 @@
         </is>
       </c>
       <c r="I73" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J73" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J73" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K73" s="2" t="inlineStr">
@@ -5839,12 +5831,12 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -5878,11 +5870,11 @@
         </is>
       </c>
       <c r="I74" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J74" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J74" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr">
@@ -5912,12 +5904,12 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -5953,9 +5945,9 @@
       <c r="I75" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J75" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+      <c r="J75" s="3" t="inlineStr">
+        <is>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K75" s="2" t="inlineStr">
@@ -5985,12 +5977,12 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -6058,12 +6050,12 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
@@ -6097,11 +6089,11 @@
         </is>
       </c>
       <c r="I77" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J77" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>3</v>
+      </c>
+      <c r="J77" s="4" t="inlineStr">
+        <is>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="K77" s="2" t="inlineStr">
@@ -6131,12 +6123,12 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
@@ -6172,9 +6164,9 @@
       <c r="I78" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="J78" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+      <c r="J78" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K78" s="2" t="inlineStr">
@@ -6204,12 +6196,12 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
@@ -6247,7 +6239,7 @@
       </c>
       <c r="J79" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K79" s="2" t="inlineStr">
@@ -6277,12 +6269,12 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
@@ -6316,11 +6308,11 @@
         </is>
       </c>
       <c r="I80" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J80" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J80" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K80" s="2" t="inlineStr">
@@ -6350,12 +6342,12 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
@@ -6380,7 +6372,7 @@
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
@@ -6388,8 +6380,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I81" s="2" t="n">
-        <v>1</v>
+      <c r="I81" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J81" s="2" t="inlineStr">
         <is>
@@ -6398,37 +6392,39 @@
       </c>
       <c r="K81" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L81" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L81" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M81" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N81" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
@@ -6462,11 +6458,11 @@
         </is>
       </c>
       <c r="I82" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J82" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J82" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K82" s="2" t="inlineStr">
@@ -6496,12 +6492,12 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
@@ -6526,7 +6522,7 @@
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr">
@@ -6534,47 +6530,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I83" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J83" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="I83" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J83" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K83" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L83" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L83" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M83" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N83" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
@@ -6608,11 +6608,11 @@
         </is>
       </c>
       <c r="I84" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J84" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>1</v>
+      </c>
+      <c r="J84" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K84" s="2" t="inlineStr">
@@ -6642,12 +6642,12 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
@@ -6681,7 +6681,7 @@
         </is>
       </c>
       <c r="I85" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J85" s="2" t="inlineStr">
         <is>
@@ -6715,12 +6715,12 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
@@ -6756,9 +6756,9 @@
       <c r="I86" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="J86" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+      <c r="J86" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K86" s="2" t="inlineStr">
@@ -6776,7 +6776,7 @@
       </c>
       <c r="N86" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O86" s="2" t="inlineStr">
@@ -6788,12 +6788,12 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
@@ -6829,9 +6829,9 @@
       <c r="I87" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J87" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="J87" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K87" s="2" t="inlineStr">
@@ -6861,12 +6861,12 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
@@ -6894,17 +6894,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H88" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H88" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I88" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J88" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K88" s="2" t="inlineStr">
@@ -6934,12 +6934,12 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
@@ -6973,11 +6973,11 @@
         </is>
       </c>
       <c r="I89" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J89" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>4</v>
+      </c>
+      <c r="J89" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K89" s="2" t="inlineStr">
@@ -7007,12 +7007,12 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
@@ -7037,38 +7037,38 @@
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>R$ 110,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I90" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J90" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J90" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K90" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L90" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M90" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N90" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O90" s="2" t="inlineStr">
@@ -7080,12 +7080,12 @@
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
@@ -7119,7 +7119,7 @@
         </is>
       </c>
       <c r="I91" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J91" s="2" t="inlineStr">
         <is>
@@ -7153,12 +7153,12 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
@@ -7183,7 +7183,7 @@
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>R$ 110,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H92" s="2" t="inlineStr">
@@ -7192,24 +7192,24 @@
         </is>
       </c>
       <c r="I92" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J92" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J92" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K92" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L92" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M92" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N92" s="2" t="inlineStr">
@@ -7226,12 +7226,12 @@
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
@@ -7299,12 +7299,12 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
@@ -7338,11 +7338,11 @@
         </is>
       </c>
       <c r="I94" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J94" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J94" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K94" s="2" t="inlineStr">
@@ -7372,12 +7372,12 @@
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
@@ -7445,12 +7445,12 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
@@ -7484,7 +7484,7 @@
         </is>
       </c>
       <c r="I96" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J96" s="2" t="inlineStr">
         <is>
@@ -7518,12 +7518,12 @@
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
@@ -7561,7 +7561,7 @@
       </c>
       <c r="J97" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K97" s="2" t="inlineStr">
@@ -7591,12 +7591,12 @@
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
@@ -7664,12 +7664,12 @@
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
@@ -7703,11 +7703,11 @@
         </is>
       </c>
       <c r="I99" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J99" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J99" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K99" s="2" t="inlineStr">
@@ -7737,12 +7737,12 @@
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
@@ -7776,11 +7776,11 @@
         </is>
       </c>
       <c r="I100" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J100" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J100" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K100" s="2" t="inlineStr">
@@ -7810,12 +7810,12 @@
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
@@ -7851,9 +7851,9 @@
       <c r="I101" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J101" s="3" t="inlineStr">
-        <is>
-          <t>▼ 66,7%</t>
+      <c r="J101" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K101" s="2" t="inlineStr">
@@ -7883,12 +7883,12 @@
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>31/03/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
@@ -7926,7 +7926,7 @@
       </c>
       <c r="J102" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K102" s="2" t="inlineStr">
@@ -7956,78 +7956,1830 @@
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>UTD-145</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor duplo com bica arthi</t>
+        </is>
+      </c>
+      <c r="E103" s="2" t="inlineStr">
+        <is>
+          <t>4498058823</t>
+        </is>
+      </c>
+      <c r="F103" s="2" t="inlineStr">
+        <is>
+          <t>R$ 157,65</t>
+        </is>
+      </c>
+      <c r="G103" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H103" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I103" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J103" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="K103" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L103" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M103" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N103" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O103" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
+        <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>UTD-145</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor duplo com bica arthi</t>
+        </is>
+      </c>
+      <c r="E104" s="2" t="inlineStr">
+        <is>
+          <t>4645710434</t>
+        </is>
+      </c>
+      <c r="F104" s="2" t="inlineStr">
+        <is>
+          <t>R$ 157,65</t>
+        </is>
+      </c>
+      <c r="G104" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H104" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I104" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J104" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
+        </is>
+      </c>
+      <c r="K104" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L104" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M104" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N104" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O104" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr">
+        <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>UTD-145</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor duplo com bica arthi</t>
+        </is>
+      </c>
+      <c r="E105" s="2" t="inlineStr">
+        <is>
+          <t>4498058823</t>
+        </is>
+      </c>
+      <c r="F105" s="2" t="inlineStr">
+        <is>
+          <t>R$ 157,65</t>
+        </is>
+      </c>
+      <c r="G105" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H105" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I105" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J105" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K105" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L105" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M105" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N105" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O105" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
+        <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>UTD-145</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor duplo com bica arthi</t>
+        </is>
+      </c>
+      <c r="E106" s="2" t="inlineStr">
+        <is>
+          <t>4645710434</t>
+        </is>
+      </c>
+      <c r="F106" s="2" t="inlineStr">
+        <is>
+          <t>R$ 157,65</t>
+        </is>
+      </c>
+      <c r="G106" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H106" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I106" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J106" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
+        </is>
+      </c>
+      <c r="K106" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L106" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M106" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N106" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O106" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr">
+        <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t>UTD-145</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor duplo com bica arthi</t>
+        </is>
+      </c>
+      <c r="E107" s="2" t="inlineStr">
+        <is>
+          <t>4498058823</t>
+        </is>
+      </c>
+      <c r="F107" s="2" t="inlineStr">
+        <is>
+          <t>R$ 157,65</t>
+        </is>
+      </c>
+      <c r="G107" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H107" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I107" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J107" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="K107" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L107" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M107" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N107" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O107" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
+        <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>UTD-145</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor duplo com bica arthi</t>
+        </is>
+      </c>
+      <c r="E108" s="2" t="inlineStr">
+        <is>
+          <t>4645710434</t>
+        </is>
+      </c>
+      <c r="F108" s="2" t="inlineStr">
+        <is>
+          <t>R$ 157,65</t>
+        </is>
+      </c>
+      <c r="G108" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H108" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I108" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J108" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="K108" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L108" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M108" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N108" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O108" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="inlineStr">
+        <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B109" s="2" t="inlineStr">
+        <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="C109" s="2" t="inlineStr">
+        <is>
+          <t>UTD-145</t>
+        </is>
+      </c>
+      <c r="D109" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor duplo com bica arthi</t>
+        </is>
+      </c>
+      <c r="E109" s="2" t="inlineStr">
+        <is>
+          <t>4498058823</t>
+        </is>
+      </c>
+      <c r="F109" s="2" t="inlineStr">
+        <is>
+          <t>R$ 157,65</t>
+        </is>
+      </c>
+      <c r="G109" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H109" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I109" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J109" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K109" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L109" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M109" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N109" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O109" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr">
+        <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="C110" s="2" t="inlineStr">
+        <is>
+          <t>UTD-145</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor duplo com bica arthi</t>
+        </is>
+      </c>
+      <c r="E110" s="2" t="inlineStr">
+        <is>
+          <t>4645710434</t>
+        </is>
+      </c>
+      <c r="F110" s="2" t="inlineStr">
+        <is>
+          <t>R$ 157,65</t>
+        </is>
+      </c>
+      <c r="G110" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H110" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I110" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J110" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
+        </is>
+      </c>
+      <c r="K110" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L110" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M110" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N110" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O110" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="2" t="inlineStr">
+        <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="B111" s="2" t="inlineStr">
+        <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="C111" s="2" t="inlineStr">
+        <is>
+          <t>UTD-145</t>
+        </is>
+      </c>
+      <c r="D111" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor duplo com bica arthi</t>
+        </is>
+      </c>
+      <c r="E111" s="2" t="inlineStr">
+        <is>
+          <t>4498058823</t>
+        </is>
+      </c>
+      <c r="F111" s="2" t="inlineStr">
+        <is>
+          <t>R$ 157,65</t>
+        </is>
+      </c>
+      <c r="G111" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H111" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I111" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J111" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K111" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L111" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M111" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N111" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O111" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="2" t="inlineStr">
+        <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="B112" s="2" t="inlineStr">
+        <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="C112" s="2" t="inlineStr">
+        <is>
+          <t>UTD-145</t>
+        </is>
+      </c>
+      <c r="D112" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor duplo com bica arthi</t>
+        </is>
+      </c>
+      <c r="E112" s="2" t="inlineStr">
+        <is>
+          <t>4645710434</t>
+        </is>
+      </c>
+      <c r="F112" s="2" t="inlineStr">
+        <is>
+          <t>R$ 157,65</t>
+        </is>
+      </c>
+      <c r="G112" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H112" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="I112" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J112" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="K112" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L112" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M112" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N112" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O112" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="2" t="inlineStr">
+        <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="B113" s="2" t="inlineStr">
+        <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="C113" s="2" t="inlineStr">
+        <is>
+          <t>UTD-145</t>
+        </is>
+      </c>
+      <c r="D113" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor duplo com bica arthi</t>
+        </is>
+      </c>
+      <c r="E113" s="2" t="inlineStr">
+        <is>
+          <t>4498058823</t>
+        </is>
+      </c>
+      <c r="F113" s="2" t="inlineStr">
+        <is>
+          <t>R$ 157,65</t>
+        </is>
+      </c>
+      <c r="G113" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H113" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I113" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J113" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="K113" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L113" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M113" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N113" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O113" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="2" t="inlineStr">
+        <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="B114" s="2" t="inlineStr">
+        <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="C114" s="2" t="inlineStr">
+        <is>
+          <t>UTD-145</t>
+        </is>
+      </c>
+      <c r="D114" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor duplo com bica arthi</t>
+        </is>
+      </c>
+      <c r="E114" s="2" t="inlineStr">
+        <is>
+          <t>4645710434</t>
+        </is>
+      </c>
+      <c r="F114" s="2" t="inlineStr">
+        <is>
+          <t>R$ 157,65</t>
+        </is>
+      </c>
+      <c r="G114" s="2" t="inlineStr">
+        <is>
+          <t>R$ 110,00</t>
+        </is>
+      </c>
+      <c r="H114" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="I114" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J114" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
+        </is>
+      </c>
+      <c r="K114" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="L114" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M114" s="2" t="inlineStr">
+        <is>
+          <t>1,1%</t>
+        </is>
+      </c>
+      <c r="N114" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O114" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="2" t="inlineStr">
+        <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="B115" s="2" t="inlineStr">
+        <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="C115" s="2" t="inlineStr">
+        <is>
+          <t>UTD-145</t>
+        </is>
+      </c>
+      <c r="D115" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor duplo com bica arthi</t>
+        </is>
+      </c>
+      <c r="E115" s="2" t="inlineStr">
+        <is>
+          <t>4498058823</t>
+        </is>
+      </c>
+      <c r="F115" s="2" t="inlineStr">
+        <is>
+          <t>R$ 157,65</t>
+        </is>
+      </c>
+      <c r="G115" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H115" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I115" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="J115" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K115" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L115" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M115" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N115" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O115" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="2" t="inlineStr">
+        <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="B116" s="2" t="inlineStr">
+        <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="C116" s="2" t="inlineStr">
+        <is>
+          <t>UTD-145</t>
+        </is>
+      </c>
+      <c r="D116" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor duplo com bica arthi</t>
+        </is>
+      </c>
+      <c r="E116" s="2" t="inlineStr">
+        <is>
+          <t>4645710434</t>
+        </is>
+      </c>
+      <c r="F116" s="2" t="inlineStr">
+        <is>
+          <t>R$ 157,65</t>
+        </is>
+      </c>
+      <c r="G116" s="2" t="inlineStr">
+        <is>
+          <t>R$ 110,00</t>
+        </is>
+      </c>
+      <c r="H116" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I116" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J116" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
+        </is>
+      </c>
+      <c r="K116" s="2" t="inlineStr">
+        <is>
+          <t>50,0%</t>
+        </is>
+      </c>
+      <c r="L116" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M116" s="2" t="inlineStr">
+        <is>
+          <t>1,2%</t>
+        </is>
+      </c>
+      <c r="N116" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O116" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="inlineStr">
+        <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="B117" s="2" t="inlineStr">
+        <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="C117" s="2" t="inlineStr">
+        <is>
+          <t>UTD-145</t>
+        </is>
+      </c>
+      <c r="D117" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor duplo com bica arthi</t>
+        </is>
+      </c>
+      <c r="E117" s="2" t="inlineStr">
+        <is>
+          <t>4498058823</t>
+        </is>
+      </c>
+      <c r="F117" s="2" t="inlineStr">
+        <is>
+          <t>R$ 157,65</t>
+        </is>
+      </c>
+      <c r="G117" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H117" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I117" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J117" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K117" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L117" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M117" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N117" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O117" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="inlineStr">
+        <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B118" s="2" t="inlineStr">
+        <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="C118" s="2" t="inlineStr">
+        <is>
+          <t>UTD-145</t>
+        </is>
+      </c>
+      <c r="D118" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor duplo com bica arthi</t>
+        </is>
+      </c>
+      <c r="E118" s="2" t="inlineStr">
+        <is>
+          <t>4645710434</t>
+        </is>
+      </c>
+      <c r="F118" s="2" t="inlineStr">
+        <is>
+          <t>R$ 157,65</t>
+        </is>
+      </c>
+      <c r="G118" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H118" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I118" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J118" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K118" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L118" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M118" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N118" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O118" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="inlineStr">
+        <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B119" s="2" t="inlineStr">
+        <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="C119" s="2" t="inlineStr">
+        <is>
+          <t>UTD-145</t>
+        </is>
+      </c>
+      <c r="D119" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor duplo com bica arthi</t>
+        </is>
+      </c>
+      <c r="E119" s="2" t="inlineStr">
+        <is>
+          <t>4498058823</t>
+        </is>
+      </c>
+      <c r="F119" s="2" t="inlineStr">
+        <is>
+          <t>R$ 157,65</t>
+        </is>
+      </c>
+      <c r="G119" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H119" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I119" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J119" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="K119" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L119" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M119" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N119" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O119" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="inlineStr">
+        <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B120" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="C120" s="2" t="inlineStr">
+        <is>
+          <t>UTD-145</t>
+        </is>
+      </c>
+      <c r="D120" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor duplo com bica arthi</t>
+        </is>
+      </c>
+      <c r="E120" s="2" t="inlineStr">
+        <is>
+          <t>4645710434</t>
+        </is>
+      </c>
+      <c r="F120" s="2" t="inlineStr">
+        <is>
+          <t>R$ 157,65</t>
+        </is>
+      </c>
+      <c r="G120" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H120" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I120" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J120" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K120" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L120" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M120" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N120" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O120" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="inlineStr">
+        <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B121" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="C121" s="2" t="inlineStr">
+        <is>
+          <t>UTD-145</t>
+        </is>
+      </c>
+      <c r="D121" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor duplo com bica arthi</t>
+        </is>
+      </c>
+      <c r="E121" s="2" t="inlineStr">
+        <is>
+          <t>4498058823</t>
+        </is>
+      </c>
+      <c r="F121" s="2" t="inlineStr">
+        <is>
+          <t>R$ 157,65</t>
+        </is>
+      </c>
+      <c r="G121" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H121" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I121" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J121" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K121" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L121" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M121" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N121" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O121" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B122" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="C122" s="2" t="inlineStr">
+        <is>
+          <t>UTD-145</t>
+        </is>
+      </c>
+      <c r="D122" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor duplo com bica arthi</t>
+        </is>
+      </c>
+      <c r="E122" s="2" t="inlineStr">
+        <is>
+          <t>4645710434</t>
+        </is>
+      </c>
+      <c r="F122" s="2" t="inlineStr">
+        <is>
+          <t>R$ 157,65</t>
+        </is>
+      </c>
+      <c r="G122" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H122" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I122" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J122" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="K122" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L122" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M122" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N122" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O122" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B123" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="C123" s="2" t="inlineStr">
+        <is>
+          <t>UTD-145</t>
+        </is>
+      </c>
+      <c r="D123" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor duplo com bica arthi</t>
+        </is>
+      </c>
+      <c r="E123" s="2" t="inlineStr">
+        <is>
+          <t>4498058823</t>
+        </is>
+      </c>
+      <c r="F123" s="2" t="inlineStr">
+        <is>
+          <t>R$ 157,65</t>
+        </is>
+      </c>
+      <c r="G123" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H123" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I123" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J123" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="K123" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L123" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M123" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N123" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O123" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B124" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B103" s="2" t="inlineStr">
+      <c r="C124" s="2" t="inlineStr">
+        <is>
+          <t>UTD-145</t>
+        </is>
+      </c>
+      <c r="D124" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor duplo com bica arthi</t>
+        </is>
+      </c>
+      <c r="E124" s="2" t="inlineStr">
+        <is>
+          <t>4645710434</t>
+        </is>
+      </c>
+      <c r="F124" s="2" t="inlineStr">
+        <is>
+          <t>R$ 157,65</t>
+        </is>
+      </c>
+      <c r="G124" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H124" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I124" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J124" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
+        </is>
+      </c>
+      <c r="K124" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L124" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M124" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N124" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O124" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B125" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="C125" s="2" t="inlineStr">
+        <is>
+          <t>UTD-145</t>
+        </is>
+      </c>
+      <c r="D125" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor duplo com bica arthi</t>
+        </is>
+      </c>
+      <c r="E125" s="2" t="inlineStr">
+        <is>
+          <t>4498058823</t>
+        </is>
+      </c>
+      <c r="F125" s="2" t="inlineStr">
+        <is>
+          <t>R$ 157,65</t>
+        </is>
+      </c>
+      <c r="G125" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H125" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I125" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J125" s="3" t="inlineStr">
+        <is>
+          <t>▼ 66,7%</t>
+        </is>
+      </c>
+      <c r="K125" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L125" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M125" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N125" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O125" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B126" s="2" t="inlineStr">
         <is>
           <t>31/03/2026</t>
         </is>
       </c>
-      <c r="C103" s="2" t="inlineStr">
-        <is>
-          <t>UTD-145</t>
-        </is>
-      </c>
-      <c r="D103" s="2" t="inlineStr">
-        <is>
-          <t>Escorredor duplo com bica arthi</t>
-        </is>
-      </c>
-      <c r="E103" s="2" t="inlineStr">
+      <c r="C126" s="2" t="inlineStr">
+        <is>
+          <t>UTD-145</t>
+        </is>
+      </c>
+      <c r="D126" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor duplo com bica arthi</t>
+        </is>
+      </c>
+      <c r="E126" s="2" t="inlineStr">
+        <is>
+          <t>4645710434</t>
+        </is>
+      </c>
+      <c r="F126" s="2" t="inlineStr">
+        <is>
+          <t>R$ 157,65</t>
+        </is>
+      </c>
+      <c r="G126" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H126" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I126" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J126" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K126" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L126" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M126" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N126" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O126" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B127" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C127" s="2" t="inlineStr">
+        <is>
+          <t>UTD-145</t>
+        </is>
+      </c>
+      <c r="D127" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor duplo com bica arthi</t>
+        </is>
+      </c>
+      <c r="E127" s="2" t="inlineStr">
         <is>
           <t>4498058823</t>
         </is>
       </c>
-      <c r="F103" s="2" t="inlineStr">
-        <is>
-          <t>R$ 157,65</t>
-        </is>
-      </c>
-      <c r="G103" s="2" t="inlineStr">
-        <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H103" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I103" s="2" t="n">
+      <c r="F127" s="2" t="inlineStr">
+        <is>
+          <t>R$ 157,65</t>
+        </is>
+      </c>
+      <c r="G127" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H127" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I127" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="J103" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K103" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L103" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M103" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="N103" s="2" t="inlineStr">
+      <c r="J127" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K127" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L127" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M127" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N127" s="2" t="inlineStr">
         <is>
           <t>Sem calcular</t>
         </is>
       </c>
-      <c r="O103" s="2" t="inlineStr">
+      <c r="O127" s="2" t="inlineStr">
         <is>
           <t>Média</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O103"/>
+  <autoFilter ref="A1:O127"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/saida_skus/SKU_UTD-145-ESCORREDOR-DUPLO-COM-BICA-ARTHI.xlsx
+++ b/saida_skus/SKU_UTD-145-ESCORREDOR-DUPLO-COM-BICA-ARTHI.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Analise" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$127</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$169</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O127"/>
+  <dimension ref="A1:O169"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -559,12 +559,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>02/06/2026</t>
+          <t>23/06/2026</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>01/06/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -592,17 +592,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H2" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I2" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J2" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
@@ -632,12 +632,12 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>02/06/2026</t>
+          <t>23/06/2026</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>01/06/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -673,9 +673,9 @@
       <c r="I3" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J3" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
@@ -705,12 +705,12 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>01/06/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>31/05/2026</t>
+          <t>21/06/2026</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>R$ 126,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -744,24 +744,24 @@
         </is>
       </c>
       <c r="I4" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L4" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -778,12 +778,12 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>01/06/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>31/05/2026</t>
+          <t>21/06/2026</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -817,7 +817,7 @@
         </is>
       </c>
       <c r="I5" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
@@ -851,12 +851,12 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>31/05/2026</t>
+          <t>21/06/2026</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>30/05/2026</t>
+          <t>20/06/2026</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -884,17 +884,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H6" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I6" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -924,12 +924,12 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>31/05/2026</t>
+          <t>21/06/2026</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>30/05/2026</t>
+          <t>20/06/2026</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -963,11 +963,11 @@
         </is>
       </c>
       <c r="I7" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J7" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -997,12 +997,12 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>30/05/2026</t>
+          <t>20/06/2026</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>29/05/2026</t>
+          <t>19/06/2026</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>R$ 126,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -1035,47 +1035,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I8" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J8" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="n">
-        <v>1</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>30/05/2026</t>
+          <t>20/06/2026</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>29/05/2026</t>
+          <t>19/06/2026</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -1109,7 +1113,7 @@
         </is>
       </c>
       <c r="I9" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
@@ -1143,12 +1147,12 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>29/05/2026</t>
+          <t>19/06/2026</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>28/05/2026</t>
+          <t>18/06/2026</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -1182,11 +1186,11 @@
         </is>
       </c>
       <c r="I10" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J10" s="3" t="inlineStr">
-        <is>
-          <t>▼ 33,3%</t>
+        <v>0</v>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1216,12 +1220,12 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>29/05/2026</t>
+          <t>19/06/2026</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>28/05/2026</t>
+          <t>18/06/2026</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -1289,12 +1293,12 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>28/05/2026</t>
+          <t>18/06/2026</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>27/05/2026</t>
+          <t>17/06/2026</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -1319,7 +1323,7 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -1327,8 +1331,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I12" s="2" t="n">
-        <v>3</v>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
@@ -1337,37 +1343,39 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>28/05/2026</t>
+          <t>18/06/2026</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>27/05/2026</t>
+          <t>17/06/2026</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -1403,9 +1411,9 @@
       <c r="I13" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J13" s="3" t="inlineStr">
-        <is>
-          <t>▼ 66,7%</t>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -1435,12 +1443,12 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>27/05/2026</t>
+          <t>17/06/2026</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>26/05/2026</t>
+          <t>16/06/2026</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -1476,9 +1484,9 @@
       <c r="I14" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J14" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1508,12 +1516,12 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>27/05/2026</t>
+          <t>17/06/2026</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>26/05/2026</t>
+          <t>16/06/2026</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1547,11 +1555,11 @@
         </is>
       </c>
       <c r="I15" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -1581,12 +1589,12 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>26/05/2026</t>
+          <t>16/06/2026</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>25/05/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1620,11 +1628,11 @@
         </is>
       </c>
       <c r="I16" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J16" s="4" t="inlineStr">
-        <is>
-          <t>▲ 50,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J16" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1654,12 +1662,12 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>26/05/2026</t>
+          <t>16/06/2026</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>25/05/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1693,11 +1701,11 @@
         </is>
       </c>
       <c r="I17" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J17" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -1727,12 +1735,12 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>25/05/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>24/05/2026</t>
+          <t>14/06/2026</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1766,11 +1774,11 @@
         </is>
       </c>
       <c r="I18" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J18" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1800,12 +1808,12 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>25/05/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>24/05/2026</t>
+          <t>14/06/2026</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -1841,9 +1849,9 @@
       <c r="I19" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J19" s="3" t="inlineStr">
-        <is>
-          <t>▼ 83,3%</t>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -1873,12 +1881,12 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>24/05/2026</t>
+          <t>14/06/2026</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>23/05/2026</t>
+          <t>13/06/2026</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -1906,17 +1914,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H20" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I20" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J20" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1946,12 +1954,12 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>24/05/2026</t>
+          <t>14/06/2026</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>23/05/2026</t>
+          <t>13/06/2026</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -1985,11 +1993,11 @@
         </is>
       </c>
       <c r="I21" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J21" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J21" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
@@ -2019,12 +2027,12 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>23/05/2026</t>
+          <t>13/06/2026</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>12/06/2026</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -2049,7 +2057,7 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>R$ 126,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
@@ -2058,24 +2066,24 @@
         </is>
       </c>
       <c r="I22" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J22" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L22" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2092,12 +2100,12 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>23/05/2026</t>
+          <t>13/06/2026</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>12/06/2026</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -2131,11 +2139,11 @@
         </is>
       </c>
       <c r="I23" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -2165,12 +2173,12 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>12/06/2026</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -2206,9 +2214,9 @@
       <c r="I24" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J24" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
@@ -2238,12 +2246,12 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>12/06/2026</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -2277,7 +2285,7 @@
         </is>
       </c>
       <c r="I25" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
@@ -2311,12 +2319,12 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>10/06/2026</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -2350,11 +2358,11 @@
         </is>
       </c>
       <c r="I26" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>1</v>
+      </c>
+      <c r="J26" s="3" t="inlineStr">
+        <is>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -2384,12 +2392,12 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>10/06/2026</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -2425,9 +2433,9 @@
       <c r="I27" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J27" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
@@ -2457,12 +2465,12 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>10/06/2026</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>09/06/2026</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -2496,7 +2504,7 @@
         </is>
       </c>
       <c r="I28" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
@@ -2530,12 +2538,12 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>10/06/2026</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>09/06/2026</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -2563,17 +2571,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H29" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I29" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J29" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -2603,12 +2611,12 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>09/06/2026</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -2644,9 +2652,9 @@
       <c r="I30" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="J30" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
@@ -2676,12 +2684,12 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>09/06/2026</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -2706,7 +2714,7 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 107,00</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
@@ -2715,24 +2723,24 @@
         </is>
       </c>
       <c r="I31" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J31" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>2</v>
+      </c>
+      <c r="J31" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>50,0%</t>
         </is>
       </c>
       <c r="L31" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -2749,12 +2757,12 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>07/06/2026</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -2788,11 +2796,11 @@
         </is>
       </c>
       <c r="I32" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J32" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>3</v>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
@@ -2822,12 +2830,12 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>07/06/2026</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -2861,7 +2869,7 @@
         </is>
       </c>
       <c r="I33" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
@@ -2895,12 +2903,12 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>07/06/2026</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>06/06/2026</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -2934,11 +2942,11 @@
         </is>
       </c>
       <c r="I34" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J34" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J34" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
@@ -2968,12 +2976,12 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>07/06/2026</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>06/06/2026</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -2998,7 +3006,7 @@
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
@@ -3006,51 +3014,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I35" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J35" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I35" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J35" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L35" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L35" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>06/06/2026</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>05/06/2026</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -3084,11 +3088,11 @@
         </is>
       </c>
       <c r="I36" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J36" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
@@ -3118,12 +3122,12 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>06/06/2026</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>05/06/2026</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -3157,7 +3161,7 @@
         </is>
       </c>
       <c r="I37" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
@@ -3191,12 +3195,12 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>05/06/2026</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>04/06/2026</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -3264,12 +3268,12 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>05/06/2026</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>04/06/2026</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -3305,9 +3309,9 @@
       <c r="I39" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J39" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J39" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
@@ -3337,12 +3341,12 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>04/06/2026</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>03/06/2026</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -3410,12 +3414,12 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>04/06/2026</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>03/06/2026</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -3449,11 +3453,11 @@
         </is>
       </c>
       <c r="I41" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J41" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J41" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
@@ -3483,12 +3487,12 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>03/06/2026</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -3556,12 +3560,12 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>03/06/2026</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -3586,7 +3590,7 @@
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
@@ -3594,51 +3598,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I43" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I43" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J43" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L43" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L43" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -3666,9 +3666,9 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H44" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H44" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I44" s="2" t="n">
@@ -3706,12 +3706,12 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -3736,7 +3736,7 @@
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
@@ -3744,51 +3744,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I45" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I45" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L45" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L45" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>31/05/2026</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -3813,7 +3809,7 @@
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 126,00</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
@@ -3831,15 +3827,15 @@
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="L46" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -3856,12 +3852,12 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>31/05/2026</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -3895,11 +3891,11 @@
         </is>
       </c>
       <c r="I47" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J47" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K47" s="2" t="inlineStr">
@@ -3929,12 +3925,12 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>31/05/2026</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>30/05/2026</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -3959,59 +3955,55 @@
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H48" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I48" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J48" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H48" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J48" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L48" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L48" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>31/05/2026</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>30/05/2026</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -4039,17 +4031,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H49" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I49" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J49" s="3" t="inlineStr">
         <is>
-          <t>▼ 100,0%</t>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K49" s="2" t="inlineStr">
@@ -4079,12 +4071,12 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>30/05/2026</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -4109,7 +4101,7 @@
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 126,00</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
@@ -4118,24 +4110,24 @@
         </is>
       </c>
       <c r="I50" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J50" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>1</v>
+      </c>
+      <c r="J50" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="L50" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -4152,12 +4144,12 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>30/05/2026</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -4182,7 +4174,7 @@
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>R$ 110,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
@@ -4200,15 +4192,15 @@
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L51" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
@@ -4225,12 +4217,12 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -4258,17 +4250,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H52" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I52" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J52" s="3" t="inlineStr">
         <is>
-          <t>▼ 100,0%</t>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="K52" s="2" t="inlineStr">
@@ -4298,12 +4290,12 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -4371,12 +4363,12 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -4401,7 +4393,7 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>R$ 110,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
@@ -4410,24 +4402,24 @@
         </is>
       </c>
       <c r="I54" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J54" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+        <v>3</v>
+      </c>
+      <c r="J54" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L54" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -4444,12 +4436,12 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -4485,9 +4477,9 @@
       <c r="I55" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J55" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="J55" s="3" t="inlineStr">
+        <is>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K55" s="2" t="inlineStr">
@@ -4517,12 +4509,12 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -4556,11 +4548,11 @@
         </is>
       </c>
       <c r="I56" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J56" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J56" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr">
@@ -4590,12 +4582,12 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -4629,11 +4621,11 @@
         </is>
       </c>
       <c r="I57" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J57" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>3</v>
+      </c>
+      <c r="J57" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K57" s="2" t="inlineStr">
@@ -4663,12 +4655,12 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -4702,11 +4694,11 @@
         </is>
       </c>
       <c r="I58" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J58" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>3</v>
+      </c>
+      <c r="J58" s="4" t="inlineStr">
+        <is>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr">
@@ -4736,12 +4728,12 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -4775,11 +4767,11 @@
         </is>
       </c>
       <c r="I59" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J59" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J59" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K59" s="2" t="inlineStr">
@@ -4809,12 +4801,12 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>24/05/2026</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -4848,11 +4840,11 @@
         </is>
       </c>
       <c r="I60" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J60" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>2</v>
+      </c>
+      <c r="J60" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K60" s="2" t="inlineStr">
@@ -4882,12 +4874,12 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>24/05/2026</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -4921,11 +4913,11 @@
         </is>
       </c>
       <c r="I61" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J61" s="3" t="inlineStr">
         <is>
-          <t>▼ 100,0%</t>
+          <t>▼ 83,3%</t>
         </is>
       </c>
       <c r="K61" s="2" t="inlineStr">
@@ -4955,12 +4947,12 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>24/05/2026</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>23/05/2026</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -4988,17 +4980,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H62" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H62" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I62" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J62" s="3" t="inlineStr">
         <is>
-          <t>▼ 100,0%</t>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K62" s="2" t="inlineStr">
@@ -5028,12 +5020,12 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>24/05/2026</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>23/05/2026</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -5067,11 +5059,11 @@
         </is>
       </c>
       <c r="I63" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J63" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>6</v>
+      </c>
+      <c r="J63" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K63" s="2" t="inlineStr">
@@ -5101,12 +5093,12 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>23/05/2026</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -5131,7 +5123,7 @@
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 126,00</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
@@ -5142,22 +5134,22 @@
       <c r="I64" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="J64" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+      <c r="J64" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>50,0%</t>
         </is>
       </c>
       <c r="L64" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
@@ -5174,12 +5166,12 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>23/05/2026</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -5213,11 +5205,11 @@
         </is>
       </c>
       <c r="I65" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J65" s="3" t="inlineStr">
-        <is>
-          <t>▼ 66,7%</t>
+        <v>3</v>
+      </c>
+      <c r="J65" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K65" s="2" t="inlineStr">
@@ -5247,12 +5239,12 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -5286,11 +5278,11 @@
         </is>
       </c>
       <c r="I66" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J66" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>1</v>
+      </c>
+      <c r="J66" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K66" s="2" t="inlineStr">
@@ -5320,12 +5312,12 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -5361,9 +5353,9 @@
       <c r="I67" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="J67" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+      <c r="J67" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K67" s="2" t="inlineStr">
@@ -5393,12 +5385,12 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -5432,11 +5424,11 @@
         </is>
       </c>
       <c r="I68" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J68" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J68" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K68" s="2" t="inlineStr">
@@ -5466,12 +5458,12 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -5505,11 +5497,11 @@
         </is>
       </c>
       <c r="I69" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J69" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J69" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K69" s="2" t="inlineStr">
@@ -5539,12 +5531,12 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
@@ -5578,11 +5570,11 @@
         </is>
       </c>
       <c r="I70" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J70" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr">
@@ -5605,19 +5597,19 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -5651,7 +5643,7 @@
         </is>
       </c>
       <c r="I71" s="2" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="J71" s="2" t="inlineStr">
         <is>
@@ -5678,19 +5670,19 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
@@ -5724,11 +5716,11 @@
         </is>
       </c>
       <c r="I72" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J72" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J72" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr">
@@ -5751,19 +5743,19 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -5799,9 +5791,9 @@
       <c r="I73" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J73" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J73" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K73" s="2" t="inlineStr">
@@ -5824,19 +5816,19 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -5870,11 +5862,11 @@
         </is>
       </c>
       <c r="I74" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J74" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J74" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr">
@@ -5897,19 +5889,19 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -5943,11 +5935,11 @@
         </is>
       </c>
       <c r="I75" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J75" s="3" t="inlineStr">
-        <is>
-          <t>▼ 66,7%</t>
+        <v>0</v>
+      </c>
+      <c r="J75" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K75" s="2" t="inlineStr">
@@ -5970,19 +5962,19 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -6016,11 +6008,11 @@
         </is>
       </c>
       <c r="I76" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J76" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K76" s="2" t="inlineStr">
@@ -6043,19 +6035,19 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
@@ -6080,7 +6072,7 @@
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
@@ -6088,47 +6080,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I77" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J77" s="4" t="inlineStr">
-        <is>
-          <t>▲ 200,0%</t>
+      <c r="I77" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J77" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K77" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L77" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L77" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M77" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N77" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
@@ -6162,11 +6158,11 @@
         </is>
       </c>
       <c r="I78" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J78" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J78" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K78" s="2" t="inlineStr">
@@ -6189,19 +6185,19 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
@@ -6235,7 +6231,7 @@
         </is>
       </c>
       <c r="I79" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J79" s="2" t="inlineStr">
         <is>
@@ -6262,19 +6258,19 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
@@ -6310,9 +6306,9 @@
       <c r="I80" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J80" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+      <c r="J80" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K80" s="2" t="inlineStr">
@@ -6335,19 +6331,19 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
@@ -6372,7 +6368,7 @@
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
@@ -6380,51 +6376,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I81" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J81" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I81" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J81" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K81" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L81" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L81" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M81" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N81" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
@@ -6458,11 +6450,11 @@
         </is>
       </c>
       <c r="I82" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J82" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J82" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K82" s="2" t="inlineStr">
@@ -6485,19 +6477,19 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
@@ -6522,7 +6514,7 @@
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr">
@@ -6530,10 +6522,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I83" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I83" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J83" s="2" t="inlineStr">
         <is>
@@ -6542,39 +6532,37 @@
       </c>
       <c r="K83" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L83" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L83" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M83" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N83" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
@@ -6610,9 +6598,9 @@
       <c r="I84" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J84" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+      <c r="J84" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K84" s="2" t="inlineStr">
@@ -6635,19 +6623,19 @@
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
@@ -6672,7 +6660,7 @@
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr">
@@ -6680,8 +6668,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I85" s="2" t="n">
-        <v>0</v>
+      <c r="I85" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J85" s="2" t="inlineStr">
         <is>
@@ -6690,37 +6680,39 @@
       </c>
       <c r="K85" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L85" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L85" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M85" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N85" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
@@ -6754,11 +6746,11 @@
         </is>
       </c>
       <c r="I86" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J86" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J86" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K86" s="2" t="inlineStr">
@@ -6776,24 +6768,24 @@
       </c>
       <c r="N86" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
@@ -6818,7 +6810,7 @@
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
@@ -6826,47 +6818,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I87" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J87" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="I87" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J87" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K87" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L87" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L87" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M87" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N87" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
@@ -6900,7 +6896,7 @@
         </is>
       </c>
       <c r="I88" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J88" s="2" t="inlineStr">
         <is>
@@ -6927,19 +6923,19 @@
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
@@ -6973,11 +6969,11 @@
         </is>
       </c>
       <c r="I89" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J89" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J89" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K89" s="2" t="inlineStr">
@@ -7000,19 +6996,19 @@
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
@@ -7037,7 +7033,7 @@
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H90" s="2" t="inlineStr">
@@ -7045,8 +7041,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I90" s="2" t="n">
-        <v>0</v>
+      <c r="I90" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J90" s="2" t="inlineStr">
         <is>
@@ -7055,37 +7053,39 @@
       </c>
       <c r="K90" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L90" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L90" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M90" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N90" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
@@ -7113,17 +7113,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H91" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H91" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I91" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J91" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J91" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K91" s="2" t="inlineStr">
@@ -7146,19 +7146,19 @@
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
@@ -7219,19 +7219,19 @@
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
@@ -7256,7 +7256,7 @@
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 110,00</t>
         </is>
       </c>
       <c r="H93" s="2" t="inlineStr">
@@ -7265,7 +7265,7 @@
         </is>
       </c>
       <c r="I93" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J93" s="2" t="inlineStr">
         <is>
@@ -7274,15 +7274,15 @@
       </c>
       <c r="K93" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>50,0%</t>
         </is>
       </c>
       <c r="L93" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M93" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="N93" s="2" t="inlineStr">
@@ -7292,19 +7292,19 @@
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
@@ -7332,9 +7332,9 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H94" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H94" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I94" s="2" t="n">
@@ -7365,19 +7365,19 @@
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
@@ -7438,19 +7438,19 @@
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
@@ -7475,7 +7475,7 @@
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 110,00</t>
         </is>
       </c>
       <c r="H96" s="2" t="inlineStr">
@@ -7484,24 +7484,24 @@
         </is>
       </c>
       <c r="I96" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J96" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>1</v>
+      </c>
+      <c r="J96" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K96" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="L96" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M96" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="N96" s="2" t="inlineStr">
@@ -7511,19 +7511,19 @@
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
@@ -7561,7 +7561,7 @@
       </c>
       <c r="J97" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K97" s="2" t="inlineStr">
@@ -7584,19 +7584,19 @@
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
@@ -7630,11 +7630,11 @@
         </is>
       </c>
       <c r="I98" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J98" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J98" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K98" s="2" t="inlineStr">
@@ -7657,19 +7657,19 @@
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
@@ -7703,11 +7703,11 @@
         </is>
       </c>
       <c r="I99" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J99" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J99" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K99" s="2" t="inlineStr">
@@ -7730,19 +7730,19 @@
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
@@ -7780,7 +7780,7 @@
       </c>
       <c r="J100" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K100" s="2" t="inlineStr">
@@ -7803,19 +7803,19 @@
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
@@ -7849,11 +7849,11 @@
         </is>
       </c>
       <c r="I101" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J101" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K101" s="2" t="inlineStr">
@@ -7876,19 +7876,19 @@
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
@@ -7922,11 +7922,11 @@
         </is>
       </c>
       <c r="I102" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J102" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K102" s="2" t="inlineStr">
@@ -7949,19 +7949,19 @@
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C103" s="2" t="inlineStr">
@@ -7995,11 +7995,11 @@
         </is>
       </c>
       <c r="I103" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J103" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J103" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K103" s="2" t="inlineStr">
@@ -8022,19 +8022,19 @@
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C104" s="2" t="inlineStr">
@@ -8068,11 +8068,11 @@
         </is>
       </c>
       <c r="I104" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J104" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J104" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K104" s="2" t="inlineStr">
@@ -8095,19 +8095,19 @@
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C105" s="2" t="inlineStr">
@@ -8145,7 +8145,7 @@
       </c>
       <c r="J105" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K105" s="2" t="inlineStr">
@@ -8168,19 +8168,19 @@
       </c>
       <c r="O105" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C106" s="2" t="inlineStr">
@@ -8214,11 +8214,11 @@
         </is>
       </c>
       <c r="I106" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J106" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J106" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K106" s="2" t="inlineStr">
@@ -8241,19 +8241,19 @@
       </c>
       <c r="O106" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C107" s="2" t="inlineStr">
@@ -8287,11 +8287,11 @@
         </is>
       </c>
       <c r="I107" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J107" s="3" t="inlineStr">
         <is>
-          <t>▼ 100,0%</t>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K107" s="2" t="inlineStr">
@@ -8314,19 +8314,19 @@
       </c>
       <c r="O107" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C108" s="2" t="inlineStr">
@@ -8364,7 +8364,7 @@
       </c>
       <c r="J108" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K108" s="2" t="inlineStr">
@@ -8387,19 +8387,19 @@
       </c>
       <c r="O108" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C109" s="2" t="inlineStr">
@@ -8433,11 +8433,11 @@
         </is>
       </c>
       <c r="I109" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J109" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>3</v>
+      </c>
+      <c r="J109" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K109" s="2" t="inlineStr">
@@ -8460,19 +8460,19 @@
       </c>
       <c r="O109" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C110" s="2" t="inlineStr">
@@ -8506,11 +8506,11 @@
         </is>
       </c>
       <c r="I110" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J110" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J110" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K110" s="2" t="inlineStr">
@@ -8533,19 +8533,19 @@
       </c>
       <c r="O110" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C111" s="2" t="inlineStr">
@@ -8579,11 +8579,11 @@
         </is>
       </c>
       <c r="I111" s="2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J111" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K111" s="2" t="inlineStr">
@@ -8606,19 +8606,19 @@
       </c>
       <c r="O111" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C112" s="2" t="inlineStr">
@@ -8646,9 +8646,9 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H112" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H112" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I112" s="2" t="n">
@@ -8686,12 +8686,12 @@
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C113" s="2" t="inlineStr">
@@ -8725,11 +8725,11 @@
         </is>
       </c>
       <c r="I113" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J113" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>6</v>
+      </c>
+      <c r="J113" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K113" s="2" t="inlineStr">
@@ -8759,12 +8759,12 @@
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C114" s="2" t="inlineStr">
@@ -8789,12 +8789,12 @@
       </c>
       <c r="G114" s="2" t="inlineStr">
         <is>
-          <t>R$ 110,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H114" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I114" s="2" t="n">
@@ -8807,20 +8807,20 @@
       </c>
       <c r="K114" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L114" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M114" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N114" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O114" s="2" t="inlineStr">
@@ -8832,12 +8832,12 @@
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C115" s="2" t="inlineStr">
@@ -8871,11 +8871,11 @@
         </is>
       </c>
       <c r="I115" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J115" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J115" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K115" s="2" t="inlineStr">
@@ -8905,12 +8905,12 @@
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C116" s="2" t="inlineStr">
@@ -8935,7 +8935,7 @@
       </c>
       <c r="G116" s="2" t="inlineStr">
         <is>
-          <t>R$ 110,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H116" s="2" t="inlineStr">
@@ -8946,22 +8946,22 @@
       <c r="I116" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="J116" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+      <c r="J116" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K116" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L116" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M116" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N116" s="2" t="inlineStr">
@@ -8978,12 +8978,12 @@
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C117" s="2" t="inlineStr">
@@ -9017,11 +9017,11 @@
         </is>
       </c>
       <c r="I117" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J117" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>1</v>
+      </c>
+      <c r="J117" s="3" t="inlineStr">
+        <is>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K117" s="2" t="inlineStr">
@@ -9051,12 +9051,12 @@
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C118" s="2" t="inlineStr">
@@ -9090,11 +9090,11 @@
         </is>
       </c>
       <c r="I118" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J118" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K118" s="2" t="inlineStr">
@@ -9124,12 +9124,12 @@
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C119" s="2" t="inlineStr">
@@ -9163,11 +9163,11 @@
         </is>
       </c>
       <c r="I119" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J119" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>3</v>
+      </c>
+      <c r="J119" s="4" t="inlineStr">
+        <is>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="K119" s="2" t="inlineStr">
@@ -9197,12 +9197,12 @@
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C120" s="2" t="inlineStr">
@@ -9236,11 +9236,11 @@
         </is>
       </c>
       <c r="I120" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J120" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>2</v>
+      </c>
+      <c r="J120" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K120" s="2" t="inlineStr">
@@ -9270,12 +9270,12 @@
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C121" s="2" t="inlineStr">
@@ -9343,12 +9343,12 @@
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C122" s="2" t="inlineStr">
@@ -9382,11 +9382,11 @@
         </is>
       </c>
       <c r="I122" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J122" s="3" t="inlineStr">
         <is>
-          <t>▼ 100,0%</t>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K122" s="2" t="inlineStr">
@@ -9416,12 +9416,12 @@
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="B123" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C123" s="2" t="inlineStr">
@@ -9446,7 +9446,7 @@
       </c>
       <c r="G123" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H123" s="2" t="inlineStr">
@@ -9454,47 +9454,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I123" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J123" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="I123" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J123" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K123" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L123" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L123" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M123" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N123" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O123" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C124" s="2" t="inlineStr">
@@ -9528,11 +9532,11 @@
         </is>
       </c>
       <c r="I124" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J124" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J124" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K124" s="2" t="inlineStr">
@@ -9562,12 +9566,12 @@
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="B125" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C125" s="2" t="inlineStr">
@@ -9592,7 +9596,7 @@
       </c>
       <c r="G125" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H125" s="2" t="inlineStr">
@@ -9600,47 +9604,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I125" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J125" s="3" t="inlineStr">
-        <is>
-          <t>▼ 66,7%</t>
+      <c r="I125" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J125" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K125" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L125" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L125" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M125" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N125" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O125" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>31/03/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C126" s="2" t="inlineStr">
@@ -9674,11 +9682,11 @@
         </is>
       </c>
       <c r="I126" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J126" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>1</v>
+      </c>
+      <c r="J126" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K126" s="2" t="inlineStr">
@@ -9708,78 +9716,3144 @@
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
+          <t>22/04/2026</t>
+        </is>
+      </c>
+      <c r="B127" s="2" t="inlineStr">
+        <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="C127" s="2" t="inlineStr">
+        <is>
+          <t>UTD-145</t>
+        </is>
+      </c>
+      <c r="D127" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor duplo com bica arthi</t>
+        </is>
+      </c>
+      <c r="E127" s="2" t="inlineStr">
+        <is>
+          <t>4498058823</t>
+        </is>
+      </c>
+      <c r="F127" s="2" t="inlineStr">
+        <is>
+          <t>R$ 157,65</t>
+        </is>
+      </c>
+      <c r="G127" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H127" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I127" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J127" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K127" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L127" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M127" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N127" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O127" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="inlineStr">
+        <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="B128" s="2" t="inlineStr">
+        <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="C128" s="2" t="inlineStr">
+        <is>
+          <t>UTD-145</t>
+        </is>
+      </c>
+      <c r="D128" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor duplo com bica arthi</t>
+        </is>
+      </c>
+      <c r="E128" s="2" t="inlineStr">
+        <is>
+          <t>4645710434</t>
+        </is>
+      </c>
+      <c r="F128" s="2" t="inlineStr">
+        <is>
+          <t>R$ 157,65</t>
+        </is>
+      </c>
+      <c r="G128" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H128" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I128" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J128" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K128" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L128" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M128" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N128" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O128" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="inlineStr">
+        <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="B129" s="2" t="inlineStr">
+        <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="C129" s="2" t="inlineStr">
+        <is>
+          <t>UTD-145</t>
+        </is>
+      </c>
+      <c r="D129" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor duplo com bica arthi</t>
+        </is>
+      </c>
+      <c r="E129" s="2" t="inlineStr">
+        <is>
+          <t>4498058823</t>
+        </is>
+      </c>
+      <c r="F129" s="2" t="inlineStr">
+        <is>
+          <t>R$ 157,65</t>
+        </is>
+      </c>
+      <c r="G129" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H129" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I129" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J129" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="K129" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L129" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M129" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N129" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O129" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="inlineStr">
+        <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="B130" s="2" t="inlineStr">
+        <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="C130" s="2" t="inlineStr">
+        <is>
+          <t>UTD-145</t>
+        </is>
+      </c>
+      <c r="D130" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor duplo com bica arthi</t>
+        </is>
+      </c>
+      <c r="E130" s="2" t="inlineStr">
+        <is>
+          <t>4645710434</t>
+        </is>
+      </c>
+      <c r="F130" s="2" t="inlineStr">
+        <is>
+          <t>R$ 157,65</t>
+        </is>
+      </c>
+      <c r="G130" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H130" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I130" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J130" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K130" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L130" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M130" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N130" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O130" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="inlineStr">
+        <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="B131" s="2" t="inlineStr">
+        <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="C131" s="2" t="inlineStr">
+        <is>
+          <t>UTD-145</t>
+        </is>
+      </c>
+      <c r="D131" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor duplo com bica arthi</t>
+        </is>
+      </c>
+      <c r="E131" s="2" t="inlineStr">
+        <is>
+          <t>4498058823</t>
+        </is>
+      </c>
+      <c r="F131" s="2" t="inlineStr">
+        <is>
+          <t>R$ 157,65</t>
+        </is>
+      </c>
+      <c r="G131" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H131" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I131" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="J131" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
+        </is>
+      </c>
+      <c r="K131" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L131" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M131" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N131" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O131" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="inlineStr">
+        <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="B132" s="2" t="inlineStr">
+        <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="C132" s="2" t="inlineStr">
+        <is>
+          <t>UTD-145</t>
+        </is>
+      </c>
+      <c r="D132" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor duplo com bica arthi</t>
+        </is>
+      </c>
+      <c r="E132" s="2" t="inlineStr">
+        <is>
+          <t>4645710434</t>
+        </is>
+      </c>
+      <c r="F132" s="2" t="inlineStr">
+        <is>
+          <t>R$ 157,65</t>
+        </is>
+      </c>
+      <c r="G132" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H132" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I132" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J132" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K132" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L132" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M132" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N132" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O132" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="inlineStr">
+        <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="B133" s="2" t="inlineStr">
+        <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="C133" s="2" t="inlineStr">
+        <is>
+          <t>UTD-145</t>
+        </is>
+      </c>
+      <c r="D133" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor duplo com bica arthi</t>
+        </is>
+      </c>
+      <c r="E133" s="2" t="inlineStr">
+        <is>
+          <t>4498058823</t>
+        </is>
+      </c>
+      <c r="F133" s="2" t="inlineStr">
+        <is>
+          <t>R$ 157,65</t>
+        </is>
+      </c>
+      <c r="G133" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H133" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I133" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J133" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K133" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L133" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M133" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N133" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O133" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="inlineStr">
+        <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="B134" s="2" t="inlineStr">
+        <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="C134" s="2" t="inlineStr">
+        <is>
+          <t>UTD-145</t>
+        </is>
+      </c>
+      <c r="D134" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor duplo com bica arthi</t>
+        </is>
+      </c>
+      <c r="E134" s="2" t="inlineStr">
+        <is>
+          <t>4645710434</t>
+        </is>
+      </c>
+      <c r="F134" s="2" t="inlineStr">
+        <is>
+          <t>R$ 157,65</t>
+        </is>
+      </c>
+      <c r="G134" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H134" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I134" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J134" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K134" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L134" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M134" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N134" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O134" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="inlineStr">
+        <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="B135" s="2" t="inlineStr">
+        <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="C135" s="2" t="inlineStr">
+        <is>
+          <t>UTD-145</t>
+        </is>
+      </c>
+      <c r="D135" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor duplo com bica arthi</t>
+        </is>
+      </c>
+      <c r="E135" s="2" t="inlineStr">
+        <is>
+          <t>4498058823</t>
+        </is>
+      </c>
+      <c r="F135" s="2" t="inlineStr">
+        <is>
+          <t>R$ 157,65</t>
+        </is>
+      </c>
+      <c r="G135" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H135" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I135" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J135" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K135" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L135" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M135" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N135" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O135" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="inlineStr">
+        <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="B136" s="2" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="C136" s="2" t="inlineStr">
+        <is>
+          <t>UTD-145</t>
+        </is>
+      </c>
+      <c r="D136" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor duplo com bica arthi</t>
+        </is>
+      </c>
+      <c r="E136" s="2" t="inlineStr">
+        <is>
+          <t>4645710434</t>
+        </is>
+      </c>
+      <c r="F136" s="2" t="inlineStr">
+        <is>
+          <t>R$ 157,65</t>
+        </is>
+      </c>
+      <c r="G136" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H136" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I136" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J136" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="K136" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L136" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M136" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N136" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O136" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="inlineStr">
+        <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="B137" s="2" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="C137" s="2" t="inlineStr">
+        <is>
+          <t>UTD-145</t>
+        </is>
+      </c>
+      <c r="D137" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor duplo com bica arthi</t>
+        </is>
+      </c>
+      <c r="E137" s="2" t="inlineStr">
+        <is>
+          <t>4498058823</t>
+        </is>
+      </c>
+      <c r="F137" s="2" t="inlineStr">
+        <is>
+          <t>R$ 157,65</t>
+        </is>
+      </c>
+      <c r="G137" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H137" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I137" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J137" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="K137" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L137" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M137" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N137" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O137" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="B138" s="2" t="inlineStr">
+        <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="C138" s="2" t="inlineStr">
+        <is>
+          <t>UTD-145</t>
+        </is>
+      </c>
+      <c r="D138" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor duplo com bica arthi</t>
+        </is>
+      </c>
+      <c r="E138" s="2" t="inlineStr">
+        <is>
+          <t>4645710434</t>
+        </is>
+      </c>
+      <c r="F138" s="2" t="inlineStr">
+        <is>
+          <t>R$ 157,65</t>
+        </is>
+      </c>
+      <c r="G138" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H138" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I138" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J138" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K138" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L138" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M138" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N138" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O138" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="B139" s="2" t="inlineStr">
+        <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="C139" s="2" t="inlineStr">
+        <is>
+          <t>UTD-145</t>
+        </is>
+      </c>
+      <c r="D139" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor duplo com bica arthi</t>
+        </is>
+      </c>
+      <c r="E139" s="2" t="inlineStr">
+        <is>
+          <t>4498058823</t>
+        </is>
+      </c>
+      <c r="F139" s="2" t="inlineStr">
+        <is>
+          <t>R$ 157,65</t>
+        </is>
+      </c>
+      <c r="G139" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H139" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I139" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J139" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="K139" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L139" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M139" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N139" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O139" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="inlineStr">
+        <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="B140" s="2" t="inlineStr">
+        <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="C140" s="2" t="inlineStr">
+        <is>
+          <t>UTD-145</t>
+        </is>
+      </c>
+      <c r="D140" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor duplo com bica arthi</t>
+        </is>
+      </c>
+      <c r="E140" s="2" t="inlineStr">
+        <is>
+          <t>4645710434</t>
+        </is>
+      </c>
+      <c r="F140" s="2" t="inlineStr">
+        <is>
+          <t>R$ 157,65</t>
+        </is>
+      </c>
+      <c r="G140" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H140" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I140" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J140" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="K140" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L140" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M140" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N140" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O140" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="inlineStr">
+        <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="B141" s="2" t="inlineStr">
+        <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="C141" s="2" t="inlineStr">
+        <is>
+          <t>UTD-145</t>
+        </is>
+      </c>
+      <c r="D141" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor duplo com bica arthi</t>
+        </is>
+      </c>
+      <c r="E141" s="2" t="inlineStr">
+        <is>
+          <t>4498058823</t>
+        </is>
+      </c>
+      <c r="F141" s="2" t="inlineStr">
+        <is>
+          <t>R$ 157,65</t>
+        </is>
+      </c>
+      <c r="G141" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H141" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I141" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J141" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="K141" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L141" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M141" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N141" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O141" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="inlineStr">
+        <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="B142" s="2" t="inlineStr">
+        <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="C142" s="2" t="inlineStr">
+        <is>
+          <t>UTD-145</t>
+        </is>
+      </c>
+      <c r="D142" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor duplo com bica arthi</t>
+        </is>
+      </c>
+      <c r="E142" s="2" t="inlineStr">
+        <is>
+          <t>4645710434</t>
+        </is>
+      </c>
+      <c r="F142" s="2" t="inlineStr">
+        <is>
+          <t>R$ 157,65</t>
+        </is>
+      </c>
+      <c r="G142" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H142" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I142" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J142" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="K142" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L142" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M142" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N142" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O142" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="inlineStr">
+        <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="B143" s="2" t="inlineStr">
+        <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="C143" s="2" t="inlineStr">
+        <is>
+          <t>UTD-145</t>
+        </is>
+      </c>
+      <c r="D143" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor duplo com bica arthi</t>
+        </is>
+      </c>
+      <c r="E143" s="2" t="inlineStr">
+        <is>
+          <t>4498058823</t>
+        </is>
+      </c>
+      <c r="F143" s="2" t="inlineStr">
+        <is>
+          <t>R$ 157,65</t>
+        </is>
+      </c>
+      <c r="G143" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H143" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I143" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J143" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="K143" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L143" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M143" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N143" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O143" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="2" t="inlineStr">
+        <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="B144" s="2" t="inlineStr">
+        <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="C144" s="2" t="inlineStr">
+        <is>
+          <t>UTD-145</t>
+        </is>
+      </c>
+      <c r="D144" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor duplo com bica arthi</t>
+        </is>
+      </c>
+      <c r="E144" s="2" t="inlineStr">
+        <is>
+          <t>4645710434</t>
+        </is>
+      </c>
+      <c r="F144" s="2" t="inlineStr">
+        <is>
+          <t>R$ 157,65</t>
+        </is>
+      </c>
+      <c r="G144" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H144" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I144" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J144" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="K144" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L144" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M144" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N144" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O144" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="2" t="inlineStr">
+        <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="B145" s="2" t="inlineStr">
+        <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="C145" s="2" t="inlineStr">
+        <is>
+          <t>UTD-145</t>
+        </is>
+      </c>
+      <c r="D145" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor duplo com bica arthi</t>
+        </is>
+      </c>
+      <c r="E145" s="2" t="inlineStr">
+        <is>
+          <t>4498058823</t>
+        </is>
+      </c>
+      <c r="F145" s="2" t="inlineStr">
+        <is>
+          <t>R$ 157,65</t>
+        </is>
+      </c>
+      <c r="G145" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H145" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I145" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J145" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="K145" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L145" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M145" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N145" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O145" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="2" t="inlineStr">
+        <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B146" s="2" t="inlineStr">
+        <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="C146" s="2" t="inlineStr">
+        <is>
+          <t>UTD-145</t>
+        </is>
+      </c>
+      <c r="D146" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor duplo com bica arthi</t>
+        </is>
+      </c>
+      <c r="E146" s="2" t="inlineStr">
+        <is>
+          <t>4645710434</t>
+        </is>
+      </c>
+      <c r="F146" s="2" t="inlineStr">
+        <is>
+          <t>R$ 157,65</t>
+        </is>
+      </c>
+      <c r="G146" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H146" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I146" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J146" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
+        </is>
+      </c>
+      <c r="K146" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L146" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M146" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N146" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O146" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="2" t="inlineStr">
+        <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B147" s="2" t="inlineStr">
+        <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="C147" s="2" t="inlineStr">
+        <is>
+          <t>UTD-145</t>
+        </is>
+      </c>
+      <c r="D147" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor duplo com bica arthi</t>
+        </is>
+      </c>
+      <c r="E147" s="2" t="inlineStr">
+        <is>
+          <t>4498058823</t>
+        </is>
+      </c>
+      <c r="F147" s="2" t="inlineStr">
+        <is>
+          <t>R$ 157,65</t>
+        </is>
+      </c>
+      <c r="G147" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H147" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I147" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J147" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K147" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L147" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M147" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N147" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O147" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="2" t="inlineStr">
+        <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="B148" s="2" t="inlineStr">
+        <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="C148" s="2" t="inlineStr">
+        <is>
+          <t>UTD-145</t>
+        </is>
+      </c>
+      <c r="D148" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor duplo com bica arthi</t>
+        </is>
+      </c>
+      <c r="E148" s="2" t="inlineStr">
+        <is>
+          <t>4645710434</t>
+        </is>
+      </c>
+      <c r="F148" s="2" t="inlineStr">
+        <is>
+          <t>R$ 157,65</t>
+        </is>
+      </c>
+      <c r="G148" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H148" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I148" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J148" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
+        </is>
+      </c>
+      <c r="K148" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L148" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M148" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N148" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O148" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="2" t="inlineStr">
+        <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="B149" s="2" t="inlineStr">
+        <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="C149" s="2" t="inlineStr">
+        <is>
+          <t>UTD-145</t>
+        </is>
+      </c>
+      <c r="D149" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor duplo com bica arthi</t>
+        </is>
+      </c>
+      <c r="E149" s="2" t="inlineStr">
+        <is>
+          <t>4498058823</t>
+        </is>
+      </c>
+      <c r="F149" s="2" t="inlineStr">
+        <is>
+          <t>R$ 157,65</t>
+        </is>
+      </c>
+      <c r="G149" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H149" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I149" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J149" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="K149" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L149" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M149" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N149" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O149" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="2" t="inlineStr">
+        <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B150" s="2" t="inlineStr">
+        <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="C150" s="2" t="inlineStr">
+        <is>
+          <t>UTD-145</t>
+        </is>
+      </c>
+      <c r="D150" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor duplo com bica arthi</t>
+        </is>
+      </c>
+      <c r="E150" s="2" t="inlineStr">
+        <is>
+          <t>4645710434</t>
+        </is>
+      </c>
+      <c r="F150" s="2" t="inlineStr">
+        <is>
+          <t>R$ 157,65</t>
+        </is>
+      </c>
+      <c r="G150" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H150" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I150" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J150" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="K150" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L150" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M150" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N150" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O150" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="2" t="inlineStr">
+        <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B151" s="2" t="inlineStr">
+        <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="C151" s="2" t="inlineStr">
+        <is>
+          <t>UTD-145</t>
+        </is>
+      </c>
+      <c r="D151" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor duplo com bica arthi</t>
+        </is>
+      </c>
+      <c r="E151" s="2" t="inlineStr">
+        <is>
+          <t>4498058823</t>
+        </is>
+      </c>
+      <c r="F151" s="2" t="inlineStr">
+        <is>
+          <t>R$ 157,65</t>
+        </is>
+      </c>
+      <c r="G151" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H151" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I151" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J151" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K151" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L151" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M151" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N151" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O151" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="2" t="inlineStr">
+        <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="B152" s="2" t="inlineStr">
+        <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="C152" s="2" t="inlineStr">
+        <is>
+          <t>UTD-145</t>
+        </is>
+      </c>
+      <c r="D152" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor duplo com bica arthi</t>
+        </is>
+      </c>
+      <c r="E152" s="2" t="inlineStr">
+        <is>
+          <t>4645710434</t>
+        </is>
+      </c>
+      <c r="F152" s="2" t="inlineStr">
+        <is>
+          <t>R$ 157,65</t>
+        </is>
+      </c>
+      <c r="G152" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H152" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I152" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J152" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
+        </is>
+      </c>
+      <c r="K152" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L152" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M152" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N152" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O152" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="2" t="inlineStr">
+        <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="B153" s="2" t="inlineStr">
+        <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="C153" s="2" t="inlineStr">
+        <is>
+          <t>UTD-145</t>
+        </is>
+      </c>
+      <c r="D153" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor duplo com bica arthi</t>
+        </is>
+      </c>
+      <c r="E153" s="2" t="inlineStr">
+        <is>
+          <t>4498058823</t>
+        </is>
+      </c>
+      <c r="F153" s="2" t="inlineStr">
+        <is>
+          <t>R$ 157,65</t>
+        </is>
+      </c>
+      <c r="G153" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H153" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I153" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J153" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K153" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L153" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M153" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N153" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O153" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="2" t="inlineStr">
+        <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="B154" s="2" t="inlineStr">
+        <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="C154" s="2" t="inlineStr">
+        <is>
+          <t>UTD-145</t>
+        </is>
+      </c>
+      <c r="D154" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor duplo com bica arthi</t>
+        </is>
+      </c>
+      <c r="E154" s="2" t="inlineStr">
+        <is>
+          <t>4645710434</t>
+        </is>
+      </c>
+      <c r="F154" s="2" t="inlineStr">
+        <is>
+          <t>R$ 157,65</t>
+        </is>
+      </c>
+      <c r="G154" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H154" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="I154" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J154" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="K154" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L154" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M154" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N154" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O154" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="2" t="inlineStr">
+        <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="B155" s="2" t="inlineStr">
+        <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="C155" s="2" t="inlineStr">
+        <is>
+          <t>UTD-145</t>
+        </is>
+      </c>
+      <c r="D155" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor duplo com bica arthi</t>
+        </is>
+      </c>
+      <c r="E155" s="2" t="inlineStr">
+        <is>
+          <t>4498058823</t>
+        </is>
+      </c>
+      <c r="F155" s="2" t="inlineStr">
+        <is>
+          <t>R$ 157,65</t>
+        </is>
+      </c>
+      <c r="G155" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H155" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I155" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J155" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="K155" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L155" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M155" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N155" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O155" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="2" t="inlineStr">
+        <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="B156" s="2" t="inlineStr">
+        <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="C156" s="2" t="inlineStr">
+        <is>
+          <t>UTD-145</t>
+        </is>
+      </c>
+      <c r="D156" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor duplo com bica arthi</t>
+        </is>
+      </c>
+      <c r="E156" s="2" t="inlineStr">
+        <is>
+          <t>4645710434</t>
+        </is>
+      </c>
+      <c r="F156" s="2" t="inlineStr">
+        <is>
+          <t>R$ 157,65</t>
+        </is>
+      </c>
+      <c r="G156" s="2" t="inlineStr">
+        <is>
+          <t>R$ 110,00</t>
+        </is>
+      </c>
+      <c r="H156" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="I156" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J156" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
+        </is>
+      </c>
+      <c r="K156" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="L156" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M156" s="2" t="inlineStr">
+        <is>
+          <t>1,1%</t>
+        </is>
+      </c>
+      <c r="N156" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O156" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="2" t="inlineStr">
+        <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="B157" s="2" t="inlineStr">
+        <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="C157" s="2" t="inlineStr">
+        <is>
+          <t>UTD-145</t>
+        </is>
+      </c>
+      <c r="D157" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor duplo com bica arthi</t>
+        </is>
+      </c>
+      <c r="E157" s="2" t="inlineStr">
+        <is>
+          <t>4498058823</t>
+        </is>
+      </c>
+      <c r="F157" s="2" t="inlineStr">
+        <is>
+          <t>R$ 157,65</t>
+        </is>
+      </c>
+      <c r="G157" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H157" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I157" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="J157" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K157" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L157" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M157" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N157" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O157" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="2" t="inlineStr">
+        <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="B158" s="2" t="inlineStr">
+        <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="C158" s="2" t="inlineStr">
+        <is>
+          <t>UTD-145</t>
+        </is>
+      </c>
+      <c r="D158" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor duplo com bica arthi</t>
+        </is>
+      </c>
+      <c r="E158" s="2" t="inlineStr">
+        <is>
+          <t>4645710434</t>
+        </is>
+      </c>
+      <c r="F158" s="2" t="inlineStr">
+        <is>
+          <t>R$ 157,65</t>
+        </is>
+      </c>
+      <c r="G158" s="2" t="inlineStr">
+        <is>
+          <t>R$ 110,00</t>
+        </is>
+      </c>
+      <c r="H158" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I158" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J158" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
+        </is>
+      </c>
+      <c r="K158" s="2" t="inlineStr">
+        <is>
+          <t>50,0%</t>
+        </is>
+      </c>
+      <c r="L158" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M158" s="2" t="inlineStr">
+        <is>
+          <t>1,2%</t>
+        </is>
+      </c>
+      <c r="N158" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O158" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="2" t="inlineStr">
+        <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="B159" s="2" t="inlineStr">
+        <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="C159" s="2" t="inlineStr">
+        <is>
+          <t>UTD-145</t>
+        </is>
+      </c>
+      <c r="D159" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor duplo com bica arthi</t>
+        </is>
+      </c>
+      <c r="E159" s="2" t="inlineStr">
+        <is>
+          <t>4498058823</t>
+        </is>
+      </c>
+      <c r="F159" s="2" t="inlineStr">
+        <is>
+          <t>R$ 157,65</t>
+        </is>
+      </c>
+      <c r="G159" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H159" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I159" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J159" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K159" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L159" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M159" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N159" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O159" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="2" t="inlineStr">
+        <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B160" s="2" t="inlineStr">
+        <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="C160" s="2" t="inlineStr">
+        <is>
+          <t>UTD-145</t>
+        </is>
+      </c>
+      <c r="D160" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor duplo com bica arthi</t>
+        </is>
+      </c>
+      <c r="E160" s="2" t="inlineStr">
+        <is>
+          <t>4645710434</t>
+        </is>
+      </c>
+      <c r="F160" s="2" t="inlineStr">
+        <is>
+          <t>R$ 157,65</t>
+        </is>
+      </c>
+      <c r="G160" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H160" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I160" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J160" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K160" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L160" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M160" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N160" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O160" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="2" t="inlineStr">
+        <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B161" s="2" t="inlineStr">
+        <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="C161" s="2" t="inlineStr">
+        <is>
+          <t>UTD-145</t>
+        </is>
+      </c>
+      <c r="D161" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor duplo com bica arthi</t>
+        </is>
+      </c>
+      <c r="E161" s="2" t="inlineStr">
+        <is>
+          <t>4498058823</t>
+        </is>
+      </c>
+      <c r="F161" s="2" t="inlineStr">
+        <is>
+          <t>R$ 157,65</t>
+        </is>
+      </c>
+      <c r="G161" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H161" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I161" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J161" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="K161" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L161" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M161" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N161" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O161" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="2" t="inlineStr">
+        <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B162" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="C162" s="2" t="inlineStr">
+        <is>
+          <t>UTD-145</t>
+        </is>
+      </c>
+      <c r="D162" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor duplo com bica arthi</t>
+        </is>
+      </c>
+      <c r="E162" s="2" t="inlineStr">
+        <is>
+          <t>4645710434</t>
+        </is>
+      </c>
+      <c r="F162" s="2" t="inlineStr">
+        <is>
+          <t>R$ 157,65</t>
+        </is>
+      </c>
+      <c r="G162" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H162" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I162" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J162" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K162" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L162" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M162" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N162" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O162" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="2" t="inlineStr">
+        <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B163" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="C163" s="2" t="inlineStr">
+        <is>
+          <t>UTD-145</t>
+        </is>
+      </c>
+      <c r="D163" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor duplo com bica arthi</t>
+        </is>
+      </c>
+      <c r="E163" s="2" t="inlineStr">
+        <is>
+          <t>4498058823</t>
+        </is>
+      </c>
+      <c r="F163" s="2" t="inlineStr">
+        <is>
+          <t>R$ 157,65</t>
+        </is>
+      </c>
+      <c r="G163" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H163" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I163" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J163" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K163" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L163" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M163" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N163" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O163" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B164" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="C164" s="2" t="inlineStr">
+        <is>
+          <t>UTD-145</t>
+        </is>
+      </c>
+      <c r="D164" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor duplo com bica arthi</t>
+        </is>
+      </c>
+      <c r="E164" s="2" t="inlineStr">
+        <is>
+          <t>4645710434</t>
+        </is>
+      </c>
+      <c r="F164" s="2" t="inlineStr">
+        <is>
+          <t>R$ 157,65</t>
+        </is>
+      </c>
+      <c r="G164" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H164" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I164" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J164" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="K164" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L164" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M164" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N164" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O164" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B165" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="C165" s="2" t="inlineStr">
+        <is>
+          <t>UTD-145</t>
+        </is>
+      </c>
+      <c r="D165" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor duplo com bica arthi</t>
+        </is>
+      </c>
+      <c r="E165" s="2" t="inlineStr">
+        <is>
+          <t>4498058823</t>
+        </is>
+      </c>
+      <c r="F165" s="2" t="inlineStr">
+        <is>
+          <t>R$ 157,65</t>
+        </is>
+      </c>
+      <c r="G165" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H165" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I165" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J165" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="K165" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L165" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M165" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N165" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O165" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B166" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B127" s="2" t="inlineStr">
+      <c r="C166" s="2" t="inlineStr">
+        <is>
+          <t>UTD-145</t>
+        </is>
+      </c>
+      <c r="D166" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor duplo com bica arthi</t>
+        </is>
+      </c>
+      <c r="E166" s="2" t="inlineStr">
+        <is>
+          <t>4645710434</t>
+        </is>
+      </c>
+      <c r="F166" s="2" t="inlineStr">
+        <is>
+          <t>R$ 157,65</t>
+        </is>
+      </c>
+      <c r="G166" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H166" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I166" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J166" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
+        </is>
+      </c>
+      <c r="K166" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L166" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M166" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N166" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O166" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B167" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="C167" s="2" t="inlineStr">
+        <is>
+          <t>UTD-145</t>
+        </is>
+      </c>
+      <c r="D167" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor duplo com bica arthi</t>
+        </is>
+      </c>
+      <c r="E167" s="2" t="inlineStr">
+        <is>
+          <t>4498058823</t>
+        </is>
+      </c>
+      <c r="F167" s="2" t="inlineStr">
+        <is>
+          <t>R$ 157,65</t>
+        </is>
+      </c>
+      <c r="G167" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H167" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I167" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J167" s="3" t="inlineStr">
+        <is>
+          <t>▼ 66,7%</t>
+        </is>
+      </c>
+      <c r="K167" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L167" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M167" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N167" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O167" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B168" s="2" t="inlineStr">
         <is>
           <t>31/03/2026</t>
         </is>
       </c>
-      <c r="C127" s="2" t="inlineStr">
-        <is>
-          <t>UTD-145</t>
-        </is>
-      </c>
-      <c r="D127" s="2" t="inlineStr">
-        <is>
-          <t>Escorredor duplo com bica arthi</t>
-        </is>
-      </c>
-      <c r="E127" s="2" t="inlineStr">
+      <c r="C168" s="2" t="inlineStr">
+        <is>
+          <t>UTD-145</t>
+        </is>
+      </c>
+      <c r="D168" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor duplo com bica arthi</t>
+        </is>
+      </c>
+      <c r="E168" s="2" t="inlineStr">
+        <is>
+          <t>4645710434</t>
+        </is>
+      </c>
+      <c r="F168" s="2" t="inlineStr">
+        <is>
+          <t>R$ 157,65</t>
+        </is>
+      </c>
+      <c r="G168" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H168" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I168" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J168" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K168" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L168" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M168" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N168" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O168" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B169" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C169" s="2" t="inlineStr">
+        <is>
+          <t>UTD-145</t>
+        </is>
+      </c>
+      <c r="D169" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor duplo com bica arthi</t>
+        </is>
+      </c>
+      <c r="E169" s="2" t="inlineStr">
         <is>
           <t>4498058823</t>
         </is>
       </c>
-      <c r="F127" s="2" t="inlineStr">
-        <is>
-          <t>R$ 157,65</t>
-        </is>
-      </c>
-      <c r="G127" s="2" t="inlineStr">
-        <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H127" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I127" s="2" t="n">
+      <c r="F169" s="2" t="inlineStr">
+        <is>
+          <t>R$ 157,65</t>
+        </is>
+      </c>
+      <c r="G169" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H169" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I169" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="J127" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K127" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L127" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M127" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="N127" s="2" t="inlineStr">
+      <c r="J169" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K169" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L169" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M169" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N169" s="2" t="inlineStr">
         <is>
           <t>Sem calcular</t>
         </is>
       </c>
-      <c r="O127" s="2" t="inlineStr">
+      <c r="O169" s="2" t="inlineStr">
         <is>
           <t>Média</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O127"/>
+  <autoFilter ref="A1:O169"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/saida_skus/SKU_UTD-145-ESCORREDOR-DUPLO-COM-BICA-ARTHI.xlsx
+++ b/saida_skus/SKU_UTD-145-ESCORREDOR-DUPLO-COM-BICA-ARTHI.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Analise" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$169</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$171</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O169"/>
+  <dimension ref="A1:O171"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -559,12 +559,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
+          <t>24/06/2026</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
           <t>23/06/2026</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>22/06/2026</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -632,14 +632,14 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
+          <t>24/06/2026</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
           <t>23/06/2026</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>22/06/2026</t>
-        </is>
-      </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -671,11 +671,11 @@
         </is>
       </c>
       <c r="I3" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
@@ -705,14 +705,14 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
+          <t>23/06/2026</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
           <t>22/06/2026</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>21/06/2026</t>
-        </is>
-      </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -746,9 +746,9 @@
       <c r="I4" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J4" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -778,14 +778,14 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
+          <t>23/06/2026</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
           <t>22/06/2026</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>21/06/2026</t>
-        </is>
-      </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -817,11 +817,11 @@
         </is>
       </c>
       <c r="I5" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>1</v>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -851,14 +851,14 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
           <t>21/06/2026</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>20/06/2026</t>
-        </is>
-      </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -890,11 +890,11 @@
         </is>
       </c>
       <c r="I6" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J6" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -924,12 +924,12 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
           <t>21/06/2026</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>20/06/2026</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -967,7 +967,7 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -997,14 +997,14 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
+          <t>21/06/2026</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
           <t>20/06/2026</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>19/06/2026</t>
-        </is>
-      </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -1035,10 +1035,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I8" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
@@ -1047,41 +1045,39 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
+          <t>21/06/2026</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
           <t>20/06/2026</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>19/06/2026</t>
-        </is>
-      </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -1113,7 +1109,7 @@
         </is>
       </c>
       <c r="I9" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
@@ -1147,14 +1143,14 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
+          <t>20/06/2026</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
           <t>19/06/2026</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>18/06/2026</t>
-        </is>
-      </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -1177,7 +1173,7 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -1185,8 +1181,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I10" s="2" t="n">
-        <v>0</v>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
@@ -1195,39 +1193,41 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
+          <t>20/06/2026</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
           <t>19/06/2026</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>18/06/2026</t>
-        </is>
-      </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -1261,9 +1261,9 @@
       <c r="I11" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J11" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1293,14 +1293,14 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
+          <t>19/06/2026</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
           <t>18/06/2026</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>17/06/2026</t>
-        </is>
-      </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -1323,7 +1323,7 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -1331,10 +1331,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I12" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
@@ -1343,41 +1341,39 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
+          <t>19/06/2026</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
           <t>18/06/2026</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>17/06/2026</t>
-        </is>
-      </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -1409,11 +1405,11 @@
         </is>
       </c>
       <c r="I13" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J13" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -1443,14 +1439,14 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
+          <t>18/06/2026</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
           <t>17/06/2026</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>16/06/2026</t>
-        </is>
-      </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -1473,7 +1469,7 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -1481,8 +1477,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I14" s="2" t="n">
-        <v>0</v>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
@@ -1491,37 +1489,39 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
+          <t>18/06/2026</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
           <t>17/06/2026</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>16/06/2026</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1589,14 +1589,14 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
+          <t>17/06/2026</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
           <t>16/06/2026</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>15/06/2026</t>
-        </is>
-      </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -1630,9 +1630,9 @@
       <c r="I16" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J16" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1662,12 +1662,12 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
+          <t>17/06/2026</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
           <t>16/06/2026</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>15/06/2026</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1735,14 +1735,14 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
+          <t>16/06/2026</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
           <t>15/06/2026</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>14/06/2026</t>
-        </is>
-      </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -1774,11 +1774,11 @@
         </is>
       </c>
       <c r="I18" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J18" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1808,12 +1808,12 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
+          <t>16/06/2026</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
           <t>15/06/2026</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>14/06/2026</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -1881,12 +1881,12 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
+          <t>15/06/2026</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
           <t>14/06/2026</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>13/06/2026</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -1954,12 +1954,12 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
+          <t>15/06/2026</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
           <t>14/06/2026</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>13/06/2026</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -1995,9 +1995,9 @@
       <c r="I21" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J21" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
@@ -2027,12 +2027,12 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
+          <t>14/06/2026</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
           <t>13/06/2026</t>
-        </is>
-      </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>12/06/2026</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -2100,14 +2100,14 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
+          <t>14/06/2026</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
           <t>13/06/2026</t>
         </is>
       </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>12/06/2026</t>
-        </is>
-      </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -2139,11 +2139,11 @@
         </is>
       </c>
       <c r="I23" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>1</v>
+      </c>
+      <c r="J23" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -2173,12 +2173,12 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
+          <t>13/06/2026</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
           <t>12/06/2026</t>
-        </is>
-      </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>11/06/2026</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -2246,14 +2246,14 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
+          <t>13/06/2026</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
           <t>12/06/2026</t>
         </is>
       </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>11/06/2026</t>
-        </is>
-      </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -2285,7 +2285,7 @@
         </is>
       </c>
       <c r="I25" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
@@ -2319,12 +2319,12 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
+          <t>12/06/2026</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
           <t>11/06/2026</t>
-        </is>
-      </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>10/06/2026</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -2360,9 +2360,9 @@
       <c r="I26" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J26" s="3" t="inlineStr">
-        <is>
-          <t>▼ 66,7%</t>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
+          <t>12/06/2026</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
           <t>11/06/2026</t>
-        </is>
-      </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>10/06/2026</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -2465,14 +2465,14 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
+          <t>11/06/2026</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
           <t>10/06/2026</t>
         </is>
       </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>09/06/2026</t>
-        </is>
-      </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -2504,11 +2504,11 @@
         </is>
       </c>
       <c r="I28" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>1</v>
+      </c>
+      <c r="J28" s="3" t="inlineStr">
+        <is>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
@@ -2538,14 +2538,14 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
+          <t>11/06/2026</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
           <t>10/06/2026</t>
         </is>
       </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>09/06/2026</t>
-        </is>
-      </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -2571,17 +2571,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H29" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I29" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J29" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -2611,14 +2611,14 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
+          <t>10/06/2026</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
           <t>09/06/2026</t>
         </is>
       </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>08/06/2026</t>
-        </is>
-      </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -2650,11 +2650,11 @@
         </is>
       </c>
       <c r="I30" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J30" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>3</v>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
@@ -2684,14 +2684,14 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
+          <t>10/06/2026</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
           <t>09/06/2026</t>
         </is>
       </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>08/06/2026</t>
-        </is>
-      </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -2714,33 +2714,33 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>R$ 107,00</t>
-        </is>
-      </c>
-      <c r="H31" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H31" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I31" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J31" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J31" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L31" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -2757,14 +2757,14 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
+          <t>09/06/2026</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
           <t>08/06/2026</t>
         </is>
       </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>07/06/2026</t>
-        </is>
-      </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -2796,11 +2796,11 @@
         </is>
       </c>
       <c r="I32" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J32" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J32" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
@@ -2830,14 +2830,14 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
+          <t>09/06/2026</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
           <t>08/06/2026</t>
         </is>
       </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>07/06/2026</t>
-        </is>
-      </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 107,00</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
@@ -2869,24 +2869,24 @@
         </is>
       </c>
       <c r="I33" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J33" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
+        </is>
+      </c>
+      <c r="K33" s="2" t="inlineStr">
+        <is>
+          <t>50,0%</t>
+        </is>
+      </c>
+      <c r="L33" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J33" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K33" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L33" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -2903,14 +2903,14 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
           <t>07/06/2026</t>
         </is>
       </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>06/06/2026</t>
-        </is>
-      </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -2942,11 +2942,11 @@
         </is>
       </c>
       <c r="I34" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J34" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>3</v>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
@@ -2976,14 +2976,14 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
           <t>07/06/2026</t>
         </is>
       </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>06/06/2026</t>
-        </is>
-      </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -3015,11 +3015,11 @@
         </is>
       </c>
       <c r="I35" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J35" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J35" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
@@ -3049,14 +3049,14 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
+          <t>07/06/2026</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
           <t>06/06/2026</t>
         </is>
       </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>05/06/2026</t>
-        </is>
-      </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -3088,11 +3088,11 @@
         </is>
       </c>
       <c r="I36" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J36" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J36" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
@@ -3122,14 +3122,14 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
+          <t>07/06/2026</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
           <t>06/06/2026</t>
         </is>
       </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>05/06/2026</t>
-        </is>
-      </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -3161,11 +3161,11 @@
         </is>
       </c>
       <c r="I37" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J37" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J37" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
@@ -3195,12 +3195,12 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
+          <t>06/06/2026</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
           <t>05/06/2026</t>
-        </is>
-      </c>
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>04/06/2026</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -3238,7 +3238,7 @@
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
@@ -3268,14 +3268,14 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
+          <t>06/06/2026</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
           <t>05/06/2026</t>
         </is>
       </c>
-      <c r="B39" s="2" t="inlineStr">
-        <is>
-          <t>04/06/2026</t>
-        </is>
-      </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -3307,7 +3307,7 @@
         </is>
       </c>
       <c r="I39" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
@@ -3341,14 +3341,14 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
+          <t>05/06/2026</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
           <t>04/06/2026</t>
         </is>
       </c>
-      <c r="B40" s="2" t="inlineStr">
-        <is>
-          <t>03/06/2026</t>
-        </is>
-      </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -3380,11 +3380,11 @@
         </is>
       </c>
       <c r="I40" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J40" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
@@ -3414,14 +3414,14 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
+          <t>05/06/2026</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
           <t>04/06/2026</t>
         </is>
       </c>
-      <c r="B41" s="2" t="inlineStr">
-        <is>
-          <t>03/06/2026</t>
-        </is>
-      </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -3455,9 +3455,9 @@
       <c r="I41" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J41" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J41" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
@@ -3487,14 +3487,14 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
+          <t>04/06/2026</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
           <t>03/06/2026</t>
         </is>
       </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>02/06/2026</t>
-        </is>
-      </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -3526,11 +3526,11 @@
         </is>
       </c>
       <c r="I42" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J42" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J42" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
@@ -3560,14 +3560,14 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
+          <t>04/06/2026</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
           <t>03/06/2026</t>
         </is>
       </c>
-      <c r="B43" s="2" t="inlineStr">
-        <is>
-          <t>02/06/2026</t>
-        </is>
-      </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -3599,11 +3599,11 @@
         </is>
       </c>
       <c r="I43" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J43" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J43" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr">
@@ -3633,14 +3633,14 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
+          <t>03/06/2026</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
           <t>02/06/2026</t>
         </is>
       </c>
-      <c r="B44" s="2" t="inlineStr">
-        <is>
-          <t>01/06/2026</t>
-        </is>
-      </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -3666,17 +3666,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H44" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I44" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J44" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J44" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
@@ -3706,12 +3706,12 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
+          <t>03/06/2026</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
           <t>02/06/2026</t>
-        </is>
-      </c>
-      <c r="B45" s="2" t="inlineStr">
-        <is>
-          <t>01/06/2026</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -3779,14 +3779,14 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
+          <t>02/06/2026</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
           <t>01/06/2026</t>
         </is>
       </c>
-      <c r="B46" s="2" t="inlineStr">
-        <is>
-          <t>31/05/2026</t>
-        </is>
-      </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -3809,33 +3809,33 @@
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>R$ 126,00</t>
-        </is>
-      </c>
-      <c r="H46" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H46" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I46" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J46" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J46" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L46" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -3852,12 +3852,12 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
+          <t>02/06/2026</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
           <t>01/06/2026</t>
-        </is>
-      </c>
-      <c r="B47" s="2" t="inlineStr">
-        <is>
-          <t>31/05/2026</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -3925,14 +3925,14 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
+          <t>01/06/2026</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
           <t>31/05/2026</t>
         </is>
       </c>
-      <c r="B48" s="2" t="inlineStr">
-        <is>
-          <t>30/05/2026</t>
-        </is>
-      </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -3955,33 +3955,33 @@
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H48" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 126,00</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I48" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J48" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J48" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="L48" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -3998,12 +3998,12 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
+          <t>01/06/2026</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
           <t>31/05/2026</t>
-        </is>
-      </c>
-      <c r="B49" s="2" t="inlineStr">
-        <is>
-          <t>30/05/2026</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -4039,9 +4039,9 @@
       <c r="I49" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J49" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+      <c r="J49" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K49" s="2" t="inlineStr">
@@ -4071,14 +4071,14 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
+          <t>31/05/2026</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
           <t>30/05/2026</t>
         </is>
       </c>
-      <c r="B50" s="2" t="inlineStr">
-        <is>
-          <t>29/05/2026</t>
-        </is>
-      </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -4101,33 +4101,33 @@
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>R$ 126,00</t>
-        </is>
-      </c>
-      <c r="H50" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H50" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I50" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J50" s="3" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L50" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -4144,14 +4144,14 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
+          <t>31/05/2026</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
           <t>30/05/2026</t>
         </is>
       </c>
-      <c r="B51" s="2" t="inlineStr">
-        <is>
-          <t>29/05/2026</t>
-        </is>
-      </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -4183,11 +4183,11 @@
         </is>
       </c>
       <c r="I51" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J51" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>1</v>
+      </c>
+      <c r="J51" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K51" s="2" t="inlineStr">
@@ -4217,14 +4217,14 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
+          <t>30/05/2026</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
           <t>29/05/2026</t>
         </is>
       </c>
-      <c r="B52" s="2" t="inlineStr">
-        <is>
-          <t>28/05/2026</t>
-        </is>
-      </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -4247,7 +4247,7 @@
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 126,00</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
@@ -4256,24 +4256,24 @@
         </is>
       </c>
       <c r="I52" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J52" s="3" t="inlineStr">
         <is>
-          <t>▼ 33,3%</t>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="L52" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -4290,14 +4290,14 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
+          <t>30/05/2026</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
           <t>29/05/2026</t>
         </is>
       </c>
-      <c r="B53" s="2" t="inlineStr">
-        <is>
-          <t>28/05/2026</t>
-        </is>
-      </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -4329,11 +4329,11 @@
         </is>
       </c>
       <c r="I53" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J53" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J53" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K53" s="2" t="inlineStr">
@@ -4363,14 +4363,14 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
+          <t>29/05/2026</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
           <t>28/05/2026</t>
         </is>
       </c>
-      <c r="B54" s="2" t="inlineStr">
-        <is>
-          <t>27/05/2026</t>
-        </is>
-      </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -4402,11 +4402,11 @@
         </is>
       </c>
       <c r="I54" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J54" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>2</v>
+      </c>
+      <c r="J54" s="3" t="inlineStr">
+        <is>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr">
@@ -4436,14 +4436,14 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
+          <t>29/05/2026</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
           <t>28/05/2026</t>
         </is>
       </c>
-      <c r="B55" s="2" t="inlineStr">
-        <is>
-          <t>27/05/2026</t>
-        </is>
-      </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -4475,11 +4475,11 @@
         </is>
       </c>
       <c r="I55" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J55" s="3" t="inlineStr">
         <is>
-          <t>▼ 66,7%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K55" s="2" t="inlineStr">
@@ -4509,14 +4509,14 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
+          <t>28/05/2026</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
           <t>27/05/2026</t>
         </is>
       </c>
-      <c r="B56" s="2" t="inlineStr">
-        <is>
-          <t>26/05/2026</t>
-        </is>
-      </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -4548,11 +4548,11 @@
         </is>
       </c>
       <c r="I56" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J56" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>3</v>
+      </c>
+      <c r="J56" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr">
@@ -4582,14 +4582,14 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
+          <t>28/05/2026</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
           <t>27/05/2026</t>
         </is>
       </c>
-      <c r="B57" s="2" t="inlineStr">
-        <is>
-          <t>26/05/2026</t>
-        </is>
-      </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -4621,11 +4621,11 @@
         </is>
       </c>
       <c r="I57" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J57" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>1</v>
+      </c>
+      <c r="J57" s="3" t="inlineStr">
+        <is>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K57" s="2" t="inlineStr">
@@ -4655,14 +4655,14 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
+          <t>27/05/2026</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
           <t>26/05/2026</t>
         </is>
       </c>
-      <c r="B58" s="2" t="inlineStr">
-        <is>
-          <t>25/05/2026</t>
-        </is>
-      </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -4694,11 +4694,11 @@
         </is>
       </c>
       <c r="I58" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J58" s="4" t="inlineStr">
-        <is>
-          <t>▲ 50,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J58" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr">
@@ -4728,14 +4728,14 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
+          <t>27/05/2026</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
           <t>26/05/2026</t>
         </is>
       </c>
-      <c r="B59" s="2" t="inlineStr">
-        <is>
-          <t>25/05/2026</t>
-        </is>
-      </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -4767,11 +4767,11 @@
         </is>
       </c>
       <c r="I59" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J59" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>3</v>
+      </c>
+      <c r="J59" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K59" s="2" t="inlineStr">
@@ -4801,14 +4801,14 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
+          <t>26/05/2026</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
           <t>25/05/2026</t>
         </is>
       </c>
-      <c r="B60" s="2" t="inlineStr">
-        <is>
-          <t>24/05/2026</t>
-        </is>
-      </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -4840,11 +4840,11 @@
         </is>
       </c>
       <c r="I60" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J60" s="4" t="inlineStr">
         <is>
-          <t>▲ 100,0%</t>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="K60" s="2" t="inlineStr">
@@ -4874,14 +4874,14 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
+          <t>26/05/2026</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
           <t>25/05/2026</t>
         </is>
       </c>
-      <c r="B61" s="2" t="inlineStr">
-        <is>
-          <t>24/05/2026</t>
-        </is>
-      </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -4913,11 +4913,11 @@
         </is>
       </c>
       <c r="I61" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J61" s="3" t="inlineStr">
         <is>
-          <t>▼ 83,3%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K61" s="2" t="inlineStr">
@@ -4947,14 +4947,14 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
+          <t>25/05/2026</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
           <t>24/05/2026</t>
         </is>
       </c>
-      <c r="B62" s="2" t="inlineStr">
-        <is>
-          <t>23/05/2026</t>
-        </is>
-      </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -4980,17 +4980,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H62" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I62" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J62" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J62" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K62" s="2" t="inlineStr">
@@ -5020,14 +5020,14 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
+          <t>25/05/2026</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
           <t>24/05/2026</t>
         </is>
       </c>
-      <c r="B63" s="2" t="inlineStr">
-        <is>
-          <t>23/05/2026</t>
-        </is>
-      </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -5059,11 +5059,11 @@
         </is>
       </c>
       <c r="I63" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J63" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J63" s="3" t="inlineStr">
+        <is>
+          <t>▼ 83,3%</t>
         </is>
       </c>
       <c r="K63" s="2" t="inlineStr">
@@ -5093,14 +5093,14 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
+          <t>24/05/2026</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
           <t>23/05/2026</t>
         </is>
       </c>
-      <c r="B64" s="2" t="inlineStr">
-        <is>
-          <t>22/05/2026</t>
-        </is>
-      </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -5123,33 +5123,33 @@
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>R$ 126,00</t>
-        </is>
-      </c>
-      <c r="H64" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H64" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I64" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J64" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J64" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L64" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
@@ -5166,14 +5166,14 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
+          <t>24/05/2026</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
           <t>23/05/2026</t>
         </is>
       </c>
-      <c r="B65" s="2" t="inlineStr">
-        <is>
-          <t>22/05/2026</t>
-        </is>
-      </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -5205,11 +5205,11 @@
         </is>
       </c>
       <c r="I65" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J65" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>6</v>
+      </c>
+      <c r="J65" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K65" s="2" t="inlineStr">
@@ -5239,14 +5239,14 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
+          <t>23/05/2026</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
           <t>22/05/2026</t>
         </is>
       </c>
-      <c r="B66" s="2" t="inlineStr">
-        <is>
-          <t>21/05/2026</t>
-        </is>
-      </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -5269,7 +5269,7 @@
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 126,00</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
@@ -5278,24 +5278,24 @@
         </is>
       </c>
       <c r="I66" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J66" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
+        </is>
+      </c>
+      <c r="K66" s="2" t="inlineStr">
+        <is>
+          <t>50,0%</t>
+        </is>
+      </c>
+      <c r="L66" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J66" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
-        </is>
-      </c>
-      <c r="K66" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L66" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="N66" s="2" t="inlineStr">
@@ -5312,12 +5312,12 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
+          <t>23/05/2026</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
           <t>22/05/2026</t>
-        </is>
-      </c>
-      <c r="B67" s="2" t="inlineStr">
-        <is>
-          <t>21/05/2026</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -5355,7 +5355,7 @@
       </c>
       <c r="J67" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K67" s="2" t="inlineStr">
@@ -5385,14 +5385,14 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
           <t>21/05/2026</t>
         </is>
       </c>
-      <c r="B68" s="2" t="inlineStr">
-        <is>
-          <t>20/05/2026</t>
-        </is>
-      </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -5424,11 +5424,11 @@
         </is>
       </c>
       <c r="I68" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J68" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>1</v>
+      </c>
+      <c r="J68" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K68" s="2" t="inlineStr">
@@ -5458,14 +5458,14 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
           <t>21/05/2026</t>
         </is>
       </c>
-      <c r="B69" s="2" t="inlineStr">
-        <is>
-          <t>20/05/2026</t>
-        </is>
-      </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -5497,11 +5497,11 @@
         </is>
       </c>
       <c r="I69" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J69" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>3</v>
+      </c>
+      <c r="J69" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K69" s="2" t="inlineStr">
@@ -5531,14 +5531,14 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
+          <t>21/05/2026</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
           <t>20/05/2026</t>
         </is>
       </c>
-      <c r="B70" s="2" t="inlineStr">
-        <is>
-          <t>19/05/2026</t>
-        </is>
-      </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -5570,7 +5570,7 @@
         </is>
       </c>
       <c r="I70" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J70" s="2" t="inlineStr">
         <is>
@@ -5604,14 +5604,14 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
+          <t>21/05/2026</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
           <t>20/05/2026</t>
         </is>
       </c>
-      <c r="B71" s="2" t="inlineStr">
-        <is>
-          <t>19/05/2026</t>
-        </is>
-      </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -5643,11 +5643,11 @@
         </is>
       </c>
       <c r="I71" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J71" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J71" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K71" s="2" t="inlineStr">
@@ -5677,12 +5677,12 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
+          <t>20/05/2026</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
           <t>19/05/2026</t>
-        </is>
-      </c>
-      <c r="B72" s="2" t="inlineStr">
-        <is>
-          <t>18/05/2026</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
@@ -5750,14 +5750,14 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
+          <t>20/05/2026</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
           <t>19/05/2026</t>
         </is>
       </c>
-      <c r="B73" s="2" t="inlineStr">
-        <is>
-          <t>18/05/2026</t>
-        </is>
-      </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -5789,7 +5789,7 @@
         </is>
       </c>
       <c r="I73" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J73" s="2" t="inlineStr">
         <is>
@@ -5823,14 +5823,14 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
           <t>18/05/2026</t>
         </is>
       </c>
-      <c r="B74" s="2" t="inlineStr">
-        <is>
-          <t>17/05/2026</t>
-        </is>
-      </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -5864,9 +5864,9 @@
       <c r="I74" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J74" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J74" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr">
@@ -5896,12 +5896,12 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
           <t>18/05/2026</t>
-        </is>
-      </c>
-      <c r="B75" s="2" t="inlineStr">
-        <is>
-          <t>17/05/2026</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -5969,14 +5969,14 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
           <t>17/05/2026</t>
         </is>
       </c>
-      <c r="B76" s="2" t="inlineStr">
-        <is>
-          <t>16/05/2026</t>
-        </is>
-      </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -6008,11 +6008,11 @@
         </is>
       </c>
       <c r="I76" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J76" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J76" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K76" s="2" t="inlineStr">
@@ -6042,14 +6042,14 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
           <t>17/05/2026</t>
         </is>
       </c>
-      <c r="B77" s="2" t="inlineStr">
-        <is>
-          <t>16/05/2026</t>
-        </is>
-      </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -6072,7 +6072,7 @@
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
@@ -6080,10 +6080,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I77" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I77" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J77" s="2" t="inlineStr">
         <is>
@@ -6092,41 +6090,39 @@
       </c>
       <c r="K77" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L77" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L77" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M77" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N77" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
+          <t>17/05/2026</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
           <t>16/05/2026</t>
         </is>
       </c>
-      <c r="B78" s="2" t="inlineStr">
-        <is>
-          <t>15/05/2026</t>
-        </is>
-      </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -6158,11 +6154,11 @@
         </is>
       </c>
       <c r="I78" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J78" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J78" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K78" s="2" t="inlineStr">
@@ -6192,14 +6188,14 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
+          <t>17/05/2026</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
           <t>16/05/2026</t>
         </is>
       </c>
-      <c r="B79" s="2" t="inlineStr">
-        <is>
-          <t>15/05/2026</t>
-        </is>
-      </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -6222,7 +6218,7 @@
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
@@ -6230,8 +6226,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I79" s="2" t="n">
-        <v>0</v>
+      <c r="I79" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J79" s="2" t="inlineStr">
         <is>
@@ -6240,39 +6238,41 @@
       </c>
       <c r="K79" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L79" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L79" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M79" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N79" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
+          <t>16/05/2026</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
           <t>15/05/2026</t>
         </is>
       </c>
-      <c r="B80" s="2" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
-        </is>
-      </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -6304,11 +6304,11 @@
         </is>
       </c>
       <c r="I80" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J80" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J80" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K80" s="2" t="inlineStr">
@@ -6338,14 +6338,14 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
+          <t>16/05/2026</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
           <t>15/05/2026</t>
         </is>
       </c>
-      <c r="B81" s="2" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
-        </is>
-      </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -6379,9 +6379,9 @@
       <c r="I81" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J81" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J81" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K81" s="2" t="inlineStr">
@@ -6411,14 +6411,14 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
+          <t>15/05/2026</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
           <t>14/05/2026</t>
         </is>
       </c>
-      <c r="B82" s="2" t="inlineStr">
-        <is>
-          <t>13/05/2026</t>
-        </is>
-      </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -6450,11 +6450,11 @@
         </is>
       </c>
       <c r="I82" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J82" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J82" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K82" s="2" t="inlineStr">
@@ -6484,14 +6484,14 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
+          <t>15/05/2026</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
           <t>14/05/2026</t>
         </is>
       </c>
-      <c r="B83" s="2" t="inlineStr">
-        <is>
-          <t>13/05/2026</t>
-        </is>
-      </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -6523,11 +6523,11 @@
         </is>
       </c>
       <c r="I83" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J83" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J83" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K83" s="2" t="inlineStr">
@@ -6557,14 +6557,14 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
+          <t>14/05/2026</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
           <t>13/05/2026</t>
         </is>
       </c>
-      <c r="B84" s="2" t="inlineStr">
-        <is>
-          <t>12/05/2026</t>
-        </is>
-      </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -6596,11 +6596,11 @@
         </is>
       </c>
       <c r="I84" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J84" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J84" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K84" s="2" t="inlineStr">
@@ -6630,14 +6630,14 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
+          <t>14/05/2026</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
           <t>13/05/2026</t>
         </is>
       </c>
-      <c r="B85" s="2" t="inlineStr">
-        <is>
-          <t>12/05/2026</t>
-        </is>
-      </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -6660,7 +6660,7 @@
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr">
@@ -6668,10 +6668,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I85" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I85" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J85" s="2" t="inlineStr">
         <is>
@@ -6680,41 +6678,39 @@
       </c>
       <c r="K85" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L85" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L85" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M85" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N85" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
+          <t>13/05/2026</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
           <t>12/05/2026</t>
         </is>
       </c>
-      <c r="B86" s="2" t="inlineStr">
-        <is>
-          <t>11/05/2026</t>
-        </is>
-      </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -6746,11 +6742,11 @@
         </is>
       </c>
       <c r="I86" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J86" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J86" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K86" s="2" t="inlineStr">
@@ -6780,12 +6776,12 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
+          <t>13/05/2026</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
           <t>12/05/2026</t>
-        </is>
-      </c>
-      <c r="B87" s="2" t="inlineStr">
-        <is>
-          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
@@ -6857,14 +6853,14 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
+          <t>12/05/2026</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
           <t>11/05/2026</t>
         </is>
       </c>
-      <c r="B88" s="2" t="inlineStr">
-        <is>
-          <t>10/05/2026</t>
-        </is>
-      </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -6896,11 +6892,11 @@
         </is>
       </c>
       <c r="I88" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J88" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J88" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K88" s="2" t="inlineStr">
@@ -6930,14 +6926,14 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
+          <t>12/05/2026</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
           <t>11/05/2026</t>
         </is>
       </c>
-      <c r="B89" s="2" t="inlineStr">
-        <is>
-          <t>10/05/2026</t>
-        </is>
-      </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -6960,7 +6956,7 @@
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H89" s="2" t="inlineStr">
@@ -6968,8 +6964,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I89" s="2" t="n">
-        <v>0</v>
+      <c r="I89" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J89" s="2" t="inlineStr">
         <is>
@@ -6978,39 +6976,41 @@
       </c>
       <c r="K89" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L89" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L89" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M89" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N89" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
+          <t>11/05/2026</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
           <t>10/05/2026</t>
         </is>
       </c>
-      <c r="B90" s="2" t="inlineStr">
-        <is>
-          <t>09/05/2026</t>
-        </is>
-      </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -7033,7 +7033,7 @@
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H90" s="2" t="inlineStr">
@@ -7041,10 +7041,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I90" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I90" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J90" s="2" t="inlineStr">
         <is>
@@ -7053,41 +7051,39 @@
       </c>
       <c r="K90" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L90" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L90" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M90" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N90" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
+          <t>11/05/2026</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
           <t>10/05/2026</t>
         </is>
       </c>
-      <c r="B91" s="2" t="inlineStr">
-        <is>
-          <t>09/05/2026</t>
-        </is>
-      </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -7113,17 +7109,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H91" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H91" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I91" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J91" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J91" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K91" s="2" t="inlineStr">
@@ -7153,14 +7149,14 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
+          <t>10/05/2026</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
           <t>09/05/2026</t>
         </is>
       </c>
-      <c r="B92" s="2" t="inlineStr">
-        <is>
-          <t>08/05/2026</t>
-        </is>
-      </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -7183,7 +7179,7 @@
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H92" s="2" t="inlineStr">
@@ -7191,8 +7187,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I92" s="2" t="n">
-        <v>0</v>
+      <c r="I92" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J92" s="2" t="inlineStr">
         <is>
@@ -7201,39 +7199,41 @@
       </c>
       <c r="K92" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L92" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L92" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M92" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N92" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
+          <t>10/05/2026</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
           <t>09/05/2026</t>
         </is>
       </c>
-      <c r="B93" s="2" t="inlineStr">
-        <is>
-          <t>08/05/2026</t>
-        </is>
-      </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -7256,33 +7256,33 @@
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>R$ 110,00</t>
-        </is>
-      </c>
-      <c r="H93" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H93" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I93" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J93" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J93" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K93" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L93" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M93" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N93" s="2" t="inlineStr">
@@ -7299,14 +7299,14 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
           <t>08/05/2026</t>
         </is>
       </c>
-      <c r="B94" s="2" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
-        </is>
-      </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -7332,17 +7332,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H94" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H94" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I94" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J94" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J94" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K94" s="2" t="inlineStr">
@@ -7372,14 +7372,14 @@
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
           <t>08/05/2026</t>
         </is>
       </c>
-      <c r="B95" s="2" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
-        </is>
-      </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -7402,7 +7402,7 @@
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 110,00</t>
         </is>
       </c>
       <c r="H95" s="2" t="inlineStr">
@@ -7411,24 +7411,24 @@
         </is>
       </c>
       <c r="I95" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J95" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J95" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K95" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>50,0%</t>
         </is>
       </c>
       <c r="L95" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M95" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="N95" s="2" t="inlineStr">
@@ -7445,14 +7445,14 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
+          <t>08/05/2026</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
           <t>07/05/2026</t>
         </is>
       </c>
-      <c r="B96" s="2" t="inlineStr">
-        <is>
-          <t>06/05/2026</t>
-        </is>
-      </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -7475,33 +7475,33 @@
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>R$ 110,00</t>
-        </is>
-      </c>
-      <c r="H96" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H96" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I96" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J96" s="3" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K96" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L96" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M96" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N96" s="2" t="inlineStr">
@@ -7518,14 +7518,14 @@
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
+          <t>08/05/2026</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
           <t>07/05/2026</t>
         </is>
       </c>
-      <c r="B97" s="2" t="inlineStr">
-        <is>
-          <t>06/05/2026</t>
-        </is>
-      </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -7557,11 +7557,11 @@
         </is>
       </c>
       <c r="I97" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J97" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J97" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K97" s="2" t="inlineStr">
@@ -7591,14 +7591,14 @@
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
           <t>06/05/2026</t>
         </is>
       </c>
-      <c r="B98" s="2" t="inlineStr">
-        <is>
-          <t>05/05/2026</t>
-        </is>
-      </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -7621,7 +7621,7 @@
       </c>
       <c r="G98" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 110,00</t>
         </is>
       </c>
       <c r="H98" s="2" t="inlineStr">
@@ -7630,24 +7630,24 @@
         </is>
       </c>
       <c r="I98" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J98" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>1</v>
+      </c>
+      <c r="J98" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K98" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="L98" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M98" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="N98" s="2" t="inlineStr">
@@ -7664,14 +7664,14 @@
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
           <t>06/05/2026</t>
         </is>
       </c>
-      <c r="B99" s="2" t="inlineStr">
-        <is>
-          <t>05/05/2026</t>
-        </is>
-      </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -7703,11 +7703,11 @@
         </is>
       </c>
       <c r="I99" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J99" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J99" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K99" s="2" t="inlineStr">
@@ -7737,12 +7737,12 @@
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
+          <t>06/05/2026</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
           <t>05/05/2026</t>
-        </is>
-      </c>
-      <c r="B100" s="2" t="inlineStr">
-        <is>
-          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
@@ -7780,7 +7780,7 @@
       </c>
       <c r="J100" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K100" s="2" t="inlineStr">
@@ -7810,14 +7810,14 @@
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
+          <t>06/05/2026</t>
+        </is>
+      </c>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
           <t>05/05/2026</t>
         </is>
       </c>
-      <c r="B101" s="2" t="inlineStr">
-        <is>
-          <t>04/05/2026</t>
-        </is>
-      </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -7849,11 +7849,11 @@
         </is>
       </c>
       <c r="I101" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J101" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J101" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K101" s="2" t="inlineStr">
@@ -7883,14 +7883,14 @@
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
+          <t>05/05/2026</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
           <t>04/05/2026</t>
         </is>
       </c>
-      <c r="B102" s="2" t="inlineStr">
-        <is>
-          <t>03/05/2026</t>
-        </is>
-      </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -7922,7 +7922,7 @@
         </is>
       </c>
       <c r="I102" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J102" s="2" t="inlineStr">
         <is>
@@ -7956,14 +7956,14 @@
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
+          <t>05/05/2026</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
           <t>04/05/2026</t>
         </is>
       </c>
-      <c r="B103" s="2" t="inlineStr">
-        <is>
-          <t>03/05/2026</t>
-        </is>
-      </c>
       <c r="C103" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -7995,11 +7995,11 @@
         </is>
       </c>
       <c r="I103" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J103" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J103" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K103" s="2" t="inlineStr">
@@ -8029,14 +8029,14 @@
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
           <t>03/05/2026</t>
         </is>
       </c>
-      <c r="B104" s="2" t="inlineStr">
-        <is>
-          <t>02/05/2026</t>
-        </is>
-      </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -8070,9 +8070,9 @@
       <c r="I104" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J104" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J104" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K104" s="2" t="inlineStr">
@@ -8102,14 +8102,14 @@
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
           <t>03/05/2026</t>
         </is>
       </c>
-      <c r="B105" s="2" t="inlineStr">
-        <is>
-          <t>02/05/2026</t>
-        </is>
-      </c>
       <c r="C105" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -8141,11 +8141,11 @@
         </is>
       </c>
       <c r="I105" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J105" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J105" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K105" s="2" t="inlineStr">
@@ -8175,14 +8175,14 @@
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
+          <t>03/05/2026</t>
+        </is>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
           <t>02/05/2026</t>
         </is>
       </c>
-      <c r="B106" s="2" t="inlineStr">
-        <is>
-          <t>01/05/2026</t>
-        </is>
-      </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -8214,11 +8214,11 @@
         </is>
       </c>
       <c r="I106" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J106" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J106" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K106" s="2" t="inlineStr">
@@ -8248,12 +8248,12 @@
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
+          <t>03/05/2026</t>
+        </is>
+      </c>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
           <t>02/05/2026</t>
-        </is>
-      </c>
-      <c r="B107" s="2" t="inlineStr">
-        <is>
-          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C107" s="2" t="inlineStr">
@@ -8289,9 +8289,9 @@
       <c r="I107" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J107" s="3" t="inlineStr">
-        <is>
-          <t>▼ 66,7%</t>
+      <c r="J107" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K107" s="2" t="inlineStr">
@@ -8321,12 +8321,12 @@
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
+          <t>02/05/2026</t>
+        </is>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
           <t>01/05/2026</t>
-        </is>
-      </c>
-      <c r="B108" s="2" t="inlineStr">
-        <is>
-          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C108" s="2" t="inlineStr">
@@ -8364,7 +8364,7 @@
       </c>
       <c r="J108" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K108" s="2" t="inlineStr">
@@ -8394,14 +8394,14 @@
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
+          <t>02/05/2026</t>
+        </is>
+      </c>
+      <c r="B109" s="2" t="inlineStr">
+        <is>
           <t>01/05/2026</t>
         </is>
       </c>
-      <c r="B109" s="2" t="inlineStr">
-        <is>
-          <t>30/04/2026</t>
-        </is>
-      </c>
       <c r="C109" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -8433,11 +8433,11 @@
         </is>
       </c>
       <c r="I109" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J109" s="3" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K109" s="2" t="inlineStr">
@@ -8467,14 +8467,14 @@
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
+          <t>01/05/2026</t>
+        </is>
+      </c>
+      <c r="B110" s="2" t="inlineStr">
+        <is>
           <t>30/04/2026</t>
         </is>
       </c>
-      <c r="B110" s="2" t="inlineStr">
-        <is>
-          <t>29/04/2026</t>
-        </is>
-      </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -8506,11 +8506,11 @@
         </is>
       </c>
       <c r="I110" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J110" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J110" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K110" s="2" t="inlineStr">
@@ -8540,14 +8540,14 @@
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
+          <t>01/05/2026</t>
+        </is>
+      </c>
+      <c r="B111" s="2" t="inlineStr">
+        <is>
           <t>30/04/2026</t>
         </is>
       </c>
-      <c r="B111" s="2" t="inlineStr">
-        <is>
-          <t>29/04/2026</t>
-        </is>
-      </c>
       <c r="C111" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -8579,11 +8579,11 @@
         </is>
       </c>
       <c r="I111" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J111" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>3</v>
+      </c>
+      <c r="J111" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K111" s="2" t="inlineStr">
@@ -8613,14 +8613,14 @@
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="B112" s="2" t="inlineStr">
+        <is>
           <t>29/04/2026</t>
         </is>
       </c>
-      <c r="B112" s="2" t="inlineStr">
-        <is>
-          <t>28/04/2026</t>
-        </is>
-      </c>
       <c r="C112" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -8652,11 +8652,11 @@
         </is>
       </c>
       <c r="I112" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J112" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J112" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K112" s="2" t="inlineStr">
@@ -8679,19 +8679,19 @@
       </c>
       <c r="O112" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="B113" s="2" t="inlineStr">
+        <is>
           <t>29/04/2026</t>
-        </is>
-      </c>
-      <c r="B113" s="2" t="inlineStr">
-        <is>
-          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C113" s="2" t="inlineStr">
@@ -8729,7 +8729,7 @@
       </c>
       <c r="J113" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K113" s="2" t="inlineStr">
@@ -8752,19 +8752,19 @@
       </c>
       <c r="O113" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
+          <t>29/04/2026</t>
+        </is>
+      </c>
+      <c r="B114" s="2" t="inlineStr">
+        <is>
           <t>28/04/2026</t>
-        </is>
-      </c>
-      <c r="B114" s="2" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C114" s="2" t="inlineStr">
@@ -8800,9 +8800,9 @@
       <c r="I114" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J114" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+      <c r="J114" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K114" s="2" t="inlineStr">
@@ -8832,14 +8832,14 @@
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
+          <t>29/04/2026</t>
+        </is>
+      </c>
+      <c r="B115" s="2" t="inlineStr">
+        <is>
           <t>28/04/2026</t>
         </is>
       </c>
-      <c r="B115" s="2" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
-        </is>
-      </c>
       <c r="C115" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -8871,11 +8871,11 @@
         </is>
       </c>
       <c r="I115" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J115" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>6</v>
+      </c>
+      <c r="J115" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K115" s="2" t="inlineStr">
@@ -8905,14 +8905,14 @@
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
+          <t>28/04/2026</t>
+        </is>
+      </c>
+      <c r="B116" s="2" t="inlineStr">
+        <is>
           <t>27/04/2026</t>
         </is>
       </c>
-      <c r="B116" s="2" t="inlineStr">
-        <is>
-          <t>26/04/2026</t>
-        </is>
-      </c>
       <c r="C116" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -8944,11 +8944,11 @@
         </is>
       </c>
       <c r="I116" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J116" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>1</v>
+      </c>
+      <c r="J116" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K116" s="2" t="inlineStr">
@@ -8978,14 +8978,14 @@
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
+          <t>28/04/2026</t>
+        </is>
+      </c>
+      <c r="B117" s="2" t="inlineStr">
+        <is>
           <t>27/04/2026</t>
         </is>
       </c>
-      <c r="B117" s="2" t="inlineStr">
-        <is>
-          <t>26/04/2026</t>
-        </is>
-      </c>
       <c r="C117" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -9017,11 +9017,11 @@
         </is>
       </c>
       <c r="I117" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J117" s="3" t="inlineStr">
         <is>
-          <t>▼ 66,7%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K117" s="2" t="inlineStr">
@@ -9051,12 +9051,12 @@
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B118" s="2" t="inlineStr">
+        <is>
           <t>26/04/2026</t>
-        </is>
-      </c>
-      <c r="B118" s="2" t="inlineStr">
-        <is>
-          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C118" s="2" t="inlineStr">
@@ -9124,14 +9124,14 @@
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B119" s="2" t="inlineStr">
+        <is>
           <t>26/04/2026</t>
         </is>
       </c>
-      <c r="B119" s="2" t="inlineStr">
-        <is>
-          <t>25/04/2026</t>
-        </is>
-      </c>
       <c r="C119" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -9163,11 +9163,11 @@
         </is>
       </c>
       <c r="I119" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J119" s="4" t="inlineStr">
-        <is>
-          <t>▲ 200,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J119" s="3" t="inlineStr">
+        <is>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K119" s="2" t="inlineStr">
@@ -9197,12 +9197,12 @@
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
+          <t>26/04/2026</t>
+        </is>
+      </c>
+      <c r="B120" s="2" t="inlineStr">
+        <is>
           <t>25/04/2026</t>
-        </is>
-      </c>
-      <c r="B120" s="2" t="inlineStr">
-        <is>
-          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C120" s="2" t="inlineStr">
@@ -9238,9 +9238,9 @@
       <c r="I120" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="J120" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+      <c r="J120" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K120" s="2" t="inlineStr">
@@ -9270,14 +9270,14 @@
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
+          <t>26/04/2026</t>
+        </is>
+      </c>
+      <c r="B121" s="2" t="inlineStr">
+        <is>
           <t>25/04/2026</t>
         </is>
       </c>
-      <c r="B121" s="2" t="inlineStr">
-        <is>
-          <t>24/04/2026</t>
-        </is>
-      </c>
       <c r="C121" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -9309,11 +9309,11 @@
         </is>
       </c>
       <c r="I121" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J121" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>3</v>
+      </c>
+      <c r="J121" s="4" t="inlineStr">
+        <is>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="K121" s="2" t="inlineStr">
@@ -9343,14 +9343,14 @@
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
+          <t>25/04/2026</t>
+        </is>
+      </c>
+      <c r="B122" s="2" t="inlineStr">
+        <is>
           <t>24/04/2026</t>
         </is>
       </c>
-      <c r="B122" s="2" t="inlineStr">
-        <is>
-          <t>23/04/2026</t>
-        </is>
-      </c>
       <c r="C122" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -9382,11 +9382,11 @@
         </is>
       </c>
       <c r="I122" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J122" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J122" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K122" s="2" t="inlineStr">
@@ -9416,14 +9416,14 @@
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
+          <t>25/04/2026</t>
+        </is>
+      </c>
+      <c r="B123" s="2" t="inlineStr">
+        <is>
           <t>24/04/2026</t>
         </is>
       </c>
-      <c r="B123" s="2" t="inlineStr">
-        <is>
-          <t>23/04/2026</t>
-        </is>
-      </c>
       <c r="C123" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -9446,7 +9446,7 @@
       </c>
       <c r="G123" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H123" s="2" t="inlineStr">
@@ -9454,10 +9454,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I123" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I123" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J123" s="2" t="inlineStr">
         <is>
@@ -9466,41 +9464,39 @@
       </c>
       <c r="K123" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L123" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L123" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M123" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N123" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O123" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
+          <t>24/04/2026</t>
+        </is>
+      </c>
+      <c r="B124" s="2" t="inlineStr">
+        <is>
           <t>23/04/2026</t>
         </is>
       </c>
-      <c r="B124" s="2" t="inlineStr">
-        <is>
-          <t>22/04/2026</t>
-        </is>
-      </c>
       <c r="C124" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -9532,11 +9528,11 @@
         </is>
       </c>
       <c r="I124" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J124" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J124" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K124" s="2" t="inlineStr">
@@ -9566,12 +9562,12 @@
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
+          <t>24/04/2026</t>
+        </is>
+      </c>
+      <c r="B125" s="2" t="inlineStr">
+        <is>
           <t>23/04/2026</t>
-        </is>
-      </c>
-      <c r="B125" s="2" t="inlineStr">
-        <is>
-          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C125" s="2" t="inlineStr">
@@ -9643,14 +9639,14 @@
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
+          <t>23/04/2026</t>
+        </is>
+      </c>
+      <c r="B126" s="2" t="inlineStr">
+        <is>
           <t>22/04/2026</t>
         </is>
       </c>
-      <c r="B126" s="2" t="inlineStr">
-        <is>
-          <t>21/04/2026</t>
-        </is>
-      </c>
       <c r="C126" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -9682,11 +9678,11 @@
         </is>
       </c>
       <c r="I126" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J126" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J126" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K126" s="2" t="inlineStr">
@@ -9716,14 +9712,14 @@
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
+          <t>23/04/2026</t>
+        </is>
+      </c>
+      <c r="B127" s="2" t="inlineStr">
+        <is>
           <t>22/04/2026</t>
         </is>
       </c>
-      <c r="B127" s="2" t="inlineStr">
-        <is>
-          <t>21/04/2026</t>
-        </is>
-      </c>
       <c r="C127" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -9746,7 +9742,7 @@
       </c>
       <c r="G127" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H127" s="2" t="inlineStr">
@@ -9754,8 +9750,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I127" s="2" t="n">
-        <v>0</v>
+      <c r="I127" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J127" s="2" t="inlineStr">
         <is>
@@ -9764,39 +9762,41 @@
       </c>
       <c r="K127" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L127" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L127" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M127" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N127" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O127" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
+          <t>22/04/2026</t>
+        </is>
+      </c>
+      <c r="B128" s="2" t="inlineStr">
+        <is>
           <t>21/04/2026</t>
         </is>
       </c>
-      <c r="B128" s="2" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
-        </is>
-      </c>
       <c r="C128" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -9828,11 +9828,11 @@
         </is>
       </c>
       <c r="I128" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J128" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>1</v>
+      </c>
+      <c r="J128" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K128" s="2" t="inlineStr">
@@ -9850,7 +9850,7 @@
       </c>
       <c r="N128" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O128" s="2" t="inlineStr">
@@ -9862,14 +9862,14 @@
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
         <is>
+          <t>22/04/2026</t>
+        </is>
+      </c>
+      <c r="B129" s="2" t="inlineStr">
+        <is>
           <t>21/04/2026</t>
         </is>
       </c>
-      <c r="B129" s="2" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
-        </is>
-      </c>
       <c r="C129" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -9903,9 +9903,9 @@
       <c r="I129" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J129" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J129" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K129" s="2" t="inlineStr">
@@ -9935,14 +9935,14 @@
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
         <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="B130" s="2" t="inlineStr">
+        <is>
           <t>20/04/2026</t>
         </is>
       </c>
-      <c r="B130" s="2" t="inlineStr">
-        <is>
-          <t>19/04/2026</t>
-        </is>
-      </c>
       <c r="C130" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -9974,7 +9974,7 @@
         </is>
       </c>
       <c r="I130" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J130" s="2" t="inlineStr">
         <is>
@@ -9996,7 +9996,7 @@
       </c>
       <c r="N130" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O130" s="2" t="inlineStr">
@@ -10008,14 +10008,14 @@
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
         <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="B131" s="2" t="inlineStr">
+        <is>
           <t>20/04/2026</t>
         </is>
       </c>
-      <c r="B131" s="2" t="inlineStr">
-        <is>
-          <t>19/04/2026</t>
-        </is>
-      </c>
       <c r="C131" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -10047,11 +10047,11 @@
         </is>
       </c>
       <c r="I131" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J131" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J131" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K131" s="2" t="inlineStr">
@@ -10081,12 +10081,12 @@
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
         <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="B132" s="2" t="inlineStr">
+        <is>
           <t>19/04/2026</t>
-        </is>
-      </c>
-      <c r="B132" s="2" t="inlineStr">
-        <is>
-          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C132" s="2" t="inlineStr">
@@ -10154,14 +10154,14 @@
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
         <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="B133" s="2" t="inlineStr">
+        <is>
           <t>19/04/2026</t>
         </is>
       </c>
-      <c r="B133" s="2" t="inlineStr">
-        <is>
-          <t>18/04/2026</t>
-        </is>
-      </c>
       <c r="C133" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -10193,11 +10193,11 @@
         </is>
       </c>
       <c r="I133" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J133" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>4</v>
+      </c>
+      <c r="J133" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K133" s="2" t="inlineStr">
@@ -10227,12 +10227,12 @@
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
         <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="B134" s="2" t="inlineStr">
+        <is>
           <t>18/04/2026</t>
-        </is>
-      </c>
-      <c r="B134" s="2" t="inlineStr">
-        <is>
-          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C134" s="2" t="inlineStr">
@@ -10300,14 +10300,14 @@
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
         <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="B135" s="2" t="inlineStr">
+        <is>
           <t>18/04/2026</t>
         </is>
       </c>
-      <c r="B135" s="2" t="inlineStr">
-        <is>
-          <t>17/04/2026</t>
-        </is>
-      </c>
       <c r="C135" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -10339,7 +10339,7 @@
         </is>
       </c>
       <c r="I135" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J135" s="2" t="inlineStr">
         <is>
@@ -10373,14 +10373,14 @@
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
         <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="B136" s="2" t="inlineStr">
+        <is>
           <t>17/04/2026</t>
         </is>
       </c>
-      <c r="B136" s="2" t="inlineStr">
-        <is>
-          <t>16/04/2026</t>
-        </is>
-      </c>
       <c r="C136" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -10414,9 +10414,9 @@
       <c r="I136" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J136" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J136" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K136" s="2" t="inlineStr">
@@ -10446,14 +10446,14 @@
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
         <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="B137" s="2" t="inlineStr">
+        <is>
           <t>17/04/2026</t>
         </is>
       </c>
-      <c r="B137" s="2" t="inlineStr">
-        <is>
-          <t>16/04/2026</t>
-        </is>
-      </c>
       <c r="C137" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -10487,9 +10487,9 @@
       <c r="I137" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J137" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J137" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K137" s="2" t="inlineStr">
@@ -10519,14 +10519,14 @@
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
         <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="B138" s="2" t="inlineStr">
+        <is>
           <t>16/04/2026</t>
         </is>
       </c>
-      <c r="B138" s="2" t="inlineStr">
-        <is>
-          <t>15/04/2026</t>
-        </is>
-      </c>
       <c r="C138" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -10558,11 +10558,11 @@
         </is>
       </c>
       <c r="I138" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J138" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J138" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K138" s="2" t="inlineStr">
@@ -10592,14 +10592,14 @@
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
         <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="B139" s="2" t="inlineStr">
+        <is>
           <t>16/04/2026</t>
         </is>
       </c>
-      <c r="B139" s="2" t="inlineStr">
-        <is>
-          <t>15/04/2026</t>
-        </is>
-      </c>
       <c r="C139" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -10631,11 +10631,11 @@
         </is>
       </c>
       <c r="I139" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J139" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J139" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K139" s="2" t="inlineStr">
@@ -10665,14 +10665,14 @@
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
         <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="B140" s="2" t="inlineStr">
+        <is>
           <t>15/04/2026</t>
         </is>
       </c>
-      <c r="B140" s="2" t="inlineStr">
-        <is>
-          <t>14/04/2026</t>
-        </is>
-      </c>
       <c r="C140" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -10704,11 +10704,11 @@
         </is>
       </c>
       <c r="I140" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J140" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J140" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K140" s="2" t="inlineStr">
@@ -10738,12 +10738,12 @@
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
         <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="B141" s="2" t="inlineStr">
+        <is>
           <t>15/04/2026</t>
-        </is>
-      </c>
-      <c r="B141" s="2" t="inlineStr">
-        <is>
-          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C141" s="2" t="inlineStr">
@@ -10811,14 +10811,14 @@
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
         <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="B142" s="2" t="inlineStr">
+        <is>
           <t>14/04/2026</t>
         </is>
       </c>
-      <c r="B142" s="2" t="inlineStr">
-        <is>
-          <t>13/04/2026</t>
-        </is>
-      </c>
       <c r="C142" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -10850,11 +10850,11 @@
         </is>
       </c>
       <c r="I142" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J142" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J142" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K142" s="2" t="inlineStr">
@@ -10884,12 +10884,12 @@
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
         <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="B143" s="2" t="inlineStr">
+        <is>
           <t>14/04/2026</t>
-        </is>
-      </c>
-      <c r="B143" s="2" t="inlineStr">
-        <is>
-          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C143" s="2" t="inlineStr">
@@ -10957,12 +10957,12 @@
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
         <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="B144" s="2" t="inlineStr">
+        <is>
           <t>13/04/2026</t>
-        </is>
-      </c>
-      <c r="B144" s="2" t="inlineStr">
-        <is>
-          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C144" s="2" t="inlineStr">
@@ -11030,12 +11030,12 @@
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
         <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="B145" s="2" t="inlineStr">
+        <is>
           <t>13/04/2026</t>
-        </is>
-      </c>
-      <c r="B145" s="2" t="inlineStr">
-        <is>
-          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C145" s="2" t="inlineStr">
@@ -11103,12 +11103,12 @@
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
         <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="B146" s="2" t="inlineStr">
+        <is>
           <t>12/04/2026</t>
-        </is>
-      </c>
-      <c r="B146" s="2" t="inlineStr">
-        <is>
-          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C146" s="2" t="inlineStr">
@@ -11144,9 +11144,9 @@
       <c r="I146" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="J146" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+      <c r="J146" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K146" s="2" t="inlineStr">
@@ -11176,12 +11176,12 @@
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
         <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="B147" s="2" t="inlineStr">
+        <is>
           <t>12/04/2026</t>
-        </is>
-      </c>
-      <c r="B147" s="2" t="inlineStr">
-        <is>
-          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C147" s="2" t="inlineStr">
@@ -11219,7 +11219,7 @@
       </c>
       <c r="J147" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K147" s="2" t="inlineStr">
@@ -11249,14 +11249,14 @@
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
         <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B148" s="2" t="inlineStr">
+        <is>
           <t>11/04/2026</t>
         </is>
       </c>
-      <c r="B148" s="2" t="inlineStr">
-        <is>
-          <t>10/04/2026</t>
-        </is>
-      </c>
       <c r="C148" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -11288,11 +11288,11 @@
         </is>
       </c>
       <c r="I148" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J148" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J148" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K148" s="2" t="inlineStr">
@@ -11322,14 +11322,14 @@
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
         <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B149" s="2" t="inlineStr">
+        <is>
           <t>11/04/2026</t>
         </is>
       </c>
-      <c r="B149" s="2" t="inlineStr">
-        <is>
-          <t>10/04/2026</t>
-        </is>
-      </c>
       <c r="C149" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -11361,11 +11361,11 @@
         </is>
       </c>
       <c r="I149" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J149" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J149" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K149" s="2" t="inlineStr">
@@ -11395,14 +11395,14 @@
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
         <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="B150" s="2" t="inlineStr">
+        <is>
           <t>10/04/2026</t>
         </is>
       </c>
-      <c r="B150" s="2" t="inlineStr">
-        <is>
-          <t>09/04/2026</t>
-        </is>
-      </c>
       <c r="C150" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -11434,11 +11434,11 @@
         </is>
       </c>
       <c r="I150" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J150" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>1</v>
+      </c>
+      <c r="J150" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K150" s="2" t="inlineStr">
@@ -11468,14 +11468,14 @@
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
         <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="B151" s="2" t="inlineStr">
+        <is>
           <t>10/04/2026</t>
         </is>
       </c>
-      <c r="B151" s="2" t="inlineStr">
-        <is>
-          <t>09/04/2026</t>
-        </is>
-      </c>
       <c r="C151" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -11507,11 +11507,11 @@
         </is>
       </c>
       <c r="I151" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J151" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J151" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K151" s="2" t="inlineStr">
@@ -11541,12 +11541,12 @@
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
         <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B152" s="2" t="inlineStr">
+        <is>
           <t>09/04/2026</t>
-        </is>
-      </c>
-      <c r="B152" s="2" t="inlineStr">
-        <is>
-          <t>08/04/2026</t>
         </is>
       </c>
       <c r="C152" s="2" t="inlineStr">
@@ -11582,9 +11582,9 @@
       <c r="I152" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="J152" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+      <c r="J152" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K152" s="2" t="inlineStr">
@@ -11614,14 +11614,14 @@
     <row r="153">
       <c r="A153" s="2" t="inlineStr">
         <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B153" s="2" t="inlineStr">
+        <is>
           <t>09/04/2026</t>
         </is>
       </c>
-      <c r="B153" s="2" t="inlineStr">
-        <is>
-          <t>08/04/2026</t>
-        </is>
-      </c>
       <c r="C153" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -11653,7 +11653,7 @@
         </is>
       </c>
       <c r="I153" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J153" s="2" t="inlineStr">
         <is>
@@ -11687,14 +11687,14 @@
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
         <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="B154" s="2" t="inlineStr">
+        <is>
           <t>08/04/2026</t>
         </is>
       </c>
-      <c r="B154" s="2" t="inlineStr">
-        <is>
-          <t>07/04/2026</t>
-        </is>
-      </c>
       <c r="C154" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -11720,17 +11720,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H154" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H154" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I154" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J154" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>2</v>
+      </c>
+      <c r="J154" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K154" s="2" t="inlineStr">
@@ -11760,14 +11760,14 @@
     <row r="155">
       <c r="A155" s="2" t="inlineStr">
         <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="B155" s="2" t="inlineStr">
+        <is>
           <t>08/04/2026</t>
         </is>
       </c>
-      <c r="B155" s="2" t="inlineStr">
-        <is>
-          <t>07/04/2026</t>
-        </is>
-      </c>
       <c r="C155" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -11801,9 +11801,9 @@
       <c r="I155" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J155" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J155" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K155" s="2" t="inlineStr">
@@ -11833,14 +11833,14 @@
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
         <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="B156" s="2" t="inlineStr">
+        <is>
           <t>07/04/2026</t>
         </is>
       </c>
-      <c r="B156" s="2" t="inlineStr">
-        <is>
-          <t>06/04/2026</t>
-        </is>
-      </c>
       <c r="C156" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -11863,38 +11863,38 @@
       </c>
       <c r="G156" s="2" t="inlineStr">
         <is>
-          <t>R$ 110,00</t>
-        </is>
-      </c>
-      <c r="H156" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H156" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I156" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J156" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+      <c r="J156" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K156" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L156" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M156" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N156" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O156" s="2" t="inlineStr">
@@ -11906,14 +11906,14 @@
     <row r="157">
       <c r="A157" s="2" t="inlineStr">
         <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="B157" s="2" t="inlineStr">
+        <is>
           <t>07/04/2026</t>
         </is>
       </c>
-      <c r="B157" s="2" t="inlineStr">
-        <is>
-          <t>06/04/2026</t>
-        </is>
-      </c>
       <c r="C157" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -11945,11 +11945,11 @@
         </is>
       </c>
       <c r="I157" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J157" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J157" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K157" s="2" t="inlineStr">
@@ -11979,14 +11979,14 @@
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
         <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="B158" s="2" t="inlineStr">
+        <is>
           <t>06/04/2026</t>
         </is>
       </c>
-      <c r="B158" s="2" t="inlineStr">
-        <is>
-          <t>05/04/2026</t>
-        </is>
-      </c>
       <c r="C158" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -12014,20 +12014,20 @@
       </c>
       <c r="H158" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I158" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J158" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J158" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K158" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="L158" s="2" t="n">
@@ -12035,12 +12035,12 @@
       </c>
       <c r="M158" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="N158" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O158" s="2" t="inlineStr">
@@ -12052,14 +12052,14 @@
     <row r="159">
       <c r="A159" s="2" t="inlineStr">
         <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="B159" s="2" t="inlineStr">
+        <is>
           <t>06/04/2026</t>
         </is>
       </c>
-      <c r="B159" s="2" t="inlineStr">
-        <is>
-          <t>05/04/2026</t>
-        </is>
-      </c>
       <c r="C159" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -12091,7 +12091,7 @@
         </is>
       </c>
       <c r="I159" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J159" s="2" t="inlineStr">
         <is>
@@ -12125,14 +12125,14 @@
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
         <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="B160" s="2" t="inlineStr">
+        <is>
           <t>05/04/2026</t>
         </is>
       </c>
-      <c r="B160" s="2" t="inlineStr">
-        <is>
-          <t>04/04/2026</t>
-        </is>
-      </c>
       <c r="C160" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -12155,7 +12155,7 @@
       </c>
       <c r="G160" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 110,00</t>
         </is>
       </c>
       <c r="H160" s="2" t="inlineStr">
@@ -12164,24 +12164,24 @@
         </is>
       </c>
       <c r="I160" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J160" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
+        </is>
+      </c>
+      <c r="K160" s="2" t="inlineStr">
+        <is>
+          <t>50,0%</t>
+        </is>
+      </c>
+      <c r="L160" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J160" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K160" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L160" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="M160" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="N160" s="2" t="inlineStr">
@@ -12198,14 +12198,14 @@
     <row r="161">
       <c r="A161" s="2" t="inlineStr">
         <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="B161" s="2" t="inlineStr">
+        <is>
           <t>05/04/2026</t>
         </is>
       </c>
-      <c r="B161" s="2" t="inlineStr">
-        <is>
-          <t>04/04/2026</t>
-        </is>
-      </c>
       <c r="C161" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -12239,9 +12239,9 @@
       <c r="I161" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J161" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J161" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K161" s="2" t="inlineStr">
@@ -12271,14 +12271,14 @@
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
         <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B162" s="2" t="inlineStr">
+        <is>
           <t>04/04/2026</t>
         </is>
       </c>
-      <c r="B162" s="2" t="inlineStr">
-        <is>
-          <t>03/04/2026</t>
-        </is>
-      </c>
       <c r="C162" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -12310,7 +12310,7 @@
         </is>
       </c>
       <c r="I162" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J162" s="2" t="inlineStr">
         <is>
@@ -12344,14 +12344,14 @@
     <row r="163">
       <c r="A163" s="2" t="inlineStr">
         <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B163" s="2" t="inlineStr">
+        <is>
           <t>04/04/2026</t>
         </is>
       </c>
-      <c r="B163" s="2" t="inlineStr">
-        <is>
-          <t>03/04/2026</t>
-        </is>
-      </c>
       <c r="C163" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -12383,11 +12383,11 @@
         </is>
       </c>
       <c r="I163" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J163" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J163" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K163" s="2" t="inlineStr">
@@ -12417,14 +12417,14 @@
     <row r="164">
       <c r="A164" s="2" t="inlineStr">
         <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B164" s="2" t="inlineStr">
+        <is>
           <t>03/04/2026</t>
         </is>
       </c>
-      <c r="B164" s="2" t="inlineStr">
-        <is>
-          <t>02/04/2026</t>
-        </is>
-      </c>
       <c r="C164" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -12458,9 +12458,9 @@
       <c r="I164" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J164" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J164" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K164" s="2" t="inlineStr">
@@ -12490,14 +12490,14 @@
     <row r="165">
       <c r="A165" s="2" t="inlineStr">
         <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B165" s="2" t="inlineStr">
+        <is>
           <t>03/04/2026</t>
         </is>
       </c>
-      <c r="B165" s="2" t="inlineStr">
-        <is>
-          <t>02/04/2026</t>
-        </is>
-      </c>
       <c r="C165" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -12529,11 +12529,11 @@
         </is>
       </c>
       <c r="I165" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J165" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J165" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K165" s="2" t="inlineStr">
@@ -12563,14 +12563,14 @@
     <row r="166">
       <c r="A166" s="2" t="inlineStr">
         <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B166" s="2" t="inlineStr">
+        <is>
           <t>02/04/2026</t>
         </is>
       </c>
-      <c r="B166" s="2" t="inlineStr">
-        <is>
-          <t>01/04/2026</t>
-        </is>
-      </c>
       <c r="C166" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -12602,11 +12602,11 @@
         </is>
       </c>
       <c r="I166" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J166" s="3" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K166" s="2" t="inlineStr">
@@ -12636,14 +12636,14 @@
     <row r="167">
       <c r="A167" s="2" t="inlineStr">
         <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B167" s="2" t="inlineStr">
+        <is>
           <t>02/04/2026</t>
         </is>
       </c>
-      <c r="B167" s="2" t="inlineStr">
-        <is>
-          <t>01/04/2026</t>
-        </is>
-      </c>
       <c r="C167" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -12675,11 +12675,11 @@
         </is>
       </c>
       <c r="I167" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J167" s="3" t="inlineStr">
         <is>
-          <t>▼ 66,7%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K167" s="2" t="inlineStr">
@@ -12709,14 +12709,14 @@
     <row r="168">
       <c r="A168" s="2" t="inlineStr">
         <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B168" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B168" s="2" t="inlineStr">
-        <is>
-          <t>31/03/2026</t>
-        </is>
-      </c>
       <c r="C168" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -12748,11 +12748,11 @@
         </is>
       </c>
       <c r="I168" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J168" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>1</v>
+      </c>
+      <c r="J168" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K168" s="2" t="inlineStr">
@@ -12782,78 +12782,224 @@
     <row r="169">
       <c r="A169" s="2" t="inlineStr">
         <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B169" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B169" s="2" t="inlineStr">
+      <c r="C169" s="2" t="inlineStr">
+        <is>
+          <t>UTD-145</t>
+        </is>
+      </c>
+      <c r="D169" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor duplo com bica arthi</t>
+        </is>
+      </c>
+      <c r="E169" s="2" t="inlineStr">
+        <is>
+          <t>4498058823</t>
+        </is>
+      </c>
+      <c r="F169" s="2" t="inlineStr">
+        <is>
+          <t>R$ 157,65</t>
+        </is>
+      </c>
+      <c r="G169" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H169" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I169" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J169" s="3" t="inlineStr">
+        <is>
+          <t>▼ 66,7%</t>
+        </is>
+      </c>
+      <c r="K169" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L169" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M169" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N169" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O169" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B170" s="2" t="inlineStr">
         <is>
           <t>31/03/2026</t>
         </is>
       </c>
-      <c r="C169" s="2" t="inlineStr">
-        <is>
-          <t>UTD-145</t>
-        </is>
-      </c>
-      <c r="D169" s="2" t="inlineStr">
-        <is>
-          <t>Escorredor duplo com bica arthi</t>
-        </is>
-      </c>
-      <c r="E169" s="2" t="inlineStr">
+      <c r="C170" s="2" t="inlineStr">
+        <is>
+          <t>UTD-145</t>
+        </is>
+      </c>
+      <c r="D170" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor duplo com bica arthi</t>
+        </is>
+      </c>
+      <c r="E170" s="2" t="inlineStr">
+        <is>
+          <t>4645710434</t>
+        </is>
+      </c>
+      <c r="F170" s="2" t="inlineStr">
+        <is>
+          <t>R$ 157,65</t>
+        </is>
+      </c>
+      <c r="G170" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H170" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I170" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J170" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K170" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L170" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M170" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N170" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O170" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B171" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C171" s="2" t="inlineStr">
+        <is>
+          <t>UTD-145</t>
+        </is>
+      </c>
+      <c r="D171" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor duplo com bica arthi</t>
+        </is>
+      </c>
+      <c r="E171" s="2" t="inlineStr">
         <is>
           <t>4498058823</t>
         </is>
       </c>
-      <c r="F169" s="2" t="inlineStr">
-        <is>
-          <t>R$ 157,65</t>
-        </is>
-      </c>
-      <c r="G169" s="2" t="inlineStr">
-        <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H169" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I169" s="2" t="n">
+      <c r="F171" s="2" t="inlineStr">
+        <is>
+          <t>R$ 157,65</t>
+        </is>
+      </c>
+      <c r="G171" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H171" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I171" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="J169" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K169" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L169" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M169" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="N169" s="2" t="inlineStr">
+      <c r="J171" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K171" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L171" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M171" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N171" s="2" t="inlineStr">
         <is>
           <t>Sem calcular</t>
         </is>
       </c>
-      <c r="O169" s="2" t="inlineStr">
+      <c r="O171" s="2" t="inlineStr">
         <is>
           <t>Média</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O169"/>
+  <autoFilter ref="A1:O171"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/saida_skus/SKU_UTD-145-ESCORREDOR-DUPLO-COM-BICA-ARTHI.xlsx
+++ b/saida_skus/SKU_UTD-145-ESCORREDOR-DUPLO-COM-BICA-ARTHI.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Analise" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$171</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$173</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O171"/>
+  <dimension ref="A1:O173"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -559,14 +559,14 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
           <t>24/06/2026</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>23/06/2026</t>
-        </is>
-      </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -589,7 +589,7 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -597,8 +597,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I2" s="2" t="n">
-        <v>0</v>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
@@ -607,39 +609,41 @@
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L2" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
           <t>24/06/2026</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>23/06/2026</t>
-        </is>
-      </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -673,9 +677,9 @@
       <c r="I3" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J3" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
@@ -705,12 +709,12 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
+          <t>24/06/2026</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
           <t>23/06/2026</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>22/06/2026</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -778,14 +782,14 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
+          <t>24/06/2026</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
           <t>23/06/2026</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>22/06/2026</t>
-        </is>
-      </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -817,11 +821,11 @@
         </is>
       </c>
       <c r="I5" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -851,14 +855,14 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
+          <t>23/06/2026</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
           <t>22/06/2026</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>21/06/2026</t>
-        </is>
-      </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -892,9 +896,9 @@
       <c r="I6" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J6" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -924,14 +928,14 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
+          <t>23/06/2026</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
           <t>22/06/2026</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>21/06/2026</t>
-        </is>
-      </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -963,11 +967,11 @@
         </is>
       </c>
       <c r="I7" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>1</v>
+      </c>
+      <c r="J7" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -997,14 +1001,14 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
           <t>21/06/2026</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>20/06/2026</t>
-        </is>
-      </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -1036,11 +1040,11 @@
         </is>
       </c>
       <c r="I8" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1070,12 +1074,12 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
           <t>21/06/2026</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>20/06/2026</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -1113,7 +1117,7 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -1143,14 +1147,14 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
+          <t>21/06/2026</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
           <t>20/06/2026</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>19/06/2026</t>
-        </is>
-      </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -1173,7 +1177,7 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -1181,10 +1185,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I10" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
@@ -1193,41 +1195,39 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
+          <t>21/06/2026</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
           <t>20/06/2026</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>19/06/2026</t>
-        </is>
-      </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -1259,7 +1259,7 @@
         </is>
       </c>
       <c r="I11" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
@@ -1293,14 +1293,14 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
+          <t>20/06/2026</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
           <t>19/06/2026</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>18/06/2026</t>
-        </is>
-      </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -1323,7 +1323,7 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -1331,8 +1331,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I12" s="2" t="n">
-        <v>0</v>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
@@ -1341,39 +1343,41 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
+          <t>20/06/2026</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
           <t>19/06/2026</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>18/06/2026</t>
-        </is>
-      </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -1407,9 +1411,9 @@
       <c r="I13" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J13" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -1439,14 +1443,14 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
+          <t>19/06/2026</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
           <t>18/06/2026</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>17/06/2026</t>
-        </is>
-      </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -1469,7 +1473,7 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -1477,10 +1481,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I14" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
@@ -1489,41 +1491,39 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
+          <t>19/06/2026</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
           <t>18/06/2026</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>17/06/2026</t>
-        </is>
-      </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -1555,11 +1555,11 @@
         </is>
       </c>
       <c r="I15" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J15" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -1589,14 +1589,14 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
+          <t>18/06/2026</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
           <t>17/06/2026</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>16/06/2026</t>
-        </is>
-      </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -1619,7 +1619,7 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -1627,8 +1627,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I16" s="2" t="n">
-        <v>0</v>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
@@ -1637,37 +1639,39 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
+          <t>18/06/2026</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
           <t>17/06/2026</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>16/06/2026</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1735,14 +1739,14 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
+          <t>17/06/2026</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
           <t>16/06/2026</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>15/06/2026</t>
-        </is>
-      </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -1776,9 +1780,9 @@
       <c r="I18" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J18" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1808,12 +1812,12 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
+          <t>17/06/2026</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
           <t>16/06/2026</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>15/06/2026</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -1881,14 +1885,14 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
+          <t>16/06/2026</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
           <t>15/06/2026</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>14/06/2026</t>
-        </is>
-      </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -1920,11 +1924,11 @@
         </is>
       </c>
       <c r="I20" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J20" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1954,12 +1958,12 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
+          <t>16/06/2026</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
           <t>15/06/2026</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>14/06/2026</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -2027,12 +2031,12 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
+          <t>15/06/2026</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
           <t>14/06/2026</t>
-        </is>
-      </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>13/06/2026</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -2100,12 +2104,12 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
+          <t>15/06/2026</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
           <t>14/06/2026</t>
-        </is>
-      </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>13/06/2026</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -2141,9 +2145,9 @@
       <c r="I23" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J23" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -2173,12 +2177,12 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
+          <t>14/06/2026</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
           <t>13/06/2026</t>
-        </is>
-      </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>12/06/2026</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -2246,14 +2250,14 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
+          <t>14/06/2026</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
           <t>13/06/2026</t>
         </is>
       </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>12/06/2026</t>
-        </is>
-      </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -2285,11 +2289,11 @@
         </is>
       </c>
       <c r="I25" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>1</v>
+      </c>
+      <c r="J25" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
@@ -2319,12 +2323,12 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
+          <t>13/06/2026</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
           <t>12/06/2026</t>
-        </is>
-      </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>11/06/2026</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -2392,14 +2396,14 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
+          <t>13/06/2026</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
           <t>12/06/2026</t>
         </is>
       </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>11/06/2026</t>
-        </is>
-      </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -2431,7 +2435,7 @@
         </is>
       </c>
       <c r="I27" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
@@ -2465,12 +2469,12 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
+          <t>12/06/2026</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
           <t>11/06/2026</t>
-        </is>
-      </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>10/06/2026</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -2506,9 +2510,9 @@
       <c r="I28" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J28" s="3" t="inlineStr">
-        <is>
-          <t>▼ 66,7%</t>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
@@ -2538,12 +2542,12 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
+          <t>12/06/2026</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
           <t>11/06/2026</t>
-        </is>
-      </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>10/06/2026</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -2611,14 +2615,14 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
+          <t>11/06/2026</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
           <t>10/06/2026</t>
         </is>
       </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>09/06/2026</t>
-        </is>
-      </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -2650,11 +2654,11 @@
         </is>
       </c>
       <c r="I30" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>1</v>
+      </c>
+      <c r="J30" s="3" t="inlineStr">
+        <is>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
@@ -2684,14 +2688,14 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
+          <t>11/06/2026</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
           <t>10/06/2026</t>
         </is>
       </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>09/06/2026</t>
-        </is>
-      </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -2717,17 +2721,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H31" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I31" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J31" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
@@ -2757,14 +2761,14 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
+          <t>10/06/2026</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
           <t>09/06/2026</t>
         </is>
       </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>08/06/2026</t>
-        </is>
-      </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -2796,11 +2800,11 @@
         </is>
       </c>
       <c r="I32" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J32" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>3</v>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
@@ -2830,14 +2834,14 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
+          <t>10/06/2026</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
           <t>09/06/2026</t>
         </is>
       </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>08/06/2026</t>
-        </is>
-      </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -2860,33 +2864,33 @@
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>R$ 107,00</t>
-        </is>
-      </c>
-      <c r="H33" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H33" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I33" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J33" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J33" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L33" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -2903,14 +2907,14 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
+          <t>09/06/2026</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
           <t>08/06/2026</t>
         </is>
       </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>07/06/2026</t>
-        </is>
-      </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -2942,11 +2946,11 @@
         </is>
       </c>
       <c r="I34" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J34" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J34" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
@@ -2976,14 +2980,14 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
+          <t>09/06/2026</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
           <t>08/06/2026</t>
         </is>
       </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>07/06/2026</t>
-        </is>
-      </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -3006,7 +3010,7 @@
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 107,00</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
@@ -3015,24 +3019,24 @@
         </is>
       </c>
       <c r="I35" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J35" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
+        </is>
+      </c>
+      <c r="K35" s="2" t="inlineStr">
+        <is>
+          <t>50,0%</t>
+        </is>
+      </c>
+      <c r="L35" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J35" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K35" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L35" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -3049,14 +3053,14 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
           <t>07/06/2026</t>
         </is>
       </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>06/06/2026</t>
-        </is>
-      </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -3088,11 +3092,11 @@
         </is>
       </c>
       <c r="I36" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J36" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>3</v>
+      </c>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
@@ -3122,14 +3126,14 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
           <t>07/06/2026</t>
         </is>
       </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>06/06/2026</t>
-        </is>
-      </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -3161,11 +3165,11 @@
         </is>
       </c>
       <c r="I37" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J37" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
@@ -3195,14 +3199,14 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
+          <t>07/06/2026</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
           <t>06/06/2026</t>
         </is>
       </c>
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>05/06/2026</t>
-        </is>
-      </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -3234,11 +3238,11 @@
         </is>
       </c>
       <c r="I38" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J38" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J38" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
@@ -3268,14 +3272,14 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
+          <t>07/06/2026</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
           <t>06/06/2026</t>
         </is>
       </c>
-      <c r="B39" s="2" t="inlineStr">
-        <is>
-          <t>05/06/2026</t>
-        </is>
-      </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -3307,11 +3311,11 @@
         </is>
       </c>
       <c r="I39" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J39" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J39" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
@@ -3341,12 +3345,12 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
+          <t>06/06/2026</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
           <t>05/06/2026</t>
-        </is>
-      </c>
-      <c r="B40" s="2" t="inlineStr">
-        <is>
-          <t>04/06/2026</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -3384,7 +3388,7 @@
       </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
@@ -3414,14 +3418,14 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
+          <t>06/06/2026</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
           <t>05/06/2026</t>
         </is>
       </c>
-      <c r="B41" s="2" t="inlineStr">
-        <is>
-          <t>04/06/2026</t>
-        </is>
-      </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -3453,7 +3457,7 @@
         </is>
       </c>
       <c r="I41" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J41" s="2" t="inlineStr">
         <is>
@@ -3487,14 +3491,14 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
+          <t>05/06/2026</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
           <t>04/06/2026</t>
         </is>
       </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>03/06/2026</t>
-        </is>
-      </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -3526,11 +3530,11 @@
         </is>
       </c>
       <c r="I42" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J42" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J42" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
@@ -3560,14 +3564,14 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
+          <t>05/06/2026</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
           <t>04/06/2026</t>
         </is>
       </c>
-      <c r="B43" s="2" t="inlineStr">
-        <is>
-          <t>03/06/2026</t>
-        </is>
-      </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -3601,9 +3605,9 @@
       <c r="I43" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J43" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J43" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr">
@@ -3633,14 +3637,14 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
+          <t>04/06/2026</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
           <t>03/06/2026</t>
         </is>
       </c>
-      <c r="B44" s="2" t="inlineStr">
-        <is>
-          <t>02/06/2026</t>
-        </is>
-      </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -3672,11 +3676,11 @@
         </is>
       </c>
       <c r="I44" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J44" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J44" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
@@ -3706,14 +3710,14 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
+          <t>04/06/2026</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
           <t>03/06/2026</t>
         </is>
       </c>
-      <c r="B45" s="2" t="inlineStr">
-        <is>
-          <t>02/06/2026</t>
-        </is>
-      </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -3745,11 +3749,11 @@
         </is>
       </c>
       <c r="I45" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J45" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J45" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr">
@@ -3779,14 +3783,14 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
+          <t>03/06/2026</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
           <t>02/06/2026</t>
         </is>
       </c>
-      <c r="B46" s="2" t="inlineStr">
-        <is>
-          <t>01/06/2026</t>
-        </is>
-      </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -3812,17 +3816,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H46" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I46" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J46" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J46" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
@@ -3852,12 +3856,12 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
+          <t>03/06/2026</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
           <t>02/06/2026</t>
-        </is>
-      </c>
-      <c r="B47" s="2" t="inlineStr">
-        <is>
-          <t>01/06/2026</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -3925,14 +3929,14 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
+          <t>02/06/2026</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
           <t>01/06/2026</t>
         </is>
       </c>
-      <c r="B48" s="2" t="inlineStr">
-        <is>
-          <t>31/05/2026</t>
-        </is>
-      </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -3955,33 +3959,33 @@
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>R$ 126,00</t>
-        </is>
-      </c>
-      <c r="H48" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H48" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I48" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J48" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J48" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L48" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -3998,12 +4002,12 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
+          <t>02/06/2026</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
           <t>01/06/2026</t>
-        </is>
-      </c>
-      <c r="B49" s="2" t="inlineStr">
-        <is>
-          <t>31/05/2026</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -4071,14 +4075,14 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
+          <t>01/06/2026</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
           <t>31/05/2026</t>
         </is>
       </c>
-      <c r="B50" s="2" t="inlineStr">
-        <is>
-          <t>30/05/2026</t>
-        </is>
-      </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -4101,33 +4105,33 @@
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H50" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 126,00</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I50" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J50" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J50" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="L50" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -4144,12 +4148,12 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
+          <t>01/06/2026</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
           <t>31/05/2026</t>
-        </is>
-      </c>
-      <c r="B51" s="2" t="inlineStr">
-        <is>
-          <t>30/05/2026</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -4185,9 +4189,9 @@
       <c r="I51" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J51" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+      <c r="J51" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K51" s="2" t="inlineStr">
@@ -4217,14 +4221,14 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
+          <t>31/05/2026</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
           <t>30/05/2026</t>
         </is>
       </c>
-      <c r="B52" s="2" t="inlineStr">
-        <is>
-          <t>29/05/2026</t>
-        </is>
-      </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -4247,33 +4251,33 @@
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>R$ 126,00</t>
-        </is>
-      </c>
-      <c r="H52" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H52" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I52" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J52" s="3" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L52" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -4290,14 +4294,14 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
+          <t>31/05/2026</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
           <t>30/05/2026</t>
         </is>
       </c>
-      <c r="B53" s="2" t="inlineStr">
-        <is>
-          <t>29/05/2026</t>
-        </is>
-      </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -4329,11 +4333,11 @@
         </is>
       </c>
       <c r="I53" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J53" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>1</v>
+      </c>
+      <c r="J53" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K53" s="2" t="inlineStr">
@@ -4363,14 +4367,14 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
+          <t>30/05/2026</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
           <t>29/05/2026</t>
         </is>
       </c>
-      <c r="B54" s="2" t="inlineStr">
-        <is>
-          <t>28/05/2026</t>
-        </is>
-      </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -4393,7 +4397,7 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 126,00</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
@@ -4402,24 +4406,24 @@
         </is>
       </c>
       <c r="I54" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J54" s="3" t="inlineStr">
         <is>
-          <t>▼ 33,3%</t>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="L54" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -4436,14 +4440,14 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
+          <t>30/05/2026</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
           <t>29/05/2026</t>
         </is>
       </c>
-      <c r="B55" s="2" t="inlineStr">
-        <is>
-          <t>28/05/2026</t>
-        </is>
-      </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -4475,11 +4479,11 @@
         </is>
       </c>
       <c r="I55" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J55" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J55" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K55" s="2" t="inlineStr">
@@ -4509,14 +4513,14 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
+          <t>29/05/2026</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
           <t>28/05/2026</t>
         </is>
       </c>
-      <c r="B56" s="2" t="inlineStr">
-        <is>
-          <t>27/05/2026</t>
-        </is>
-      </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -4548,11 +4552,11 @@
         </is>
       </c>
       <c r="I56" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J56" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>2</v>
+      </c>
+      <c r="J56" s="3" t="inlineStr">
+        <is>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr">
@@ -4582,14 +4586,14 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
+          <t>29/05/2026</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
           <t>28/05/2026</t>
         </is>
       </c>
-      <c r="B57" s="2" t="inlineStr">
-        <is>
-          <t>27/05/2026</t>
-        </is>
-      </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -4621,11 +4625,11 @@
         </is>
       </c>
       <c r="I57" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J57" s="3" t="inlineStr">
         <is>
-          <t>▼ 66,7%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K57" s="2" t="inlineStr">
@@ -4655,14 +4659,14 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
+          <t>28/05/2026</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
           <t>27/05/2026</t>
         </is>
       </c>
-      <c r="B58" s="2" t="inlineStr">
-        <is>
-          <t>26/05/2026</t>
-        </is>
-      </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -4694,11 +4698,11 @@
         </is>
       </c>
       <c r="I58" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J58" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>3</v>
+      </c>
+      <c r="J58" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr">
@@ -4728,14 +4732,14 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
+          <t>28/05/2026</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
           <t>27/05/2026</t>
         </is>
       </c>
-      <c r="B59" s="2" t="inlineStr">
-        <is>
-          <t>26/05/2026</t>
-        </is>
-      </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -4767,11 +4771,11 @@
         </is>
       </c>
       <c r="I59" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J59" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>1</v>
+      </c>
+      <c r="J59" s="3" t="inlineStr">
+        <is>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K59" s="2" t="inlineStr">
@@ -4801,14 +4805,14 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
+          <t>27/05/2026</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
           <t>26/05/2026</t>
         </is>
       </c>
-      <c r="B60" s="2" t="inlineStr">
-        <is>
-          <t>25/05/2026</t>
-        </is>
-      </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -4840,11 +4844,11 @@
         </is>
       </c>
       <c r="I60" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J60" s="4" t="inlineStr">
-        <is>
-          <t>▲ 50,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J60" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K60" s="2" t="inlineStr">
@@ -4874,14 +4878,14 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
+          <t>27/05/2026</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
           <t>26/05/2026</t>
         </is>
       </c>
-      <c r="B61" s="2" t="inlineStr">
-        <is>
-          <t>25/05/2026</t>
-        </is>
-      </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -4913,11 +4917,11 @@
         </is>
       </c>
       <c r="I61" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J61" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>3</v>
+      </c>
+      <c r="J61" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K61" s="2" t="inlineStr">
@@ -4947,14 +4951,14 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
+          <t>26/05/2026</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
           <t>25/05/2026</t>
         </is>
       </c>
-      <c r="B62" s="2" t="inlineStr">
-        <is>
-          <t>24/05/2026</t>
-        </is>
-      </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -4986,11 +4990,11 @@
         </is>
       </c>
       <c r="I62" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J62" s="4" t="inlineStr">
         <is>
-          <t>▲ 100,0%</t>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="K62" s="2" t="inlineStr">
@@ -5020,14 +5024,14 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
+          <t>26/05/2026</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
           <t>25/05/2026</t>
         </is>
       </c>
-      <c r="B63" s="2" t="inlineStr">
-        <is>
-          <t>24/05/2026</t>
-        </is>
-      </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -5059,11 +5063,11 @@
         </is>
       </c>
       <c r="I63" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J63" s="3" t="inlineStr">
         <is>
-          <t>▼ 83,3%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K63" s="2" t="inlineStr">
@@ -5093,14 +5097,14 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
+          <t>25/05/2026</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
           <t>24/05/2026</t>
         </is>
       </c>
-      <c r="B64" s="2" t="inlineStr">
-        <is>
-          <t>23/05/2026</t>
-        </is>
-      </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -5126,17 +5130,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H64" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I64" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J64" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J64" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K64" s="2" t="inlineStr">
@@ -5166,14 +5170,14 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
+          <t>25/05/2026</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
           <t>24/05/2026</t>
         </is>
       </c>
-      <c r="B65" s="2" t="inlineStr">
-        <is>
-          <t>23/05/2026</t>
-        </is>
-      </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -5205,11 +5209,11 @@
         </is>
       </c>
       <c r="I65" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J65" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J65" s="3" t="inlineStr">
+        <is>
+          <t>▼ 83,3%</t>
         </is>
       </c>
       <c r="K65" s="2" t="inlineStr">
@@ -5239,14 +5243,14 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
+          <t>24/05/2026</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
           <t>23/05/2026</t>
         </is>
       </c>
-      <c r="B66" s="2" t="inlineStr">
-        <is>
-          <t>22/05/2026</t>
-        </is>
-      </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -5269,33 +5273,33 @@
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>R$ 126,00</t>
-        </is>
-      </c>
-      <c r="H66" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H66" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I66" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J66" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J66" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L66" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N66" s="2" t="inlineStr">
@@ -5312,14 +5316,14 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
+          <t>24/05/2026</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
           <t>23/05/2026</t>
         </is>
       </c>
-      <c r="B67" s="2" t="inlineStr">
-        <is>
-          <t>22/05/2026</t>
-        </is>
-      </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -5351,11 +5355,11 @@
         </is>
       </c>
       <c r="I67" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J67" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>6</v>
+      </c>
+      <c r="J67" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K67" s="2" t="inlineStr">
@@ -5385,14 +5389,14 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
+          <t>23/05/2026</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
           <t>22/05/2026</t>
         </is>
       </c>
-      <c r="B68" s="2" t="inlineStr">
-        <is>
-          <t>21/05/2026</t>
-        </is>
-      </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -5415,7 +5419,7 @@
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 126,00</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
@@ -5424,24 +5428,24 @@
         </is>
       </c>
       <c r="I68" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J68" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
+        </is>
+      </c>
+      <c r="K68" s="2" t="inlineStr">
+        <is>
+          <t>50,0%</t>
+        </is>
+      </c>
+      <c r="L68" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J68" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
-        </is>
-      </c>
-      <c r="K68" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L68" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="M68" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="N68" s="2" t="inlineStr">
@@ -5458,12 +5462,12 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
+          <t>23/05/2026</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
           <t>22/05/2026</t>
-        </is>
-      </c>
-      <c r="B69" s="2" t="inlineStr">
-        <is>
-          <t>21/05/2026</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -5501,7 +5505,7 @@
       </c>
       <c r="J69" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K69" s="2" t="inlineStr">
@@ -5531,14 +5535,14 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
           <t>21/05/2026</t>
         </is>
       </c>
-      <c r="B70" s="2" t="inlineStr">
-        <is>
-          <t>20/05/2026</t>
-        </is>
-      </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -5570,11 +5574,11 @@
         </is>
       </c>
       <c r="I70" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J70" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>1</v>
+      </c>
+      <c r="J70" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr">
@@ -5604,14 +5608,14 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
           <t>21/05/2026</t>
         </is>
       </c>
-      <c r="B71" s="2" t="inlineStr">
-        <is>
-          <t>20/05/2026</t>
-        </is>
-      </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -5643,11 +5647,11 @@
         </is>
       </c>
       <c r="I71" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J71" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>3</v>
+      </c>
+      <c r="J71" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K71" s="2" t="inlineStr">
@@ -5677,14 +5681,14 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
+          <t>21/05/2026</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
           <t>20/05/2026</t>
         </is>
       </c>
-      <c r="B72" s="2" t="inlineStr">
-        <is>
-          <t>19/05/2026</t>
-        </is>
-      </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -5716,7 +5720,7 @@
         </is>
       </c>
       <c r="I72" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J72" s="2" t="inlineStr">
         <is>
@@ -5750,14 +5754,14 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
+          <t>21/05/2026</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
           <t>20/05/2026</t>
         </is>
       </c>
-      <c r="B73" s="2" t="inlineStr">
-        <is>
-          <t>19/05/2026</t>
-        </is>
-      </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -5789,11 +5793,11 @@
         </is>
       </c>
       <c r="I73" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J73" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J73" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K73" s="2" t="inlineStr">
@@ -5823,12 +5827,12 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
+          <t>20/05/2026</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
           <t>19/05/2026</t>
-        </is>
-      </c>
-      <c r="B74" s="2" t="inlineStr">
-        <is>
-          <t>18/05/2026</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -5896,14 +5900,14 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
+          <t>20/05/2026</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
           <t>19/05/2026</t>
         </is>
       </c>
-      <c r="B75" s="2" t="inlineStr">
-        <is>
-          <t>18/05/2026</t>
-        </is>
-      </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -5935,7 +5939,7 @@
         </is>
       </c>
       <c r="I75" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J75" s="2" t="inlineStr">
         <is>
@@ -5969,14 +5973,14 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
           <t>18/05/2026</t>
         </is>
       </c>
-      <c r="B76" s="2" t="inlineStr">
-        <is>
-          <t>17/05/2026</t>
-        </is>
-      </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -6010,9 +6014,9 @@
       <c r="I76" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J76" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J76" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K76" s="2" t="inlineStr">
@@ -6042,12 +6046,12 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
           <t>18/05/2026</t>
-        </is>
-      </c>
-      <c r="B77" s="2" t="inlineStr">
-        <is>
-          <t>17/05/2026</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
@@ -6115,14 +6119,14 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
           <t>17/05/2026</t>
         </is>
       </c>
-      <c r="B78" s="2" t="inlineStr">
-        <is>
-          <t>16/05/2026</t>
-        </is>
-      </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -6154,11 +6158,11 @@
         </is>
       </c>
       <c r="I78" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J78" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J78" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K78" s="2" t="inlineStr">
@@ -6188,14 +6192,14 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
           <t>17/05/2026</t>
         </is>
       </c>
-      <c r="B79" s="2" t="inlineStr">
-        <is>
-          <t>16/05/2026</t>
-        </is>
-      </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -6218,7 +6222,7 @@
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
@@ -6226,10 +6230,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I79" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I79" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J79" s="2" t="inlineStr">
         <is>
@@ -6238,41 +6240,39 @@
       </c>
       <c r="K79" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L79" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L79" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M79" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N79" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
+          <t>17/05/2026</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
           <t>16/05/2026</t>
         </is>
       </c>
-      <c r="B80" s="2" t="inlineStr">
-        <is>
-          <t>15/05/2026</t>
-        </is>
-      </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -6304,11 +6304,11 @@
         </is>
       </c>
       <c r="I80" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J80" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J80" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K80" s="2" t="inlineStr">
@@ -6338,14 +6338,14 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
+          <t>17/05/2026</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
           <t>16/05/2026</t>
         </is>
       </c>
-      <c r="B81" s="2" t="inlineStr">
-        <is>
-          <t>15/05/2026</t>
-        </is>
-      </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -6368,7 +6368,7 @@
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
@@ -6376,8 +6376,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I81" s="2" t="n">
-        <v>0</v>
+      <c r="I81" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J81" s="2" t="inlineStr">
         <is>
@@ -6386,39 +6388,41 @@
       </c>
       <c r="K81" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L81" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L81" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M81" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N81" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
+          <t>16/05/2026</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
           <t>15/05/2026</t>
         </is>
       </c>
-      <c r="B82" s="2" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
-        </is>
-      </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -6450,11 +6454,11 @@
         </is>
       </c>
       <c r="I82" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J82" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J82" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K82" s="2" t="inlineStr">
@@ -6484,14 +6488,14 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
+          <t>16/05/2026</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
           <t>15/05/2026</t>
         </is>
       </c>
-      <c r="B83" s="2" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
-        </is>
-      </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -6525,9 +6529,9 @@
       <c r="I83" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J83" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J83" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K83" s="2" t="inlineStr">
@@ -6557,14 +6561,14 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
+          <t>15/05/2026</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
           <t>14/05/2026</t>
         </is>
       </c>
-      <c r="B84" s="2" t="inlineStr">
-        <is>
-          <t>13/05/2026</t>
-        </is>
-      </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -6596,11 +6600,11 @@
         </is>
       </c>
       <c r="I84" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J84" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J84" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K84" s="2" t="inlineStr">
@@ -6630,14 +6634,14 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
+          <t>15/05/2026</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
           <t>14/05/2026</t>
         </is>
       </c>
-      <c r="B85" s="2" t="inlineStr">
-        <is>
-          <t>13/05/2026</t>
-        </is>
-      </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -6669,11 +6673,11 @@
         </is>
       </c>
       <c r="I85" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J85" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J85" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K85" s="2" t="inlineStr">
@@ -6703,14 +6707,14 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
+          <t>14/05/2026</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
           <t>13/05/2026</t>
         </is>
       </c>
-      <c r="B86" s="2" t="inlineStr">
-        <is>
-          <t>12/05/2026</t>
-        </is>
-      </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -6742,11 +6746,11 @@
         </is>
       </c>
       <c r="I86" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J86" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J86" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K86" s="2" t="inlineStr">
@@ -6776,14 +6780,14 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
+          <t>14/05/2026</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
           <t>13/05/2026</t>
         </is>
       </c>
-      <c r="B87" s="2" t="inlineStr">
-        <is>
-          <t>12/05/2026</t>
-        </is>
-      </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -6806,7 +6810,7 @@
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
@@ -6814,10 +6818,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I87" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I87" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J87" s="2" t="inlineStr">
         <is>
@@ -6826,41 +6828,39 @@
       </c>
       <c r="K87" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L87" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L87" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M87" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N87" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
+          <t>13/05/2026</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
           <t>12/05/2026</t>
         </is>
       </c>
-      <c r="B88" s="2" t="inlineStr">
-        <is>
-          <t>11/05/2026</t>
-        </is>
-      </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -6892,11 +6892,11 @@
         </is>
       </c>
       <c r="I88" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J88" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J88" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K88" s="2" t="inlineStr">
@@ -6926,12 +6926,12 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
+          <t>13/05/2026</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
           <t>12/05/2026</t>
-        </is>
-      </c>
-      <c r="B89" s="2" t="inlineStr">
-        <is>
-          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
@@ -7003,14 +7003,14 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
+          <t>12/05/2026</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
           <t>11/05/2026</t>
         </is>
       </c>
-      <c r="B90" s="2" t="inlineStr">
-        <is>
-          <t>10/05/2026</t>
-        </is>
-      </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -7042,11 +7042,11 @@
         </is>
       </c>
       <c r="I90" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J90" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J90" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K90" s="2" t="inlineStr">
@@ -7076,14 +7076,14 @@
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
+          <t>12/05/2026</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
           <t>11/05/2026</t>
         </is>
       </c>
-      <c r="B91" s="2" t="inlineStr">
-        <is>
-          <t>10/05/2026</t>
-        </is>
-      </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -7106,7 +7106,7 @@
       </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H91" s="2" t="inlineStr">
@@ -7114,8 +7114,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I91" s="2" t="n">
-        <v>0</v>
+      <c r="I91" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J91" s="2" t="inlineStr">
         <is>
@@ -7124,39 +7126,41 @@
       </c>
       <c r="K91" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L91" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L91" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M91" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N91" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
+          <t>11/05/2026</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
           <t>10/05/2026</t>
         </is>
       </c>
-      <c r="B92" s="2" t="inlineStr">
-        <is>
-          <t>09/05/2026</t>
-        </is>
-      </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -7179,7 +7183,7 @@
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H92" s="2" t="inlineStr">
@@ -7187,10 +7191,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I92" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I92" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J92" s="2" t="inlineStr">
         <is>
@@ -7199,41 +7201,39 @@
       </c>
       <c r="K92" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L92" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L92" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M92" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N92" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
+          <t>11/05/2026</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
           <t>10/05/2026</t>
         </is>
       </c>
-      <c r="B93" s="2" t="inlineStr">
-        <is>
-          <t>09/05/2026</t>
-        </is>
-      </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -7259,17 +7259,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H93" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H93" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I93" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J93" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J93" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K93" s="2" t="inlineStr">
@@ -7299,14 +7299,14 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
+          <t>10/05/2026</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
           <t>09/05/2026</t>
         </is>
       </c>
-      <c r="B94" s="2" t="inlineStr">
-        <is>
-          <t>08/05/2026</t>
-        </is>
-      </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -7329,7 +7329,7 @@
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H94" s="2" t="inlineStr">
@@ -7337,8 +7337,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I94" s="2" t="n">
-        <v>0</v>
+      <c r="I94" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J94" s="2" t="inlineStr">
         <is>
@@ -7347,39 +7349,41 @@
       </c>
       <c r="K94" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L94" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L94" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M94" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N94" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
+          <t>10/05/2026</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
           <t>09/05/2026</t>
         </is>
       </c>
-      <c r="B95" s="2" t="inlineStr">
-        <is>
-          <t>08/05/2026</t>
-        </is>
-      </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -7402,33 +7406,33 @@
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>R$ 110,00</t>
-        </is>
-      </c>
-      <c r="H95" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H95" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I95" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J95" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J95" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K95" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L95" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M95" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N95" s="2" t="inlineStr">
@@ -7445,14 +7449,14 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
           <t>08/05/2026</t>
         </is>
       </c>
-      <c r="B96" s="2" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
-        </is>
-      </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -7478,17 +7482,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H96" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H96" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I96" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J96" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J96" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K96" s="2" t="inlineStr">
@@ -7518,14 +7522,14 @@
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
           <t>08/05/2026</t>
         </is>
       </c>
-      <c r="B97" s="2" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
-        </is>
-      </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -7548,7 +7552,7 @@
       </c>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 110,00</t>
         </is>
       </c>
       <c r="H97" s="2" t="inlineStr">
@@ -7557,24 +7561,24 @@
         </is>
       </c>
       <c r="I97" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J97" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J97" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K97" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>50,0%</t>
         </is>
       </c>
       <c r="L97" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M97" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="N97" s="2" t="inlineStr">
@@ -7591,14 +7595,14 @@
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
+          <t>08/05/2026</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
           <t>07/05/2026</t>
         </is>
       </c>
-      <c r="B98" s="2" t="inlineStr">
-        <is>
-          <t>06/05/2026</t>
-        </is>
-      </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -7621,33 +7625,33 @@
       </c>
       <c r="G98" s="2" t="inlineStr">
         <is>
-          <t>R$ 110,00</t>
-        </is>
-      </c>
-      <c r="H98" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H98" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I98" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J98" s="3" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K98" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L98" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M98" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N98" s="2" t="inlineStr">
@@ -7664,14 +7668,14 @@
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
+          <t>08/05/2026</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
           <t>07/05/2026</t>
         </is>
       </c>
-      <c r="B99" s="2" t="inlineStr">
-        <is>
-          <t>06/05/2026</t>
-        </is>
-      </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -7703,11 +7707,11 @@
         </is>
       </c>
       <c r="I99" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J99" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J99" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K99" s="2" t="inlineStr">
@@ -7737,14 +7741,14 @@
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
           <t>06/05/2026</t>
         </is>
       </c>
-      <c r="B100" s="2" t="inlineStr">
-        <is>
-          <t>05/05/2026</t>
-        </is>
-      </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -7767,7 +7771,7 @@
       </c>
       <c r="G100" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 110,00</t>
         </is>
       </c>
       <c r="H100" s="2" t="inlineStr">
@@ -7776,24 +7780,24 @@
         </is>
       </c>
       <c r="I100" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J100" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>1</v>
+      </c>
+      <c r="J100" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K100" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="L100" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M100" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="N100" s="2" t="inlineStr">
@@ -7810,14 +7814,14 @@
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
           <t>06/05/2026</t>
         </is>
       </c>
-      <c r="B101" s="2" t="inlineStr">
-        <is>
-          <t>05/05/2026</t>
-        </is>
-      </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -7849,11 +7853,11 @@
         </is>
       </c>
       <c r="I101" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J101" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J101" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K101" s="2" t="inlineStr">
@@ -7883,12 +7887,12 @@
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
+          <t>06/05/2026</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
           <t>05/05/2026</t>
-        </is>
-      </c>
-      <c r="B102" s="2" t="inlineStr">
-        <is>
-          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
@@ -7926,7 +7930,7 @@
       </c>
       <c r="J102" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K102" s="2" t="inlineStr">
@@ -7956,14 +7960,14 @@
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
+          <t>06/05/2026</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
           <t>05/05/2026</t>
         </is>
       </c>
-      <c r="B103" s="2" t="inlineStr">
-        <is>
-          <t>04/05/2026</t>
-        </is>
-      </c>
       <c r="C103" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -7995,11 +7999,11 @@
         </is>
       </c>
       <c r="I103" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J103" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J103" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K103" s="2" t="inlineStr">
@@ -8029,14 +8033,14 @@
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
+          <t>05/05/2026</t>
+        </is>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
           <t>04/05/2026</t>
         </is>
       </c>
-      <c r="B104" s="2" t="inlineStr">
-        <is>
-          <t>03/05/2026</t>
-        </is>
-      </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -8068,7 +8072,7 @@
         </is>
       </c>
       <c r="I104" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J104" s="2" t="inlineStr">
         <is>
@@ -8102,14 +8106,14 @@
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
+          <t>05/05/2026</t>
+        </is>
+      </c>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
           <t>04/05/2026</t>
         </is>
       </c>
-      <c r="B105" s="2" t="inlineStr">
-        <is>
-          <t>03/05/2026</t>
-        </is>
-      </c>
       <c r="C105" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -8141,11 +8145,11 @@
         </is>
       </c>
       <c r="I105" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J105" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J105" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K105" s="2" t="inlineStr">
@@ -8175,14 +8179,14 @@
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
           <t>03/05/2026</t>
         </is>
       </c>
-      <c r="B106" s="2" t="inlineStr">
-        <is>
-          <t>02/05/2026</t>
-        </is>
-      </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -8216,9 +8220,9 @@
       <c r="I106" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J106" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J106" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K106" s="2" t="inlineStr">
@@ -8248,14 +8252,14 @@
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
           <t>03/05/2026</t>
         </is>
       </c>
-      <c r="B107" s="2" t="inlineStr">
-        <is>
-          <t>02/05/2026</t>
-        </is>
-      </c>
       <c r="C107" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -8287,11 +8291,11 @@
         </is>
       </c>
       <c r="I107" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J107" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J107" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K107" s="2" t="inlineStr">
@@ -8321,14 +8325,14 @@
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
+          <t>03/05/2026</t>
+        </is>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
           <t>02/05/2026</t>
         </is>
       </c>
-      <c r="B108" s="2" t="inlineStr">
-        <is>
-          <t>01/05/2026</t>
-        </is>
-      </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -8360,11 +8364,11 @@
         </is>
       </c>
       <c r="I108" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J108" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J108" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K108" s="2" t="inlineStr">
@@ -8394,12 +8398,12 @@
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
+          <t>03/05/2026</t>
+        </is>
+      </c>
+      <c r="B109" s="2" t="inlineStr">
+        <is>
           <t>02/05/2026</t>
-        </is>
-      </c>
-      <c r="B109" s="2" t="inlineStr">
-        <is>
-          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C109" s="2" t="inlineStr">
@@ -8435,9 +8439,9 @@
       <c r="I109" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J109" s="3" t="inlineStr">
-        <is>
-          <t>▼ 66,7%</t>
+      <c r="J109" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K109" s="2" t="inlineStr">
@@ -8467,12 +8471,12 @@
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
+          <t>02/05/2026</t>
+        </is>
+      </c>
+      <c r="B110" s="2" t="inlineStr">
+        <is>
           <t>01/05/2026</t>
-        </is>
-      </c>
-      <c r="B110" s="2" t="inlineStr">
-        <is>
-          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C110" s="2" t="inlineStr">
@@ -8510,7 +8514,7 @@
       </c>
       <c r="J110" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K110" s="2" t="inlineStr">
@@ -8540,14 +8544,14 @@
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
+          <t>02/05/2026</t>
+        </is>
+      </c>
+      <c r="B111" s="2" t="inlineStr">
+        <is>
           <t>01/05/2026</t>
         </is>
       </c>
-      <c r="B111" s="2" t="inlineStr">
-        <is>
-          <t>30/04/2026</t>
-        </is>
-      </c>
       <c r="C111" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -8579,11 +8583,11 @@
         </is>
       </c>
       <c r="I111" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J111" s="3" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K111" s="2" t="inlineStr">
@@ -8613,14 +8617,14 @@
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
+          <t>01/05/2026</t>
+        </is>
+      </c>
+      <c r="B112" s="2" t="inlineStr">
+        <is>
           <t>30/04/2026</t>
         </is>
       </c>
-      <c r="B112" s="2" t="inlineStr">
-        <is>
-          <t>29/04/2026</t>
-        </is>
-      </c>
       <c r="C112" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -8652,11 +8656,11 @@
         </is>
       </c>
       <c r="I112" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J112" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J112" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K112" s="2" t="inlineStr">
@@ -8686,14 +8690,14 @@
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
+          <t>01/05/2026</t>
+        </is>
+      </c>
+      <c r="B113" s="2" t="inlineStr">
+        <is>
           <t>30/04/2026</t>
         </is>
       </c>
-      <c r="B113" s="2" t="inlineStr">
-        <is>
-          <t>29/04/2026</t>
-        </is>
-      </c>
       <c r="C113" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -8725,11 +8729,11 @@
         </is>
       </c>
       <c r="I113" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J113" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>3</v>
+      </c>
+      <c r="J113" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K113" s="2" t="inlineStr">
@@ -8759,14 +8763,14 @@
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="B114" s="2" t="inlineStr">
+        <is>
           <t>29/04/2026</t>
         </is>
       </c>
-      <c r="B114" s="2" t="inlineStr">
-        <is>
-          <t>28/04/2026</t>
-        </is>
-      </c>
       <c r="C114" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -8798,11 +8802,11 @@
         </is>
       </c>
       <c r="I114" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J114" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J114" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K114" s="2" t="inlineStr">
@@ -8825,19 +8829,19 @@
       </c>
       <c r="O114" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="B115" s="2" t="inlineStr">
+        <is>
           <t>29/04/2026</t>
-        </is>
-      </c>
-      <c r="B115" s="2" t="inlineStr">
-        <is>
-          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C115" s="2" t="inlineStr">
@@ -8875,7 +8879,7 @@
       </c>
       <c r="J115" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K115" s="2" t="inlineStr">
@@ -8898,19 +8902,19 @@
       </c>
       <c r="O115" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
+          <t>29/04/2026</t>
+        </is>
+      </c>
+      <c r="B116" s="2" t="inlineStr">
+        <is>
           <t>28/04/2026</t>
-        </is>
-      </c>
-      <c r="B116" s="2" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C116" s="2" t="inlineStr">
@@ -8946,9 +8950,9 @@
       <c r="I116" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J116" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+      <c r="J116" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K116" s="2" t="inlineStr">
@@ -8978,14 +8982,14 @@
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
+          <t>29/04/2026</t>
+        </is>
+      </c>
+      <c r="B117" s="2" t="inlineStr">
+        <is>
           <t>28/04/2026</t>
         </is>
       </c>
-      <c r="B117" s="2" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
-        </is>
-      </c>
       <c r="C117" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -9017,11 +9021,11 @@
         </is>
       </c>
       <c r="I117" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J117" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>6</v>
+      </c>
+      <c r="J117" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K117" s="2" t="inlineStr">
@@ -9051,14 +9055,14 @@
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
+          <t>28/04/2026</t>
+        </is>
+      </c>
+      <c r="B118" s="2" t="inlineStr">
+        <is>
           <t>27/04/2026</t>
         </is>
       </c>
-      <c r="B118" s="2" t="inlineStr">
-        <is>
-          <t>26/04/2026</t>
-        </is>
-      </c>
       <c r="C118" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -9090,11 +9094,11 @@
         </is>
       </c>
       <c r="I118" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J118" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>1</v>
+      </c>
+      <c r="J118" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K118" s="2" t="inlineStr">
@@ -9124,14 +9128,14 @@
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
+          <t>28/04/2026</t>
+        </is>
+      </c>
+      <c r="B119" s="2" t="inlineStr">
+        <is>
           <t>27/04/2026</t>
         </is>
       </c>
-      <c r="B119" s="2" t="inlineStr">
-        <is>
-          <t>26/04/2026</t>
-        </is>
-      </c>
       <c r="C119" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -9163,11 +9167,11 @@
         </is>
       </c>
       <c r="I119" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J119" s="3" t="inlineStr">
         <is>
-          <t>▼ 66,7%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K119" s="2" t="inlineStr">
@@ -9197,12 +9201,12 @@
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B120" s="2" t="inlineStr">
+        <is>
           <t>26/04/2026</t>
-        </is>
-      </c>
-      <c r="B120" s="2" t="inlineStr">
-        <is>
-          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C120" s="2" t="inlineStr">
@@ -9270,14 +9274,14 @@
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B121" s="2" t="inlineStr">
+        <is>
           <t>26/04/2026</t>
         </is>
       </c>
-      <c r="B121" s="2" t="inlineStr">
-        <is>
-          <t>25/04/2026</t>
-        </is>
-      </c>
       <c r="C121" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -9309,11 +9313,11 @@
         </is>
       </c>
       <c r="I121" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J121" s="4" t="inlineStr">
-        <is>
-          <t>▲ 200,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J121" s="3" t="inlineStr">
+        <is>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K121" s="2" t="inlineStr">
@@ -9343,12 +9347,12 @@
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
+          <t>26/04/2026</t>
+        </is>
+      </c>
+      <c r="B122" s="2" t="inlineStr">
+        <is>
           <t>25/04/2026</t>
-        </is>
-      </c>
-      <c r="B122" s="2" t="inlineStr">
-        <is>
-          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C122" s="2" t="inlineStr">
@@ -9384,9 +9388,9 @@
       <c r="I122" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="J122" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+      <c r="J122" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K122" s="2" t="inlineStr">
@@ -9416,14 +9420,14 @@
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
+          <t>26/04/2026</t>
+        </is>
+      </c>
+      <c r="B123" s="2" t="inlineStr">
+        <is>
           <t>25/04/2026</t>
         </is>
       </c>
-      <c r="B123" s="2" t="inlineStr">
-        <is>
-          <t>24/04/2026</t>
-        </is>
-      </c>
       <c r="C123" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -9455,11 +9459,11 @@
         </is>
       </c>
       <c r="I123" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J123" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>3</v>
+      </c>
+      <c r="J123" s="4" t="inlineStr">
+        <is>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="K123" s="2" t="inlineStr">
@@ -9489,14 +9493,14 @@
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
+          <t>25/04/2026</t>
+        </is>
+      </c>
+      <c r="B124" s="2" t="inlineStr">
+        <is>
           <t>24/04/2026</t>
         </is>
       </c>
-      <c r="B124" s="2" t="inlineStr">
-        <is>
-          <t>23/04/2026</t>
-        </is>
-      </c>
       <c r="C124" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -9528,11 +9532,11 @@
         </is>
       </c>
       <c r="I124" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J124" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J124" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K124" s="2" t="inlineStr">
@@ -9562,14 +9566,14 @@
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
+          <t>25/04/2026</t>
+        </is>
+      </c>
+      <c r="B125" s="2" t="inlineStr">
+        <is>
           <t>24/04/2026</t>
         </is>
       </c>
-      <c r="B125" s="2" t="inlineStr">
-        <is>
-          <t>23/04/2026</t>
-        </is>
-      </c>
       <c r="C125" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -9592,7 +9596,7 @@
       </c>
       <c r="G125" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H125" s="2" t="inlineStr">
@@ -9600,10 +9604,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I125" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I125" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J125" s="2" t="inlineStr">
         <is>
@@ -9612,41 +9614,39 @@
       </c>
       <c r="K125" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L125" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L125" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M125" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N125" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O125" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
+          <t>24/04/2026</t>
+        </is>
+      </c>
+      <c r="B126" s="2" t="inlineStr">
+        <is>
           <t>23/04/2026</t>
         </is>
       </c>
-      <c r="B126" s="2" t="inlineStr">
-        <is>
-          <t>22/04/2026</t>
-        </is>
-      </c>
       <c r="C126" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -9678,11 +9678,11 @@
         </is>
       </c>
       <c r="I126" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J126" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J126" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K126" s="2" t="inlineStr">
@@ -9712,12 +9712,12 @@
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
+          <t>24/04/2026</t>
+        </is>
+      </c>
+      <c r="B127" s="2" t="inlineStr">
+        <is>
           <t>23/04/2026</t>
-        </is>
-      </c>
-      <c r="B127" s="2" t="inlineStr">
-        <is>
-          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C127" s="2" t="inlineStr">
@@ -9789,14 +9789,14 @@
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
+          <t>23/04/2026</t>
+        </is>
+      </c>
+      <c r="B128" s="2" t="inlineStr">
+        <is>
           <t>22/04/2026</t>
         </is>
       </c>
-      <c r="B128" s="2" t="inlineStr">
-        <is>
-          <t>21/04/2026</t>
-        </is>
-      </c>
       <c r="C128" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -9828,11 +9828,11 @@
         </is>
       </c>
       <c r="I128" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J128" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J128" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K128" s="2" t="inlineStr">
@@ -9862,14 +9862,14 @@
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
         <is>
+          <t>23/04/2026</t>
+        </is>
+      </c>
+      <c r="B129" s="2" t="inlineStr">
+        <is>
           <t>22/04/2026</t>
         </is>
       </c>
-      <c r="B129" s="2" t="inlineStr">
-        <is>
-          <t>21/04/2026</t>
-        </is>
-      </c>
       <c r="C129" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -9892,7 +9892,7 @@
       </c>
       <c r="G129" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H129" s="2" t="inlineStr">
@@ -9900,8 +9900,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I129" s="2" t="n">
-        <v>0</v>
+      <c r="I129" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J129" s="2" t="inlineStr">
         <is>
@@ -9910,39 +9912,41 @@
       </c>
       <c r="K129" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L129" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L129" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M129" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N129" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O129" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
         <is>
+          <t>22/04/2026</t>
+        </is>
+      </c>
+      <c r="B130" s="2" t="inlineStr">
+        <is>
           <t>21/04/2026</t>
         </is>
       </c>
-      <c r="B130" s="2" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
-        </is>
-      </c>
       <c r="C130" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -9974,11 +9978,11 @@
         </is>
       </c>
       <c r="I130" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J130" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>1</v>
+      </c>
+      <c r="J130" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K130" s="2" t="inlineStr">
@@ -9996,7 +10000,7 @@
       </c>
       <c r="N130" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O130" s="2" t="inlineStr">
@@ -10008,14 +10012,14 @@
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
         <is>
+          <t>22/04/2026</t>
+        </is>
+      </c>
+      <c r="B131" s="2" t="inlineStr">
+        <is>
           <t>21/04/2026</t>
         </is>
       </c>
-      <c r="B131" s="2" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
-        </is>
-      </c>
       <c r="C131" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -10049,9 +10053,9 @@
       <c r="I131" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J131" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J131" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K131" s="2" t="inlineStr">
@@ -10081,14 +10085,14 @@
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
         <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="B132" s="2" t="inlineStr">
+        <is>
           <t>20/04/2026</t>
         </is>
       </c>
-      <c r="B132" s="2" t="inlineStr">
-        <is>
-          <t>19/04/2026</t>
-        </is>
-      </c>
       <c r="C132" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -10120,7 +10124,7 @@
         </is>
       </c>
       <c r="I132" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J132" s="2" t="inlineStr">
         <is>
@@ -10142,7 +10146,7 @@
       </c>
       <c r="N132" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O132" s="2" t="inlineStr">
@@ -10154,14 +10158,14 @@
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
         <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="B133" s="2" t="inlineStr">
+        <is>
           <t>20/04/2026</t>
         </is>
       </c>
-      <c r="B133" s="2" t="inlineStr">
-        <is>
-          <t>19/04/2026</t>
-        </is>
-      </c>
       <c r="C133" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -10193,11 +10197,11 @@
         </is>
       </c>
       <c r="I133" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J133" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J133" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K133" s="2" t="inlineStr">
@@ -10227,12 +10231,12 @@
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
         <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="B134" s="2" t="inlineStr">
+        <is>
           <t>19/04/2026</t>
-        </is>
-      </c>
-      <c r="B134" s="2" t="inlineStr">
-        <is>
-          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C134" s="2" t="inlineStr">
@@ -10300,14 +10304,14 @@
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
         <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="B135" s="2" t="inlineStr">
+        <is>
           <t>19/04/2026</t>
         </is>
       </c>
-      <c r="B135" s="2" t="inlineStr">
-        <is>
-          <t>18/04/2026</t>
-        </is>
-      </c>
       <c r="C135" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -10339,11 +10343,11 @@
         </is>
       </c>
       <c r="I135" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J135" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>4</v>
+      </c>
+      <c r="J135" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K135" s="2" t="inlineStr">
@@ -10373,12 +10377,12 @@
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
         <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="B136" s="2" t="inlineStr">
+        <is>
           <t>18/04/2026</t>
-        </is>
-      </c>
-      <c r="B136" s="2" t="inlineStr">
-        <is>
-          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C136" s="2" t="inlineStr">
@@ -10446,14 +10450,14 @@
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
         <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="B137" s="2" t="inlineStr">
+        <is>
           <t>18/04/2026</t>
         </is>
       </c>
-      <c r="B137" s="2" t="inlineStr">
-        <is>
-          <t>17/04/2026</t>
-        </is>
-      </c>
       <c r="C137" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -10485,7 +10489,7 @@
         </is>
       </c>
       <c r="I137" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J137" s="2" t="inlineStr">
         <is>
@@ -10519,14 +10523,14 @@
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
         <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="B138" s="2" t="inlineStr">
+        <is>
           <t>17/04/2026</t>
         </is>
       </c>
-      <c r="B138" s="2" t="inlineStr">
-        <is>
-          <t>16/04/2026</t>
-        </is>
-      </c>
       <c r="C138" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -10560,9 +10564,9 @@
       <c r="I138" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J138" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J138" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K138" s="2" t="inlineStr">
@@ -10592,14 +10596,14 @@
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
         <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="B139" s="2" t="inlineStr">
+        <is>
           <t>17/04/2026</t>
         </is>
       </c>
-      <c r="B139" s="2" t="inlineStr">
-        <is>
-          <t>16/04/2026</t>
-        </is>
-      </c>
       <c r="C139" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -10633,9 +10637,9 @@
       <c r="I139" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J139" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J139" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K139" s="2" t="inlineStr">
@@ -10665,14 +10669,14 @@
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
         <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="B140" s="2" t="inlineStr">
+        <is>
           <t>16/04/2026</t>
         </is>
       </c>
-      <c r="B140" s="2" t="inlineStr">
-        <is>
-          <t>15/04/2026</t>
-        </is>
-      </c>
       <c r="C140" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -10704,11 +10708,11 @@
         </is>
       </c>
       <c r="I140" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J140" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J140" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K140" s="2" t="inlineStr">
@@ -10738,14 +10742,14 @@
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
         <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="B141" s="2" t="inlineStr">
+        <is>
           <t>16/04/2026</t>
         </is>
       </c>
-      <c r="B141" s="2" t="inlineStr">
-        <is>
-          <t>15/04/2026</t>
-        </is>
-      </c>
       <c r="C141" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -10777,11 +10781,11 @@
         </is>
       </c>
       <c r="I141" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J141" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J141" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K141" s="2" t="inlineStr">
@@ -10811,14 +10815,14 @@
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
         <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="B142" s="2" t="inlineStr">
+        <is>
           <t>15/04/2026</t>
         </is>
       </c>
-      <c r="B142" s="2" t="inlineStr">
-        <is>
-          <t>14/04/2026</t>
-        </is>
-      </c>
       <c r="C142" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -10850,11 +10854,11 @@
         </is>
       </c>
       <c r="I142" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J142" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J142" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K142" s="2" t="inlineStr">
@@ -10884,12 +10888,12 @@
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
         <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="B143" s="2" t="inlineStr">
+        <is>
           <t>15/04/2026</t>
-        </is>
-      </c>
-      <c r="B143" s="2" t="inlineStr">
-        <is>
-          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C143" s="2" t="inlineStr">
@@ -10957,14 +10961,14 @@
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
         <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="B144" s="2" t="inlineStr">
+        <is>
           <t>14/04/2026</t>
         </is>
       </c>
-      <c r="B144" s="2" t="inlineStr">
-        <is>
-          <t>13/04/2026</t>
-        </is>
-      </c>
       <c r="C144" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -10996,11 +11000,11 @@
         </is>
       </c>
       <c r="I144" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J144" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J144" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K144" s="2" t="inlineStr">
@@ -11030,12 +11034,12 @@
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
         <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="B145" s="2" t="inlineStr">
+        <is>
           <t>14/04/2026</t>
-        </is>
-      </c>
-      <c r="B145" s="2" t="inlineStr">
-        <is>
-          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C145" s="2" t="inlineStr">
@@ -11103,12 +11107,12 @@
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
         <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="B146" s="2" t="inlineStr">
+        <is>
           <t>13/04/2026</t>
-        </is>
-      </c>
-      <c r="B146" s="2" t="inlineStr">
-        <is>
-          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C146" s="2" t="inlineStr">
@@ -11176,12 +11180,12 @@
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
         <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="B147" s="2" t="inlineStr">
+        <is>
           <t>13/04/2026</t>
-        </is>
-      </c>
-      <c r="B147" s="2" t="inlineStr">
-        <is>
-          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C147" s="2" t="inlineStr">
@@ -11249,12 +11253,12 @@
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
         <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="B148" s="2" t="inlineStr">
+        <is>
           <t>12/04/2026</t>
-        </is>
-      </c>
-      <c r="B148" s="2" t="inlineStr">
-        <is>
-          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C148" s="2" t="inlineStr">
@@ -11290,9 +11294,9 @@
       <c r="I148" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="J148" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+      <c r="J148" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K148" s="2" t="inlineStr">
@@ -11322,12 +11326,12 @@
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
         <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="B149" s="2" t="inlineStr">
+        <is>
           <t>12/04/2026</t>
-        </is>
-      </c>
-      <c r="B149" s="2" t="inlineStr">
-        <is>
-          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C149" s="2" t="inlineStr">
@@ -11365,7 +11369,7 @@
       </c>
       <c r="J149" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K149" s="2" t="inlineStr">
@@ -11395,14 +11399,14 @@
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
         <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B150" s="2" t="inlineStr">
+        <is>
           <t>11/04/2026</t>
         </is>
       </c>
-      <c r="B150" s="2" t="inlineStr">
-        <is>
-          <t>10/04/2026</t>
-        </is>
-      </c>
       <c r="C150" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -11434,11 +11438,11 @@
         </is>
       </c>
       <c r="I150" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J150" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J150" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K150" s="2" t="inlineStr">
@@ -11468,14 +11472,14 @@
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
         <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B151" s="2" t="inlineStr">
+        <is>
           <t>11/04/2026</t>
         </is>
       </c>
-      <c r="B151" s="2" t="inlineStr">
-        <is>
-          <t>10/04/2026</t>
-        </is>
-      </c>
       <c r="C151" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -11507,11 +11511,11 @@
         </is>
       </c>
       <c r="I151" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J151" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J151" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K151" s="2" t="inlineStr">
@@ -11541,14 +11545,14 @@
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
         <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="B152" s="2" t="inlineStr">
+        <is>
           <t>10/04/2026</t>
         </is>
       </c>
-      <c r="B152" s="2" t="inlineStr">
-        <is>
-          <t>09/04/2026</t>
-        </is>
-      </c>
       <c r="C152" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -11580,11 +11584,11 @@
         </is>
       </c>
       <c r="I152" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J152" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>1</v>
+      </c>
+      <c r="J152" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K152" s="2" t="inlineStr">
@@ -11614,14 +11618,14 @@
     <row r="153">
       <c r="A153" s="2" t="inlineStr">
         <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="B153" s="2" t="inlineStr">
+        <is>
           <t>10/04/2026</t>
         </is>
       </c>
-      <c r="B153" s="2" t="inlineStr">
-        <is>
-          <t>09/04/2026</t>
-        </is>
-      </c>
       <c r="C153" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -11653,11 +11657,11 @@
         </is>
       </c>
       <c r="I153" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J153" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J153" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K153" s="2" t="inlineStr">
@@ -11687,12 +11691,12 @@
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
         <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B154" s="2" t="inlineStr">
+        <is>
           <t>09/04/2026</t>
-        </is>
-      </c>
-      <c r="B154" s="2" t="inlineStr">
-        <is>
-          <t>08/04/2026</t>
         </is>
       </c>
       <c r="C154" s="2" t="inlineStr">
@@ -11728,9 +11732,9 @@
       <c r="I154" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="J154" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+      <c r="J154" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K154" s="2" t="inlineStr">
@@ -11760,14 +11764,14 @@
     <row r="155">
       <c r="A155" s="2" t="inlineStr">
         <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B155" s="2" t="inlineStr">
+        <is>
           <t>09/04/2026</t>
         </is>
       </c>
-      <c r="B155" s="2" t="inlineStr">
-        <is>
-          <t>08/04/2026</t>
-        </is>
-      </c>
       <c r="C155" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -11799,7 +11803,7 @@
         </is>
       </c>
       <c r="I155" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J155" s="2" t="inlineStr">
         <is>
@@ -11833,14 +11837,14 @@
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
         <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="B156" s="2" t="inlineStr">
+        <is>
           <t>08/04/2026</t>
         </is>
       </c>
-      <c r="B156" s="2" t="inlineStr">
-        <is>
-          <t>07/04/2026</t>
-        </is>
-      </c>
       <c r="C156" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -11866,17 +11870,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H156" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H156" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I156" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J156" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>2</v>
+      </c>
+      <c r="J156" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K156" s="2" t="inlineStr">
@@ -11906,14 +11910,14 @@
     <row r="157">
       <c r="A157" s="2" t="inlineStr">
         <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="B157" s="2" t="inlineStr">
+        <is>
           <t>08/04/2026</t>
         </is>
       </c>
-      <c r="B157" s="2" t="inlineStr">
-        <is>
-          <t>07/04/2026</t>
-        </is>
-      </c>
       <c r="C157" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -11947,9 +11951,9 @@
       <c r="I157" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J157" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J157" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K157" s="2" t="inlineStr">
@@ -11979,14 +11983,14 @@
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
         <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="B158" s="2" t="inlineStr">
+        <is>
           <t>07/04/2026</t>
         </is>
       </c>
-      <c r="B158" s="2" t="inlineStr">
-        <is>
-          <t>06/04/2026</t>
-        </is>
-      </c>
       <c r="C158" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -12009,38 +12013,38 @@
       </c>
       <c r="G158" s="2" t="inlineStr">
         <is>
-          <t>R$ 110,00</t>
-        </is>
-      </c>
-      <c r="H158" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H158" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I158" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J158" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+      <c r="J158" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K158" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L158" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M158" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N158" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O158" s="2" t="inlineStr">
@@ -12052,14 +12056,14 @@
     <row r="159">
       <c r="A159" s="2" t="inlineStr">
         <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="B159" s="2" t="inlineStr">
+        <is>
           <t>07/04/2026</t>
         </is>
       </c>
-      <c r="B159" s="2" t="inlineStr">
-        <is>
-          <t>06/04/2026</t>
-        </is>
-      </c>
       <c r="C159" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -12091,11 +12095,11 @@
         </is>
       </c>
       <c r="I159" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J159" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J159" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K159" s="2" t="inlineStr">
@@ -12125,14 +12129,14 @@
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
         <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="B160" s="2" t="inlineStr">
+        <is>
           <t>06/04/2026</t>
         </is>
       </c>
-      <c r="B160" s="2" t="inlineStr">
-        <is>
-          <t>05/04/2026</t>
-        </is>
-      </c>
       <c r="C160" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -12160,20 +12164,20 @@
       </c>
       <c r="H160" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I160" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J160" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J160" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K160" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="L160" s="2" t="n">
@@ -12181,12 +12185,12 @@
       </c>
       <c r="M160" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="N160" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O160" s="2" t="inlineStr">
@@ -12198,14 +12202,14 @@
     <row r="161">
       <c r="A161" s="2" t="inlineStr">
         <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="B161" s="2" t="inlineStr">
+        <is>
           <t>06/04/2026</t>
         </is>
       </c>
-      <c r="B161" s="2" t="inlineStr">
-        <is>
-          <t>05/04/2026</t>
-        </is>
-      </c>
       <c r="C161" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -12237,7 +12241,7 @@
         </is>
       </c>
       <c r="I161" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J161" s="2" t="inlineStr">
         <is>
@@ -12271,14 +12275,14 @@
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
         <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="B162" s="2" t="inlineStr">
+        <is>
           <t>05/04/2026</t>
         </is>
       </c>
-      <c r="B162" s="2" t="inlineStr">
-        <is>
-          <t>04/04/2026</t>
-        </is>
-      </c>
       <c r="C162" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -12301,7 +12305,7 @@
       </c>
       <c r="G162" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 110,00</t>
         </is>
       </c>
       <c r="H162" s="2" t="inlineStr">
@@ -12310,24 +12314,24 @@
         </is>
       </c>
       <c r="I162" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J162" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
+        </is>
+      </c>
+      <c r="K162" s="2" t="inlineStr">
+        <is>
+          <t>50,0%</t>
+        </is>
+      </c>
+      <c r="L162" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J162" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K162" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L162" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="M162" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="N162" s="2" t="inlineStr">
@@ -12344,14 +12348,14 @@
     <row r="163">
       <c r="A163" s="2" t="inlineStr">
         <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="B163" s="2" t="inlineStr">
+        <is>
           <t>05/04/2026</t>
         </is>
       </c>
-      <c r="B163" s="2" t="inlineStr">
-        <is>
-          <t>04/04/2026</t>
-        </is>
-      </c>
       <c r="C163" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -12385,9 +12389,9 @@
       <c r="I163" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J163" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J163" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K163" s="2" t="inlineStr">
@@ -12417,14 +12421,14 @@
     <row r="164">
       <c r="A164" s="2" t="inlineStr">
         <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B164" s="2" t="inlineStr">
+        <is>
           <t>04/04/2026</t>
         </is>
       </c>
-      <c r="B164" s="2" t="inlineStr">
-        <is>
-          <t>03/04/2026</t>
-        </is>
-      </c>
       <c r="C164" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -12456,7 +12460,7 @@
         </is>
       </c>
       <c r="I164" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J164" s="2" t="inlineStr">
         <is>
@@ -12490,14 +12494,14 @@
     <row r="165">
       <c r="A165" s="2" t="inlineStr">
         <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B165" s="2" t="inlineStr">
+        <is>
           <t>04/04/2026</t>
         </is>
       </c>
-      <c r="B165" s="2" t="inlineStr">
-        <is>
-          <t>03/04/2026</t>
-        </is>
-      </c>
       <c r="C165" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -12529,11 +12533,11 @@
         </is>
       </c>
       <c r="I165" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J165" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J165" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K165" s="2" t="inlineStr">
@@ -12563,14 +12567,14 @@
     <row r="166">
       <c r="A166" s="2" t="inlineStr">
         <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B166" s="2" t="inlineStr">
+        <is>
           <t>03/04/2026</t>
         </is>
       </c>
-      <c r="B166" s="2" t="inlineStr">
-        <is>
-          <t>02/04/2026</t>
-        </is>
-      </c>
       <c r="C166" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -12604,9 +12608,9 @@
       <c r="I166" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J166" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J166" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K166" s="2" t="inlineStr">
@@ -12636,14 +12640,14 @@
     <row r="167">
       <c r="A167" s="2" t="inlineStr">
         <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B167" s="2" t="inlineStr">
+        <is>
           <t>03/04/2026</t>
         </is>
       </c>
-      <c r="B167" s="2" t="inlineStr">
-        <is>
-          <t>02/04/2026</t>
-        </is>
-      </c>
       <c r="C167" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -12675,11 +12679,11 @@
         </is>
       </c>
       <c r="I167" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J167" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J167" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K167" s="2" t="inlineStr">
@@ -12709,14 +12713,14 @@
     <row r="168">
       <c r="A168" s="2" t="inlineStr">
         <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B168" s="2" t="inlineStr">
+        <is>
           <t>02/04/2026</t>
         </is>
       </c>
-      <c r="B168" s="2" t="inlineStr">
-        <is>
-          <t>01/04/2026</t>
-        </is>
-      </c>
       <c r="C168" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -12748,11 +12752,11 @@
         </is>
       </c>
       <c r="I168" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J168" s="3" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K168" s="2" t="inlineStr">
@@ -12782,14 +12786,14 @@
     <row r="169">
       <c r="A169" s="2" t="inlineStr">
         <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B169" s="2" t="inlineStr">
+        <is>
           <t>02/04/2026</t>
         </is>
       </c>
-      <c r="B169" s="2" t="inlineStr">
-        <is>
-          <t>01/04/2026</t>
-        </is>
-      </c>
       <c r="C169" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -12821,11 +12825,11 @@
         </is>
       </c>
       <c r="I169" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J169" s="3" t="inlineStr">
         <is>
-          <t>▼ 66,7%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K169" s="2" t="inlineStr">
@@ -12855,14 +12859,14 @@
     <row r="170">
       <c r="A170" s="2" t="inlineStr">
         <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B170" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B170" s="2" t="inlineStr">
-        <is>
-          <t>31/03/2026</t>
-        </is>
-      </c>
       <c r="C170" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -12894,11 +12898,11 @@
         </is>
       </c>
       <c r="I170" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J170" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>1</v>
+      </c>
+      <c r="J170" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K170" s="2" t="inlineStr">
@@ -12928,78 +12932,224 @@
     <row r="171">
       <c r="A171" s="2" t="inlineStr">
         <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B171" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B171" s="2" t="inlineStr">
+      <c r="C171" s="2" t="inlineStr">
+        <is>
+          <t>UTD-145</t>
+        </is>
+      </c>
+      <c r="D171" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor duplo com bica arthi</t>
+        </is>
+      </c>
+      <c r="E171" s="2" t="inlineStr">
+        <is>
+          <t>4498058823</t>
+        </is>
+      </c>
+      <c r="F171" s="2" t="inlineStr">
+        <is>
+          <t>R$ 157,65</t>
+        </is>
+      </c>
+      <c r="G171" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H171" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I171" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J171" s="3" t="inlineStr">
+        <is>
+          <t>▼ 66,7%</t>
+        </is>
+      </c>
+      <c r="K171" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L171" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M171" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N171" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O171" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B172" s="2" t="inlineStr">
         <is>
           <t>31/03/2026</t>
         </is>
       </c>
-      <c r="C171" s="2" t="inlineStr">
-        <is>
-          <t>UTD-145</t>
-        </is>
-      </c>
-      <c r="D171" s="2" t="inlineStr">
-        <is>
-          <t>Escorredor duplo com bica arthi</t>
-        </is>
-      </c>
-      <c r="E171" s="2" t="inlineStr">
+      <c r="C172" s="2" t="inlineStr">
+        <is>
+          <t>UTD-145</t>
+        </is>
+      </c>
+      <c r="D172" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor duplo com bica arthi</t>
+        </is>
+      </c>
+      <c r="E172" s="2" t="inlineStr">
+        <is>
+          <t>4645710434</t>
+        </is>
+      </c>
+      <c r="F172" s="2" t="inlineStr">
+        <is>
+          <t>R$ 157,65</t>
+        </is>
+      </c>
+      <c r="G172" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H172" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I172" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J172" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K172" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L172" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M172" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N172" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O172" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B173" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C173" s="2" t="inlineStr">
+        <is>
+          <t>UTD-145</t>
+        </is>
+      </c>
+      <c r="D173" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor duplo com bica arthi</t>
+        </is>
+      </c>
+      <c r="E173" s="2" t="inlineStr">
         <is>
           <t>4498058823</t>
         </is>
       </c>
-      <c r="F171" s="2" t="inlineStr">
-        <is>
-          <t>R$ 157,65</t>
-        </is>
-      </c>
-      <c r="G171" s="2" t="inlineStr">
-        <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H171" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I171" s="2" t="n">
+      <c r="F173" s="2" t="inlineStr">
+        <is>
+          <t>R$ 157,65</t>
+        </is>
+      </c>
+      <c r="G173" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H173" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I173" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="J171" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K171" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L171" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M171" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="N171" s="2" t="inlineStr">
+      <c r="J173" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K173" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L173" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M173" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N173" s="2" t="inlineStr">
         <is>
           <t>Sem calcular</t>
         </is>
       </c>
-      <c r="O171" s="2" t="inlineStr">
+      <c r="O173" s="2" t="inlineStr">
         <is>
           <t>Média</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O171"/>
+  <autoFilter ref="A1:O173"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/saida_skus/SKU_UTD-145-ESCORREDOR-DUPLO-COM-BICA-ARTHI.xlsx
+++ b/saida_skus/SKU_UTD-145-ESCORREDOR-DUPLO-COM-BICA-ARTHI.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Analise" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$173</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$175</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O173"/>
+  <dimension ref="A1:O175"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -559,14 +559,14 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
+          <t>26/06/2026</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
           <t>25/06/2026</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>24/06/2026</t>
-        </is>
-      </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -589,7 +589,7 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -597,10 +597,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I2" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I2" s="2" t="n">
+        <v>7</v>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
@@ -609,41 +607,39 @@
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L2" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
+          <t>26/06/2026</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
           <t>25/06/2026</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>24/06/2026</t>
-        </is>
-      </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -666,7 +662,7 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
@@ -674,8 +670,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I3" s="2" t="n">
-        <v>0</v>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
@@ -684,39 +682,41 @@
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L3" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
           <t>24/06/2026</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>23/06/2026</t>
-        </is>
-      </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -739,7 +739,7 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -747,8 +747,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I4" s="2" t="n">
-        <v>0</v>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
@@ -757,39 +759,41 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
           <t>24/06/2026</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>23/06/2026</t>
-        </is>
-      </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -823,9 +827,9 @@
       <c r="I5" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J5" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -855,12 +859,12 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
+          <t>24/06/2026</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
           <t>23/06/2026</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>22/06/2026</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -928,14 +932,14 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
+          <t>24/06/2026</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
           <t>23/06/2026</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>22/06/2026</t>
-        </is>
-      </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -967,11 +971,11 @@
         </is>
       </c>
       <c r="I7" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -1001,14 +1005,14 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
+          <t>23/06/2026</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
           <t>22/06/2026</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>21/06/2026</t>
-        </is>
-      </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -1042,9 +1046,9 @@
       <c r="I8" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J8" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1074,14 +1078,14 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
+          <t>23/06/2026</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
           <t>22/06/2026</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>21/06/2026</t>
-        </is>
-      </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -1113,11 +1117,11 @@
         </is>
       </c>
       <c r="I9" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>1</v>
+      </c>
+      <c r="J9" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -1147,14 +1151,14 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
           <t>21/06/2026</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>20/06/2026</t>
-        </is>
-      </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -1186,11 +1190,11 @@
         </is>
       </c>
       <c r="I10" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J10" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1220,12 +1224,12 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
           <t>21/06/2026</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>20/06/2026</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -1263,7 +1267,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1293,14 +1297,14 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
+          <t>21/06/2026</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
           <t>20/06/2026</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>19/06/2026</t>
-        </is>
-      </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -1323,7 +1327,7 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -1331,10 +1335,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I12" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
@@ -1343,41 +1345,39 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
+          <t>21/06/2026</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
           <t>20/06/2026</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>19/06/2026</t>
-        </is>
-      </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -1409,7 +1409,7 @@
         </is>
       </c>
       <c r="I13" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
@@ -1443,14 +1443,14 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
+          <t>20/06/2026</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
           <t>19/06/2026</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>18/06/2026</t>
-        </is>
-      </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -1473,7 +1473,7 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -1481,8 +1481,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I14" s="2" t="n">
-        <v>0</v>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
@@ -1491,39 +1493,41 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
+          <t>20/06/2026</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
           <t>19/06/2026</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>18/06/2026</t>
-        </is>
-      </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -1557,9 +1561,9 @@
       <c r="I15" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J15" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -1589,14 +1593,14 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
+          <t>19/06/2026</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
           <t>18/06/2026</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>17/06/2026</t>
-        </is>
-      </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -1619,7 +1623,7 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -1627,10 +1631,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I16" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
@@ -1639,41 +1641,39 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
+          <t>19/06/2026</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
           <t>18/06/2026</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>17/06/2026</t>
-        </is>
-      </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -1705,11 +1705,11 @@
         </is>
       </c>
       <c r="I17" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J17" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -1739,14 +1739,14 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
+          <t>18/06/2026</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
           <t>17/06/2026</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>16/06/2026</t>
-        </is>
-      </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -1769,7 +1769,7 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
@@ -1777,8 +1777,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I18" s="2" t="n">
-        <v>0</v>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
@@ -1787,37 +1789,39 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
+          <t>18/06/2026</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
           <t>17/06/2026</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>16/06/2026</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -1885,14 +1889,14 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
+          <t>17/06/2026</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
           <t>16/06/2026</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>15/06/2026</t>
-        </is>
-      </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -1926,9 +1930,9 @@
       <c r="I20" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J20" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1958,12 +1962,12 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
+          <t>17/06/2026</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
           <t>16/06/2026</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>15/06/2026</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -2031,14 +2035,14 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
+          <t>16/06/2026</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
           <t>15/06/2026</t>
         </is>
       </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>14/06/2026</t>
-        </is>
-      </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -2070,11 +2074,11 @@
         </is>
       </c>
       <c r="I22" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J22" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
@@ -2104,12 +2108,12 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
+          <t>16/06/2026</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
           <t>15/06/2026</t>
-        </is>
-      </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>14/06/2026</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -2177,12 +2181,12 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
+          <t>15/06/2026</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
           <t>14/06/2026</t>
-        </is>
-      </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>13/06/2026</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -2250,12 +2254,12 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
+          <t>15/06/2026</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
           <t>14/06/2026</t>
-        </is>
-      </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>13/06/2026</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -2291,9 +2295,9 @@
       <c r="I25" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J25" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
@@ -2323,12 +2327,12 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
+          <t>14/06/2026</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
           <t>13/06/2026</t>
-        </is>
-      </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>12/06/2026</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -2396,14 +2400,14 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
+          <t>14/06/2026</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
           <t>13/06/2026</t>
         </is>
       </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>12/06/2026</t>
-        </is>
-      </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -2435,11 +2439,11 @@
         </is>
       </c>
       <c r="I27" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>1</v>
+      </c>
+      <c r="J27" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
@@ -2469,12 +2473,12 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
+          <t>13/06/2026</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
           <t>12/06/2026</t>
-        </is>
-      </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>11/06/2026</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -2542,14 +2546,14 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
+          <t>13/06/2026</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
           <t>12/06/2026</t>
         </is>
       </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>11/06/2026</t>
-        </is>
-      </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -2581,7 +2585,7 @@
         </is>
       </c>
       <c r="I29" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
@@ -2615,12 +2619,12 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
+          <t>12/06/2026</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
           <t>11/06/2026</t>
-        </is>
-      </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>10/06/2026</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -2656,9 +2660,9 @@
       <c r="I30" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J30" s="3" t="inlineStr">
-        <is>
-          <t>▼ 66,7%</t>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
@@ -2688,12 +2692,12 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
+          <t>12/06/2026</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
           <t>11/06/2026</t>
-        </is>
-      </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>10/06/2026</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -2761,14 +2765,14 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
+          <t>11/06/2026</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
           <t>10/06/2026</t>
         </is>
       </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>09/06/2026</t>
-        </is>
-      </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -2800,11 +2804,11 @@
         </is>
       </c>
       <c r="I32" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J32" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>1</v>
+      </c>
+      <c r="J32" s="3" t="inlineStr">
+        <is>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
@@ -2834,14 +2838,14 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
+          <t>11/06/2026</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
           <t>10/06/2026</t>
         </is>
       </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>09/06/2026</t>
-        </is>
-      </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -2867,17 +2871,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H33" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I33" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J33" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
@@ -2907,14 +2911,14 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
+          <t>10/06/2026</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
           <t>09/06/2026</t>
         </is>
       </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>08/06/2026</t>
-        </is>
-      </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -2946,11 +2950,11 @@
         </is>
       </c>
       <c r="I34" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J34" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>3</v>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
@@ -2980,14 +2984,14 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
+          <t>10/06/2026</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
           <t>09/06/2026</t>
         </is>
       </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>08/06/2026</t>
-        </is>
-      </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -3010,33 +3014,33 @@
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>R$ 107,00</t>
-        </is>
-      </c>
-      <c r="H35" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H35" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I35" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J35" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J35" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L35" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -3053,14 +3057,14 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
+          <t>09/06/2026</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
           <t>08/06/2026</t>
         </is>
       </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>07/06/2026</t>
-        </is>
-      </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -3092,11 +3096,11 @@
         </is>
       </c>
       <c r="I36" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J36" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J36" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
@@ -3126,14 +3130,14 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
+          <t>09/06/2026</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
           <t>08/06/2026</t>
         </is>
       </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>07/06/2026</t>
-        </is>
-      </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -3156,7 +3160,7 @@
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 107,00</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
@@ -3165,24 +3169,24 @@
         </is>
       </c>
       <c r="I37" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J37" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
+        </is>
+      </c>
+      <c r="K37" s="2" t="inlineStr">
+        <is>
+          <t>50,0%</t>
+        </is>
+      </c>
+      <c r="L37" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J37" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K37" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L37" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -3199,14 +3203,14 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
           <t>07/06/2026</t>
         </is>
       </c>
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>06/06/2026</t>
-        </is>
-      </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -3238,11 +3242,11 @@
         </is>
       </c>
       <c r="I38" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J38" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>3</v>
+      </c>
+      <c r="J38" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
@@ -3272,14 +3276,14 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
           <t>07/06/2026</t>
         </is>
       </c>
-      <c r="B39" s="2" t="inlineStr">
-        <is>
-          <t>06/06/2026</t>
-        </is>
-      </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -3311,11 +3315,11 @@
         </is>
       </c>
       <c r="I39" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J39" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J39" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
@@ -3345,14 +3349,14 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
+          <t>07/06/2026</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
           <t>06/06/2026</t>
         </is>
       </c>
-      <c r="B40" s="2" t="inlineStr">
-        <is>
-          <t>05/06/2026</t>
-        </is>
-      </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -3384,11 +3388,11 @@
         </is>
       </c>
       <c r="I40" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J40" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J40" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
@@ -3418,14 +3422,14 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
+          <t>07/06/2026</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
           <t>06/06/2026</t>
         </is>
       </c>
-      <c r="B41" s="2" t="inlineStr">
-        <is>
-          <t>05/06/2026</t>
-        </is>
-      </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -3457,11 +3461,11 @@
         </is>
       </c>
       <c r="I41" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J41" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J41" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
@@ -3491,12 +3495,12 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
+          <t>06/06/2026</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
           <t>05/06/2026</t>
-        </is>
-      </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>04/06/2026</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -3534,7 +3538,7 @@
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
@@ -3564,14 +3568,14 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
+          <t>06/06/2026</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
           <t>05/06/2026</t>
         </is>
       </c>
-      <c r="B43" s="2" t="inlineStr">
-        <is>
-          <t>04/06/2026</t>
-        </is>
-      </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -3603,7 +3607,7 @@
         </is>
       </c>
       <c r="I43" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J43" s="2" t="inlineStr">
         <is>
@@ -3637,14 +3641,14 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
+          <t>05/06/2026</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
           <t>04/06/2026</t>
         </is>
       </c>
-      <c r="B44" s="2" t="inlineStr">
-        <is>
-          <t>03/06/2026</t>
-        </is>
-      </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -3676,11 +3680,11 @@
         </is>
       </c>
       <c r="I44" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J44" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J44" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
@@ -3710,14 +3714,14 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
+          <t>05/06/2026</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
           <t>04/06/2026</t>
         </is>
       </c>
-      <c r="B45" s="2" t="inlineStr">
-        <is>
-          <t>03/06/2026</t>
-        </is>
-      </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -3751,9 +3755,9 @@
       <c r="I45" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J45" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J45" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr">
@@ -3783,14 +3787,14 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
+          <t>04/06/2026</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
           <t>03/06/2026</t>
         </is>
       </c>
-      <c r="B46" s="2" t="inlineStr">
-        <is>
-          <t>02/06/2026</t>
-        </is>
-      </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -3822,11 +3826,11 @@
         </is>
       </c>
       <c r="I46" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J46" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J46" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
@@ -3856,14 +3860,14 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
+          <t>04/06/2026</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
           <t>03/06/2026</t>
         </is>
       </c>
-      <c r="B47" s="2" t="inlineStr">
-        <is>
-          <t>02/06/2026</t>
-        </is>
-      </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -3895,11 +3899,11 @@
         </is>
       </c>
       <c r="I47" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J47" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J47" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K47" s="2" t="inlineStr">
@@ -3929,14 +3933,14 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
+          <t>03/06/2026</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
           <t>02/06/2026</t>
         </is>
       </c>
-      <c r="B48" s="2" t="inlineStr">
-        <is>
-          <t>01/06/2026</t>
-        </is>
-      </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -3962,17 +3966,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H48" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I48" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J48" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J48" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr">
@@ -4002,12 +4006,12 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
+          <t>03/06/2026</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
           <t>02/06/2026</t>
-        </is>
-      </c>
-      <c r="B49" s="2" t="inlineStr">
-        <is>
-          <t>01/06/2026</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -4075,14 +4079,14 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
+          <t>02/06/2026</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
           <t>01/06/2026</t>
         </is>
       </c>
-      <c r="B50" s="2" t="inlineStr">
-        <is>
-          <t>31/05/2026</t>
-        </is>
-      </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -4105,33 +4109,33 @@
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>R$ 126,00</t>
-        </is>
-      </c>
-      <c r="H50" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H50" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I50" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J50" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J50" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L50" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -4148,12 +4152,12 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
+          <t>02/06/2026</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
           <t>01/06/2026</t>
-        </is>
-      </c>
-      <c r="B51" s="2" t="inlineStr">
-        <is>
-          <t>31/05/2026</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -4221,14 +4225,14 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
+          <t>01/06/2026</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
           <t>31/05/2026</t>
         </is>
       </c>
-      <c r="B52" s="2" t="inlineStr">
-        <is>
-          <t>30/05/2026</t>
-        </is>
-      </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -4251,33 +4255,33 @@
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H52" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 126,00</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I52" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J52" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J52" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="L52" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -4294,12 +4298,12 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
+          <t>01/06/2026</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
           <t>31/05/2026</t>
-        </is>
-      </c>
-      <c r="B53" s="2" t="inlineStr">
-        <is>
-          <t>30/05/2026</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -4335,9 +4339,9 @@
       <c r="I53" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J53" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+      <c r="J53" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K53" s="2" t="inlineStr">
@@ -4367,14 +4371,14 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
+          <t>31/05/2026</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
           <t>30/05/2026</t>
         </is>
       </c>
-      <c r="B54" s="2" t="inlineStr">
-        <is>
-          <t>29/05/2026</t>
-        </is>
-      </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -4397,33 +4401,33 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>R$ 126,00</t>
-        </is>
-      </c>
-      <c r="H54" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H54" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I54" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J54" s="3" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L54" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -4440,14 +4444,14 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
+          <t>31/05/2026</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
           <t>30/05/2026</t>
         </is>
       </c>
-      <c r="B55" s="2" t="inlineStr">
-        <is>
-          <t>29/05/2026</t>
-        </is>
-      </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -4479,11 +4483,11 @@
         </is>
       </c>
       <c r="I55" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J55" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>1</v>
+      </c>
+      <c r="J55" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K55" s="2" t="inlineStr">
@@ -4513,14 +4517,14 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
+          <t>30/05/2026</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
           <t>29/05/2026</t>
         </is>
       </c>
-      <c r="B56" s="2" t="inlineStr">
-        <is>
-          <t>28/05/2026</t>
-        </is>
-      </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -4543,7 +4547,7 @@
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 126,00</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
@@ -4552,24 +4556,24 @@
         </is>
       </c>
       <c r="I56" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J56" s="3" t="inlineStr">
         <is>
-          <t>▼ 33,3%</t>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="L56" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -4586,14 +4590,14 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
+          <t>30/05/2026</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
           <t>29/05/2026</t>
         </is>
       </c>
-      <c r="B57" s="2" t="inlineStr">
-        <is>
-          <t>28/05/2026</t>
-        </is>
-      </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -4625,11 +4629,11 @@
         </is>
       </c>
       <c r="I57" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J57" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J57" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K57" s="2" t="inlineStr">
@@ -4659,14 +4663,14 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
+          <t>29/05/2026</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
           <t>28/05/2026</t>
         </is>
       </c>
-      <c r="B58" s="2" t="inlineStr">
-        <is>
-          <t>27/05/2026</t>
-        </is>
-      </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -4698,11 +4702,11 @@
         </is>
       </c>
       <c r="I58" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J58" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>2</v>
+      </c>
+      <c r="J58" s="3" t="inlineStr">
+        <is>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr">
@@ -4732,14 +4736,14 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
+          <t>29/05/2026</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
           <t>28/05/2026</t>
         </is>
       </c>
-      <c r="B59" s="2" t="inlineStr">
-        <is>
-          <t>27/05/2026</t>
-        </is>
-      </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -4771,11 +4775,11 @@
         </is>
       </c>
       <c r="I59" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J59" s="3" t="inlineStr">
         <is>
-          <t>▼ 66,7%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K59" s="2" t="inlineStr">
@@ -4805,14 +4809,14 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
+          <t>28/05/2026</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
           <t>27/05/2026</t>
         </is>
       </c>
-      <c r="B60" s="2" t="inlineStr">
-        <is>
-          <t>26/05/2026</t>
-        </is>
-      </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -4844,11 +4848,11 @@
         </is>
       </c>
       <c r="I60" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J60" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>3</v>
+      </c>
+      <c r="J60" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K60" s="2" t="inlineStr">
@@ -4878,14 +4882,14 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
+          <t>28/05/2026</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
           <t>27/05/2026</t>
         </is>
       </c>
-      <c r="B61" s="2" t="inlineStr">
-        <is>
-          <t>26/05/2026</t>
-        </is>
-      </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -4917,11 +4921,11 @@
         </is>
       </c>
       <c r="I61" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J61" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>1</v>
+      </c>
+      <c r="J61" s="3" t="inlineStr">
+        <is>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K61" s="2" t="inlineStr">
@@ -4951,14 +4955,14 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
+          <t>27/05/2026</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
           <t>26/05/2026</t>
         </is>
       </c>
-      <c r="B62" s="2" t="inlineStr">
-        <is>
-          <t>25/05/2026</t>
-        </is>
-      </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -4990,11 +4994,11 @@
         </is>
       </c>
       <c r="I62" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J62" s="4" t="inlineStr">
-        <is>
-          <t>▲ 50,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J62" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K62" s="2" t="inlineStr">
@@ -5024,14 +5028,14 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
+          <t>27/05/2026</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
           <t>26/05/2026</t>
         </is>
       </c>
-      <c r="B63" s="2" t="inlineStr">
-        <is>
-          <t>25/05/2026</t>
-        </is>
-      </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -5063,11 +5067,11 @@
         </is>
       </c>
       <c r="I63" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J63" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>3</v>
+      </c>
+      <c r="J63" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K63" s="2" t="inlineStr">
@@ -5097,14 +5101,14 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
+          <t>26/05/2026</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
           <t>25/05/2026</t>
         </is>
       </c>
-      <c r="B64" s="2" t="inlineStr">
-        <is>
-          <t>24/05/2026</t>
-        </is>
-      </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -5136,11 +5140,11 @@
         </is>
       </c>
       <c r="I64" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J64" s="4" t="inlineStr">
         <is>
-          <t>▲ 100,0%</t>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="K64" s="2" t="inlineStr">
@@ -5170,14 +5174,14 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
+          <t>26/05/2026</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
           <t>25/05/2026</t>
         </is>
       </c>
-      <c r="B65" s="2" t="inlineStr">
-        <is>
-          <t>24/05/2026</t>
-        </is>
-      </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -5209,11 +5213,11 @@
         </is>
       </c>
       <c r="I65" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J65" s="3" t="inlineStr">
         <is>
-          <t>▼ 83,3%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K65" s="2" t="inlineStr">
@@ -5243,14 +5247,14 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
+          <t>25/05/2026</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
           <t>24/05/2026</t>
         </is>
       </c>
-      <c r="B66" s="2" t="inlineStr">
-        <is>
-          <t>23/05/2026</t>
-        </is>
-      </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -5276,17 +5280,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H66" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I66" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J66" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J66" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K66" s="2" t="inlineStr">
@@ -5316,14 +5320,14 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
+          <t>25/05/2026</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
           <t>24/05/2026</t>
         </is>
       </c>
-      <c r="B67" s="2" t="inlineStr">
-        <is>
-          <t>23/05/2026</t>
-        </is>
-      </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -5355,11 +5359,11 @@
         </is>
       </c>
       <c r="I67" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J67" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J67" s="3" t="inlineStr">
+        <is>
+          <t>▼ 83,3%</t>
         </is>
       </c>
       <c r="K67" s="2" t="inlineStr">
@@ -5389,14 +5393,14 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
+          <t>24/05/2026</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
           <t>23/05/2026</t>
         </is>
       </c>
-      <c r="B68" s="2" t="inlineStr">
-        <is>
-          <t>22/05/2026</t>
-        </is>
-      </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -5419,33 +5423,33 @@
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>R$ 126,00</t>
-        </is>
-      </c>
-      <c r="H68" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H68" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I68" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J68" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J68" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K68" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L68" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M68" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N68" s="2" t="inlineStr">
@@ -5462,14 +5466,14 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
+          <t>24/05/2026</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
           <t>23/05/2026</t>
         </is>
       </c>
-      <c r="B69" s="2" t="inlineStr">
-        <is>
-          <t>22/05/2026</t>
-        </is>
-      </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -5501,11 +5505,11 @@
         </is>
       </c>
       <c r="I69" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J69" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>6</v>
+      </c>
+      <c r="J69" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K69" s="2" t="inlineStr">
@@ -5535,14 +5539,14 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
+          <t>23/05/2026</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
           <t>22/05/2026</t>
         </is>
       </c>
-      <c r="B70" s="2" t="inlineStr">
-        <is>
-          <t>21/05/2026</t>
-        </is>
-      </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -5565,7 +5569,7 @@
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 126,00</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
@@ -5574,24 +5578,24 @@
         </is>
       </c>
       <c r="I70" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J70" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
+        </is>
+      </c>
+      <c r="K70" s="2" t="inlineStr">
+        <is>
+          <t>50,0%</t>
+        </is>
+      </c>
+      <c r="L70" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J70" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
-        </is>
-      </c>
-      <c r="K70" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L70" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="N70" s="2" t="inlineStr">
@@ -5608,12 +5612,12 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
+          <t>23/05/2026</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
           <t>22/05/2026</t>
-        </is>
-      </c>
-      <c r="B71" s="2" t="inlineStr">
-        <is>
-          <t>21/05/2026</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -5651,7 +5655,7 @@
       </c>
       <c r="J71" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K71" s="2" t="inlineStr">
@@ -5681,14 +5685,14 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
           <t>21/05/2026</t>
         </is>
       </c>
-      <c r="B72" s="2" t="inlineStr">
-        <is>
-          <t>20/05/2026</t>
-        </is>
-      </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -5720,11 +5724,11 @@
         </is>
       </c>
       <c r="I72" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J72" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>1</v>
+      </c>
+      <c r="J72" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr">
@@ -5754,14 +5758,14 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
           <t>21/05/2026</t>
         </is>
       </c>
-      <c r="B73" s="2" t="inlineStr">
-        <is>
-          <t>20/05/2026</t>
-        </is>
-      </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -5793,11 +5797,11 @@
         </is>
       </c>
       <c r="I73" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J73" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>3</v>
+      </c>
+      <c r="J73" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K73" s="2" t="inlineStr">
@@ -5827,14 +5831,14 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
+          <t>21/05/2026</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
           <t>20/05/2026</t>
         </is>
       </c>
-      <c r="B74" s="2" t="inlineStr">
-        <is>
-          <t>19/05/2026</t>
-        </is>
-      </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -5866,7 +5870,7 @@
         </is>
       </c>
       <c r="I74" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J74" s="2" t="inlineStr">
         <is>
@@ -5900,14 +5904,14 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
+          <t>21/05/2026</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
           <t>20/05/2026</t>
         </is>
       </c>
-      <c r="B75" s="2" t="inlineStr">
-        <is>
-          <t>19/05/2026</t>
-        </is>
-      </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -5939,11 +5943,11 @@
         </is>
       </c>
       <c r="I75" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J75" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J75" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K75" s="2" t="inlineStr">
@@ -5973,12 +5977,12 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
+          <t>20/05/2026</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
           <t>19/05/2026</t>
-        </is>
-      </c>
-      <c r="B76" s="2" t="inlineStr">
-        <is>
-          <t>18/05/2026</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -6046,14 +6050,14 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
+          <t>20/05/2026</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
           <t>19/05/2026</t>
         </is>
       </c>
-      <c r="B77" s="2" t="inlineStr">
-        <is>
-          <t>18/05/2026</t>
-        </is>
-      </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -6085,7 +6089,7 @@
         </is>
       </c>
       <c r="I77" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J77" s="2" t="inlineStr">
         <is>
@@ -6119,14 +6123,14 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
           <t>18/05/2026</t>
         </is>
       </c>
-      <c r="B78" s="2" t="inlineStr">
-        <is>
-          <t>17/05/2026</t>
-        </is>
-      </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -6160,9 +6164,9 @@
       <c r="I78" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J78" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J78" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K78" s="2" t="inlineStr">
@@ -6192,12 +6196,12 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
           <t>18/05/2026</t>
-        </is>
-      </c>
-      <c r="B79" s="2" t="inlineStr">
-        <is>
-          <t>17/05/2026</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
@@ -6265,14 +6269,14 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
           <t>17/05/2026</t>
         </is>
       </c>
-      <c r="B80" s="2" t="inlineStr">
-        <is>
-          <t>16/05/2026</t>
-        </is>
-      </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -6304,11 +6308,11 @@
         </is>
       </c>
       <c r="I80" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J80" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J80" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K80" s="2" t="inlineStr">
@@ -6338,14 +6342,14 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
           <t>17/05/2026</t>
         </is>
       </c>
-      <c r="B81" s="2" t="inlineStr">
-        <is>
-          <t>16/05/2026</t>
-        </is>
-      </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -6368,7 +6372,7 @@
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
@@ -6376,10 +6380,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I81" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I81" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J81" s="2" t="inlineStr">
         <is>
@@ -6388,41 +6390,39 @@
       </c>
       <c r="K81" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L81" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L81" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M81" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N81" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
+          <t>17/05/2026</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
           <t>16/05/2026</t>
         </is>
       </c>
-      <c r="B82" s="2" t="inlineStr">
-        <is>
-          <t>15/05/2026</t>
-        </is>
-      </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -6454,11 +6454,11 @@
         </is>
       </c>
       <c r="I82" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J82" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J82" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K82" s="2" t="inlineStr">
@@ -6488,14 +6488,14 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
+          <t>17/05/2026</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
           <t>16/05/2026</t>
         </is>
       </c>
-      <c r="B83" s="2" t="inlineStr">
-        <is>
-          <t>15/05/2026</t>
-        </is>
-      </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -6518,7 +6518,7 @@
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr">
@@ -6526,8 +6526,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I83" s="2" t="n">
-        <v>0</v>
+      <c r="I83" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J83" s="2" t="inlineStr">
         <is>
@@ -6536,39 +6538,41 @@
       </c>
       <c r="K83" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L83" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L83" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M83" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N83" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
+          <t>16/05/2026</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
           <t>15/05/2026</t>
         </is>
       </c>
-      <c r="B84" s="2" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
-        </is>
-      </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -6600,11 +6604,11 @@
         </is>
       </c>
       <c r="I84" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J84" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J84" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K84" s="2" t="inlineStr">
@@ -6634,14 +6638,14 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
+          <t>16/05/2026</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
           <t>15/05/2026</t>
         </is>
       </c>
-      <c r="B85" s="2" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
-        </is>
-      </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -6675,9 +6679,9 @@
       <c r="I85" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J85" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J85" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K85" s="2" t="inlineStr">
@@ -6707,14 +6711,14 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
+          <t>15/05/2026</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
           <t>14/05/2026</t>
         </is>
       </c>
-      <c r="B86" s="2" t="inlineStr">
-        <is>
-          <t>13/05/2026</t>
-        </is>
-      </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -6746,11 +6750,11 @@
         </is>
       </c>
       <c r="I86" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J86" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J86" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K86" s="2" t="inlineStr">
@@ -6780,14 +6784,14 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
+          <t>15/05/2026</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
           <t>14/05/2026</t>
         </is>
       </c>
-      <c r="B87" s="2" t="inlineStr">
-        <is>
-          <t>13/05/2026</t>
-        </is>
-      </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -6819,11 +6823,11 @@
         </is>
       </c>
       <c r="I87" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J87" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J87" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K87" s="2" t="inlineStr">
@@ -6853,14 +6857,14 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
+          <t>14/05/2026</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
           <t>13/05/2026</t>
         </is>
       </c>
-      <c r="B88" s="2" t="inlineStr">
-        <is>
-          <t>12/05/2026</t>
-        </is>
-      </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -6892,11 +6896,11 @@
         </is>
       </c>
       <c r="I88" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J88" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J88" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K88" s="2" t="inlineStr">
@@ -6926,14 +6930,14 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
+          <t>14/05/2026</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
           <t>13/05/2026</t>
         </is>
       </c>
-      <c r="B89" s="2" t="inlineStr">
-        <is>
-          <t>12/05/2026</t>
-        </is>
-      </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -6956,7 +6960,7 @@
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H89" s="2" t="inlineStr">
@@ -6964,10 +6968,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I89" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I89" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J89" s="2" t="inlineStr">
         <is>
@@ -6976,41 +6978,39 @@
       </c>
       <c r="K89" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L89" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L89" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M89" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N89" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
+          <t>13/05/2026</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
           <t>12/05/2026</t>
         </is>
       </c>
-      <c r="B90" s="2" t="inlineStr">
-        <is>
-          <t>11/05/2026</t>
-        </is>
-      </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -7042,11 +7042,11 @@
         </is>
       </c>
       <c r="I90" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J90" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J90" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K90" s="2" t="inlineStr">
@@ -7076,12 +7076,12 @@
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
+          <t>13/05/2026</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
           <t>12/05/2026</t>
-        </is>
-      </c>
-      <c r="B91" s="2" t="inlineStr">
-        <is>
-          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
@@ -7153,14 +7153,14 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
+          <t>12/05/2026</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
           <t>11/05/2026</t>
         </is>
       </c>
-      <c r="B92" s="2" t="inlineStr">
-        <is>
-          <t>10/05/2026</t>
-        </is>
-      </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -7192,11 +7192,11 @@
         </is>
       </c>
       <c r="I92" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J92" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J92" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K92" s="2" t="inlineStr">
@@ -7226,14 +7226,14 @@
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
+          <t>12/05/2026</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
           <t>11/05/2026</t>
         </is>
       </c>
-      <c r="B93" s="2" t="inlineStr">
-        <is>
-          <t>10/05/2026</t>
-        </is>
-      </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -7256,7 +7256,7 @@
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H93" s="2" t="inlineStr">
@@ -7264,8 +7264,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I93" s="2" t="n">
-        <v>0</v>
+      <c r="I93" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J93" s="2" t="inlineStr">
         <is>
@@ -7274,39 +7276,41 @@
       </c>
       <c r="K93" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L93" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L93" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M93" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N93" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
+          <t>11/05/2026</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
           <t>10/05/2026</t>
         </is>
       </c>
-      <c r="B94" s="2" t="inlineStr">
-        <is>
-          <t>09/05/2026</t>
-        </is>
-      </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -7329,7 +7333,7 @@
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H94" s="2" t="inlineStr">
@@ -7337,10 +7341,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I94" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I94" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J94" s="2" t="inlineStr">
         <is>
@@ -7349,41 +7351,39 @@
       </c>
       <c r="K94" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L94" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L94" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M94" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N94" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
+          <t>11/05/2026</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
           <t>10/05/2026</t>
         </is>
       </c>
-      <c r="B95" s="2" t="inlineStr">
-        <is>
-          <t>09/05/2026</t>
-        </is>
-      </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -7409,17 +7409,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H95" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H95" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I95" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J95" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J95" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K95" s="2" t="inlineStr">
@@ -7449,14 +7449,14 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
+          <t>10/05/2026</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
           <t>09/05/2026</t>
         </is>
       </c>
-      <c r="B96" s="2" t="inlineStr">
-        <is>
-          <t>08/05/2026</t>
-        </is>
-      </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -7479,7 +7479,7 @@
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H96" s="2" t="inlineStr">
@@ -7487,8 +7487,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I96" s="2" t="n">
-        <v>0</v>
+      <c r="I96" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J96" s="2" t="inlineStr">
         <is>
@@ -7497,39 +7499,41 @@
       </c>
       <c r="K96" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L96" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L96" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M96" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N96" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
+          <t>10/05/2026</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
           <t>09/05/2026</t>
         </is>
       </c>
-      <c r="B97" s="2" t="inlineStr">
-        <is>
-          <t>08/05/2026</t>
-        </is>
-      </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -7552,33 +7556,33 @@
       </c>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t>R$ 110,00</t>
-        </is>
-      </c>
-      <c r="H97" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H97" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I97" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J97" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J97" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K97" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L97" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M97" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N97" s="2" t="inlineStr">
@@ -7595,14 +7599,14 @@
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
           <t>08/05/2026</t>
         </is>
       </c>
-      <c r="B98" s="2" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
-        </is>
-      </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -7628,17 +7632,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H98" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H98" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I98" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J98" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J98" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K98" s="2" t="inlineStr">
@@ -7668,14 +7672,14 @@
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
           <t>08/05/2026</t>
         </is>
       </c>
-      <c r="B99" s="2" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
-        </is>
-      </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -7698,7 +7702,7 @@
       </c>
       <c r="G99" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 110,00</t>
         </is>
       </c>
       <c r="H99" s="2" t="inlineStr">
@@ -7707,24 +7711,24 @@
         </is>
       </c>
       <c r="I99" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J99" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J99" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K99" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>50,0%</t>
         </is>
       </c>
       <c r="L99" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M99" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="N99" s="2" t="inlineStr">
@@ -7741,14 +7745,14 @@
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
+          <t>08/05/2026</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
           <t>07/05/2026</t>
         </is>
       </c>
-      <c r="B100" s="2" t="inlineStr">
-        <is>
-          <t>06/05/2026</t>
-        </is>
-      </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -7771,33 +7775,33 @@
       </c>
       <c r="G100" s="2" t="inlineStr">
         <is>
-          <t>R$ 110,00</t>
-        </is>
-      </c>
-      <c r="H100" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H100" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I100" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J100" s="3" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K100" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L100" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M100" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N100" s="2" t="inlineStr">
@@ -7814,14 +7818,14 @@
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
+          <t>08/05/2026</t>
+        </is>
+      </c>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
           <t>07/05/2026</t>
         </is>
       </c>
-      <c r="B101" s="2" t="inlineStr">
-        <is>
-          <t>06/05/2026</t>
-        </is>
-      </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -7853,11 +7857,11 @@
         </is>
       </c>
       <c r="I101" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J101" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J101" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K101" s="2" t="inlineStr">
@@ -7887,14 +7891,14 @@
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
           <t>06/05/2026</t>
         </is>
       </c>
-      <c r="B102" s="2" t="inlineStr">
-        <is>
-          <t>05/05/2026</t>
-        </is>
-      </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -7917,7 +7921,7 @@
       </c>
       <c r="G102" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 110,00</t>
         </is>
       </c>
       <c r="H102" s="2" t="inlineStr">
@@ -7926,24 +7930,24 @@
         </is>
       </c>
       <c r="I102" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J102" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>1</v>
+      </c>
+      <c r="J102" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K102" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="L102" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M102" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="N102" s="2" t="inlineStr">
@@ -7960,14 +7964,14 @@
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
           <t>06/05/2026</t>
         </is>
       </c>
-      <c r="B103" s="2" t="inlineStr">
-        <is>
-          <t>05/05/2026</t>
-        </is>
-      </c>
       <c r="C103" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -7999,11 +8003,11 @@
         </is>
       </c>
       <c r="I103" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J103" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J103" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K103" s="2" t="inlineStr">
@@ -8033,12 +8037,12 @@
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
+          <t>06/05/2026</t>
+        </is>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
           <t>05/05/2026</t>
-        </is>
-      </c>
-      <c r="B104" s="2" t="inlineStr">
-        <is>
-          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C104" s="2" t="inlineStr">
@@ -8076,7 +8080,7 @@
       </c>
       <c r="J104" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K104" s="2" t="inlineStr">
@@ -8106,14 +8110,14 @@
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
+          <t>06/05/2026</t>
+        </is>
+      </c>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
           <t>05/05/2026</t>
         </is>
       </c>
-      <c r="B105" s="2" t="inlineStr">
-        <is>
-          <t>04/05/2026</t>
-        </is>
-      </c>
       <c r="C105" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -8145,11 +8149,11 @@
         </is>
       </c>
       <c r="I105" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J105" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J105" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K105" s="2" t="inlineStr">
@@ -8179,14 +8183,14 @@
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
+          <t>05/05/2026</t>
+        </is>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
           <t>04/05/2026</t>
         </is>
       </c>
-      <c r="B106" s="2" t="inlineStr">
-        <is>
-          <t>03/05/2026</t>
-        </is>
-      </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -8218,7 +8222,7 @@
         </is>
       </c>
       <c r="I106" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J106" s="2" t="inlineStr">
         <is>
@@ -8252,14 +8256,14 @@
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
+          <t>05/05/2026</t>
+        </is>
+      </c>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
           <t>04/05/2026</t>
         </is>
       </c>
-      <c r="B107" s="2" t="inlineStr">
-        <is>
-          <t>03/05/2026</t>
-        </is>
-      </c>
       <c r="C107" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -8291,11 +8295,11 @@
         </is>
       </c>
       <c r="I107" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J107" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J107" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K107" s="2" t="inlineStr">
@@ -8325,14 +8329,14 @@
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
           <t>03/05/2026</t>
         </is>
       </c>
-      <c r="B108" s="2" t="inlineStr">
-        <is>
-          <t>02/05/2026</t>
-        </is>
-      </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -8366,9 +8370,9 @@
       <c r="I108" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J108" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J108" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K108" s="2" t="inlineStr">
@@ -8398,14 +8402,14 @@
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="B109" s="2" t="inlineStr">
+        <is>
           <t>03/05/2026</t>
         </is>
       </c>
-      <c r="B109" s="2" t="inlineStr">
-        <is>
-          <t>02/05/2026</t>
-        </is>
-      </c>
       <c r="C109" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -8437,11 +8441,11 @@
         </is>
       </c>
       <c r="I109" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J109" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J109" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K109" s="2" t="inlineStr">
@@ -8471,14 +8475,14 @@
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
+          <t>03/05/2026</t>
+        </is>
+      </c>
+      <c r="B110" s="2" t="inlineStr">
+        <is>
           <t>02/05/2026</t>
         </is>
       </c>
-      <c r="B110" s="2" t="inlineStr">
-        <is>
-          <t>01/05/2026</t>
-        </is>
-      </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -8510,11 +8514,11 @@
         </is>
       </c>
       <c r="I110" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J110" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J110" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K110" s="2" t="inlineStr">
@@ -8544,12 +8548,12 @@
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
+          <t>03/05/2026</t>
+        </is>
+      </c>
+      <c r="B111" s="2" t="inlineStr">
+        <is>
           <t>02/05/2026</t>
-        </is>
-      </c>
-      <c r="B111" s="2" t="inlineStr">
-        <is>
-          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C111" s="2" t="inlineStr">
@@ -8585,9 +8589,9 @@
       <c r="I111" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J111" s="3" t="inlineStr">
-        <is>
-          <t>▼ 66,7%</t>
+      <c r="J111" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K111" s="2" t="inlineStr">
@@ -8617,12 +8621,12 @@
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
+          <t>02/05/2026</t>
+        </is>
+      </c>
+      <c r="B112" s="2" t="inlineStr">
+        <is>
           <t>01/05/2026</t>
-        </is>
-      </c>
-      <c r="B112" s="2" t="inlineStr">
-        <is>
-          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C112" s="2" t="inlineStr">
@@ -8660,7 +8664,7 @@
       </c>
       <c r="J112" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K112" s="2" t="inlineStr">
@@ -8690,14 +8694,14 @@
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
+          <t>02/05/2026</t>
+        </is>
+      </c>
+      <c r="B113" s="2" t="inlineStr">
+        <is>
           <t>01/05/2026</t>
         </is>
       </c>
-      <c r="B113" s="2" t="inlineStr">
-        <is>
-          <t>30/04/2026</t>
-        </is>
-      </c>
       <c r="C113" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -8729,11 +8733,11 @@
         </is>
       </c>
       <c r="I113" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J113" s="3" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K113" s="2" t="inlineStr">
@@ -8763,14 +8767,14 @@
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
+          <t>01/05/2026</t>
+        </is>
+      </c>
+      <c r="B114" s="2" t="inlineStr">
+        <is>
           <t>30/04/2026</t>
         </is>
       </c>
-      <c r="B114" s="2" t="inlineStr">
-        <is>
-          <t>29/04/2026</t>
-        </is>
-      </c>
       <c r="C114" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -8802,11 +8806,11 @@
         </is>
       </c>
       <c r="I114" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J114" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J114" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K114" s="2" t="inlineStr">
@@ -8836,14 +8840,14 @@
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
+          <t>01/05/2026</t>
+        </is>
+      </c>
+      <c r="B115" s="2" t="inlineStr">
+        <is>
           <t>30/04/2026</t>
         </is>
       </c>
-      <c r="B115" s="2" t="inlineStr">
-        <is>
-          <t>29/04/2026</t>
-        </is>
-      </c>
       <c r="C115" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -8875,11 +8879,11 @@
         </is>
       </c>
       <c r="I115" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J115" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>3</v>
+      </c>
+      <c r="J115" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K115" s="2" t="inlineStr">
@@ -8909,14 +8913,14 @@
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="B116" s="2" t="inlineStr">
+        <is>
           <t>29/04/2026</t>
         </is>
       </c>
-      <c r="B116" s="2" t="inlineStr">
-        <is>
-          <t>28/04/2026</t>
-        </is>
-      </c>
       <c r="C116" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -8948,11 +8952,11 @@
         </is>
       </c>
       <c r="I116" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J116" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J116" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K116" s="2" t="inlineStr">
@@ -8975,19 +8979,19 @@
       </c>
       <c r="O116" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="B117" s="2" t="inlineStr">
+        <is>
           <t>29/04/2026</t>
-        </is>
-      </c>
-      <c r="B117" s="2" t="inlineStr">
-        <is>
-          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C117" s="2" t="inlineStr">
@@ -9025,7 +9029,7 @@
       </c>
       <c r="J117" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K117" s="2" t="inlineStr">
@@ -9048,19 +9052,19 @@
       </c>
       <c r="O117" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
+          <t>29/04/2026</t>
+        </is>
+      </c>
+      <c r="B118" s="2" t="inlineStr">
+        <is>
           <t>28/04/2026</t>
-        </is>
-      </c>
-      <c r="B118" s="2" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C118" s="2" t="inlineStr">
@@ -9096,9 +9100,9 @@
       <c r="I118" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J118" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+      <c r="J118" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K118" s="2" t="inlineStr">
@@ -9128,14 +9132,14 @@
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
+          <t>29/04/2026</t>
+        </is>
+      </c>
+      <c r="B119" s="2" t="inlineStr">
+        <is>
           <t>28/04/2026</t>
         </is>
       </c>
-      <c r="B119" s="2" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
-        </is>
-      </c>
       <c r="C119" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -9167,11 +9171,11 @@
         </is>
       </c>
       <c r="I119" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J119" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>6</v>
+      </c>
+      <c r="J119" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K119" s="2" t="inlineStr">
@@ -9201,14 +9205,14 @@
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
+          <t>28/04/2026</t>
+        </is>
+      </c>
+      <c r="B120" s="2" t="inlineStr">
+        <is>
           <t>27/04/2026</t>
         </is>
       </c>
-      <c r="B120" s="2" t="inlineStr">
-        <is>
-          <t>26/04/2026</t>
-        </is>
-      </c>
       <c r="C120" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -9240,11 +9244,11 @@
         </is>
       </c>
       <c r="I120" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J120" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>1</v>
+      </c>
+      <c r="J120" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K120" s="2" t="inlineStr">
@@ -9274,14 +9278,14 @@
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
+          <t>28/04/2026</t>
+        </is>
+      </c>
+      <c r="B121" s="2" t="inlineStr">
+        <is>
           <t>27/04/2026</t>
         </is>
       </c>
-      <c r="B121" s="2" t="inlineStr">
-        <is>
-          <t>26/04/2026</t>
-        </is>
-      </c>
       <c r="C121" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -9313,11 +9317,11 @@
         </is>
       </c>
       <c r="I121" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J121" s="3" t="inlineStr">
         <is>
-          <t>▼ 66,7%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K121" s="2" t="inlineStr">
@@ -9347,12 +9351,12 @@
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B122" s="2" t="inlineStr">
+        <is>
           <t>26/04/2026</t>
-        </is>
-      </c>
-      <c r="B122" s="2" t="inlineStr">
-        <is>
-          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C122" s="2" t="inlineStr">
@@ -9420,14 +9424,14 @@
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B123" s="2" t="inlineStr">
+        <is>
           <t>26/04/2026</t>
         </is>
       </c>
-      <c r="B123" s="2" t="inlineStr">
-        <is>
-          <t>25/04/2026</t>
-        </is>
-      </c>
       <c r="C123" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -9459,11 +9463,11 @@
         </is>
       </c>
       <c r="I123" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J123" s="4" t="inlineStr">
-        <is>
-          <t>▲ 200,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J123" s="3" t="inlineStr">
+        <is>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K123" s="2" t="inlineStr">
@@ -9493,12 +9497,12 @@
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
+          <t>26/04/2026</t>
+        </is>
+      </c>
+      <c r="B124" s="2" t="inlineStr">
+        <is>
           <t>25/04/2026</t>
-        </is>
-      </c>
-      <c r="B124" s="2" t="inlineStr">
-        <is>
-          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C124" s="2" t="inlineStr">
@@ -9534,9 +9538,9 @@
       <c r="I124" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="J124" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+      <c r="J124" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K124" s="2" t="inlineStr">
@@ -9566,14 +9570,14 @@
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
+          <t>26/04/2026</t>
+        </is>
+      </c>
+      <c r="B125" s="2" t="inlineStr">
+        <is>
           <t>25/04/2026</t>
         </is>
       </c>
-      <c r="B125" s="2" t="inlineStr">
-        <is>
-          <t>24/04/2026</t>
-        </is>
-      </c>
       <c r="C125" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -9605,11 +9609,11 @@
         </is>
       </c>
       <c r="I125" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J125" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>3</v>
+      </c>
+      <c r="J125" s="4" t="inlineStr">
+        <is>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="K125" s="2" t="inlineStr">
@@ -9639,14 +9643,14 @@
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
+          <t>25/04/2026</t>
+        </is>
+      </c>
+      <c r="B126" s="2" t="inlineStr">
+        <is>
           <t>24/04/2026</t>
         </is>
       </c>
-      <c r="B126" s="2" t="inlineStr">
-        <is>
-          <t>23/04/2026</t>
-        </is>
-      </c>
       <c r="C126" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -9678,11 +9682,11 @@
         </is>
       </c>
       <c r="I126" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J126" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J126" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K126" s="2" t="inlineStr">
@@ -9712,14 +9716,14 @@
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
+          <t>25/04/2026</t>
+        </is>
+      </c>
+      <c r="B127" s="2" t="inlineStr">
+        <is>
           <t>24/04/2026</t>
         </is>
       </c>
-      <c r="B127" s="2" t="inlineStr">
-        <is>
-          <t>23/04/2026</t>
-        </is>
-      </c>
       <c r="C127" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -9742,7 +9746,7 @@
       </c>
       <c r="G127" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H127" s="2" t="inlineStr">
@@ -9750,10 +9754,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I127" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I127" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J127" s="2" t="inlineStr">
         <is>
@@ -9762,41 +9764,39 @@
       </c>
       <c r="K127" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L127" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L127" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M127" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N127" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O127" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
+          <t>24/04/2026</t>
+        </is>
+      </c>
+      <c r="B128" s="2" t="inlineStr">
+        <is>
           <t>23/04/2026</t>
         </is>
       </c>
-      <c r="B128" s="2" t="inlineStr">
-        <is>
-          <t>22/04/2026</t>
-        </is>
-      </c>
       <c r="C128" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -9828,11 +9828,11 @@
         </is>
       </c>
       <c r="I128" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J128" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J128" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K128" s="2" t="inlineStr">
@@ -9862,12 +9862,12 @@
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
         <is>
+          <t>24/04/2026</t>
+        </is>
+      </c>
+      <c r="B129" s="2" t="inlineStr">
+        <is>
           <t>23/04/2026</t>
-        </is>
-      </c>
-      <c r="B129" s="2" t="inlineStr">
-        <is>
-          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C129" s="2" t="inlineStr">
@@ -9939,14 +9939,14 @@
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
         <is>
+          <t>23/04/2026</t>
+        </is>
+      </c>
+      <c r="B130" s="2" t="inlineStr">
+        <is>
           <t>22/04/2026</t>
         </is>
       </c>
-      <c r="B130" s="2" t="inlineStr">
-        <is>
-          <t>21/04/2026</t>
-        </is>
-      </c>
       <c r="C130" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -9978,11 +9978,11 @@
         </is>
       </c>
       <c r="I130" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J130" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J130" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K130" s="2" t="inlineStr">
@@ -10012,14 +10012,14 @@
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
         <is>
+          <t>23/04/2026</t>
+        </is>
+      </c>
+      <c r="B131" s="2" t="inlineStr">
+        <is>
           <t>22/04/2026</t>
         </is>
       </c>
-      <c r="B131" s="2" t="inlineStr">
-        <is>
-          <t>21/04/2026</t>
-        </is>
-      </c>
       <c r="C131" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -10042,7 +10042,7 @@
       </c>
       <c r="G131" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H131" s="2" t="inlineStr">
@@ -10050,8 +10050,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I131" s="2" t="n">
-        <v>0</v>
+      <c r="I131" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J131" s="2" t="inlineStr">
         <is>
@@ -10060,39 +10062,41 @@
       </c>
       <c r="K131" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L131" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L131" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M131" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N131" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O131" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
         <is>
+          <t>22/04/2026</t>
+        </is>
+      </c>
+      <c r="B132" s="2" t="inlineStr">
+        <is>
           <t>21/04/2026</t>
         </is>
       </c>
-      <c r="B132" s="2" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
-        </is>
-      </c>
       <c r="C132" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -10124,11 +10128,11 @@
         </is>
       </c>
       <c r="I132" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J132" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>1</v>
+      </c>
+      <c r="J132" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K132" s="2" t="inlineStr">
@@ -10146,7 +10150,7 @@
       </c>
       <c r="N132" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O132" s="2" t="inlineStr">
@@ -10158,14 +10162,14 @@
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
         <is>
+          <t>22/04/2026</t>
+        </is>
+      </c>
+      <c r="B133" s="2" t="inlineStr">
+        <is>
           <t>21/04/2026</t>
         </is>
       </c>
-      <c r="B133" s="2" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
-        </is>
-      </c>
       <c r="C133" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -10199,9 +10203,9 @@
       <c r="I133" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J133" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J133" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K133" s="2" t="inlineStr">
@@ -10231,14 +10235,14 @@
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
         <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="B134" s="2" t="inlineStr">
+        <is>
           <t>20/04/2026</t>
         </is>
       </c>
-      <c r="B134" s="2" t="inlineStr">
-        <is>
-          <t>19/04/2026</t>
-        </is>
-      </c>
       <c r="C134" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -10270,7 +10274,7 @@
         </is>
       </c>
       <c r="I134" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J134" s="2" t="inlineStr">
         <is>
@@ -10292,7 +10296,7 @@
       </c>
       <c r="N134" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O134" s="2" t="inlineStr">
@@ -10304,14 +10308,14 @@
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
         <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="B135" s="2" t="inlineStr">
+        <is>
           <t>20/04/2026</t>
         </is>
       </c>
-      <c r="B135" s="2" t="inlineStr">
-        <is>
-          <t>19/04/2026</t>
-        </is>
-      </c>
       <c r="C135" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -10343,11 +10347,11 @@
         </is>
       </c>
       <c r="I135" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J135" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J135" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K135" s="2" t="inlineStr">
@@ -10377,12 +10381,12 @@
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
         <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="B136" s="2" t="inlineStr">
+        <is>
           <t>19/04/2026</t>
-        </is>
-      </c>
-      <c r="B136" s="2" t="inlineStr">
-        <is>
-          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C136" s="2" t="inlineStr">
@@ -10450,14 +10454,14 @@
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
         <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="B137" s="2" t="inlineStr">
+        <is>
           <t>19/04/2026</t>
         </is>
       </c>
-      <c r="B137" s="2" t="inlineStr">
-        <is>
-          <t>18/04/2026</t>
-        </is>
-      </c>
       <c r="C137" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -10489,11 +10493,11 @@
         </is>
       </c>
       <c r="I137" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J137" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>4</v>
+      </c>
+      <c r="J137" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K137" s="2" t="inlineStr">
@@ -10523,12 +10527,12 @@
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
         <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="B138" s="2" t="inlineStr">
+        <is>
           <t>18/04/2026</t>
-        </is>
-      </c>
-      <c r="B138" s="2" t="inlineStr">
-        <is>
-          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C138" s="2" t="inlineStr">
@@ -10596,14 +10600,14 @@
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
         <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="B139" s="2" t="inlineStr">
+        <is>
           <t>18/04/2026</t>
         </is>
       </c>
-      <c r="B139" s="2" t="inlineStr">
-        <is>
-          <t>17/04/2026</t>
-        </is>
-      </c>
       <c r="C139" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -10635,7 +10639,7 @@
         </is>
       </c>
       <c r="I139" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J139" s="2" t="inlineStr">
         <is>
@@ -10669,14 +10673,14 @@
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
         <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="B140" s="2" t="inlineStr">
+        <is>
           <t>17/04/2026</t>
         </is>
       </c>
-      <c r="B140" s="2" t="inlineStr">
-        <is>
-          <t>16/04/2026</t>
-        </is>
-      </c>
       <c r="C140" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -10710,9 +10714,9 @@
       <c r="I140" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J140" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J140" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K140" s="2" t="inlineStr">
@@ -10742,14 +10746,14 @@
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
         <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="B141" s="2" t="inlineStr">
+        <is>
           <t>17/04/2026</t>
         </is>
       </c>
-      <c r="B141" s="2" t="inlineStr">
-        <is>
-          <t>16/04/2026</t>
-        </is>
-      </c>
       <c r="C141" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -10783,9 +10787,9 @@
       <c r="I141" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J141" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J141" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K141" s="2" t="inlineStr">
@@ -10815,14 +10819,14 @@
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
         <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="B142" s="2" t="inlineStr">
+        <is>
           <t>16/04/2026</t>
         </is>
       </c>
-      <c r="B142" s="2" t="inlineStr">
-        <is>
-          <t>15/04/2026</t>
-        </is>
-      </c>
       <c r="C142" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -10854,11 +10858,11 @@
         </is>
       </c>
       <c r="I142" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J142" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J142" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K142" s="2" t="inlineStr">
@@ -10888,14 +10892,14 @@
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
         <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="B143" s="2" t="inlineStr">
+        <is>
           <t>16/04/2026</t>
         </is>
       </c>
-      <c r="B143" s="2" t="inlineStr">
-        <is>
-          <t>15/04/2026</t>
-        </is>
-      </c>
       <c r="C143" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -10927,11 +10931,11 @@
         </is>
       </c>
       <c r="I143" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J143" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J143" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K143" s="2" t="inlineStr">
@@ -10961,14 +10965,14 @@
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
         <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="B144" s="2" t="inlineStr">
+        <is>
           <t>15/04/2026</t>
         </is>
       </c>
-      <c r="B144" s="2" t="inlineStr">
-        <is>
-          <t>14/04/2026</t>
-        </is>
-      </c>
       <c r="C144" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -11000,11 +11004,11 @@
         </is>
       </c>
       <c r="I144" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J144" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J144" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K144" s="2" t="inlineStr">
@@ -11034,12 +11038,12 @@
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
         <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="B145" s="2" t="inlineStr">
+        <is>
           <t>15/04/2026</t>
-        </is>
-      </c>
-      <c r="B145" s="2" t="inlineStr">
-        <is>
-          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C145" s="2" t="inlineStr">
@@ -11107,14 +11111,14 @@
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
         <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="B146" s="2" t="inlineStr">
+        <is>
           <t>14/04/2026</t>
         </is>
       </c>
-      <c r="B146" s="2" t="inlineStr">
-        <is>
-          <t>13/04/2026</t>
-        </is>
-      </c>
       <c r="C146" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -11146,11 +11150,11 @@
         </is>
       </c>
       <c r="I146" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J146" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J146" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K146" s="2" t="inlineStr">
@@ -11180,12 +11184,12 @@
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
         <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="B147" s="2" t="inlineStr">
+        <is>
           <t>14/04/2026</t>
-        </is>
-      </c>
-      <c r="B147" s="2" t="inlineStr">
-        <is>
-          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C147" s="2" t="inlineStr">
@@ -11253,12 +11257,12 @@
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
         <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="B148" s="2" t="inlineStr">
+        <is>
           <t>13/04/2026</t>
-        </is>
-      </c>
-      <c r="B148" s="2" t="inlineStr">
-        <is>
-          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C148" s="2" t="inlineStr">
@@ -11326,12 +11330,12 @@
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
         <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="B149" s="2" t="inlineStr">
+        <is>
           <t>13/04/2026</t>
-        </is>
-      </c>
-      <c r="B149" s="2" t="inlineStr">
-        <is>
-          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C149" s="2" t="inlineStr">
@@ -11399,12 +11403,12 @@
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
         <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="B150" s="2" t="inlineStr">
+        <is>
           <t>12/04/2026</t>
-        </is>
-      </c>
-      <c r="B150" s="2" t="inlineStr">
-        <is>
-          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C150" s="2" t="inlineStr">
@@ -11440,9 +11444,9 @@
       <c r="I150" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="J150" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+      <c r="J150" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K150" s="2" t="inlineStr">
@@ -11472,12 +11476,12 @@
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
         <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="B151" s="2" t="inlineStr">
+        <is>
           <t>12/04/2026</t>
-        </is>
-      </c>
-      <c r="B151" s="2" t="inlineStr">
-        <is>
-          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C151" s="2" t="inlineStr">
@@ -11515,7 +11519,7 @@
       </c>
       <c r="J151" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K151" s="2" t="inlineStr">
@@ -11545,14 +11549,14 @@
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
         <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B152" s="2" t="inlineStr">
+        <is>
           <t>11/04/2026</t>
         </is>
       </c>
-      <c r="B152" s="2" t="inlineStr">
-        <is>
-          <t>10/04/2026</t>
-        </is>
-      </c>
       <c r="C152" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -11584,11 +11588,11 @@
         </is>
       </c>
       <c r="I152" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J152" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J152" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K152" s="2" t="inlineStr">
@@ -11618,14 +11622,14 @@
     <row r="153">
       <c r="A153" s="2" t="inlineStr">
         <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B153" s="2" t="inlineStr">
+        <is>
           <t>11/04/2026</t>
         </is>
       </c>
-      <c r="B153" s="2" t="inlineStr">
-        <is>
-          <t>10/04/2026</t>
-        </is>
-      </c>
       <c r="C153" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -11657,11 +11661,11 @@
         </is>
       </c>
       <c r="I153" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J153" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J153" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K153" s="2" t="inlineStr">
@@ -11691,14 +11695,14 @@
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
         <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="B154" s="2" t="inlineStr">
+        <is>
           <t>10/04/2026</t>
         </is>
       </c>
-      <c r="B154" s="2" t="inlineStr">
-        <is>
-          <t>09/04/2026</t>
-        </is>
-      </c>
       <c r="C154" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -11730,11 +11734,11 @@
         </is>
       </c>
       <c r="I154" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J154" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>1</v>
+      </c>
+      <c r="J154" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K154" s="2" t="inlineStr">
@@ -11764,14 +11768,14 @@
     <row r="155">
       <c r="A155" s="2" t="inlineStr">
         <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="B155" s="2" t="inlineStr">
+        <is>
           <t>10/04/2026</t>
         </is>
       </c>
-      <c r="B155" s="2" t="inlineStr">
-        <is>
-          <t>09/04/2026</t>
-        </is>
-      </c>
       <c r="C155" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -11803,11 +11807,11 @@
         </is>
       </c>
       <c r="I155" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J155" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J155" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K155" s="2" t="inlineStr">
@@ -11837,12 +11841,12 @@
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
         <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B156" s="2" t="inlineStr">
+        <is>
           <t>09/04/2026</t>
-        </is>
-      </c>
-      <c r="B156" s="2" t="inlineStr">
-        <is>
-          <t>08/04/2026</t>
         </is>
       </c>
       <c r="C156" s="2" t="inlineStr">
@@ -11878,9 +11882,9 @@
       <c r="I156" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="J156" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+      <c r="J156" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K156" s="2" t="inlineStr">
@@ -11910,14 +11914,14 @@
     <row r="157">
       <c r="A157" s="2" t="inlineStr">
         <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B157" s="2" t="inlineStr">
+        <is>
           <t>09/04/2026</t>
         </is>
       </c>
-      <c r="B157" s="2" t="inlineStr">
-        <is>
-          <t>08/04/2026</t>
-        </is>
-      </c>
       <c r="C157" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -11949,7 +11953,7 @@
         </is>
       </c>
       <c r="I157" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J157" s="2" t="inlineStr">
         <is>
@@ -11983,14 +11987,14 @@
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
         <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="B158" s="2" t="inlineStr">
+        <is>
           <t>08/04/2026</t>
         </is>
       </c>
-      <c r="B158" s="2" t="inlineStr">
-        <is>
-          <t>07/04/2026</t>
-        </is>
-      </c>
       <c r="C158" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -12016,17 +12020,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H158" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H158" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I158" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J158" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>2</v>
+      </c>
+      <c r="J158" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K158" s="2" t="inlineStr">
@@ -12056,14 +12060,14 @@
     <row r="159">
       <c r="A159" s="2" t="inlineStr">
         <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="B159" s="2" t="inlineStr">
+        <is>
           <t>08/04/2026</t>
         </is>
       </c>
-      <c r="B159" s="2" t="inlineStr">
-        <is>
-          <t>07/04/2026</t>
-        </is>
-      </c>
       <c r="C159" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -12097,9 +12101,9 @@
       <c r="I159" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J159" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J159" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K159" s="2" t="inlineStr">
@@ -12129,14 +12133,14 @@
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
         <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="B160" s="2" t="inlineStr">
+        <is>
           <t>07/04/2026</t>
         </is>
       </c>
-      <c r="B160" s="2" t="inlineStr">
-        <is>
-          <t>06/04/2026</t>
-        </is>
-      </c>
       <c r="C160" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -12159,38 +12163,38 @@
       </c>
       <c r="G160" s="2" t="inlineStr">
         <is>
-          <t>R$ 110,00</t>
-        </is>
-      </c>
-      <c r="H160" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H160" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I160" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J160" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+      <c r="J160" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K160" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L160" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M160" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N160" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O160" s="2" t="inlineStr">
@@ -12202,14 +12206,14 @@
     <row r="161">
       <c r="A161" s="2" t="inlineStr">
         <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="B161" s="2" t="inlineStr">
+        <is>
           <t>07/04/2026</t>
         </is>
       </c>
-      <c r="B161" s="2" t="inlineStr">
-        <is>
-          <t>06/04/2026</t>
-        </is>
-      </c>
       <c r="C161" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -12241,11 +12245,11 @@
         </is>
       </c>
       <c r="I161" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J161" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J161" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K161" s="2" t="inlineStr">
@@ -12275,14 +12279,14 @@
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
         <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="B162" s="2" t="inlineStr">
+        <is>
           <t>06/04/2026</t>
         </is>
       </c>
-      <c r="B162" s="2" t="inlineStr">
-        <is>
-          <t>05/04/2026</t>
-        </is>
-      </c>
       <c r="C162" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -12310,20 +12314,20 @@
       </c>
       <c r="H162" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I162" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J162" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J162" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K162" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="L162" s="2" t="n">
@@ -12331,12 +12335,12 @@
       </c>
       <c r="M162" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="N162" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O162" s="2" t="inlineStr">
@@ -12348,14 +12352,14 @@
     <row r="163">
       <c r="A163" s="2" t="inlineStr">
         <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="B163" s="2" t="inlineStr">
+        <is>
           <t>06/04/2026</t>
         </is>
       </c>
-      <c r="B163" s="2" t="inlineStr">
-        <is>
-          <t>05/04/2026</t>
-        </is>
-      </c>
       <c r="C163" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -12387,7 +12391,7 @@
         </is>
       </c>
       <c r="I163" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J163" s="2" t="inlineStr">
         <is>
@@ -12421,14 +12425,14 @@
     <row r="164">
       <c r="A164" s="2" t="inlineStr">
         <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="B164" s="2" t="inlineStr">
+        <is>
           <t>05/04/2026</t>
         </is>
       </c>
-      <c r="B164" s="2" t="inlineStr">
-        <is>
-          <t>04/04/2026</t>
-        </is>
-      </c>
       <c r="C164" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -12451,7 +12455,7 @@
       </c>
       <c r="G164" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 110,00</t>
         </is>
       </c>
       <c r="H164" s="2" t="inlineStr">
@@ -12460,24 +12464,24 @@
         </is>
       </c>
       <c r="I164" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J164" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
+        </is>
+      </c>
+      <c r="K164" s="2" t="inlineStr">
+        <is>
+          <t>50,0%</t>
+        </is>
+      </c>
+      <c r="L164" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J164" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K164" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L164" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="M164" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="N164" s="2" t="inlineStr">
@@ -12494,14 +12498,14 @@
     <row r="165">
       <c r="A165" s="2" t="inlineStr">
         <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="B165" s="2" t="inlineStr">
+        <is>
           <t>05/04/2026</t>
         </is>
       </c>
-      <c r="B165" s="2" t="inlineStr">
-        <is>
-          <t>04/04/2026</t>
-        </is>
-      </c>
       <c r="C165" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -12535,9 +12539,9 @@
       <c r="I165" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J165" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J165" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K165" s="2" t="inlineStr">
@@ -12567,14 +12571,14 @@
     <row r="166">
       <c r="A166" s="2" t="inlineStr">
         <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B166" s="2" t="inlineStr">
+        <is>
           <t>04/04/2026</t>
         </is>
       </c>
-      <c r="B166" s="2" t="inlineStr">
-        <is>
-          <t>03/04/2026</t>
-        </is>
-      </c>
       <c r="C166" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -12606,7 +12610,7 @@
         </is>
       </c>
       <c r="I166" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J166" s="2" t="inlineStr">
         <is>
@@ -12640,14 +12644,14 @@
     <row r="167">
       <c r="A167" s="2" t="inlineStr">
         <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B167" s="2" t="inlineStr">
+        <is>
           <t>04/04/2026</t>
         </is>
       </c>
-      <c r="B167" s="2" t="inlineStr">
-        <is>
-          <t>03/04/2026</t>
-        </is>
-      </c>
       <c r="C167" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -12679,11 +12683,11 @@
         </is>
       </c>
       <c r="I167" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J167" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J167" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K167" s="2" t="inlineStr">
@@ -12713,14 +12717,14 @@
     <row r="168">
       <c r="A168" s="2" t="inlineStr">
         <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B168" s="2" t="inlineStr">
+        <is>
           <t>03/04/2026</t>
         </is>
       </c>
-      <c r="B168" s="2" t="inlineStr">
-        <is>
-          <t>02/04/2026</t>
-        </is>
-      </c>
       <c r="C168" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -12754,9 +12758,9 @@
       <c r="I168" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J168" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J168" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K168" s="2" t="inlineStr">
@@ -12786,14 +12790,14 @@
     <row r="169">
       <c r="A169" s="2" t="inlineStr">
         <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B169" s="2" t="inlineStr">
+        <is>
           <t>03/04/2026</t>
         </is>
       </c>
-      <c r="B169" s="2" t="inlineStr">
-        <is>
-          <t>02/04/2026</t>
-        </is>
-      </c>
       <c r="C169" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -12825,11 +12829,11 @@
         </is>
       </c>
       <c r="I169" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J169" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J169" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K169" s="2" t="inlineStr">
@@ -12859,14 +12863,14 @@
     <row r="170">
       <c r="A170" s="2" t="inlineStr">
         <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B170" s="2" t="inlineStr">
+        <is>
           <t>02/04/2026</t>
         </is>
       </c>
-      <c r="B170" s="2" t="inlineStr">
-        <is>
-          <t>01/04/2026</t>
-        </is>
-      </c>
       <c r="C170" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -12898,11 +12902,11 @@
         </is>
       </c>
       <c r="I170" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J170" s="3" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K170" s="2" t="inlineStr">
@@ -12932,14 +12936,14 @@
     <row r="171">
       <c r="A171" s="2" t="inlineStr">
         <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B171" s="2" t="inlineStr">
+        <is>
           <t>02/04/2026</t>
         </is>
       </c>
-      <c r="B171" s="2" t="inlineStr">
-        <is>
-          <t>01/04/2026</t>
-        </is>
-      </c>
       <c r="C171" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -12971,11 +12975,11 @@
         </is>
       </c>
       <c r="I171" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J171" s="3" t="inlineStr">
         <is>
-          <t>▼ 66,7%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K171" s="2" t="inlineStr">
@@ -13005,14 +13009,14 @@
     <row r="172">
       <c r="A172" s="2" t="inlineStr">
         <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B172" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B172" s="2" t="inlineStr">
-        <is>
-          <t>31/03/2026</t>
-        </is>
-      </c>
       <c r="C172" s="2" t="inlineStr">
         <is>
           <t>UTD-145</t>
@@ -13044,11 +13048,11 @@
         </is>
       </c>
       <c r="I172" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J172" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>1</v>
+      </c>
+      <c r="J172" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K172" s="2" t="inlineStr">
@@ -13078,78 +13082,224 @@
     <row r="173">
       <c r="A173" s="2" t="inlineStr">
         <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B173" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B173" s="2" t="inlineStr">
+      <c r="C173" s="2" t="inlineStr">
+        <is>
+          <t>UTD-145</t>
+        </is>
+      </c>
+      <c r="D173" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor duplo com bica arthi</t>
+        </is>
+      </c>
+      <c r="E173" s="2" t="inlineStr">
+        <is>
+          <t>4498058823</t>
+        </is>
+      </c>
+      <c r="F173" s="2" t="inlineStr">
+        <is>
+          <t>R$ 157,65</t>
+        </is>
+      </c>
+      <c r="G173" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H173" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I173" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J173" s="3" t="inlineStr">
+        <is>
+          <t>▼ 66,7%</t>
+        </is>
+      </c>
+      <c r="K173" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L173" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M173" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N173" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O173" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B174" s="2" t="inlineStr">
         <is>
           <t>31/03/2026</t>
         </is>
       </c>
-      <c r="C173" s="2" t="inlineStr">
-        <is>
-          <t>UTD-145</t>
-        </is>
-      </c>
-      <c r="D173" s="2" t="inlineStr">
-        <is>
-          <t>Escorredor duplo com bica arthi</t>
-        </is>
-      </c>
-      <c r="E173" s="2" t="inlineStr">
+      <c r="C174" s="2" t="inlineStr">
+        <is>
+          <t>UTD-145</t>
+        </is>
+      </c>
+      <c r="D174" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor duplo com bica arthi</t>
+        </is>
+      </c>
+      <c r="E174" s="2" t="inlineStr">
+        <is>
+          <t>4645710434</t>
+        </is>
+      </c>
+      <c r="F174" s="2" t="inlineStr">
+        <is>
+          <t>R$ 157,65</t>
+        </is>
+      </c>
+      <c r="G174" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H174" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I174" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J174" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K174" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L174" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M174" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N174" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O174" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B175" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C175" s="2" t="inlineStr">
+        <is>
+          <t>UTD-145</t>
+        </is>
+      </c>
+      <c r="D175" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor duplo com bica arthi</t>
+        </is>
+      </c>
+      <c r="E175" s="2" t="inlineStr">
         <is>
           <t>4498058823</t>
         </is>
       </c>
-      <c r="F173" s="2" t="inlineStr">
-        <is>
-          <t>R$ 157,65</t>
-        </is>
-      </c>
-      <c r="G173" s="2" t="inlineStr">
-        <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H173" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I173" s="2" t="n">
+      <c r="F175" s="2" t="inlineStr">
+        <is>
+          <t>R$ 157,65</t>
+        </is>
+      </c>
+      <c r="G175" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H175" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I175" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="J173" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K173" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L173" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M173" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="N173" s="2" t="inlineStr">
+      <c r="J175" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K175" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L175" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M175" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N175" s="2" t="inlineStr">
         <is>
           <t>Sem calcular</t>
         </is>
       </c>
-      <c r="O173" s="2" t="inlineStr">
+      <c r="O175" s="2" t="inlineStr">
         <is>
           <t>Média</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O173"/>
+  <autoFilter ref="A1:O175"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/saida_skus/SKU_UTD-145-ESCORREDOR-DUPLO-COM-BICA-ARTHI.xlsx
+++ b/saida_skus/SKU_UTD-145-ESCORREDOR-DUPLO-COM-BICA-ARTHI.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Analise" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$175</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$183</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O175"/>
+  <dimension ref="A1:O183"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -559,12 +559,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>26/06/2026</t>
+          <t>30/06/2026</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>25/06/2026</t>
+          <t>29/06/2026</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -589,7 +589,7 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 107,00</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -598,24 +598,24 @@
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J2" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>1</v>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>▼ 75,0%</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="L2" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
@@ -632,12 +632,12 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>26/06/2026</t>
+          <t>30/06/2026</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>25/06/2026</t>
+          <t>29/06/2026</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -662,7 +662,7 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
@@ -670,10 +670,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I3" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I3" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
@@ -682,39 +680,37 @@
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L3" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L3" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>25/06/2026</t>
+          <t>29/06/2026</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>24/06/2026</t>
+          <t>28/06/2026</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -739,7 +735,7 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -747,51 +743,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I4" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="J4" s="4" t="inlineStr">
+        <is>
+          <t>▲ 300,0%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>25/06/2026</t>
+          <t>29/06/2026</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>24/06/2026</t>
+          <t>28/06/2026</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -827,9 +819,9 @@
       <c r="I5" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -859,12 +851,12 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>24/06/2026</t>
+          <t>28/06/2026</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>23/06/2026</t>
+          <t>27/06/2026</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -898,11 +890,11 @@
         </is>
       </c>
       <c r="I6" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -932,12 +924,12 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>24/06/2026</t>
+          <t>28/06/2026</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>23/06/2026</t>
+          <t>27/06/2026</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -971,11 +963,11 @@
         </is>
       </c>
       <c r="I7" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -1005,12 +997,12 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>23/06/2026</t>
+          <t>27/06/2026</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>22/06/2026</t>
+          <t>26/06/2026</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -1044,11 +1036,11 @@
         </is>
       </c>
       <c r="I8" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>1</v>
+      </c>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>▼ 85,7%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1078,12 +1070,12 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>23/06/2026</t>
+          <t>27/06/2026</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>22/06/2026</t>
+          <t>26/06/2026</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -1117,11 +1109,11 @@
         </is>
       </c>
       <c r="I9" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J9" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -1151,12 +1143,12 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>22/06/2026</t>
+          <t>26/06/2026</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>21/06/2026</t>
+          <t>25/06/2026</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -1190,11 +1182,11 @@
         </is>
       </c>
       <c r="I10" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>7</v>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1224,12 +1216,12 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>22/06/2026</t>
+          <t>26/06/2026</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>21/06/2026</t>
+          <t>25/06/2026</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -1254,7 +1246,7 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1262,47 +1254,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I11" s="2" t="n">
-        <v>2</v>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>21/06/2026</t>
+          <t>25/06/2026</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>20/06/2026</t>
+          <t>24/06/2026</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -1327,7 +1323,7 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -1335,8 +1331,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I12" s="2" t="n">
-        <v>1</v>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
@@ -1345,37 +1343,39 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>21/06/2026</t>
+          <t>25/06/2026</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>20/06/2026</t>
+          <t>24/06/2026</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -1409,7 +1409,7 @@
         </is>
       </c>
       <c r="I13" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
@@ -1443,12 +1443,12 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>20/06/2026</t>
+          <t>24/06/2026</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>19/06/2026</t>
+          <t>23/06/2026</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -1473,7 +1473,7 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -1481,10 +1481,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I14" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
@@ -1493,39 +1491,37 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>20/06/2026</t>
+          <t>24/06/2026</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>19/06/2026</t>
+          <t>23/06/2026</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1561,9 +1557,9 @@
       <c r="I15" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="J15" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -1593,12 +1589,12 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>19/06/2026</t>
+          <t>23/06/2026</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>18/06/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1666,12 +1662,12 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>19/06/2026</t>
+          <t>23/06/2026</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>18/06/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1705,11 +1701,11 @@
         </is>
       </c>
       <c r="I17" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
-          <t>▼ 100,0%</t>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -1739,12 +1735,12 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>18/06/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>17/06/2026</t>
+          <t>21/06/2026</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1769,7 +1765,7 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
@@ -1777,51 +1773,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I18" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>18/06/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>17/06/2026</t>
+          <t>21/06/2026</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -1855,7 +1847,7 @@
         </is>
       </c>
       <c r="I19" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
@@ -1889,12 +1881,12 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>17/06/2026</t>
+          <t>21/06/2026</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>16/06/2026</t>
+          <t>20/06/2026</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -1928,7 +1920,7 @@
         </is>
       </c>
       <c r="I20" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
@@ -1962,12 +1954,12 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>17/06/2026</t>
+          <t>21/06/2026</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>16/06/2026</t>
+          <t>20/06/2026</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -2001,11 +1993,11 @@
         </is>
       </c>
       <c r="I21" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
@@ -2035,12 +2027,12 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>16/06/2026</t>
+          <t>20/06/2026</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>19/06/2026</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -2065,7 +2057,7 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
@@ -2073,47 +2065,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I22" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J22" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>16/06/2026</t>
+          <t>20/06/2026</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>19/06/2026</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -2147,11 +2143,11 @@
         </is>
       </c>
       <c r="I23" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -2181,12 +2177,12 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>19/06/2026</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>14/06/2026</t>
+          <t>18/06/2026</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -2220,11 +2216,11 @@
         </is>
       </c>
       <c r="I24" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
@@ -2254,12 +2250,12 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>19/06/2026</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>14/06/2026</t>
+          <t>18/06/2026</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -2293,11 +2289,11 @@
         </is>
       </c>
       <c r="I25" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J25" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
@@ -2327,12 +2323,12 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>14/06/2026</t>
+          <t>18/06/2026</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>13/06/2026</t>
+          <t>17/06/2026</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -2357,7 +2353,7 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
@@ -2365,47 +2361,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I26" s="2" t="n">
-        <v>1</v>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>14/06/2026</t>
+          <t>18/06/2026</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>13/06/2026</t>
+          <t>17/06/2026</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -2441,9 +2441,9 @@
       <c r="I27" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J27" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
@@ -2473,12 +2473,12 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>13/06/2026</t>
+          <t>17/06/2026</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>12/06/2026</t>
+          <t>16/06/2026</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -2512,11 +2512,11 @@
         </is>
       </c>
       <c r="I28" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
@@ -2546,12 +2546,12 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>13/06/2026</t>
+          <t>17/06/2026</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>12/06/2026</t>
+          <t>16/06/2026</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -2585,11 +2585,11 @@
         </is>
       </c>
       <c r="I29" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -2619,12 +2619,12 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>12/06/2026</t>
+          <t>16/06/2026</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>11/06/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -2658,11 +2658,11 @@
         </is>
       </c>
       <c r="I30" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J30" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
@@ -2692,12 +2692,12 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>12/06/2026</t>
+          <t>16/06/2026</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>11/06/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -2731,11 +2731,11 @@
         </is>
       </c>
       <c r="I31" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>11/06/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>10/06/2026</t>
+          <t>14/06/2026</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -2806,9 +2806,9 @@
       <c r="I32" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J32" s="3" t="inlineStr">
-        <is>
-          <t>▼ 66,7%</t>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
@@ -2838,12 +2838,12 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>11/06/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>10/06/2026</t>
+          <t>14/06/2026</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -2877,11 +2877,11 @@
         </is>
       </c>
       <c r="I33" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
@@ -2911,12 +2911,12 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>10/06/2026</t>
+          <t>14/06/2026</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>09/06/2026</t>
+          <t>13/06/2026</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -2950,11 +2950,11 @@
         </is>
       </c>
       <c r="I34" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
@@ -2984,12 +2984,12 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>10/06/2026</t>
+          <t>14/06/2026</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>09/06/2026</t>
+          <t>13/06/2026</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -3017,17 +3017,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H35" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I35" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
-          <t>▼ 100,0%</t>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
@@ -3057,12 +3057,12 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>09/06/2026</t>
+          <t>13/06/2026</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>12/06/2026</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -3096,11 +3096,11 @@
         </is>
       </c>
       <c r="I36" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J36" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
@@ -3130,12 +3130,12 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>09/06/2026</t>
+          <t>13/06/2026</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>12/06/2026</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -3160,7 +3160,7 @@
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>R$ 107,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
@@ -3171,22 +3171,22 @@
       <c r="I37" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="J37" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L37" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -3203,12 +3203,12 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>12/06/2026</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>07/06/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -3242,11 +3242,11 @@
         </is>
       </c>
       <c r="I38" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
@@ -3276,12 +3276,12 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>12/06/2026</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>07/06/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -3315,7 +3315,7 @@
         </is>
       </c>
       <c r="I39" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
@@ -3349,12 +3349,12 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>07/06/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>06/06/2026</t>
+          <t>10/06/2026</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -3388,11 +3388,11 @@
         </is>
       </c>
       <c r="I40" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
-          <t>▼ 100,0%</t>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
@@ -3422,12 +3422,12 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>07/06/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>06/06/2026</t>
+          <t>10/06/2026</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -3463,9 +3463,9 @@
       <c r="I41" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J41" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J41" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
@@ -3495,12 +3495,12 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>06/06/2026</t>
+          <t>10/06/2026</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>05/06/2026</t>
+          <t>09/06/2026</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -3534,11 +3534,11 @@
         </is>
       </c>
       <c r="I42" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
@@ -3568,12 +3568,12 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>06/06/2026</t>
+          <t>10/06/2026</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>05/06/2026</t>
+          <t>09/06/2026</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -3601,17 +3601,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H43" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H43" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I43" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J43" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J43" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr">
@@ -3641,12 +3641,12 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>05/06/2026</t>
+          <t>09/06/2026</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>04/06/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -3680,11 +3680,11 @@
         </is>
       </c>
       <c r="I44" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J44" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J44" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
@@ -3714,12 +3714,12 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>05/06/2026</t>
+          <t>09/06/2026</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>04/06/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -3744,7 +3744,7 @@
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 107,00</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
@@ -3753,24 +3753,24 @@
         </is>
       </c>
       <c r="I45" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J45" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>2</v>
+      </c>
+      <c r="J45" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>50,0%</t>
         </is>
       </c>
       <c r="L45" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -3787,12 +3787,12 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>04/06/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>03/06/2026</t>
+          <t>07/06/2026</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -3826,11 +3826,11 @@
         </is>
       </c>
       <c r="I46" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J46" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>3</v>
+      </c>
+      <c r="J46" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
@@ -3860,12 +3860,12 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>04/06/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>03/06/2026</t>
+          <t>07/06/2026</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -3899,11 +3899,11 @@
         </is>
       </c>
       <c r="I47" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J47" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J47" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K47" s="2" t="inlineStr">
@@ -3933,12 +3933,12 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>03/06/2026</t>
+          <t>07/06/2026</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>02/06/2026</t>
+          <t>06/06/2026</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -3972,11 +3972,11 @@
         </is>
       </c>
       <c r="I48" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J48" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J48" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr">
@@ -4006,12 +4006,12 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>03/06/2026</t>
+          <t>07/06/2026</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>02/06/2026</t>
+          <t>06/06/2026</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -4045,11 +4045,11 @@
         </is>
       </c>
       <c r="I49" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J49" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J49" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K49" s="2" t="inlineStr">
@@ -4079,12 +4079,12 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>02/06/2026</t>
+          <t>06/06/2026</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>01/06/2026</t>
+          <t>05/06/2026</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -4112,17 +4112,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H50" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I50" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J50" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J50" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K50" s="2" t="inlineStr">
@@ -4152,12 +4152,12 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>02/06/2026</t>
+          <t>06/06/2026</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>01/06/2026</t>
+          <t>05/06/2026</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -4195,7 +4195,7 @@
       </c>
       <c r="J51" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K51" s="2" t="inlineStr">
@@ -4225,12 +4225,12 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>01/06/2026</t>
+          <t>05/06/2026</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>31/05/2026</t>
+          <t>04/06/2026</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -4255,7 +4255,7 @@
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>R$ 126,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
@@ -4273,15 +4273,15 @@
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L52" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -4298,12 +4298,12 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>01/06/2026</t>
+          <t>05/06/2026</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>31/05/2026</t>
+          <t>04/06/2026</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -4337,11 +4337,11 @@
         </is>
       </c>
       <c r="I53" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J53" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K53" s="2" t="inlineStr">
@@ -4371,12 +4371,12 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>31/05/2026</t>
+          <t>04/06/2026</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>30/05/2026</t>
+          <t>03/06/2026</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -4404,9 +4404,9 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H54" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I54" s="2" t="n">
@@ -4444,12 +4444,12 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>31/05/2026</t>
+          <t>04/06/2026</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>30/05/2026</t>
+          <t>03/06/2026</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -4483,11 +4483,11 @@
         </is>
       </c>
       <c r="I55" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J55" s="3" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K55" s="2" t="inlineStr">
@@ -4517,12 +4517,12 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>30/05/2026</t>
+          <t>03/06/2026</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>29/05/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -4547,7 +4547,7 @@
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>R$ 126,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
@@ -4558,22 +4558,22 @@
       <c r="I56" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J56" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+      <c r="J56" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L56" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -4590,12 +4590,12 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>30/05/2026</t>
+          <t>03/06/2026</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>29/05/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -4629,11 +4629,11 @@
         </is>
       </c>
       <c r="I57" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J57" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K57" s="2" t="inlineStr">
@@ -4663,12 +4663,12 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>29/05/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>28/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -4696,17 +4696,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H58" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H58" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I58" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J58" s="3" t="inlineStr">
         <is>
-          <t>▼ 33,3%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr">
@@ -4736,12 +4736,12 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>29/05/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>28/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -4775,11 +4775,11 @@
         </is>
       </c>
       <c r="I59" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J59" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J59" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K59" s="2" t="inlineStr">
@@ -4809,12 +4809,12 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>28/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>27/05/2026</t>
+          <t>31/05/2026</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -4839,7 +4839,7 @@
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 126,00</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
@@ -4848,7 +4848,7 @@
         </is>
       </c>
       <c r="I60" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J60" s="2" t="inlineStr">
         <is>
@@ -4857,15 +4857,15 @@
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="L60" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr">
@@ -4882,12 +4882,12 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>28/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>27/05/2026</t>
+          <t>31/05/2026</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -4923,9 +4923,9 @@
       <c r="I61" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J61" s="3" t="inlineStr">
-        <is>
-          <t>▼ 66,7%</t>
+      <c r="J61" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K61" s="2" t="inlineStr">
@@ -4955,12 +4955,12 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>27/05/2026</t>
+          <t>31/05/2026</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>26/05/2026</t>
+          <t>30/05/2026</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -4988,9 +4988,9 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H62" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H62" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I62" s="2" t="n">
@@ -5028,12 +5028,12 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>27/05/2026</t>
+          <t>31/05/2026</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>26/05/2026</t>
+          <t>30/05/2026</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -5067,11 +5067,11 @@
         </is>
       </c>
       <c r="I63" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J63" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>1</v>
+      </c>
+      <c r="J63" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K63" s="2" t="inlineStr">
@@ -5101,12 +5101,12 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>26/05/2026</t>
+          <t>30/05/2026</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>25/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -5131,7 +5131,7 @@
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 126,00</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
@@ -5140,24 +5140,24 @@
         </is>
       </c>
       <c r="I64" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J64" s="4" t="inlineStr">
-        <is>
-          <t>▲ 50,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J64" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="L64" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
@@ -5174,12 +5174,12 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>26/05/2026</t>
+          <t>30/05/2026</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>25/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -5213,11 +5213,11 @@
         </is>
       </c>
       <c r="I65" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J65" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J65" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K65" s="2" t="inlineStr">
@@ -5247,12 +5247,12 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>25/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>24/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -5288,9 +5288,9 @@
       <c r="I66" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="J66" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+      <c r="J66" s="3" t="inlineStr">
+        <is>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="K66" s="2" t="inlineStr">
@@ -5320,12 +5320,12 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>25/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>24/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -5359,11 +5359,11 @@
         </is>
       </c>
       <c r="I67" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J67" s="3" t="inlineStr">
         <is>
-          <t>▼ 83,3%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K67" s="2" t="inlineStr">
@@ -5393,12 +5393,12 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>24/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>23/05/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -5426,17 +5426,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H68" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H68" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I68" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J68" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+        <v>3</v>
+      </c>
+      <c r="J68" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K68" s="2" t="inlineStr">
@@ -5466,12 +5466,12 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>24/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>23/05/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -5505,11 +5505,11 @@
         </is>
       </c>
       <c r="I69" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J69" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J69" s="3" t="inlineStr">
+        <is>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K69" s="2" t="inlineStr">
@@ -5539,12 +5539,12 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>23/05/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
@@ -5569,7 +5569,7 @@
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>R$ 126,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
@@ -5578,24 +5578,24 @@
         </is>
       </c>
       <c r="I70" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J70" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J70" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L70" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N70" s="2" t="inlineStr">
@@ -5612,12 +5612,12 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>23/05/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -5655,7 +5655,7 @@
       </c>
       <c r="J71" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K71" s="2" t="inlineStr">
@@ -5685,12 +5685,12 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
@@ -5724,11 +5724,11 @@
         </is>
       </c>
       <c r="I72" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J72" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+        <v>3</v>
+      </c>
+      <c r="J72" s="4" t="inlineStr">
+        <is>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr">
@@ -5758,12 +5758,12 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -5797,11 +5797,11 @@
         </is>
       </c>
       <c r="I73" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J73" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J73" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K73" s="2" t="inlineStr">
@@ -5831,12 +5831,12 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>24/05/2026</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -5872,9 +5872,9 @@
       <c r="I74" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="J74" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="J74" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr">
@@ -5904,12 +5904,12 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>24/05/2026</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -5943,11 +5943,11 @@
         </is>
       </c>
       <c r="I75" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J75" s="3" t="inlineStr">
         <is>
-          <t>▼ 100,0%</t>
+          <t>▼ 83,3%</t>
         </is>
       </c>
       <c r="K75" s="2" t="inlineStr">
@@ -5977,12 +5977,12 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>24/05/2026</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>23/05/2026</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -6010,17 +6010,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H76" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H76" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I76" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J76" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>1</v>
+      </c>
+      <c r="J76" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K76" s="2" t="inlineStr">
@@ -6050,12 +6050,12 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>24/05/2026</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>23/05/2026</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
@@ -6089,11 +6089,11 @@
         </is>
       </c>
       <c r="I77" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J77" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>6</v>
+      </c>
+      <c r="J77" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K77" s="2" t="inlineStr">
@@ -6123,12 +6123,12 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>23/05/2026</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
@@ -6153,7 +6153,7 @@
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 126,00</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
@@ -6162,24 +6162,24 @@
         </is>
       </c>
       <c r="I78" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J78" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>2</v>
+      </c>
+      <c r="J78" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K78" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>50,0%</t>
         </is>
       </c>
       <c r="L78" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M78" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="N78" s="2" t="inlineStr">
@@ -6196,12 +6196,12 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>23/05/2026</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
@@ -6235,11 +6235,11 @@
         </is>
       </c>
       <c r="I79" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J79" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K79" s="2" t="inlineStr">
@@ -6269,12 +6269,12 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
@@ -6308,11 +6308,11 @@
         </is>
       </c>
       <c r="I80" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J80" s="3" t="inlineStr">
         <is>
-          <t>▼ 100,0%</t>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K80" s="2" t="inlineStr">
@@ -6342,12 +6342,12 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
@@ -6381,7 +6381,7 @@
         </is>
       </c>
       <c r="I81" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J81" s="2" t="inlineStr">
         <is>
@@ -6415,12 +6415,12 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
@@ -6454,7 +6454,7 @@
         </is>
       </c>
       <c r="I82" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J82" s="2" t="inlineStr">
         <is>
@@ -6488,12 +6488,12 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
@@ -6518,7 +6518,7 @@
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr">
@@ -6526,51 +6526,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I83" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J83" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I83" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J83" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K83" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L83" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L83" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M83" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N83" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
@@ -6606,9 +6602,9 @@
       <c r="I84" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J84" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J84" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K84" s="2" t="inlineStr">
@@ -6638,12 +6634,12 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
@@ -6677,7 +6673,7 @@
         </is>
       </c>
       <c r="I85" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J85" s="2" t="inlineStr">
         <is>
@@ -6711,12 +6707,12 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
@@ -6750,7 +6746,7 @@
         </is>
       </c>
       <c r="I86" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J86" s="2" t="inlineStr">
         <is>
@@ -6784,12 +6780,12 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
@@ -6825,9 +6821,9 @@
       <c r="I87" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J87" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J87" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K87" s="2" t="inlineStr">
@@ -6857,12 +6853,12 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
@@ -6930,12 +6926,12 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
@@ -6969,7 +6965,7 @@
         </is>
       </c>
       <c r="I89" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J89" s="2" t="inlineStr">
         <is>
@@ -7003,12 +6999,12 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
@@ -7076,12 +7072,12 @@
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
@@ -7153,12 +7149,12 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
@@ -7226,12 +7222,12 @@
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
@@ -7256,7 +7252,7 @@
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H93" s="2" t="inlineStr">
@@ -7264,10 +7260,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I93" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I93" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J93" s="2" t="inlineStr">
         <is>
@@ -7276,39 +7270,37 @@
       </c>
       <c r="K93" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L93" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L93" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M93" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N93" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
@@ -7376,12 +7368,12 @@
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
@@ -7417,9 +7409,9 @@
       <c r="I95" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J95" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="J95" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K95" s="2" t="inlineStr">
@@ -7449,12 +7441,12 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
@@ -7479,7 +7471,7 @@
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H96" s="2" t="inlineStr">
@@ -7487,51 +7479,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I96" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J96" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I96" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J96" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K96" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L96" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L96" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M96" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N96" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
@@ -7559,17 +7547,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H97" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H97" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I97" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J97" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J97" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K97" s="2" t="inlineStr">
@@ -7599,12 +7587,12 @@
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
@@ -7638,7 +7626,7 @@
         </is>
       </c>
       <c r="I98" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J98" s="2" t="inlineStr">
         <is>
@@ -7672,12 +7660,12 @@
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
@@ -7702,7 +7690,7 @@
       </c>
       <c r="G99" s="2" t="inlineStr">
         <is>
-          <t>R$ 110,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H99" s="2" t="inlineStr">
@@ -7710,8 +7698,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I99" s="2" t="n">
-        <v>2</v>
+      <c r="I99" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J99" s="2" t="inlineStr">
         <is>
@@ -7720,37 +7710,39 @@
       </c>
       <c r="K99" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
-        </is>
-      </c>
-      <c r="L99" s="2" t="n">
-        <v>1</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L99" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M99" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N99" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
@@ -7778,9 +7770,9 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H100" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H100" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I100" s="2" t="n">
@@ -7818,12 +7810,12 @@
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
@@ -7848,7 +7840,7 @@
       </c>
       <c r="G101" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H101" s="2" t="inlineStr">
@@ -7856,47 +7848,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I101" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J101" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="I101" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J101" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K101" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L101" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L101" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M101" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N101" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
@@ -7921,7 +7917,7 @@
       </c>
       <c r="G102" s="2" t="inlineStr">
         <is>
-          <t>R$ 110,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H102" s="2" t="inlineStr">
@@ -7932,22 +7928,22 @@
       <c r="I102" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J102" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+      <c r="J102" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K102" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L102" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M102" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N102" s="2" t="inlineStr">
@@ -7964,12 +7960,12 @@
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C103" s="2" t="inlineStr">
@@ -8003,7 +7999,7 @@
         </is>
       </c>
       <c r="I103" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J103" s="2" t="inlineStr">
         <is>
@@ -8037,12 +8033,12 @@
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C104" s="2" t="inlineStr">
@@ -8067,7 +8063,7 @@
       </c>
       <c r="G104" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H104" s="2" t="inlineStr">
@@ -8075,47 +8071,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I104" s="2" t="n">
-        <v>2</v>
+      <c r="I104" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J104" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K104" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L104" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L104" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M104" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N104" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C105" s="2" t="inlineStr">
@@ -8143,9 +8143,9 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H105" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H105" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I105" s="2" t="n">
@@ -8183,12 +8183,12 @@
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C106" s="2" t="inlineStr">
@@ -8222,7 +8222,7 @@
         </is>
       </c>
       <c r="I106" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J106" s="2" t="inlineStr">
         <is>
@@ -8256,12 +8256,12 @@
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C107" s="2" t="inlineStr">
@@ -8286,7 +8286,7 @@
       </c>
       <c r="G107" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 110,00</t>
         </is>
       </c>
       <c r="H107" s="2" t="inlineStr">
@@ -8304,15 +8304,15 @@
       </c>
       <c r="K107" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>50,0%</t>
         </is>
       </c>
       <c r="L107" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M107" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="N107" s="2" t="inlineStr">
@@ -8329,12 +8329,12 @@
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C108" s="2" t="inlineStr">
@@ -8362,17 +8362,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H108" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H108" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I108" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J108" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="J108" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K108" s="2" t="inlineStr">
@@ -8402,12 +8402,12 @@
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C109" s="2" t="inlineStr">
@@ -8475,12 +8475,12 @@
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C110" s="2" t="inlineStr">
@@ -8505,7 +8505,7 @@
       </c>
       <c r="G110" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 110,00</t>
         </is>
       </c>
       <c r="H110" s="2" t="inlineStr">
@@ -8514,24 +8514,24 @@
         </is>
       </c>
       <c r="I110" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J110" s="3" t="inlineStr">
         <is>
-          <t>▼ 100,0%</t>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K110" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="L110" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M110" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="N110" s="2" t="inlineStr">
@@ -8548,12 +8548,12 @@
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C111" s="2" t="inlineStr">
@@ -8591,7 +8591,7 @@
       </c>
       <c r="J111" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K111" s="2" t="inlineStr">
@@ -8621,12 +8621,12 @@
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C112" s="2" t="inlineStr">
@@ -8694,12 +8694,12 @@
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C113" s="2" t="inlineStr">
@@ -8733,11 +8733,11 @@
         </is>
       </c>
       <c r="I113" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J113" s="3" t="inlineStr">
         <is>
-          <t>▼ 66,7%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K113" s="2" t="inlineStr">
@@ -8767,12 +8767,12 @@
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C114" s="2" t="inlineStr">
@@ -8840,12 +8840,12 @@
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C115" s="2" t="inlineStr">
@@ -8879,11 +8879,11 @@
         </is>
       </c>
       <c r="I115" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J115" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J115" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K115" s="2" t="inlineStr">
@@ -8913,12 +8913,12 @@
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C116" s="2" t="inlineStr">
@@ -8954,9 +8954,9 @@
       <c r="I116" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J116" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J116" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K116" s="2" t="inlineStr">
@@ -8986,12 +8986,12 @@
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C117" s="2" t="inlineStr">
@@ -9025,11 +9025,11 @@
         </is>
       </c>
       <c r="I117" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J117" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J117" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K117" s="2" t="inlineStr">
@@ -9059,12 +9059,12 @@
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C118" s="2" t="inlineStr">
@@ -9098,11 +9098,11 @@
         </is>
       </c>
       <c r="I118" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J118" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J118" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K118" s="2" t="inlineStr">
@@ -9125,19 +9125,19 @@
       </c>
       <c r="O118" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C119" s="2" t="inlineStr">
@@ -9171,11 +9171,11 @@
         </is>
       </c>
       <c r="I119" s="2" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="J119" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K119" s="2" t="inlineStr">
@@ -9198,19 +9198,19 @@
       </c>
       <c r="O119" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C120" s="2" t="inlineStr">
@@ -9244,11 +9244,11 @@
         </is>
       </c>
       <c r="I120" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J120" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J120" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K120" s="2" t="inlineStr">
@@ -9271,19 +9271,19 @@
       </c>
       <c r="O120" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C121" s="2" t="inlineStr">
@@ -9317,11 +9317,11 @@
         </is>
       </c>
       <c r="I121" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J121" s="3" t="inlineStr">
         <is>
-          <t>▼ 100,0%</t>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K121" s="2" t="inlineStr">
@@ -9344,19 +9344,19 @@
       </c>
       <c r="O121" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C122" s="2" t="inlineStr">
@@ -9394,7 +9394,7 @@
       </c>
       <c r="J122" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K122" s="2" t="inlineStr">
@@ -9417,19 +9417,19 @@
       </c>
       <c r="O122" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="B123" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C123" s="2" t="inlineStr">
@@ -9463,11 +9463,11 @@
         </is>
       </c>
       <c r="I123" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J123" s="3" t="inlineStr">
         <is>
-          <t>▼ 66,7%</t>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K123" s="2" t="inlineStr">
@@ -9490,19 +9490,19 @@
       </c>
       <c r="O123" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C124" s="2" t="inlineStr">
@@ -9536,11 +9536,11 @@
         </is>
       </c>
       <c r="I124" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J124" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J124" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K124" s="2" t="inlineStr">
@@ -9563,19 +9563,19 @@
       </c>
       <c r="O124" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="B125" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C125" s="2" t="inlineStr">
@@ -9609,11 +9609,11 @@
         </is>
       </c>
       <c r="I125" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J125" s="4" t="inlineStr">
-        <is>
-          <t>▲ 200,0%</t>
+        <v>6</v>
+      </c>
+      <c r="J125" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K125" s="2" t="inlineStr">
@@ -9636,19 +9636,19 @@
       </c>
       <c r="O125" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C126" s="2" t="inlineStr">
@@ -9682,11 +9682,11 @@
         </is>
       </c>
       <c r="I126" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J126" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J126" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K126" s="2" t="inlineStr">
@@ -9716,12 +9716,12 @@
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B127" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C127" s="2" t="inlineStr">
@@ -9755,7 +9755,7 @@
         </is>
       </c>
       <c r="I127" s="2" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="J127" s="2" t="inlineStr">
         <is>
@@ -9789,12 +9789,12 @@
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="B128" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C128" s="2" t="inlineStr">
@@ -9862,12 +9862,12 @@
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="B129" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C129" s="2" t="inlineStr">
@@ -9892,7 +9892,7 @@
       </c>
       <c r="G129" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H129" s="2" t="inlineStr">
@@ -9900,51 +9900,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I129" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J129" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I129" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J129" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K129" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L129" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L129" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M129" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N129" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O129" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="B130" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C130" s="2" t="inlineStr">
@@ -9980,9 +9976,9 @@
       <c r="I130" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="J130" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+      <c r="J130" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K130" s="2" t="inlineStr">
@@ -10012,12 +10008,12 @@
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="B131" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C131" s="2" t="inlineStr">
@@ -10042,7 +10038,7 @@
       </c>
       <c r="G131" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H131" s="2" t="inlineStr">
@@ -10050,51 +10046,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I131" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J131" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I131" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J131" s="3" t="inlineStr">
+        <is>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K131" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L131" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L131" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M131" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N131" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O131" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="B132" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C132" s="2" t="inlineStr">
@@ -10128,11 +10120,11 @@
         </is>
       </c>
       <c r="I132" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J132" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J132" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K132" s="2" t="inlineStr">
@@ -10162,12 +10154,12 @@
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="B133" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C133" s="2" t="inlineStr">
@@ -10201,11 +10193,11 @@
         </is>
       </c>
       <c r="I133" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J133" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>3</v>
+      </c>
+      <c r="J133" s="4" t="inlineStr">
+        <is>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="K133" s="2" t="inlineStr">
@@ -10235,12 +10227,12 @@
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="B134" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C134" s="2" t="inlineStr">
@@ -10276,9 +10268,9 @@
       <c r="I134" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="J134" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="J134" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K134" s="2" t="inlineStr">
@@ -10296,7 +10288,7 @@
       </c>
       <c r="N134" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O134" s="2" t="inlineStr">
@@ -10308,12 +10300,12 @@
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="B135" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C135" s="2" t="inlineStr">
@@ -10347,11 +10339,11 @@
         </is>
       </c>
       <c r="I135" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J135" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J135" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K135" s="2" t="inlineStr">
@@ -10381,12 +10373,12 @@
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="B136" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C136" s="2" t="inlineStr">
@@ -10420,11 +10412,11 @@
         </is>
       </c>
       <c r="I136" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J136" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>1</v>
+      </c>
+      <c r="J136" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K136" s="2" t="inlineStr">
@@ -10454,12 +10446,12 @@
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="B137" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C137" s="2" t="inlineStr">
@@ -10484,7 +10476,7 @@
       </c>
       <c r="G137" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H137" s="2" t="inlineStr">
@@ -10492,47 +10484,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I137" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J137" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+      <c r="I137" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J137" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K137" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L137" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L137" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M137" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N137" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O137" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="B138" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C138" s="2" t="inlineStr">
@@ -10566,11 +10562,11 @@
         </is>
       </c>
       <c r="I138" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J138" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>2</v>
+      </c>
+      <c r="J138" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K138" s="2" t="inlineStr">
@@ -10600,12 +10596,12 @@
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="B139" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C139" s="2" t="inlineStr">
@@ -10630,7 +10626,7 @@
       </c>
       <c r="G139" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H139" s="2" t="inlineStr">
@@ -10638,8 +10634,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I139" s="2" t="n">
-        <v>2</v>
+      <c r="I139" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J139" s="2" t="inlineStr">
         <is>
@@ -10648,37 +10646,39 @@
       </c>
       <c r="K139" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L139" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L139" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M139" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N139" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O139" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="B140" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C140" s="2" t="inlineStr">
@@ -10712,11 +10712,11 @@
         </is>
       </c>
       <c r="I140" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J140" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>1</v>
+      </c>
+      <c r="J140" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K140" s="2" t="inlineStr">
@@ -10746,12 +10746,12 @@
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="B141" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C141" s="2" t="inlineStr">
@@ -10819,12 +10819,12 @@
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="B142" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C142" s="2" t="inlineStr">
@@ -10858,11 +10858,11 @@
         </is>
       </c>
       <c r="I142" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J142" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J142" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K142" s="2" t="inlineStr">
@@ -10880,7 +10880,7 @@
       </c>
       <c r="N142" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O142" s="2" t="inlineStr">
@@ -10892,12 +10892,12 @@
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="B143" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C143" s="2" t="inlineStr">
@@ -10965,12 +10965,12 @@
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="B144" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C144" s="2" t="inlineStr">
@@ -11004,7 +11004,7 @@
         </is>
       </c>
       <c r="I144" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J144" s="2" t="inlineStr">
         <is>
@@ -11038,12 +11038,12 @@
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="B145" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C145" s="2" t="inlineStr">
@@ -11077,11 +11077,11 @@
         </is>
       </c>
       <c r="I145" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J145" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>4</v>
+      </c>
+      <c r="J145" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K145" s="2" t="inlineStr">
@@ -11111,12 +11111,12 @@
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="B146" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C146" s="2" t="inlineStr">
@@ -11152,9 +11152,9 @@
       <c r="I146" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J146" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J146" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K146" s="2" t="inlineStr">
@@ -11184,12 +11184,12 @@
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="B147" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C147" s="2" t="inlineStr">
@@ -11223,11 +11223,11 @@
         </is>
       </c>
       <c r="I147" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J147" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K147" s="2" t="inlineStr">
@@ -11257,12 +11257,12 @@
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="B148" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C148" s="2" t="inlineStr">
@@ -11296,11 +11296,11 @@
         </is>
       </c>
       <c r="I148" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J148" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K148" s="2" t="inlineStr">
@@ -11330,12 +11330,12 @@
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="B149" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C149" s="2" t="inlineStr">
@@ -11369,11 +11369,11 @@
         </is>
       </c>
       <c r="I149" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J149" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K149" s="2" t="inlineStr">
@@ -11403,12 +11403,12 @@
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="B150" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C150" s="2" t="inlineStr">
@@ -11442,11 +11442,11 @@
         </is>
       </c>
       <c r="I150" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J150" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J150" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K150" s="2" t="inlineStr">
@@ -11476,12 +11476,12 @@
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="B151" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C151" s="2" t="inlineStr">
@@ -11515,11 +11515,11 @@
         </is>
       </c>
       <c r="I151" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J151" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J151" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K151" s="2" t="inlineStr">
@@ -11549,12 +11549,12 @@
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="B152" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C152" s="2" t="inlineStr">
@@ -11590,9 +11590,9 @@
       <c r="I152" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="J152" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+      <c r="J152" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K152" s="2" t="inlineStr">
@@ -11622,12 +11622,12 @@
     <row r="153">
       <c r="A153" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="B153" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C153" s="2" t="inlineStr">
@@ -11665,7 +11665,7 @@
       </c>
       <c r="J153" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K153" s="2" t="inlineStr">
@@ -11695,12 +11695,12 @@
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="B154" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C154" s="2" t="inlineStr">
@@ -11734,11 +11734,11 @@
         </is>
       </c>
       <c r="I154" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J154" s="3" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K154" s="2" t="inlineStr">
@@ -11768,12 +11768,12 @@
     <row r="155">
       <c r="A155" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="B155" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C155" s="2" t="inlineStr">
@@ -11807,11 +11807,11 @@
         </is>
       </c>
       <c r="I155" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J155" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J155" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K155" s="2" t="inlineStr">
@@ -11841,12 +11841,12 @@
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="B156" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C156" s="2" t="inlineStr">
@@ -11914,12 +11914,12 @@
     <row r="157">
       <c r="A157" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="B157" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C157" s="2" t="inlineStr">
@@ -11953,11 +11953,11 @@
         </is>
       </c>
       <c r="I157" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J157" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K157" s="2" t="inlineStr">
@@ -11987,12 +11987,12 @@
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="B158" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C158" s="2" t="inlineStr">
@@ -12028,9 +12028,9 @@
       <c r="I158" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="J158" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+      <c r="J158" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K158" s="2" t="inlineStr">
@@ -12060,12 +12060,12 @@
     <row r="159">
       <c r="A159" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="B159" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C159" s="2" t="inlineStr">
@@ -12099,11 +12099,11 @@
         </is>
       </c>
       <c r="I159" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J159" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K159" s="2" t="inlineStr">
@@ -12133,12 +12133,12 @@
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="B160" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C160" s="2" t="inlineStr">
@@ -12166,17 +12166,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H160" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H160" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I160" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J160" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>2</v>
+      </c>
+      <c r="J160" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K160" s="2" t="inlineStr">
@@ -12206,12 +12206,12 @@
     <row r="161">
       <c r="A161" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="B161" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C161" s="2" t="inlineStr">
@@ -12245,11 +12245,11 @@
         </is>
       </c>
       <c r="I161" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J161" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J161" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K161" s="2" t="inlineStr">
@@ -12279,12 +12279,12 @@
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="B162" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="C162" s="2" t="inlineStr">
@@ -12309,12 +12309,12 @@
       </c>
       <c r="G162" s="2" t="inlineStr">
         <is>
-          <t>R$ 110,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H162" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I162" s="2" t="n">
@@ -12327,20 +12327,20 @@
       </c>
       <c r="K162" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L162" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M162" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N162" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O162" s="2" t="inlineStr">
@@ -12352,12 +12352,12 @@
     <row r="163">
       <c r="A163" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="B163" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="C163" s="2" t="inlineStr">
@@ -12391,11 +12391,11 @@
         </is>
       </c>
       <c r="I163" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J163" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J163" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K163" s="2" t="inlineStr">
@@ -12425,12 +12425,12 @@
     <row r="164">
       <c r="A164" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="B164" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="C164" s="2" t="inlineStr">
@@ -12455,7 +12455,7 @@
       </c>
       <c r="G164" s="2" t="inlineStr">
         <is>
-          <t>R$ 110,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H164" s="2" t="inlineStr">
@@ -12466,22 +12466,22 @@
       <c r="I164" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="J164" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+      <c r="J164" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K164" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L164" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M164" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N164" s="2" t="inlineStr">
@@ -12498,12 +12498,12 @@
     <row r="165">
       <c r="A165" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="B165" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="C165" s="2" t="inlineStr">
@@ -12537,7 +12537,7 @@
         </is>
       </c>
       <c r="I165" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J165" s="2" t="inlineStr">
         <is>
@@ -12571,12 +12571,12 @@
     <row r="166">
       <c r="A166" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="B166" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="C166" s="2" t="inlineStr">
@@ -12610,11 +12610,11 @@
         </is>
       </c>
       <c r="I166" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J166" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>2</v>
+      </c>
+      <c r="J166" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K166" s="2" t="inlineStr">
@@ -12644,12 +12644,12 @@
     <row r="167">
       <c r="A167" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="B167" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="C167" s="2" t="inlineStr">
@@ -12685,9 +12685,9 @@
       <c r="I167" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J167" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J167" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K167" s="2" t="inlineStr">
@@ -12717,12 +12717,12 @@
     <row r="168">
       <c r="A168" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="B168" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="C168" s="2" t="inlineStr">
@@ -12750,17 +12750,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H168" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H168" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I168" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J168" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K168" s="2" t="inlineStr">
@@ -12790,12 +12790,12 @@
     <row r="169">
       <c r="A169" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="B169" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="C169" s="2" t="inlineStr">
@@ -12829,11 +12829,11 @@
         </is>
       </c>
       <c r="I169" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J169" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J169" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K169" s="2" t="inlineStr">
@@ -12863,12 +12863,12 @@
     <row r="170">
       <c r="A170" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="B170" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="C170" s="2" t="inlineStr">
@@ -12893,38 +12893,38 @@
       </c>
       <c r="G170" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 110,00</t>
         </is>
       </c>
       <c r="H170" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I170" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J170" s="3" t="inlineStr">
         <is>
-          <t>▼ 100,0%</t>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K170" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="L170" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M170" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="N170" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O170" s="2" t="inlineStr">
@@ -12936,12 +12936,12 @@
     <row r="171">
       <c r="A171" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="B171" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="C171" s="2" t="inlineStr">
@@ -12975,11 +12975,11 @@
         </is>
       </c>
       <c r="I171" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J171" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>3</v>
+      </c>
+      <c r="J171" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K171" s="2" t="inlineStr">
@@ -13009,12 +13009,12 @@
     <row r="172">
       <c r="A172" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="B172" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="C172" s="2" t="inlineStr">
@@ -13039,7 +13039,7 @@
       </c>
       <c r="G172" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 110,00</t>
         </is>
       </c>
       <c r="H172" s="2" t="inlineStr">
@@ -13048,24 +13048,24 @@
         </is>
       </c>
       <c r="I172" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J172" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
+        </is>
+      </c>
+      <c r="K172" s="2" t="inlineStr">
+        <is>
+          <t>50,0%</t>
+        </is>
+      </c>
+      <c r="L172" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J172" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
-        </is>
-      </c>
-      <c r="K172" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L172" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="M172" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="N172" s="2" t="inlineStr">
@@ -13082,12 +13082,12 @@
     <row r="173">
       <c r="A173" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="B173" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="C173" s="2" t="inlineStr">
@@ -13121,11 +13121,11 @@
         </is>
       </c>
       <c r="I173" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J173" s="3" t="inlineStr">
-        <is>
-          <t>▼ 66,7%</t>
+        <v>0</v>
+      </c>
+      <c r="J173" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K173" s="2" t="inlineStr">
@@ -13155,12 +13155,12 @@
     <row r="174">
       <c r="A174" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="B174" s="2" t="inlineStr">
         <is>
-          <t>31/03/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="C174" s="2" t="inlineStr">
@@ -13194,7 +13194,7 @@
         </is>
       </c>
       <c r="I174" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J174" s="2" t="inlineStr">
         <is>
@@ -13228,78 +13228,662 @@
     <row r="175">
       <c r="A175" s="2" t="inlineStr">
         <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B175" s="2" t="inlineStr">
+        <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="C175" s="2" t="inlineStr">
+        <is>
+          <t>UTD-145</t>
+        </is>
+      </c>
+      <c r="D175" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor duplo com bica arthi</t>
+        </is>
+      </c>
+      <c r="E175" s="2" t="inlineStr">
+        <is>
+          <t>4498058823</t>
+        </is>
+      </c>
+      <c r="F175" s="2" t="inlineStr">
+        <is>
+          <t>R$ 157,65</t>
+        </is>
+      </c>
+      <c r="G175" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H175" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I175" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J175" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="K175" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L175" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M175" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N175" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O175" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="2" t="inlineStr">
+        <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B176" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="C176" s="2" t="inlineStr">
+        <is>
+          <t>UTD-145</t>
+        </is>
+      </c>
+      <c r="D176" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor duplo com bica arthi</t>
+        </is>
+      </c>
+      <c r="E176" s="2" t="inlineStr">
+        <is>
+          <t>4645710434</t>
+        </is>
+      </c>
+      <c r="F176" s="2" t="inlineStr">
+        <is>
+          <t>R$ 157,65</t>
+        </is>
+      </c>
+      <c r="G176" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H176" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I176" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J176" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K176" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L176" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M176" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N176" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O176" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="2" t="inlineStr">
+        <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B177" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="C177" s="2" t="inlineStr">
+        <is>
+          <t>UTD-145</t>
+        </is>
+      </c>
+      <c r="D177" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor duplo com bica arthi</t>
+        </is>
+      </c>
+      <c r="E177" s="2" t="inlineStr">
+        <is>
+          <t>4498058823</t>
+        </is>
+      </c>
+      <c r="F177" s="2" t="inlineStr">
+        <is>
+          <t>R$ 157,65</t>
+        </is>
+      </c>
+      <c r="G177" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H177" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I177" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J177" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K177" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L177" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M177" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N177" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O177" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B178" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="C178" s="2" t="inlineStr">
+        <is>
+          <t>UTD-145</t>
+        </is>
+      </c>
+      <c r="D178" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor duplo com bica arthi</t>
+        </is>
+      </c>
+      <c r="E178" s="2" t="inlineStr">
+        <is>
+          <t>4645710434</t>
+        </is>
+      </c>
+      <c r="F178" s="2" t="inlineStr">
+        <is>
+          <t>R$ 157,65</t>
+        </is>
+      </c>
+      <c r="G178" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H178" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I178" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J178" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="K178" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L178" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M178" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N178" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O178" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B179" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="C179" s="2" t="inlineStr">
+        <is>
+          <t>UTD-145</t>
+        </is>
+      </c>
+      <c r="D179" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor duplo com bica arthi</t>
+        </is>
+      </c>
+      <c r="E179" s="2" t="inlineStr">
+        <is>
+          <t>4498058823</t>
+        </is>
+      </c>
+      <c r="F179" s="2" t="inlineStr">
+        <is>
+          <t>R$ 157,65</t>
+        </is>
+      </c>
+      <c r="G179" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H179" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I179" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J179" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="K179" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L179" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M179" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N179" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O179" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B180" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B175" s="2" t="inlineStr">
+      <c r="C180" s="2" t="inlineStr">
+        <is>
+          <t>UTD-145</t>
+        </is>
+      </c>
+      <c r="D180" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor duplo com bica arthi</t>
+        </is>
+      </c>
+      <c r="E180" s="2" t="inlineStr">
+        <is>
+          <t>4645710434</t>
+        </is>
+      </c>
+      <c r="F180" s="2" t="inlineStr">
+        <is>
+          <t>R$ 157,65</t>
+        </is>
+      </c>
+      <c r="G180" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H180" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I180" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J180" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
+        </is>
+      </c>
+      <c r="K180" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L180" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M180" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N180" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O180" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B181" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="C181" s="2" t="inlineStr">
+        <is>
+          <t>UTD-145</t>
+        </is>
+      </c>
+      <c r="D181" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor duplo com bica arthi</t>
+        </is>
+      </c>
+      <c r="E181" s="2" t="inlineStr">
+        <is>
+          <t>4498058823</t>
+        </is>
+      </c>
+      <c r="F181" s="2" t="inlineStr">
+        <is>
+          <t>R$ 157,65</t>
+        </is>
+      </c>
+      <c r="G181" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H181" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I181" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J181" s="3" t="inlineStr">
+        <is>
+          <t>▼ 66,7%</t>
+        </is>
+      </c>
+      <c r="K181" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L181" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M181" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N181" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O181" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B182" s="2" t="inlineStr">
         <is>
           <t>31/03/2026</t>
         </is>
       </c>
-      <c r="C175" s="2" t="inlineStr">
-        <is>
-          <t>UTD-145</t>
-        </is>
-      </c>
-      <c r="D175" s="2" t="inlineStr">
-        <is>
-          <t>Escorredor duplo com bica arthi</t>
-        </is>
-      </c>
-      <c r="E175" s="2" t="inlineStr">
+      <c r="C182" s="2" t="inlineStr">
+        <is>
+          <t>UTD-145</t>
+        </is>
+      </c>
+      <c r="D182" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor duplo com bica arthi</t>
+        </is>
+      </c>
+      <c r="E182" s="2" t="inlineStr">
+        <is>
+          <t>4645710434</t>
+        </is>
+      </c>
+      <c r="F182" s="2" t="inlineStr">
+        <is>
+          <t>R$ 157,65</t>
+        </is>
+      </c>
+      <c r="G182" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H182" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I182" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J182" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K182" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L182" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M182" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N182" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O182" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B183" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C183" s="2" t="inlineStr">
+        <is>
+          <t>UTD-145</t>
+        </is>
+      </c>
+      <c r="D183" s="2" t="inlineStr">
+        <is>
+          <t>Escorredor duplo com bica arthi</t>
+        </is>
+      </c>
+      <c r="E183" s="2" t="inlineStr">
         <is>
           <t>4498058823</t>
         </is>
       </c>
-      <c r="F175" s="2" t="inlineStr">
-        <is>
-          <t>R$ 157,65</t>
-        </is>
-      </c>
-      <c r="G175" s="2" t="inlineStr">
-        <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H175" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I175" s="2" t="n">
+      <c r="F183" s="2" t="inlineStr">
+        <is>
+          <t>R$ 157,65</t>
+        </is>
+      </c>
+      <c r="G183" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H183" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I183" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="J175" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K175" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L175" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M175" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="N175" s="2" t="inlineStr">
+      <c r="J183" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K183" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L183" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M183" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N183" s="2" t="inlineStr">
         <is>
           <t>Sem calcular</t>
         </is>
       </c>
-      <c r="O175" s="2" t="inlineStr">
+      <c r="O183" s="2" t="inlineStr">
         <is>
           <t>Média</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O175"/>
+  <autoFilter ref="A1:O183"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>